--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76502C5A-D9B4-A74B-A10D-C8735D63B3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E668E0-EF2B-514A-835C-ED06C3B53A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,9 +192,6 @@
     <t>DECIMAL(15,2)</t>
   </si>
   <si>
-    <t>sum, avg, min, max</t>
-  </si>
-  <si>
     <t>Current liquid money available. Use this for 'total savings' or 'wealthiest customers' metrics.</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
     <t>DECIMAL(4,2)</t>
   </si>
   <si>
-    <t>avg, min, max</t>
-  </si>
-  <si>
     <t>The annual percentage yield interest tracking rate assigned to this savings account.</t>
   </si>
   <si>
@@ -306,9 +300,6 @@
     <t>credit_limit</t>
   </si>
   <si>
-    <t>sum, avg</t>
-  </si>
-  <si>
     <t>The maximum revolving credit threshold limit extended to the customer.</t>
   </si>
   <si>
@@ -484,6 +475,15 @@
   </si>
   <si>
     <t>Unsecured personal loan facility.</t>
+  </si>
+  <si>
+    <t>sum, average, min, max</t>
+  </si>
+  <si>
+    <t>average, min, max</t>
+  </si>
+  <si>
+    <t>sum, average</t>
   </si>
 </sst>
 </file>
@@ -1217,13 +1217,13 @@
         <v>33</v>
       </c>
       <c r="G12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
         <v>56</v>
-      </c>
-      <c r="H12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1231,22 +1231,22 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
         <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1254,7 +1254,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
         <v>32</v>
@@ -1263,13 +1263,13 @@
         <v>33</v>
       </c>
       <c r="H14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" t="s">
         <v>63</v>
-      </c>
-      <c r="I14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1277,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -1289,7 +1289,7 @@
         <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1315,7 +1315,7 @@
         <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1335,7 +1335,7 @@
         <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1343,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
@@ -1352,13 +1352,13 @@
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="H18" t="s">
         <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1366,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
@@ -1378,7 +1378,7 @@
         <v>29</v>
       </c>
       <c r="J19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1386,22 +1386,22 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
         <v>58</v>
       </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
       <c r="D20" t="s">
         <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="H20" t="s">
         <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1409,7 +1409,7 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
@@ -1418,13 +1418,13 @@
         <v>33</v>
       </c>
       <c r="H21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
@@ -1444,7 +1444,7 @@
         <v>29</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1470,7 +1470,7 @@
         <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1478,7 +1478,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -1487,13 +1487,13 @@
         <v>33</v>
       </c>
       <c r="H24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1501,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
@@ -1510,13 +1510,13 @@
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="H25" t="s">
         <v>29</v>
       </c>
       <c r="J25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1524,7 +1524,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
         <v>55</v>
@@ -1533,13 +1533,13 @@
         <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="H26" t="s">
         <v>29</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1547,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
@@ -1559,7 +1559,7 @@
         <v>29</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1567,7 +1567,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -1576,13 +1576,13 @@
         <v>33</v>
       </c>
       <c r="H28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1590,7 +1590,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
         <v>27</v>
@@ -1602,7 +1602,7 @@
         <v>29</v>
       </c>
       <c r="J29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1628,7 +1628,7 @@
         <v>29</v>
       </c>
       <c r="J30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1636,7 +1636,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -1648,7 +1648,7 @@
         <v>29</v>
       </c>
       <c r="J31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -1656,7 +1656,7 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
         <v>55</v>
@@ -1665,13 +1665,13 @@
         <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="H32" t="s">
         <v>29</v>
       </c>
       <c r="J32" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1679,7 +1679,7 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>55</v>
@@ -1688,13 +1688,13 @@
         <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="H33" t="s">
         <v>29</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1702,7 +1702,7 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>40</v>
@@ -1714,7 +1714,7 @@
         <v>29</v>
       </c>
       <c r="J34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1722,7 +1722,7 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
         <v>32</v>
@@ -1731,13 +1731,13 @@
         <v>33</v>
       </c>
       <c r="H35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1745,7 +1745,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
@@ -1757,7 +1757,7 @@
         <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -1774,7 +1774,7 @@
         <v>33</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
         <v>50</v>
@@ -1783,7 +1783,7 @@
         <v>29</v>
       </c>
       <c r="J37" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1791,7 +1791,7 @@
         <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
@@ -1800,13 +1800,13 @@
         <v>33</v>
       </c>
       <c r="G38" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="H38" t="s">
         <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -1814,7 +1814,7 @@
         <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
@@ -1823,13 +1823,13 @@
         <v>33</v>
       </c>
       <c r="H39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -1837,10 +1837,10 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
         <v>33</v>
@@ -1849,7 +1849,7 @@
         <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -1857,7 +1857,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -1869,7 +1869,7 @@
         <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -1877,7 +1877,7 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
@@ -1889,7 +1889,7 @@
         <v>29</v>
       </c>
       <c r="J42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -1897,7 +1897,7 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -1909,7 +1909,7 @@
         <v>43</v>
       </c>
       <c r="J43" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -1917,7 +1917,7 @@
         <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
@@ -1929,7 +1929,7 @@
         <v>43</v>
       </c>
       <c r="J44" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -1937,7 +1937,7 @@
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
@@ -1946,13 +1946,13 @@
         <v>33</v>
       </c>
       <c r="G45" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
       <c r="J45" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -1960,22 +1960,22 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D46" t="s">
         <v>33</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="H46" t="s">
         <v>29</v>
       </c>
       <c r="J46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2003,13 +2003,13 @@
         <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -2017,16 +2017,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -2034,16 +2034,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -2051,16 +2051,16 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -2068,16 +2068,16 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2088,13 +2088,13 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2102,16 +2102,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -2119,16 +2119,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -2136,16 +2136,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E668E0-EF2B-514A-835C-ED06C3B53A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E668E0-EF2B-514A-835C-ED06C3B53A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEA1656-F8F8-A64A-A901-1546E0DBAF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -505,12 +505,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -540,11 +546,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -852,7 +862,7 @@
   <cols>
     <col min="1" max="1" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.6640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -862,7 +872,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -873,7 +883,7 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -884,7 +894,7 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -895,7 +905,7 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -906,7 +916,7 @@
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -917,7 +927,7 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -928,7 +938,7 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -939,7 +949,7 @@
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -957,9 +967,9 @@
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="91.6640625" bestFit="1" customWidth="1"/>
@@ -978,7 +988,7 @@
       <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1170,7 +1180,7 @@
       <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F10" t="s">
@@ -1305,7 +1315,7 @@
       <c r="D16" t="s">
         <v>33</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F16" t="s">
@@ -1460,7 +1470,7 @@
       <c r="D23" t="s">
         <v>33</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F23" t="s">
@@ -1618,7 +1628,7 @@
       <c r="D30" t="s">
         <v>33</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F30" t="s">
@@ -1773,7 +1783,7 @@
       <c r="D37" t="s">
         <v>33</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
         <v>101</v>
       </c>
       <c r="F37" t="s">

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEA1656-F8F8-A64A-A901-1546E0DBAF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3558B712-47B7-9D4A-B655-B66F96CA2773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -968,7 +968,7 @@
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="47.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" bestFit="1" customWidth="1"/>
@@ -991,7 +991,7 @@
       <c r="E1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1183,7 +1183,7 @@
       <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H10" t="s">
@@ -1318,7 +1318,7 @@
       <c r="E16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H16" t="s">
@@ -1473,7 +1473,7 @@
       <c r="E23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H23" t="s">
@@ -1631,7 +1631,7 @@
       <c r="E30" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H30" t="s">
@@ -1786,7 +1786,7 @@
       <c r="E37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H37" t="s">

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3558B712-47B7-9D4A-B655-B66F96CA2773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76675445-7905-4C4B-9268-2AD33BD61849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,13 +16,14 @@
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
     <sheet name="Columns" sheetId="2" r:id="rId2"/>
     <sheet name="Value_Mappings" sheetId="3" r:id="rId3"/>
+    <sheet name="Golden_Queries" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="167">
   <si>
     <t>Table Name</t>
   </si>
@@ -484,13 +485,52 @@
   </si>
   <si>
     <t>sum, average</t>
+  </si>
+  <si>
+    <t>user_intent</t>
+  </si>
+  <si>
+    <t>Show customers who have a birthday this week</t>
+  </si>
+  <si>
+    <t>Show deposits approaching maturity in the next 7 days</t>
+  </si>
+  <si>
+    <t>Show active customers with their savings balance</t>
+  </si>
+  <si>
+    <t>Show top 5 customers with highest savings balance</t>
+  </si>
+  <si>
+    <t>SELECT customer_id, first_name, last_name, birth_date FROM cai_customers WHERE weekofyear(birth_date) = weekofyear(current_date());</t>
+  </si>
+  <si>
+    <t>SELECT deposit_id, customer_id, principal_amount, maturity_date FROM cai_deposits WHERE maturity_date BETWEEN current_date() AND days_add(current_date(), 7);</t>
+  </si>
+  <si>
+    <t>SELECT c.customer_id, c.first_name, c.last_name, s.balance FROM cai_customers c INNER JOIN cai_savings s ON c.customer_id = s.customer_id WHERE s.status = 'ACTIVE';</t>
+  </si>
+  <si>
+    <t>SELECT c.customer_id, c.first_name, c.last_name, s.balance FROM cai_customers c INNER JOIN cai_savings s ON c.customer_id = s.customer_id ORDER BY s.balance DESC LIMIT 5;</t>
+  </si>
+  <si>
+    <t>complexity</t>
+  </si>
+  <si>
+    <t>sql_template</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,19 +544,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -546,15 +588,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -862,7 +905,7 @@
   <cols>
     <col min="1" max="1" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.6640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -872,7 +915,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -883,7 +926,7 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -894,7 +937,7 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -905,7 +948,7 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -916,7 +959,7 @@
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -927,7 +970,7 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -938,7 +981,7 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -949,7 +992,7 @@
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -967,9 +1010,9 @@
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="91.6640625" bestFit="1" customWidth="1"/>
@@ -988,13 +1031,13 @@
       <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1180,10 +1223,10 @@
       <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H10" t="s">
@@ -1226,7 +1269,7 @@
       <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H12" t="s">
@@ -1249,7 +1292,7 @@
       <c r="D13" t="s">
         <v>33</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H13" t="s">
@@ -1315,10 +1358,10 @@
       <c r="D16" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H16" t="s">
@@ -1361,7 +1404,7 @@
       <c r="D18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H18" t="s">
@@ -1404,7 +1447,7 @@
       <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H20" t="s">
@@ -1470,10 +1513,10 @@
       <c r="D23" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H23" t="s">
@@ -1519,7 +1562,7 @@
       <c r="D25" t="s">
         <v>33</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H25" t="s">
@@ -1542,7 +1585,7 @@
       <c r="D26" t="s">
         <v>33</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H26" t="s">
@@ -1628,10 +1671,10 @@
       <c r="D30" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H30" t="s">
@@ -1674,7 +1717,7 @@
       <c r="D32" t="s">
         <v>33</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="4" t="s">
         <v>153</v>
       </c>
       <c r="H32" t="s">
@@ -1697,7 +1740,7 @@
       <c r="D33" t="s">
         <v>33</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H33" t="s">
@@ -1783,10 +1826,10 @@
       <c r="D37" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H37" t="s">
@@ -1809,7 +1852,7 @@
       <c r="D38" t="s">
         <v>33</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H38" t="s">
@@ -1955,7 +1998,7 @@
       <c r="D45" t="s">
         <v>33</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="4" t="s">
         <v>153</v>
       </c>
       <c r="H45" t="s">
@@ -1978,7 +2021,7 @@
       <c r="D46" t="s">
         <v>33</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H46" t="s">
@@ -2161,4 +2204,73 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30159596-74E1-AB4A-8605-D929B81467D2}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="136.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37B40D7-E07E-3D4C-B86E-5FAD1CFC9E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B159B9-A89D-7441-8769-9C98EFEE7AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="32060" windowHeight="16700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="1820" windowWidth="32060" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5376" uniqueCount="1139">
   <si>
     <t>Table Name</t>
   </si>
@@ -3449,12 +3449,21 @@
   <si>
     <t>complexity</t>
   </si>
+  <si>
+    <t>sum, average, min, max</t>
+  </si>
+  <si>
+    <t>belongs_to</t>
+  </si>
+  <si>
+    <t>customer_performance.mdm_id; customer_kplus.mdm_id; customer_icons.mdm_id; customer_dplk.mdm_id; customer_creditcard.mdm_id; customer_wms.mdm_id</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3466,6 +3475,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3506,11 +3522,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3817,6 +3834,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -4423,10 +4445,10 @@
   <dimension ref="A1:J1009"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1640625" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" customWidth="1"/>
+    <col min="4" max="4" width="86.6640625" customWidth="1"/>
     <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -4623,6 +4645,9 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
+      <c r="H9" t="s">
+        <v>1136</v>
+      </c>
       <c r="I9" t="s">
         <v>1129</v>
       </c>
@@ -4643,6 +4668,9 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
+      <c r="H10" t="s">
+        <v>1136</v>
+      </c>
       <c r="I10" t="s">
         <v>1129</v>
       </c>
@@ -4683,6 +4711,9 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
+      <c r="H12" t="s">
+        <v>1136</v>
+      </c>
       <c r="I12" t="s">
         <v>1129</v>
       </c>
@@ -4763,6 +4794,9 @@
       <c r="E16" t="b">
         <v>0</v>
       </c>
+      <c r="H16" t="s">
+        <v>1136</v>
+      </c>
       <c r="I16" t="s">
         <v>1129</v>
       </c>
@@ -4783,6 +4817,9 @@
       <c r="E17" t="b">
         <v>0</v>
       </c>
+      <c r="H17" t="s">
+        <v>1136</v>
+      </c>
       <c r="I17" t="s">
         <v>1129</v>
       </c>
@@ -4803,6 +4840,9 @@
       <c r="E18" t="b">
         <v>0</v>
       </c>
+      <c r="H18" t="s">
+        <v>1136</v>
+      </c>
       <c r="I18" t="s">
         <v>1129</v>
       </c>
@@ -4843,6 +4883,9 @@
       <c r="E20" t="b">
         <v>0</v>
       </c>
+      <c r="H20" t="s">
+        <v>1136</v>
+      </c>
       <c r="I20" t="s">
         <v>1129</v>
       </c>
@@ -4883,6 +4926,9 @@
       <c r="E22" t="b">
         <v>0</v>
       </c>
+      <c r="H22" t="s">
+        <v>1136</v>
+      </c>
       <c r="I22" t="s">
         <v>1129</v>
       </c>
@@ -4903,6 +4949,9 @@
       <c r="E23" t="b">
         <v>0</v>
       </c>
+      <c r="H23" t="s">
+        <v>1136</v>
+      </c>
       <c r="I23" t="s">
         <v>1129</v>
       </c>
@@ -4943,6 +4992,9 @@
       <c r="E25" t="b">
         <v>0</v>
       </c>
+      <c r="H25" t="s">
+        <v>1136</v>
+      </c>
       <c r="I25" t="s">
         <v>1129</v>
       </c>
@@ -4983,6 +5035,9 @@
       <c r="E27" t="b">
         <v>0</v>
       </c>
+      <c r="H27" t="s">
+        <v>1136</v>
+      </c>
       <c r="I27" t="s">
         <v>1129</v>
       </c>
@@ -5003,6 +5058,9 @@
       <c r="E28" t="b">
         <v>0</v>
       </c>
+      <c r="H28" t="s">
+        <v>1136</v>
+      </c>
       <c r="I28" t="s">
         <v>1129</v>
       </c>
@@ -5023,6 +5081,9 @@
       <c r="E29" t="b">
         <v>0</v>
       </c>
+      <c r="H29" t="s">
+        <v>1136</v>
+      </c>
       <c r="I29" t="s">
         <v>1129</v>
       </c>
@@ -5043,6 +5104,9 @@
       <c r="E30" t="b">
         <v>0</v>
       </c>
+      <c r="H30" t="s">
+        <v>1136</v>
+      </c>
       <c r="I30" t="s">
         <v>1129</v>
       </c>
@@ -5063,6 +5127,9 @@
       <c r="E31" t="b">
         <v>0</v>
       </c>
+      <c r="H31" t="s">
+        <v>1136</v>
+      </c>
       <c r="I31" t="s">
         <v>1129</v>
       </c>
@@ -5083,6 +5150,9 @@
       <c r="E32" t="b">
         <v>0</v>
       </c>
+      <c r="H32" t="s">
+        <v>1136</v>
+      </c>
       <c r="I32" t="s">
         <v>1129</v>
       </c>
@@ -5103,6 +5173,9 @@
       <c r="E33" t="b">
         <v>0</v>
       </c>
+      <c r="H33" t="s">
+        <v>1136</v>
+      </c>
       <c r="I33" t="s">
         <v>1129</v>
       </c>
@@ -5143,6 +5216,9 @@
       <c r="E35" t="b">
         <v>0</v>
       </c>
+      <c r="H35" t="s">
+        <v>1136</v>
+      </c>
       <c r="I35" t="s">
         <v>1129</v>
       </c>
@@ -5163,6 +5239,9 @@
       <c r="E36" t="b">
         <v>0</v>
       </c>
+      <c r="H36" t="s">
+        <v>1136</v>
+      </c>
       <c r="I36" t="s">
         <v>1129</v>
       </c>
@@ -5263,6 +5342,9 @@
       <c r="E41" t="b">
         <v>0</v>
       </c>
+      <c r="H41" t="s">
+        <v>1136</v>
+      </c>
       <c r="I41" t="s">
         <v>1129</v>
       </c>
@@ -5283,6 +5365,9 @@
       <c r="E42" t="b">
         <v>0</v>
       </c>
+      <c r="H42" t="s">
+        <v>1136</v>
+      </c>
       <c r="I42" t="s">
         <v>1129</v>
       </c>
@@ -5303,6 +5388,9 @@
       <c r="E43" t="b">
         <v>0</v>
       </c>
+      <c r="H43" t="s">
+        <v>1136</v>
+      </c>
       <c r="I43" t="s">
         <v>1129</v>
       </c>
@@ -5321,7 +5409,10 @@
         <v>768</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1137</v>
       </c>
       <c r="I44" t="s">
         <v>1129</v>
@@ -5343,6 +5434,9 @@
       <c r="E45" t="b">
         <v>0</v>
       </c>
+      <c r="H45" t="s">
+        <v>1136</v>
+      </c>
       <c r="I45" t="s">
         <v>1129</v>
       </c>
@@ -5363,6 +5457,9 @@
       <c r="E46" t="b">
         <v>0</v>
       </c>
+      <c r="H46" t="s">
+        <v>1136</v>
+      </c>
       <c r="I46" t="s">
         <v>1129</v>
       </c>
@@ -5423,6 +5520,9 @@
       <c r="E49" t="b">
         <v>0</v>
       </c>
+      <c r="H49" t="s">
+        <v>1136</v>
+      </c>
       <c r="I49" t="s">
         <v>1129</v>
       </c>
@@ -5463,6 +5563,9 @@
       <c r="E51" t="b">
         <v>0</v>
       </c>
+      <c r="G51" t="s">
+        <v>1137</v>
+      </c>
       <c r="I51" t="s">
         <v>1129</v>
       </c>
@@ -5541,7 +5644,7 @@
         <v>779</v>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="s">
         <v>1129</v>
@@ -5603,6 +5706,9 @@
       <c r="E58" t="b">
         <v>0</v>
       </c>
+      <c r="G58" t="s">
+        <v>1137</v>
+      </c>
       <c r="I58" t="s">
         <v>1129</v>
       </c>
@@ -5683,6 +5789,9 @@
       <c r="E62" t="b">
         <v>0</v>
       </c>
+      <c r="G62" t="s">
+        <v>1137</v>
+      </c>
       <c r="I62" t="s">
         <v>1129</v>
       </c>
@@ -5901,7 +6010,10 @@
         <v>768</v>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1137</v>
       </c>
       <c r="I73" t="s">
         <v>1129</v>
@@ -5943,6 +6055,9 @@
       <c r="E75" t="b">
         <v>0</v>
       </c>
+      <c r="G75" t="s">
+        <v>1137</v>
+      </c>
       <c r="I75" t="s">
         <v>1129</v>
       </c>
@@ -5983,6 +6098,9 @@
       <c r="E77" t="b">
         <v>0</v>
       </c>
+      <c r="G77" t="s">
+        <v>1137</v>
+      </c>
       <c r="I77" t="s">
         <v>1129</v>
       </c>
@@ -6023,6 +6141,9 @@
       <c r="E79" t="b">
         <v>0</v>
       </c>
+      <c r="G79" t="s">
+        <v>1137</v>
+      </c>
       <c r="I79" t="s">
         <v>1129</v>
       </c>
@@ -6043,6 +6164,9 @@
       <c r="E80" t="b">
         <v>0</v>
       </c>
+      <c r="G80" t="s">
+        <v>1137</v>
+      </c>
       <c r="I80" t="s">
         <v>1129</v>
       </c>
@@ -6283,6 +6407,9 @@
       <c r="E92" t="b">
         <v>0</v>
       </c>
+      <c r="G92" t="s">
+        <v>1137</v>
+      </c>
       <c r="I92" t="s">
         <v>1129</v>
       </c>
@@ -6343,6 +6470,9 @@
       <c r="E95" t="b">
         <v>0</v>
       </c>
+      <c r="H95" t="s">
+        <v>1136</v>
+      </c>
       <c r="I95" t="s">
         <v>1129</v>
       </c>
@@ -6463,6 +6593,9 @@
       <c r="E101" t="b">
         <v>0</v>
       </c>
+      <c r="G101" t="s">
+        <v>1137</v>
+      </c>
       <c r="I101" t="s">
         <v>1129</v>
       </c>
@@ -6543,6 +6676,9 @@
       <c r="E105" t="b">
         <v>0</v>
       </c>
+      <c r="H105" t="s">
+        <v>1136</v>
+      </c>
       <c r="I105" t="s">
         <v>1129</v>
       </c>
@@ -6601,7 +6737,10 @@
         <v>768</v>
       </c>
       <c r="E108" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1137</v>
       </c>
       <c r="I108" t="s">
         <v>1129</v>
@@ -6643,6 +6782,9 @@
       <c r="E110" t="b">
         <v>0</v>
       </c>
+      <c r="G110" t="s">
+        <v>1137</v>
+      </c>
       <c r="I110" t="s">
         <v>1129</v>
       </c>
@@ -6703,6 +6845,9 @@
       <c r="E113" t="b">
         <v>0</v>
       </c>
+      <c r="G113" t="s">
+        <v>1137</v>
+      </c>
       <c r="I113" t="s">
         <v>1129</v>
       </c>
@@ -6723,6 +6868,9 @@
       <c r="E114" t="b">
         <v>0</v>
       </c>
+      <c r="G114" t="s">
+        <v>1137</v>
+      </c>
       <c r="I114" t="s">
         <v>1129</v>
       </c>
@@ -6901,7 +7049,7 @@
         <v>779</v>
       </c>
       <c r="E123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="s">
         <v>1129</v>
@@ -7103,6 +7251,9 @@
       <c r="E133" t="b">
         <v>0</v>
       </c>
+      <c r="G133" t="s">
+        <v>1137</v>
+      </c>
       <c r="I133" t="s">
         <v>1129</v>
       </c>
@@ -7121,7 +7272,10 @@
         <v>768</v>
       </c>
       <c r="E134" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>1137</v>
       </c>
       <c r="I134" t="s">
         <v>1129</v>
@@ -7223,6 +7377,9 @@
       <c r="E139" t="b">
         <v>0</v>
       </c>
+      <c r="G139" t="s">
+        <v>1137</v>
+      </c>
       <c r="I139" t="s">
         <v>1129</v>
       </c>
@@ -7380,6 +7537,9 @@
       <c r="E147" t="b">
         <v>0</v>
       </c>
+      <c r="G147" t="s">
+        <v>1137</v>
+      </c>
       <c r="I147" t="s">
         <v>1129</v>
       </c>
@@ -7514,6 +7674,9 @@
       <c r="E154" t="b">
         <v>0</v>
       </c>
+      <c r="G154" t="s">
+        <v>1137</v>
+      </c>
       <c r="I154" t="s">
         <v>1129</v>
       </c>
@@ -7863,7 +8026,10 @@
         <v>768</v>
       </c>
       <c r="E172" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G172" t="s">
+        <v>1137</v>
       </c>
       <c r="I172" t="s">
         <v>1129</v>
@@ -7965,6 +8131,9 @@
       <c r="E177" t="b">
         <v>0</v>
       </c>
+      <c r="G177" t="s">
+        <v>1137</v>
+      </c>
       <c r="I177" t="s">
         <v>1129</v>
       </c>
@@ -8065,6 +8234,9 @@
       <c r="E182" t="b">
         <v>0</v>
       </c>
+      <c r="G182" t="s">
+        <v>1137</v>
+      </c>
       <c r="I182" t="s">
         <v>1129</v>
       </c>
@@ -8085,6 +8257,9 @@
       <c r="E183" t="b">
         <v>0</v>
       </c>
+      <c r="G183" t="s">
+        <v>1137</v>
+      </c>
       <c r="I183" t="s">
         <v>1129</v>
       </c>
@@ -8125,6 +8300,9 @@
       <c r="E185" t="b">
         <v>0</v>
       </c>
+      <c r="G185" t="s">
+        <v>1137</v>
+      </c>
       <c r="I185" t="s">
         <v>1129</v>
       </c>
@@ -8185,6 +8363,9 @@
       <c r="E188" t="b">
         <v>0</v>
       </c>
+      <c r="G188" t="s">
+        <v>1137</v>
+      </c>
       <c r="I188" t="s">
         <v>1129</v>
       </c>
@@ -8245,6 +8426,9 @@
       <c r="E191" t="b">
         <v>0</v>
       </c>
+      <c r="H191" t="s">
+        <v>1136</v>
+      </c>
       <c r="I191" t="s">
         <v>1129</v>
       </c>
@@ -8285,6 +8469,9 @@
       <c r="E193" t="b">
         <v>0</v>
       </c>
+      <c r="H193" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I193" t="s">
         <v>1129</v>
       </c>
@@ -8305,6 +8492,9 @@
       <c r="E194" t="b">
         <v>0</v>
       </c>
+      <c r="H194" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I194" t="s">
         <v>1129</v>
       </c>
@@ -8325,6 +8515,9 @@
       <c r="E195" t="b">
         <v>0</v>
       </c>
+      <c r="H195" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I195" t="s">
         <v>1129</v>
       </c>
@@ -8345,6 +8538,9 @@
       <c r="E196" t="b">
         <v>0</v>
       </c>
+      <c r="H196" t="s">
+        <v>1136</v>
+      </c>
       <c r="I196" t="s">
         <v>1129</v>
       </c>
@@ -8365,6 +8561,9 @@
       <c r="E197" t="b">
         <v>0</v>
       </c>
+      <c r="H197" t="s">
+        <v>1136</v>
+      </c>
       <c r="I197" t="s">
         <v>1129</v>
       </c>
@@ -8385,6 +8584,9 @@
       <c r="E198" t="b">
         <v>0</v>
       </c>
+      <c r="H198" t="s">
+        <v>1136</v>
+      </c>
       <c r="I198" t="s">
         <v>1129</v>
       </c>
@@ -8405,6 +8607,9 @@
       <c r="E199" t="b">
         <v>0</v>
       </c>
+      <c r="H199" t="s">
+        <v>1136</v>
+      </c>
       <c r="I199" t="s">
         <v>1129</v>
       </c>
@@ -8425,6 +8630,9 @@
       <c r="E200" t="b">
         <v>0</v>
       </c>
+      <c r="H200" t="s">
+        <v>1136</v>
+      </c>
       <c r="I200" t="s">
         <v>1129</v>
       </c>
@@ -8445,6 +8653,9 @@
       <c r="E201" t="b">
         <v>0</v>
       </c>
+      <c r="H201" t="s">
+        <v>1136</v>
+      </c>
       <c r="I201" t="s">
         <v>1129</v>
       </c>
@@ -8465,6 +8676,9 @@
       <c r="E202" t="b">
         <v>0</v>
       </c>
+      <c r="H202" t="s">
+        <v>1136</v>
+      </c>
       <c r="I202" t="s">
         <v>1129</v>
       </c>
@@ -8485,6 +8699,9 @@
       <c r="E203" t="b">
         <v>0</v>
       </c>
+      <c r="H203" t="s">
+        <v>1136</v>
+      </c>
       <c r="I203" t="s">
         <v>1129</v>
       </c>
@@ -8505,6 +8722,9 @@
       <c r="E204" t="b">
         <v>0</v>
       </c>
+      <c r="H204" t="s">
+        <v>1136</v>
+      </c>
       <c r="I204" t="s">
         <v>1129</v>
       </c>
@@ -8525,6 +8745,9 @@
       <c r="E205" t="b">
         <v>0</v>
       </c>
+      <c r="H205" t="s">
+        <v>1136</v>
+      </c>
       <c r="I205" t="s">
         <v>1129</v>
       </c>
@@ -8545,6 +8768,9 @@
       <c r="E206" t="b">
         <v>0</v>
       </c>
+      <c r="H206" t="s">
+        <v>1136</v>
+      </c>
       <c r="I206" t="s">
         <v>1129</v>
       </c>
@@ -8585,6 +8811,9 @@
       <c r="E208" t="b">
         <v>0</v>
       </c>
+      <c r="H208" t="s">
+        <v>1136</v>
+      </c>
       <c r="I208" t="s">
         <v>1129</v>
       </c>
@@ -8605,6 +8834,9 @@
       <c r="E209" t="b">
         <v>0</v>
       </c>
+      <c r="H209" t="s">
+        <v>1136</v>
+      </c>
       <c r="I209" t="s">
         <v>1129</v>
       </c>
@@ -8625,6 +8857,9 @@
       <c r="E210" t="b">
         <v>0</v>
       </c>
+      <c r="H210" t="s">
+        <v>1136</v>
+      </c>
       <c r="I210" t="s">
         <v>1129</v>
       </c>
@@ -8803,7 +9038,10 @@
         <v>768</v>
       </c>
       <c r="E219" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G219" t="s">
+        <v>1137</v>
       </c>
       <c r="I219" t="s">
         <v>1129</v>
@@ -9045,6 +9283,9 @@
       <c r="E231" t="b">
         <v>0</v>
       </c>
+      <c r="G231" t="s">
+        <v>1137</v>
+      </c>
       <c r="I231" t="s">
         <v>1129</v>
       </c>
@@ -9085,6 +9326,12 @@
       <c r="E233" t="b">
         <v>0</v>
       </c>
+      <c r="F233" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G233" t="s">
+        <v>1137</v>
+      </c>
       <c r="I233" t="s">
         <v>1129</v>
       </c>
@@ -9325,6 +9572,9 @@
       <c r="E245" t="b">
         <v>0</v>
       </c>
+      <c r="H245" t="s">
+        <v>1136</v>
+      </c>
       <c r="I245" t="s">
         <v>1129</v>
       </c>
@@ -9445,6 +9695,9 @@
       <c r="E251" t="b">
         <v>0</v>
       </c>
+      <c r="H251" t="s">
+        <v>1136</v>
+      </c>
       <c r="I251" t="s">
         <v>1129</v>
       </c>
@@ -9525,6 +9778,9 @@
       <c r="E255" t="b">
         <v>0</v>
       </c>
+      <c r="H255" t="s">
+        <v>1136</v>
+      </c>
       <c r="I255" t="s">
         <v>1129</v>
       </c>
@@ -9725,6 +9981,9 @@
       <c r="E265" t="b">
         <v>0</v>
       </c>
+      <c r="H265" t="s">
+        <v>1136</v>
+      </c>
       <c r="I265" t="s">
         <v>1129</v>
       </c>
@@ -10085,6 +10344,12 @@
       <c r="E283" t="b">
         <v>0</v>
       </c>
+      <c r="F283" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1137</v>
+      </c>
       <c r="I283" t="s">
         <v>1129</v>
       </c>
@@ -10185,6 +10450,12 @@
       <c r="E288" t="b">
         <v>0</v>
       </c>
+      <c r="F288" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1137</v>
+      </c>
       <c r="I288" t="s">
         <v>1129</v>
       </c>
@@ -10245,6 +10516,9 @@
       <c r="E291" t="b">
         <v>0</v>
       </c>
+      <c r="G291" t="s">
+        <v>1137</v>
+      </c>
       <c r="I291" t="s">
         <v>1129</v>
       </c>
@@ -10305,6 +10579,9 @@
       <c r="E294" t="b">
         <v>0</v>
       </c>
+      <c r="G294" t="s">
+        <v>1137</v>
+      </c>
       <c r="I294" t="s">
         <v>1129</v>
       </c>
@@ -10485,6 +10762,9 @@
       <c r="E303" t="b">
         <v>0</v>
       </c>
+      <c r="H303" t="s">
+        <v>1136</v>
+      </c>
       <c r="I303" t="s">
         <v>1129</v>
       </c>
@@ -10545,6 +10825,9 @@
       <c r="E306" t="b">
         <v>0</v>
       </c>
+      <c r="H306" t="s">
+        <v>1136</v>
+      </c>
       <c r="I306" t="s">
         <v>1129</v>
       </c>
@@ -10745,6 +11028,9 @@
       <c r="E316" t="b">
         <v>0</v>
       </c>
+      <c r="G316" t="s">
+        <v>1137</v>
+      </c>
       <c r="I316" t="s">
         <v>1129</v>
       </c>
@@ -11265,6 +11551,9 @@
       <c r="E342" t="b">
         <v>0</v>
       </c>
+      <c r="H342" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I342" t="s">
         <v>1129</v>
       </c>
@@ -11325,6 +11614,9 @@
       <c r="E345" t="b">
         <v>0</v>
       </c>
+      <c r="H345" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I345" t="s">
         <v>1129</v>
       </c>
@@ -11365,6 +11657,9 @@
       <c r="E347" t="b">
         <v>0</v>
       </c>
+      <c r="H347" t="s">
+        <v>1136</v>
+      </c>
       <c r="I347" t="s">
         <v>1129</v>
       </c>
@@ -11405,6 +11700,9 @@
       <c r="E349" t="b">
         <v>0</v>
       </c>
+      <c r="H349" t="s">
+        <v>1136</v>
+      </c>
       <c r="I349" t="s">
         <v>1129</v>
       </c>
@@ -11425,6 +11723,9 @@
       <c r="E350" t="b">
         <v>0</v>
       </c>
+      <c r="H350" t="s">
+        <v>1136</v>
+      </c>
       <c r="I350" t="s">
         <v>1129</v>
       </c>
@@ -11465,6 +11766,9 @@
       <c r="E352" t="b">
         <v>0</v>
       </c>
+      <c r="H352" t="s">
+        <v>1136</v>
+      </c>
       <c r="I352" t="s">
         <v>1129</v>
       </c>
@@ -11545,6 +11849,9 @@
       <c r="E356" t="b">
         <v>0</v>
       </c>
+      <c r="H356" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I356" t="s">
         <v>1129</v>
       </c>
@@ -11625,6 +11932,9 @@
       <c r="E360" t="b">
         <v>0</v>
       </c>
+      <c r="H360" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I360" t="s">
         <v>1129</v>
       </c>
@@ -12285,6 +12595,12 @@
       <c r="E393" t="b">
         <v>0</v>
       </c>
+      <c r="F393" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G393" t="s">
+        <v>1137</v>
+      </c>
       <c r="I393" t="s">
         <v>1129</v>
       </c>
@@ -12325,6 +12641,9 @@
       <c r="E395" t="b">
         <v>0</v>
       </c>
+      <c r="G395" t="s">
+        <v>1137</v>
+      </c>
       <c r="I395" t="s">
         <v>1129</v>
       </c>
@@ -12485,6 +12804,9 @@
       <c r="E403" t="b">
         <v>0</v>
       </c>
+      <c r="H403" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I403" t="s">
         <v>1129</v>
       </c>
@@ -12845,6 +13167,9 @@
       <c r="E421" t="b">
         <v>0</v>
       </c>
+      <c r="H421" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I421" t="s">
         <v>1129</v>
       </c>
@@ -13145,6 +13470,9 @@
       <c r="E436" t="b">
         <v>0</v>
       </c>
+      <c r="H436" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I436" t="s">
         <v>1129</v>
       </c>
@@ -13485,6 +13813,9 @@
       <c r="E453" t="b">
         <v>0</v>
       </c>
+      <c r="H453" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I453" t="s">
         <v>1129</v>
       </c>
@@ -13505,6 +13836,9 @@
       <c r="E454" t="b">
         <v>0</v>
       </c>
+      <c r="H454" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I454" t="s">
         <v>1129</v>
       </c>
@@ -13545,6 +13879,9 @@
       <c r="E456" t="b">
         <v>0</v>
       </c>
+      <c r="H456" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I456" t="s">
         <v>1129</v>
       </c>
@@ -13565,6 +13902,12 @@
       <c r="E457" t="b">
         <v>0</v>
       </c>
+      <c r="F457" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G457" t="s">
+        <v>1137</v>
+      </c>
       <c r="I457" t="s">
         <v>1129</v>
       </c>
@@ -13625,6 +13968,9 @@
       <c r="E460" t="b">
         <v>0</v>
       </c>
+      <c r="H460" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I460" t="s">
         <v>1129</v>
       </c>
@@ -13665,6 +14011,9 @@
       <c r="E462" t="b">
         <v>0</v>
       </c>
+      <c r="G462" t="s">
+        <v>1137</v>
+      </c>
       <c r="I462" t="s">
         <v>1129</v>
       </c>
@@ -13705,6 +14054,9 @@
       <c r="E464" t="b">
         <v>0</v>
       </c>
+      <c r="H464" t="s">
+        <v>1136</v>
+      </c>
       <c r="I464" t="s">
         <v>1129</v>
       </c>
@@ -13745,6 +14097,12 @@
       <c r="E466" t="b">
         <v>0</v>
       </c>
+      <c r="F466" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G466" t="s">
+        <v>1137</v>
+      </c>
       <c r="I466" t="s">
         <v>1129</v>
       </c>
@@ -14125,6 +14483,9 @@
       <c r="E485" t="b">
         <v>0</v>
       </c>
+      <c r="H485" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I485" t="s">
         <v>1129</v>
       </c>
@@ -14165,6 +14526,9 @@
       <c r="E487" t="b">
         <v>0</v>
       </c>
+      <c r="H487" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I487" t="s">
         <v>1129</v>
       </c>
@@ -14205,6 +14569,9 @@
       <c r="E489" t="b">
         <v>0</v>
       </c>
+      <c r="H489" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I489" t="s">
         <v>1129</v>
       </c>
@@ -14285,6 +14652,9 @@
       <c r="E493" t="b">
         <v>0</v>
       </c>
+      <c r="H493" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I493" t="s">
         <v>1129</v>
       </c>
@@ -14485,6 +14855,9 @@
       <c r="E503" t="b">
         <v>0</v>
       </c>
+      <c r="H503" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I503" t="s">
         <v>1129</v>
       </c>
@@ -14705,6 +15078,9 @@
       <c r="E514" t="b">
         <v>0</v>
       </c>
+      <c r="H514" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I514" t="s">
         <v>1129</v>
       </c>
@@ -14805,6 +15181,9 @@
       <c r="E519" t="b">
         <v>0</v>
       </c>
+      <c r="H519" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I519" t="s">
         <v>1129</v>
       </c>
@@ -14825,6 +15204,9 @@
       <c r="E520" t="b">
         <v>0</v>
       </c>
+      <c r="H520" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I520" t="s">
         <v>1129</v>
       </c>
@@ -15765,6 +16147,9 @@
       <c r="E567" t="b">
         <v>0</v>
       </c>
+      <c r="G567" t="s">
+        <v>1137</v>
+      </c>
       <c r="I567" t="s">
         <v>1129</v>
       </c>
@@ -17205,6 +17590,9 @@
       <c r="E639" t="b">
         <v>0</v>
       </c>
+      <c r="H639" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I639" t="s">
         <v>1129</v>
       </c>
@@ -17665,6 +18053,9 @@
       <c r="E662" t="b">
         <v>0</v>
       </c>
+      <c r="G662" t="s">
+        <v>1137</v>
+      </c>
       <c r="I662" t="s">
         <v>1129</v>
       </c>
@@ -18305,6 +18696,9 @@
       <c r="E694" t="b">
         <v>0</v>
       </c>
+      <c r="G694" t="s">
+        <v>1137</v>
+      </c>
       <c r="I694" t="s">
         <v>1129</v>
       </c>
@@ -18425,6 +18819,9 @@
       <c r="E700" t="b">
         <v>0</v>
       </c>
+      <c r="G700" s="2" t="s">
+        <v>1137</v>
+      </c>
       <c r="I700" t="s">
         <v>1129</v>
       </c>
@@ -18865,6 +19262,9 @@
       <c r="E722" t="b">
         <v>0</v>
       </c>
+      <c r="H722" s="2" t="s">
+        <v>1136</v>
+      </c>
       <c r="I722" t="s">
         <v>1129</v>
       </c>
@@ -19065,6 +19465,9 @@
       <c r="E732" t="b">
         <v>0</v>
       </c>
+      <c r="G732" t="s">
+        <v>1137</v>
+      </c>
       <c r="I732" t="s">
         <v>1129</v>
       </c>
@@ -21725,6 +22128,9 @@
       <c r="E865" t="b">
         <v>0</v>
       </c>
+      <c r="G865" t="s">
+        <v>1137</v>
+      </c>
       <c r="I865" t="s">
         <v>1129</v>
       </c>
@@ -21785,6 +22191,9 @@
       <c r="E868" t="b">
         <v>0</v>
       </c>
+      <c r="G868" t="s">
+        <v>1137</v>
+      </c>
       <c r="I868" t="s">
         <v>1129</v>
       </c>
@@ -21965,6 +22374,9 @@
       <c r="E877" t="b">
         <v>0</v>
       </c>
+      <c r="H877" t="s">
+        <v>1136</v>
+      </c>
       <c r="I877" t="s">
         <v>1129</v>
       </c>
@@ -22005,6 +22417,9 @@
       <c r="E879" t="b">
         <v>0</v>
       </c>
+      <c r="H879" t="s">
+        <v>1136</v>
+      </c>
       <c r="I879" t="s">
         <v>1129</v>
       </c>
@@ -22145,6 +22560,9 @@
       <c r="E886" t="b">
         <v>0</v>
       </c>
+      <c r="H886" t="s">
+        <v>1136</v>
+      </c>
       <c r="I886" t="s">
         <v>1129</v>
       </c>
@@ -22205,6 +22623,9 @@
       <c r="E889" t="b">
         <v>0</v>
       </c>
+      <c r="H889" t="s">
+        <v>1136</v>
+      </c>
       <c r="I889" t="s">
         <v>1129</v>
       </c>
@@ -22225,6 +22646,9 @@
       <c r="E890" t="b">
         <v>0</v>
       </c>
+      <c r="H890" t="s">
+        <v>1136</v>
+      </c>
       <c r="I890" t="s">
         <v>1129</v>
       </c>
@@ -22245,6 +22669,9 @@
       <c r="E891" t="b">
         <v>0</v>
       </c>
+      <c r="H891" t="s">
+        <v>1136</v>
+      </c>
       <c r="I891" t="s">
         <v>1129</v>
       </c>
@@ -22325,6 +22752,9 @@
       <c r="E895" t="b">
         <v>0</v>
       </c>
+      <c r="H895" t="s">
+        <v>1136</v>
+      </c>
       <c r="I895" t="s">
         <v>1129</v>
       </c>
@@ -22385,6 +22815,9 @@
       <c r="E898" t="b">
         <v>0</v>
       </c>
+      <c r="H898" t="s">
+        <v>1136</v>
+      </c>
       <c r="I898" t="s">
         <v>1129</v>
       </c>
@@ -22405,6 +22838,9 @@
       <c r="E899" t="b">
         <v>0</v>
       </c>
+      <c r="H899" t="s">
+        <v>1136</v>
+      </c>
       <c r="I899" t="s">
         <v>1129</v>
       </c>
@@ -22465,6 +22901,9 @@
       <c r="E902" t="b">
         <v>0</v>
       </c>
+      <c r="H902" t="s">
+        <v>1136</v>
+      </c>
       <c r="I902" t="s">
         <v>1129</v>
       </c>
@@ -22545,6 +22984,9 @@
       <c r="E906" t="b">
         <v>0</v>
       </c>
+      <c r="G906" t="s">
+        <v>1137</v>
+      </c>
       <c r="I906" t="s">
         <v>1129</v>
       </c>
@@ -22565,6 +23007,9 @@
       <c r="E907" t="b">
         <v>0</v>
       </c>
+      <c r="H907" t="s">
+        <v>1136</v>
+      </c>
       <c r="I907" t="s">
         <v>1129</v>
       </c>
@@ -22625,6 +23070,9 @@
       <c r="E910" t="b">
         <v>0</v>
       </c>
+      <c r="H910" t="s">
+        <v>1136</v>
+      </c>
       <c r="I910" t="s">
         <v>1129</v>
       </c>
@@ -22645,6 +23093,9 @@
       <c r="E911" t="b">
         <v>0</v>
       </c>
+      <c r="H911" t="s">
+        <v>1136</v>
+      </c>
       <c r="I911" t="s">
         <v>1129</v>
       </c>
@@ -22665,6 +23116,9 @@
       <c r="E912" t="b">
         <v>0</v>
       </c>
+      <c r="H912" t="s">
+        <v>1136</v>
+      </c>
       <c r="I912" t="s">
         <v>1129</v>
       </c>
@@ -22745,6 +23199,9 @@
       <c r="E916" t="b">
         <v>0</v>
       </c>
+      <c r="H916" t="s">
+        <v>1136</v>
+      </c>
       <c r="I916" t="s">
         <v>1129</v>
       </c>
@@ -22825,6 +23282,9 @@
       <c r="E920" t="b">
         <v>0</v>
       </c>
+      <c r="H920" t="s">
+        <v>1136</v>
+      </c>
       <c r="I920" t="s">
         <v>1129</v>
       </c>
@@ -22845,6 +23305,9 @@
       <c r="E921" t="b">
         <v>0</v>
       </c>
+      <c r="H921" t="s">
+        <v>1136</v>
+      </c>
       <c r="I921" t="s">
         <v>1129</v>
       </c>
@@ -22885,6 +23348,9 @@
       <c r="E923" t="b">
         <v>0</v>
       </c>
+      <c r="H923" t="s">
+        <v>1136</v>
+      </c>
       <c r="I923" t="s">
         <v>1129</v>
       </c>
@@ -22905,6 +23371,9 @@
       <c r="E924" t="b">
         <v>0</v>
       </c>
+      <c r="H924" t="s">
+        <v>1136</v>
+      </c>
       <c r="I924" t="s">
         <v>1129</v>
       </c>
@@ -22925,6 +23394,9 @@
       <c r="E925" t="b">
         <v>0</v>
       </c>
+      <c r="H925" t="s">
+        <v>1136</v>
+      </c>
       <c r="I925" t="s">
         <v>1129</v>
       </c>
@@ -23005,6 +23477,9 @@
       <c r="E929" t="b">
         <v>0</v>
       </c>
+      <c r="H929" t="s">
+        <v>1136</v>
+      </c>
       <c r="I929" t="s">
         <v>1129</v>
       </c>
@@ -23085,6 +23560,9 @@
       <c r="E933" t="b">
         <v>0</v>
       </c>
+      <c r="G933" t="s">
+        <v>1137</v>
+      </c>
       <c r="I933" t="s">
         <v>1129</v>
       </c>
@@ -23145,6 +23623,9 @@
       <c r="E936" t="b">
         <v>0</v>
       </c>
+      <c r="H936" t="s">
+        <v>1136</v>
+      </c>
       <c r="I936" t="s">
         <v>1129</v>
       </c>
@@ -23165,6 +23646,9 @@
       <c r="E937" t="b">
         <v>0</v>
       </c>
+      <c r="H937" t="s">
+        <v>1136</v>
+      </c>
       <c r="I937" t="s">
         <v>1129</v>
       </c>
@@ -23185,6 +23669,9 @@
       <c r="E938" t="b">
         <v>0</v>
       </c>
+      <c r="H938" t="s">
+        <v>1136</v>
+      </c>
       <c r="I938" t="s">
         <v>1129</v>
       </c>
@@ -23205,6 +23692,9 @@
       <c r="E939" t="b">
         <v>0</v>
       </c>
+      <c r="H939" t="s">
+        <v>1136</v>
+      </c>
       <c r="I939" t="s">
         <v>1129</v>
       </c>
@@ -23245,6 +23735,9 @@
       <c r="E941" t="b">
         <v>0</v>
       </c>
+      <c r="H941" t="s">
+        <v>1136</v>
+      </c>
       <c r="I941" t="s">
         <v>1129</v>
       </c>
@@ -23345,6 +23838,9 @@
       <c r="E946" t="b">
         <v>0</v>
       </c>
+      <c r="H946" t="s">
+        <v>1136</v>
+      </c>
       <c r="I946" t="s">
         <v>1129</v>
       </c>
@@ -23425,6 +23921,9 @@
       <c r="E950" t="b">
         <v>0</v>
       </c>
+      <c r="H950" t="s">
+        <v>1136</v>
+      </c>
       <c r="I950" t="s">
         <v>1129</v>
       </c>
@@ -23505,6 +24004,9 @@
       <c r="E954" t="b">
         <v>0</v>
       </c>
+      <c r="H954" t="s">
+        <v>1136</v>
+      </c>
       <c r="I954" t="s">
         <v>1129</v>
       </c>
@@ -23525,6 +24027,9 @@
       <c r="E955" t="b">
         <v>0</v>
       </c>
+      <c r="H955" t="s">
+        <v>1136</v>
+      </c>
       <c r="I955" t="s">
         <v>1129</v>
       </c>
@@ -23565,6 +24070,9 @@
       <c r="E957" t="b">
         <v>0</v>
       </c>
+      <c r="H957" t="s">
+        <v>1136</v>
+      </c>
       <c r="I957" t="s">
         <v>1129</v>
       </c>
@@ -23625,6 +24133,9 @@
       <c r="E960" t="b">
         <v>0</v>
       </c>
+      <c r="H960" t="s">
+        <v>1136</v>
+      </c>
       <c r="I960" t="s">
         <v>1129</v>
       </c>
@@ -23685,6 +24196,9 @@
       <c r="E963" t="b">
         <v>0</v>
       </c>
+      <c r="G963" t="s">
+        <v>1137</v>
+      </c>
       <c r="I963" t="s">
         <v>1129</v>
       </c>
@@ -23725,6 +24239,9 @@
       <c r="E965" t="b">
         <v>0</v>
       </c>
+      <c r="H965" t="s">
+        <v>1136</v>
+      </c>
       <c r="I965" t="s">
         <v>1129</v>
       </c>
@@ -23745,6 +24262,9 @@
       <c r="E966" t="b">
         <v>0</v>
       </c>
+      <c r="H966" t="s">
+        <v>1136</v>
+      </c>
       <c r="I966" t="s">
         <v>1129</v>
       </c>
@@ -23765,6 +24285,9 @@
       <c r="E967" t="b">
         <v>0</v>
       </c>
+      <c r="H967" t="s">
+        <v>1136</v>
+      </c>
       <c r="I967" t="s">
         <v>1129</v>
       </c>
@@ -23845,6 +24368,9 @@
       <c r="E971" t="b">
         <v>0</v>
       </c>
+      <c r="H971" t="s">
+        <v>1136</v>
+      </c>
       <c r="I971" t="s">
         <v>1129</v>
       </c>
@@ -23885,6 +24411,9 @@
       <c r="E973" t="b">
         <v>0</v>
       </c>
+      <c r="H973" t="s">
+        <v>1136</v>
+      </c>
       <c r="I973" t="s">
         <v>1129</v>
       </c>
@@ -23925,6 +24454,9 @@
       <c r="E975" t="b">
         <v>0</v>
       </c>
+      <c r="H975" t="s">
+        <v>1136</v>
+      </c>
       <c r="I975" t="s">
         <v>1129</v>
       </c>
@@ -24005,6 +24537,9 @@
       <c r="E979" t="b">
         <v>0</v>
       </c>
+      <c r="H979" t="s">
+        <v>1136</v>
+      </c>
       <c r="I979" t="s">
         <v>1129</v>
       </c>
@@ -24105,6 +24640,9 @@
       <c r="E984" t="b">
         <v>0</v>
       </c>
+      <c r="G984" t="s">
+        <v>1137</v>
+      </c>
       <c r="I984" t="s">
         <v>1129</v>
       </c>
@@ -24245,6 +24783,9 @@
       <c r="E991" t="b">
         <v>0</v>
       </c>
+      <c r="H991" t="s">
+        <v>1136</v>
+      </c>
       <c r="I991" t="s">
         <v>1129</v>
       </c>
@@ -24285,6 +24826,9 @@
       <c r="E993" t="b">
         <v>0</v>
       </c>
+      <c r="H993" t="s">
+        <v>1136</v>
+      </c>
       <c r="I993" t="s">
         <v>1129</v>
       </c>
@@ -24304,6 +24848,9 @@
       </c>
       <c r="E994" t="b">
         <v>0</v>
+      </c>
+      <c r="H994" t="s">
+        <v>1136</v>
       </c>
       <c r="I994" t="s">
         <v>1129</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B159B9-A89D-7441-8769-9C98EFEE7AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6128C858-0376-FD47-99E3-379F9FAAE810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="1820" windowWidth="32060" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="1820" windowWidth="32060" windowHeight="16700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5376" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5382" uniqueCount="1140">
   <si>
     <t>Table Name</t>
   </si>
@@ -3456,7 +3456,10 @@
     <t>belongs_to</t>
   </si>
   <si>
-    <t>customer_performance.mdm_id; customer_kplus.mdm_id; customer_icons.mdm_id; customer_dplk.mdm_id; customer_creditcard.mdm_id; customer_wms.mdm_id</t>
+    <t>customer_performance.mdm_id</t>
+  </si>
+  <si>
+    <t>customer_beneficial_owner.bo_id_type</t>
   </si>
 </sst>
 </file>
@@ -4442,6 +4445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J1009"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4450,7 +4454,7 @@
     <col min="3" max="3" width="32.6640625" customWidth="1"/>
     <col min="4" max="4" width="86.6640625" customWidth="1"/>
     <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
@@ -4489,7 +4493,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4509,7 +4513,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4529,7 +4533,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4549,7 +4553,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4569,7 +4573,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4589,7 +4593,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4609,7 +4613,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4629,7 +4633,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -4652,7 +4656,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -4675,7 +4679,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -4695,7 +4699,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -4718,7 +4722,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4738,7 +4742,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -4758,7 +4762,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -4778,7 +4782,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -4801,7 +4805,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -4847,7 +4851,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -4867,7 +4871,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -4890,7 +4894,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -4910,7 +4914,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -4933,7 +4937,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -4956,7 +4960,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -4976,7 +4980,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -4999,7 +5003,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -5019,7 +5023,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -5042,7 +5046,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -5065,7 +5069,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -5088,7 +5092,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -5111,7 +5115,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -5134,7 +5138,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -5157,7 +5161,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -5180,7 +5184,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -5200,7 +5204,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -5223,7 +5227,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -5246,7 +5250,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -5266,7 +5270,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -5286,7 +5290,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -5306,7 +5310,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -5326,7 +5330,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -5349,7 +5353,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -5372,7 +5376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -5411,14 +5415,11 @@
       <c r="E44" t="b">
         <v>1</v>
       </c>
-      <c r="G44" t="s">
-        <v>1137</v>
-      </c>
       <c r="I44" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -5441,7 +5442,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -5464,7 +5465,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -5484,7 +5485,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -5504,7 +5505,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -5527,7 +5528,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -5547,7 +5548,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -5570,7 +5571,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -5590,7 +5591,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -5610,7 +5611,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -5630,7 +5631,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -5644,13 +5645,19 @@
         <v>779</v>
       </c>
       <c r="E55" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1137</v>
       </c>
       <c r="I55" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -5670,7 +5677,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -5690,7 +5697,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -5713,7 +5720,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -5733,7 +5740,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -5753,7 +5760,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -5773,7 +5780,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -5796,7 +5803,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -5816,7 +5823,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -5836,7 +5843,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -5856,7 +5863,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -5876,7 +5883,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -5896,7 +5903,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -5916,7 +5923,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -5936,7 +5943,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -5956,7 +5963,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -5976,7 +5983,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -5996,7 +6003,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -6010,7 +6017,10 @@
         <v>768</v>
       </c>
       <c r="E73" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1138</v>
       </c>
       <c r="G73" t="s">
         <v>1137</v>
@@ -6019,7 +6029,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -6039,7 +6049,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -6062,7 +6072,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -6082,7 +6092,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -6105,7 +6115,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -6125,7 +6135,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -6148,7 +6158,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -6171,7 +6181,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -6191,7 +6201,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -6211,7 +6221,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -6231,7 +6241,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -6251,7 +6261,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -6271,7 +6281,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>7</v>
       </c>
@@ -6291,7 +6301,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -6311,7 +6321,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -6331,7 +6341,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -6351,7 +6361,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -6371,7 +6381,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -6391,7 +6401,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -6414,7 +6424,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -6434,7 +6444,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -6454,7 +6464,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -6477,7 +6487,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -6497,7 +6507,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -6517,7 +6527,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -6537,7 +6547,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -6557,7 +6567,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -6577,7 +6587,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -6600,7 +6610,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -6620,7 +6630,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -6640,7 +6650,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>7</v>
       </c>
@@ -6660,7 +6670,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>7</v>
       </c>
@@ -6683,7 +6693,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -6703,7 +6713,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -6723,7 +6733,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -6737,7 +6747,10 @@
         <v>768</v>
       </c>
       <c r="E108" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1138</v>
       </c>
       <c r="G108" t="s">
         <v>1137</v>
@@ -6746,7 +6759,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -6766,7 +6779,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -6789,7 +6802,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -6809,7 +6822,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -6829,7 +6842,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -6852,7 +6865,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -6875,7 +6888,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -6895,7 +6908,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -6915,7 +6928,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -6935,7 +6948,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -6955,7 +6968,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>8</v>
       </c>
@@ -6975,7 +6988,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -6995,7 +7008,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -7015,7 +7028,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -7055,7 +7068,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -7075,7 +7088,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -7095,7 +7108,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -7115,7 +7128,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -7135,7 +7148,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -7155,7 +7168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -7175,7 +7188,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -7195,7 +7208,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -7215,7 +7228,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -7235,7 +7248,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -7258,7 +7271,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -7272,7 +7285,10 @@
         <v>768</v>
       </c>
       <c r="E134" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1138</v>
       </c>
       <c r="G134" t="s">
         <v>1137</v>
@@ -7281,7 +7297,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -7301,7 +7317,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -7321,7 +7337,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -7341,7 +7357,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -7361,7 +7377,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -7384,7 +7400,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -7404,7 +7420,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -7424,7 +7440,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -7441,7 +7457,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -7461,7 +7477,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -7481,7 +7497,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -7501,7 +7517,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -7521,7 +7537,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -7544,7 +7560,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -7561,7 +7577,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -7581,7 +7597,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -7601,7 +7617,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -7621,7 +7637,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -7638,7 +7654,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>10</v>
       </c>
@@ -7658,7 +7674,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -7681,7 +7697,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>10</v>
       </c>
@@ -7701,7 +7717,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -7718,7 +7734,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -7738,7 +7754,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -7758,7 +7774,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -7775,7 +7791,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -7795,7 +7811,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>10</v>
       </c>
@@ -7815,7 +7831,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>10</v>
       </c>
@@ -7835,7 +7851,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>10</v>
       </c>
@@ -7855,7 +7871,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>10</v>
       </c>
@@ -7875,7 +7891,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>10</v>
       </c>
@@ -7895,7 +7911,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -7915,7 +7931,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>10</v>
       </c>
@@ -7935,7 +7951,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -7955,7 +7971,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>10</v>
       </c>
@@ -7975,7 +7991,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -7995,7 +8011,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -8012,7 +8028,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>10</v>
       </c>
@@ -8026,7 +8042,10 @@
         <v>768</v>
       </c>
       <c r="E172" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1138</v>
       </c>
       <c r="G172" t="s">
         <v>1137</v>
@@ -8035,7 +8054,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>10</v>
       </c>
@@ -8055,7 +8074,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -8075,7 +8094,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>10</v>
       </c>
@@ -8095,7 +8114,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>10</v>
       </c>
@@ -8115,7 +8134,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>10</v>
       </c>
@@ -8138,7 +8157,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -8158,7 +8177,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -8178,7 +8197,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>11</v>
       </c>
@@ -8198,7 +8217,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -8218,7 +8237,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -8241,7 +8260,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -8264,7 +8283,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -8284,7 +8303,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -8307,7 +8326,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -8327,7 +8346,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -8347,7 +8366,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -8370,7 +8389,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -8390,7 +8409,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -8410,7 +8429,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -8433,7 +8452,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -8453,7 +8472,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -8476,7 +8495,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -8499,7 +8518,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>13</v>
       </c>
@@ -8522,7 +8541,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -8545,7 +8564,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -8568,7 +8587,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>13</v>
       </c>
@@ -8591,7 +8610,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -8614,7 +8633,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -8637,7 +8656,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>13</v>
       </c>
@@ -8660,7 +8679,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -8683,7 +8702,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -8706,7 +8725,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -8729,7 +8748,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -8752,7 +8771,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -8775,7 +8794,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -8795,7 +8814,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -8818,7 +8837,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -8841,7 +8860,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -8864,7 +8883,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>14</v>
       </c>
@@ -8884,7 +8903,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>14</v>
       </c>
@@ -8904,7 +8923,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>15</v>
       </c>
@@ -8924,7 +8943,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>15</v>
       </c>
@@ -8944,7 +8963,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>15</v>
       </c>
@@ -8964,7 +8983,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>15</v>
       </c>
@@ -8984,7 +9003,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -9004,7 +9023,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>15</v>
       </c>
@@ -9024,7 +9043,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -9038,7 +9057,10 @@
         <v>768</v>
       </c>
       <c r="E219" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1138</v>
       </c>
       <c r="G219" t="s">
         <v>1137</v>
@@ -9047,7 +9069,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -9067,7 +9089,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -9087,7 +9109,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -9107,7 +9129,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -9127,7 +9149,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -9147,7 +9169,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -9167,7 +9189,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -9187,7 +9209,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -9207,7 +9229,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -9227,7 +9249,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -9247,7 +9269,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -9267,7 +9289,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -9290,7 +9312,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>17</v>
       </c>
@@ -9310,7 +9332,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>17</v>
       </c>
@@ -9336,7 +9358,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -9356,7 +9378,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -9376,7 +9398,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>19</v>
       </c>
@@ -9396,7 +9418,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>19</v>
       </c>
@@ -9416,7 +9438,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -9436,7 +9458,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>19</v>
       </c>
@@ -9456,7 +9478,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -9476,7 +9498,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>19</v>
       </c>
@@ -9496,7 +9518,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>19</v>
       </c>
@@ -9516,7 +9538,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>19</v>
       </c>
@@ -9536,7 +9558,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>19</v>
       </c>
@@ -9556,7 +9578,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>19</v>
       </c>
@@ -9579,7 +9601,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>19</v>
       </c>
@@ -9599,7 +9621,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>19</v>
       </c>
@@ -9619,7 +9641,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>19</v>
       </c>
@@ -9639,7 +9661,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -9659,7 +9681,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>19</v>
       </c>
@@ -9679,7 +9701,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>19</v>
       </c>
@@ -9702,7 +9724,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>19</v>
       </c>
@@ -9722,7 +9744,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>19</v>
       </c>
@@ -9742,7 +9764,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>19</v>
       </c>
@@ -9762,7 +9784,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>19</v>
       </c>
@@ -9785,7 +9807,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>19</v>
       </c>
@@ -9805,7 +9827,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>19</v>
       </c>
@@ -9825,7 +9847,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -9845,7 +9867,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>19</v>
       </c>
@@ -9865,7 +9887,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>19</v>
       </c>
@@ -9885,7 +9907,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>19</v>
       </c>
@@ -9905,7 +9927,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>19</v>
       </c>
@@ -9925,7 +9947,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>19</v>
       </c>
@@ -9945,7 +9967,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>19</v>
       </c>
@@ -9965,7 +9987,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>19</v>
       </c>
@@ -9988,7 +10010,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>19</v>
       </c>
@@ -10008,7 +10030,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -10028,7 +10050,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>20</v>
       </c>
@@ -10048,7 +10070,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>20</v>
       </c>
@@ -10068,7 +10090,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>20</v>
       </c>
@@ -10088,7 +10110,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>21</v>
       </c>
@@ -10108,7 +10130,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>22</v>
       </c>
@@ -10128,7 +10150,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>22</v>
       </c>
@@ -10148,7 +10170,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>22</v>
       </c>
@@ -10168,7 +10190,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>22</v>
       </c>
@@ -10188,7 +10210,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>23</v>
       </c>
@@ -10208,7 +10230,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -10228,7 +10250,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>23</v>
       </c>
@@ -10248,7 +10270,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>24</v>
       </c>
@@ -10268,7 +10290,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>25</v>
       </c>
@@ -10288,7 +10310,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>25</v>
       </c>
@@ -10308,7 +10330,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>25</v>
       </c>
@@ -10328,7 +10350,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>25</v>
       </c>
@@ -10354,7 +10376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>26</v>
       </c>
@@ -10374,7 +10396,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>26</v>
       </c>
@@ -10394,7 +10416,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>26</v>
       </c>
@@ -10414,7 +10436,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>26</v>
       </c>
@@ -10434,7 +10456,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>26</v>
       </c>
@@ -10460,7 +10482,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>27</v>
       </c>
@@ -10480,7 +10502,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>28</v>
       </c>
@@ -10500,7 +10522,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>29</v>
       </c>
@@ -10523,7 +10545,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>29</v>
       </c>
@@ -10543,7 +10565,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>29</v>
       </c>
@@ -10563,7 +10585,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>30</v>
       </c>
@@ -10586,7 +10608,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>30</v>
       </c>
@@ -10606,7 +10628,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>30</v>
       </c>
@@ -10626,7 +10648,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>31</v>
       </c>
@@ -10646,7 +10668,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>31</v>
       </c>
@@ -10666,7 +10688,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>32</v>
       </c>
@@ -10686,7 +10708,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>32</v>
       </c>
@@ -10706,7 +10728,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>32</v>
       </c>
@@ -10726,7 +10748,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>33</v>
       </c>
@@ -10746,7 +10768,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>34</v>
       </c>
@@ -10769,7 +10791,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>34</v>
       </c>
@@ -10789,7 +10811,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>34</v>
       </c>
@@ -10809,7 +10831,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>34</v>
       </c>
@@ -10832,7 +10854,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>34</v>
       </c>
@@ -10852,7 +10874,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>34</v>
       </c>
@@ -10872,7 +10894,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>34</v>
       </c>
@@ -10892,7 +10914,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>34</v>
       </c>
@@ -10912,7 +10934,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>34</v>
       </c>
@@ -10932,7 +10954,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>34</v>
       </c>
@@ -10952,7 +10974,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>34</v>
       </c>
@@ -10972,7 +10994,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>34</v>
       </c>
@@ -10992,7 +11014,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>34</v>
       </c>
@@ -11012,7 +11034,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>34</v>
       </c>
@@ -11035,7 +11057,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>34</v>
       </c>
@@ -11055,7 +11077,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>34</v>
       </c>
@@ -11075,7 +11097,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>35</v>
       </c>
@@ -11095,7 +11117,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>35</v>
       </c>
@@ -11115,7 +11137,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>35</v>
       </c>
@@ -11135,7 +11157,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>36</v>
       </c>
@@ -11155,7 +11177,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>36</v>
       </c>
@@ -11175,7 +11197,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>37</v>
       </c>
@@ -11195,7 +11217,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>38</v>
       </c>
@@ -11215,7 +11237,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>38</v>
       </c>
@@ -11235,7 +11257,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>38</v>
       </c>
@@ -11255,7 +11277,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>38</v>
       </c>
@@ -11275,7 +11297,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>39</v>
       </c>
@@ -11295,7 +11317,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>39</v>
       </c>
@@ -11315,7 +11337,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>39</v>
       </c>
@@ -11335,7 +11357,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>39</v>
       </c>
@@ -11355,7 +11377,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>39</v>
       </c>
@@ -11375,7 +11397,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>39</v>
       </c>
@@ -11395,7 +11417,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>39</v>
       </c>
@@ -11415,7 +11437,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>39</v>
       </c>
@@ -11435,7 +11457,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>39</v>
       </c>
@@ -11455,7 +11477,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>39</v>
       </c>
@@ -11475,7 +11497,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -11495,7 +11517,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -11515,7 +11537,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>40</v>
       </c>
@@ -11535,7 +11557,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>41</v>
       </c>
@@ -11558,7 +11580,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -11578,7 +11600,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>41</v>
       </c>
@@ -11598,7 +11620,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>41</v>
       </c>
@@ -11621,7 +11643,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>41</v>
       </c>
@@ -11641,7 +11663,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>42</v>
       </c>
@@ -11664,7 +11686,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>42</v>
       </c>
@@ -11684,7 +11706,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>42</v>
       </c>
@@ -11707,7 +11729,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>42</v>
       </c>
@@ -11730,7 +11752,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>42</v>
       </c>
@@ -11750,7 +11772,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>42</v>
       </c>
@@ -11773,7 +11795,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>43</v>
       </c>
@@ -11793,7 +11815,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>43</v>
       </c>
@@ -11813,7 +11835,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>43</v>
       </c>
@@ -11833,7 +11855,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>43</v>
       </c>
@@ -11856,7 +11878,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>43</v>
       </c>
@@ -11876,7 +11898,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>44</v>
       </c>
@@ -11896,7 +11918,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>44</v>
       </c>
@@ -11916,7 +11938,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>44</v>
       </c>
@@ -11939,7 +11961,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>44</v>
       </c>
@@ -11959,7 +11981,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>45</v>
       </c>
@@ -11979,7 +12001,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>46</v>
       </c>
@@ -11999,7 +12021,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>46</v>
       </c>
@@ -12019,7 +12041,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>46</v>
       </c>
@@ -12039,7 +12061,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>46</v>
       </c>
@@ -12059,7 +12081,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>46</v>
       </c>
@@ -12079,7 +12101,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>46</v>
       </c>
@@ -12099,7 +12121,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>46</v>
       </c>
@@ -12119,7 +12141,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>46</v>
       </c>
@@ -12139,7 +12161,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>46</v>
       </c>
@@ -12159,7 +12181,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>46</v>
       </c>
@@ -12179,7 +12201,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>46</v>
       </c>
@@ -12199,7 +12221,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>46</v>
       </c>
@@ -12219,7 +12241,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>46</v>
       </c>
@@ -12239,7 +12261,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>46</v>
       </c>
@@ -12259,7 +12281,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>46</v>
       </c>
@@ -12279,7 +12301,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>46</v>
       </c>
@@ -12299,7 +12321,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>46</v>
       </c>
@@ -12319,7 +12341,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>46</v>
       </c>
@@ -12339,7 +12361,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>46</v>
       </c>
@@ -12359,7 +12381,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>46</v>
       </c>
@@ -12379,7 +12401,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>46</v>
       </c>
@@ -12399,7 +12421,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>46</v>
       </c>
@@ -12419,7 +12441,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>47</v>
       </c>
@@ -12439,7 +12461,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>47</v>
       </c>
@@ -12459,7 +12481,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>47</v>
       </c>
@@ -12479,7 +12501,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>47</v>
       </c>
@@ -12499,7 +12521,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>47</v>
       </c>
@@ -12519,7 +12541,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>47</v>
       </c>
@@ -12539,7 +12561,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>47</v>
       </c>
@@ -12559,7 +12581,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>47</v>
       </c>
@@ -12579,7 +12601,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>48</v>
       </c>
@@ -12605,7 +12627,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>48</v>
       </c>
@@ -12625,7 +12647,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>48</v>
       </c>
@@ -12648,7 +12670,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>48</v>
       </c>
@@ -12668,7 +12690,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>48</v>
       </c>
@@ -12688,7 +12710,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>49</v>
       </c>
@@ -12708,7 +12730,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>49</v>
       </c>
@@ -12728,7 +12750,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>49</v>
       </c>
@@ -12748,7 +12770,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>49</v>
       </c>
@@ -12768,7 +12790,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>49</v>
       </c>
@@ -12788,7 +12810,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>49</v>
       </c>
@@ -12811,7 +12833,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>49</v>
       </c>
@@ -12831,7 +12853,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>49</v>
       </c>
@@ -12851,7 +12873,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>49</v>
       </c>
@@ -12871,7 +12893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>49</v>
       </c>
@@ -12891,7 +12913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>49</v>
       </c>
@@ -12911,7 +12933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>49</v>
       </c>
@@ -12931,7 +12953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>49</v>
       </c>
@@ -12951,7 +12973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>49</v>
       </c>
@@ -12971,7 +12993,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>49</v>
       </c>
@@ -12991,7 +13013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>49</v>
       </c>
@@ -13011,7 +13033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>49</v>
       </c>
@@ -13031,7 +13053,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>49</v>
       </c>
@@ -13051,7 +13073,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>49</v>
       </c>
@@ -13071,7 +13093,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>49</v>
       </c>
@@ -13091,7 +13113,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>49</v>
       </c>
@@ -13111,7 +13133,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>49</v>
       </c>
@@ -13131,7 +13153,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>49</v>
       </c>
@@ -13151,7 +13173,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>49</v>
       </c>
@@ -13174,7 +13196,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>49</v>
       </c>
@@ -13194,7 +13216,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>49</v>
       </c>
@@ -13214,7 +13236,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>49</v>
       </c>
@@ -13234,7 +13256,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>49</v>
       </c>
@@ -13254,7 +13276,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>49</v>
       </c>
@@ -13274,7 +13296,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>50</v>
       </c>
@@ -13294,7 +13316,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>50</v>
       </c>
@@ -13314,7 +13336,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>50</v>
       </c>
@@ -13334,7 +13356,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>50</v>
       </c>
@@ -13354,7 +13376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>50</v>
       </c>
@@ -13374,7 +13396,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>50</v>
       </c>
@@ -13394,7 +13416,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>51</v>
       </c>
@@ -13414,7 +13436,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>52</v>
       </c>
@@ -13434,7 +13456,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>52</v>
       </c>
@@ -13454,7 +13476,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>52</v>
       </c>
@@ -13477,7 +13499,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>52</v>
       </c>
@@ -13497,7 +13519,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>52</v>
       </c>
@@ -13517,7 +13539,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>52</v>
       </c>
@@ -13537,7 +13559,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>52</v>
       </c>
@@ -13557,7 +13579,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>52</v>
       </c>
@@ -13577,7 +13599,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>52</v>
       </c>
@@ -13597,7 +13619,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>52</v>
       </c>
@@ -13617,7 +13639,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>52</v>
       </c>
@@ -13637,7 +13659,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>52</v>
       </c>
@@ -13657,7 +13679,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>52</v>
       </c>
@@ -13677,7 +13699,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>52</v>
       </c>
@@ -13697,7 +13719,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>52</v>
       </c>
@@ -13717,7 +13739,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>52</v>
       </c>
@@ -13737,7 +13759,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>52</v>
       </c>
@@ -13757,7 +13779,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>52</v>
       </c>
@@ -13777,7 +13799,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>52</v>
       </c>
@@ -13797,7 +13819,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>52</v>
       </c>
@@ -13820,7 +13842,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>52</v>
       </c>
@@ -13843,7 +13865,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>52</v>
       </c>
@@ -13863,7 +13885,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>52</v>
       </c>
@@ -13886,7 +13908,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>52</v>
       </c>
@@ -13912,7 +13934,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>52</v>
       </c>
@@ -13932,7 +13954,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>52</v>
       </c>
@@ -13952,7 +13974,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>52</v>
       </c>
@@ -13975,7 +13997,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>52</v>
       </c>
@@ -13995,7 +14017,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>53</v>
       </c>
@@ -14018,7 +14040,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>53</v>
       </c>
@@ -14038,7 +14060,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>53</v>
       </c>
@@ -14061,7 +14083,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>53</v>
       </c>
@@ -14081,7 +14103,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>53</v>
       </c>
@@ -14107,7 +14129,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>53</v>
       </c>
@@ -14127,7 +14149,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>53</v>
       </c>
@@ -14147,7 +14169,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>53</v>
       </c>
@@ -14167,7 +14189,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>53</v>
       </c>
@@ -14187,7 +14209,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>53</v>
       </c>
@@ -14207,7 +14229,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>53</v>
       </c>
@@ -14227,7 +14249,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>53</v>
       </c>
@@ -14247,7 +14269,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>54</v>
       </c>
@@ -14267,7 +14289,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>54</v>
       </c>
@@ -14287,7 +14309,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>55</v>
       </c>
@@ -14307,7 +14329,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>55</v>
       </c>
@@ -14327,7 +14349,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>55</v>
       </c>
@@ -14347,7 +14369,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>55</v>
       </c>
@@ -14367,7 +14389,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>55</v>
       </c>
@@ -14387,7 +14409,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>56</v>
       </c>
@@ -14407,7 +14429,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>56</v>
       </c>
@@ -14427,7 +14449,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>56</v>
       </c>
@@ -14447,7 +14469,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>56</v>
       </c>
@@ -14467,7 +14489,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>56</v>
       </c>
@@ -14490,7 +14512,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>56</v>
       </c>
@@ -14510,7 +14532,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>56</v>
       </c>
@@ -14533,7 +14555,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>56</v>
       </c>
@@ -14553,7 +14575,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>56</v>
       </c>
@@ -14576,7 +14598,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>56</v>
       </c>
@@ -14596,7 +14618,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>56</v>
       </c>
@@ -14616,7 +14638,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>56</v>
       </c>
@@ -14636,7 +14658,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>56</v>
       </c>
@@ -14659,7 +14681,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>56</v>
       </c>
@@ -14679,7 +14701,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>56</v>
       </c>
@@ -14699,7 +14721,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>56</v>
       </c>
@@ -14719,7 +14741,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>56</v>
       </c>
@@ -14739,7 +14761,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>56</v>
       </c>
@@ -14759,7 +14781,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>56</v>
       </c>
@@ -14779,7 +14801,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>56</v>
       </c>
@@ -14799,7 +14821,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>56</v>
       </c>
@@ -14819,7 +14841,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>56</v>
       </c>
@@ -14839,7 +14861,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>56</v>
       </c>
@@ -14862,7 +14884,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>56</v>
       </c>
@@ -14882,7 +14904,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>56</v>
       </c>
@@ -14902,7 +14924,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>56</v>
       </c>
@@ -14922,7 +14944,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>56</v>
       </c>
@@ -14942,7 +14964,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>56</v>
       </c>
@@ -14962,7 +14984,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>56</v>
       </c>
@@ -14982,7 +15004,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>56</v>
       </c>
@@ -15002,7 +15024,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>56</v>
       </c>
@@ -15022,7 +15044,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>56</v>
       </c>
@@ -15042,7 +15064,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>56</v>
       </c>
@@ -15062,7 +15084,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>56</v>
       </c>
@@ -15085,7 +15107,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>56</v>
       </c>
@@ -15105,7 +15127,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>56</v>
       </c>
@@ -15125,7 +15147,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>56</v>
       </c>
@@ -15145,7 +15167,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>56</v>
       </c>
@@ -15165,7 +15187,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>56</v>
       </c>
@@ -15188,7 +15210,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>56</v>
       </c>
@@ -15211,7 +15233,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>57</v>
       </c>
@@ -15231,7 +15253,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>57</v>
       </c>
@@ -15251,7 +15273,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>57</v>
       </c>
@@ -15271,7 +15293,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>58</v>
       </c>
@@ -15291,7 +15313,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>58</v>
       </c>
@@ -15311,7 +15333,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>58</v>
       </c>
@@ -15331,7 +15353,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>59</v>
       </c>
@@ -15351,7 +15373,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>59</v>
       </c>
@@ -15371,7 +15393,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>60</v>
       </c>
@@ -15391,7 +15413,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>60</v>
       </c>
@@ -15411,7 +15433,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>61</v>
       </c>
@@ -15431,7 +15453,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>61</v>
       </c>
@@ -15451,7 +15473,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>61</v>
       </c>
@@ -15471,7 +15493,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>62</v>
       </c>
@@ -15491,7 +15513,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>62</v>
       </c>
@@ -15511,7 +15533,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>62</v>
       </c>
@@ -15531,7 +15553,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>62</v>
       </c>
@@ -15551,7 +15573,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>62</v>
       </c>
@@ -15571,7 +15593,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>62</v>
       </c>
@@ -15591,7 +15613,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>62</v>
       </c>
@@ -15611,7 +15633,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>62</v>
       </c>
@@ -15631,7 +15653,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>62</v>
       </c>
@@ -15651,7 +15673,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>62</v>
       </c>
@@ -15671,7 +15693,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>62</v>
       </c>
@@ -15691,7 +15713,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>62</v>
       </c>
@@ -15711,7 +15733,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>62</v>
       </c>
@@ -15731,7 +15753,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>62</v>
       </c>
@@ -15751,7 +15773,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>62</v>
       </c>
@@ -15771,7 +15793,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>62</v>
       </c>
@@ -15791,7 +15813,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>62</v>
       </c>
@@ -15811,7 +15833,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>62</v>
       </c>
@@ -15831,7 +15853,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>62</v>
       </c>
@@ -15851,7 +15873,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>62</v>
       </c>
@@ -15871,7 +15893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>62</v>
       </c>
@@ -15891,7 +15913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>62</v>
       </c>
@@ -15911,7 +15933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>62</v>
       </c>
@@ -15931,7 +15953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>62</v>
       </c>
@@ -15951,7 +15973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>62</v>
       </c>
@@ -15971,7 +15993,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>62</v>
       </c>
@@ -15991,7 +16013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>62</v>
       </c>
@@ -16011,7 +16033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>62</v>
       </c>
@@ -16031,7 +16053,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>62</v>
       </c>
@@ -16051,7 +16073,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>62</v>
       </c>
@@ -16071,7 +16093,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>62</v>
       </c>
@@ -16091,7 +16113,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>62</v>
       </c>
@@ -16111,7 +16133,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>62</v>
       </c>
@@ -16131,7 +16153,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>62</v>
       </c>
@@ -16154,7 +16176,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>62</v>
       </c>
@@ -16174,7 +16196,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>62</v>
       </c>
@@ -16194,7 +16216,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>62</v>
       </c>
@@ -16214,7 +16236,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>62</v>
       </c>
@@ -16234,7 +16256,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>62</v>
       </c>
@@ -16254,7 +16276,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>62</v>
       </c>
@@ -16274,7 +16296,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>62</v>
       </c>
@@ -16294,7 +16316,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>62</v>
       </c>
@@ -16314,7 +16336,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>62</v>
       </c>
@@ -16334,7 +16356,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>62</v>
       </c>
@@ -16354,7 +16376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>62</v>
       </c>
@@ -16374,7 +16396,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>62</v>
       </c>
@@ -16394,7 +16416,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>62</v>
       </c>
@@ -16414,7 +16436,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>62</v>
       </c>
@@ -16434,7 +16456,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>62</v>
       </c>
@@ -16454,7 +16476,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>62</v>
       </c>
@@ -16474,7 +16496,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>62</v>
       </c>
@@ -16494,7 +16516,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>62</v>
       </c>
@@ -16514,7 +16536,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>62</v>
       </c>
@@ -16534,7 +16556,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>62</v>
       </c>
@@ -16554,7 +16576,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>62</v>
       </c>
@@ -16574,7 +16596,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>62</v>
       </c>
@@ -16594,7 +16616,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>62</v>
       </c>
@@ -16614,7 +16636,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>62</v>
       </c>
@@ -16634,7 +16656,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>62</v>
       </c>
@@ -16654,7 +16676,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>62</v>
       </c>
@@ -16674,7 +16696,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>62</v>
       </c>
@@ -16694,7 +16716,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>62</v>
       </c>
@@ -16714,7 +16736,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>62</v>
       </c>
@@ -16734,7 +16756,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>62</v>
       </c>
@@ -16754,7 +16776,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>62</v>
       </c>
@@ -16774,7 +16796,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>62</v>
       </c>
@@ -16794,7 +16816,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>62</v>
       </c>
@@ -16814,7 +16836,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>62</v>
       </c>
@@ -16834,7 +16856,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>62</v>
       </c>
@@ -16854,7 +16876,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>62</v>
       </c>
@@ -16874,7 +16896,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>62</v>
       </c>
@@ -16894,7 +16916,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>62</v>
       </c>
@@ -16914,7 +16936,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>62</v>
       </c>
@@ -16934,7 +16956,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>62</v>
       </c>
@@ -16954,7 +16976,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>62</v>
       </c>
@@ -16974,7 +16996,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>62</v>
       </c>
@@ -16994,7 +17016,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>62</v>
       </c>
@@ -17014,7 +17036,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>62</v>
       </c>
@@ -17034,7 +17056,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>62</v>
       </c>
@@ -17054,7 +17076,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>62</v>
       </c>
@@ -17074,7 +17096,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>62</v>
       </c>
@@ -17094,7 +17116,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>62</v>
       </c>
@@ -17114,7 +17136,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>62</v>
       </c>
@@ -17134,7 +17156,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>62</v>
       </c>
@@ -17154,7 +17176,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>62</v>
       </c>
@@ -17174,7 +17196,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>62</v>
       </c>
@@ -17194,7 +17216,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>62</v>
       </c>
@@ -17214,7 +17236,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>62</v>
       </c>
@@ -17234,7 +17256,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>62</v>
       </c>
@@ -17254,7 +17276,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>62</v>
       </c>
@@ -17274,7 +17296,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>62</v>
       </c>
@@ -17294,7 +17316,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>62</v>
       </c>
@@ -17314,7 +17336,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>62</v>
       </c>
@@ -17334,7 +17356,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>62</v>
       </c>
@@ -17354,7 +17376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>62</v>
       </c>
@@ -17374,7 +17396,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>62</v>
       </c>
@@ -17394,7 +17416,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>62</v>
       </c>
@@ -17414,7 +17436,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>62</v>
       </c>
@@ -17434,7 +17456,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>62</v>
       </c>
@@ -17454,7 +17476,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>62</v>
       </c>
@@ -17474,7 +17496,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>62</v>
       </c>
@@ -17494,7 +17516,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>62</v>
       </c>
@@ -17514,7 +17536,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>62</v>
       </c>
@@ -17534,7 +17556,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>62</v>
       </c>
@@ -17554,7 +17576,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>62</v>
       </c>
@@ -17574,7 +17596,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>62</v>
       </c>
@@ -17597,7 +17619,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>62</v>
       </c>
@@ -17617,7 +17639,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>62</v>
       </c>
@@ -17637,7 +17659,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>62</v>
       </c>
@@ -17657,7 +17679,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>62</v>
       </c>
@@ -17677,7 +17699,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>62</v>
       </c>
@@ -17697,7 +17719,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>62</v>
       </c>
@@ -17717,7 +17739,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>62</v>
       </c>
@@ -17737,7 +17759,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>62</v>
       </c>
@@ -17757,7 +17779,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>62</v>
       </c>
@@ -17777,7 +17799,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>62</v>
       </c>
@@ -17797,7 +17819,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>62</v>
       </c>
@@ -17817,7 +17839,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>62</v>
       </c>
@@ -17837,7 +17859,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>62</v>
       </c>
@@ -17857,7 +17879,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>62</v>
       </c>
@@ -17877,7 +17899,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>62</v>
       </c>
@@ -17897,7 +17919,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>62</v>
       </c>
@@ -17917,7 +17939,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>62</v>
       </c>
@@ -17937,7 +17959,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>62</v>
       </c>
@@ -17957,7 +17979,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>62</v>
       </c>
@@ -17977,7 +17999,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>62</v>
       </c>
@@ -17997,7 +18019,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>62</v>
       </c>
@@ -18017,7 +18039,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>62</v>
       </c>
@@ -18037,7 +18059,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>62</v>
       </c>
@@ -18060,7 +18082,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>62</v>
       </c>
@@ -18080,7 +18102,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>62</v>
       </c>
@@ -18100,7 +18122,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>62</v>
       </c>
@@ -18120,7 +18142,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>62</v>
       </c>
@@ -18140,7 +18162,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>62</v>
       </c>
@@ -18160,7 +18182,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>62</v>
       </c>
@@ -18180,7 +18202,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>62</v>
       </c>
@@ -18200,7 +18222,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>62</v>
       </c>
@@ -18220,7 +18242,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>62</v>
       </c>
@@ -18240,7 +18262,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>62</v>
       </c>
@@ -18260,7 +18282,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>62</v>
       </c>
@@ -18280,7 +18302,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>62</v>
       </c>
@@ -18300,7 +18322,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>62</v>
       </c>
@@ -18320,7 +18342,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>62</v>
       </c>
@@ -18340,7 +18362,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>62</v>
       </c>
@@ -18360,7 +18382,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>62</v>
       </c>
@@ -18380,7 +18402,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>62</v>
       </c>
@@ -18400,7 +18422,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>62</v>
       </c>
@@ -18420,7 +18442,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>62</v>
       </c>
@@ -18440,7 +18462,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>62</v>
       </c>
@@ -18460,7 +18482,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>62</v>
       </c>
@@ -18480,7 +18502,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>62</v>
       </c>
@@ -18500,7 +18522,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>62</v>
       </c>
@@ -18520,7 +18542,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>62</v>
       </c>
@@ -18540,7 +18562,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>62</v>
       </c>
@@ -18560,7 +18582,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>62</v>
       </c>
@@ -18580,7 +18602,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>62</v>
       </c>
@@ -18600,7 +18622,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>62</v>
       </c>
@@ -18620,7 +18642,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>62</v>
       </c>
@@ -18640,7 +18662,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>62</v>
       </c>
@@ -18660,7 +18682,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>62</v>
       </c>
@@ -18680,7 +18702,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>62</v>
       </c>
@@ -18703,7 +18725,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>62</v>
       </c>
@@ -18723,7 +18745,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>62</v>
       </c>
@@ -18743,7 +18765,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>62</v>
       </c>
@@ -18763,7 +18785,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>63</v>
       </c>
@@ -18783,7 +18805,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>63</v>
       </c>
@@ -18803,7 +18825,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>63</v>
       </c>
@@ -18826,7 +18848,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>63</v>
       </c>
@@ -18846,7 +18868,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>63</v>
       </c>
@@ -18866,7 +18888,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
         <v>63</v>
       </c>
@@ -18886,7 +18908,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>63</v>
       </c>
@@ -18906,7 +18928,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>63</v>
       </c>
@@ -18926,7 +18948,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>63</v>
       </c>
@@ -18946,7 +18968,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
         <v>63</v>
       </c>
@@ -18966,7 +18988,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>63</v>
       </c>
@@ -18986,7 +19008,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>63</v>
       </c>
@@ -19006,7 +19028,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>63</v>
       </c>
@@ -19026,7 +19048,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>63</v>
       </c>
@@ -19046,7 +19068,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>63</v>
       </c>
@@ -19066,7 +19088,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>63</v>
       </c>
@@ -19086,7 +19108,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>64</v>
       </c>
@@ -19106,7 +19128,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>64</v>
       </c>
@@ -19126,7 +19148,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
         <v>64</v>
       </c>
@@ -19146,7 +19168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>64</v>
       </c>
@@ -19166,7 +19188,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>64</v>
       </c>
@@ -19186,7 +19208,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
         <v>64</v>
       </c>
@@ -19206,7 +19228,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>64</v>
       </c>
@@ -19226,7 +19248,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
         <v>64</v>
       </c>
@@ -19246,7 +19268,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>64</v>
       </c>
@@ -19269,7 +19291,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>64</v>
       </c>
@@ -19289,7 +19311,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>64</v>
       </c>
@@ -19309,7 +19331,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
         <v>64</v>
       </c>
@@ -19329,7 +19351,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>64</v>
       </c>
@@ -19349,7 +19371,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>64</v>
       </c>
@@ -19369,7 +19391,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>64</v>
       </c>
@@ -19389,7 +19411,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>64</v>
       </c>
@@ -19409,7 +19431,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
         <v>64</v>
       </c>
@@ -19429,7 +19451,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>64</v>
       </c>
@@ -19449,7 +19471,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>64</v>
       </c>
@@ -19472,7 +19494,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>64</v>
       </c>
@@ -19492,7 +19514,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>64</v>
       </c>
@@ -19512,7 +19534,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>64</v>
       </c>
@@ -19532,7 +19554,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>64</v>
       </c>
@@ -19552,7 +19574,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>64</v>
       </c>
@@ -19572,7 +19594,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>64</v>
       </c>
@@ -19592,7 +19614,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>64</v>
       </c>
@@ -19612,7 +19634,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>64</v>
       </c>
@@ -19632,7 +19654,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>64</v>
       </c>
@@ -19652,7 +19674,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
         <v>64</v>
       </c>
@@ -19672,7 +19694,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>64</v>
       </c>
@@ -19692,7 +19714,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>64</v>
       </c>
@@ -19712,7 +19734,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>64</v>
       </c>
@@ -19732,7 +19754,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>64</v>
       </c>
@@ -19752,7 +19774,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>64</v>
       </c>
@@ -19772,7 +19794,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
         <v>64</v>
       </c>
@@ -19792,7 +19814,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>64</v>
       </c>
@@ -19812,7 +19834,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>64</v>
       </c>
@@ -19832,7 +19854,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>64</v>
       </c>
@@ -19852,7 +19874,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>64</v>
       </c>
@@ -19872,7 +19894,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
         <v>64</v>
       </c>
@@ -19892,7 +19914,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>64</v>
       </c>
@@ -19912,7 +19934,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
         <v>64</v>
       </c>
@@ -19932,7 +19954,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>64</v>
       </c>
@@ -19952,7 +19974,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>64</v>
       </c>
@@ -19972,7 +19994,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>64</v>
       </c>
@@ -19992,7 +20014,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>64</v>
       </c>
@@ -20012,7 +20034,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>64</v>
       </c>
@@ -20032,7 +20054,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
         <v>64</v>
       </c>
@@ -20052,7 +20074,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
         <v>64</v>
       </c>
@@ -20072,7 +20094,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>64</v>
       </c>
@@ -20092,7 +20114,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
         <v>64</v>
       </c>
@@ -20112,7 +20134,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
         <v>64</v>
       </c>
@@ -20132,7 +20154,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
         <v>64</v>
       </c>
@@ -20152,7 +20174,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
         <v>64</v>
       </c>
@@ -20172,7 +20194,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
         <v>64</v>
       </c>
@@ -20192,7 +20214,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>64</v>
       </c>
@@ -20212,7 +20234,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
         <v>64</v>
       </c>
@@ -20232,7 +20254,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>64</v>
       </c>
@@ -20252,7 +20274,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>64</v>
       </c>
@@ -20272,7 +20294,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>64</v>
       </c>
@@ -20292,7 +20314,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
         <v>64</v>
       </c>
@@ -20312,7 +20334,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
         <v>64</v>
       </c>
@@ -20332,7 +20354,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>64</v>
       </c>
@@ -20352,7 +20374,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
         <v>64</v>
       </c>
@@ -20372,7 +20394,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>64</v>
       </c>
@@ -20392,7 +20414,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>64</v>
       </c>
@@ -20412,7 +20434,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>64</v>
       </c>
@@ -20432,7 +20454,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>64</v>
       </c>
@@ -20452,7 +20474,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>64</v>
       </c>
@@ -20472,7 +20494,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>64</v>
       </c>
@@ -20492,7 +20514,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>64</v>
       </c>
@@ -20512,7 +20534,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>64</v>
       </c>
@@ -20532,7 +20554,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>64</v>
       </c>
@@ -20552,7 +20574,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>64</v>
       </c>
@@ -20572,7 +20594,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
         <v>64</v>
       </c>
@@ -20592,7 +20614,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>64</v>
       </c>
@@ -20612,7 +20634,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>64</v>
       </c>
@@ -20632,7 +20654,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>64</v>
       </c>
@@ -20652,7 +20674,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
         <v>64</v>
       </c>
@@ -20672,7 +20694,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
         <v>64</v>
       </c>
@@ -20692,7 +20714,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>64</v>
       </c>
@@ -20712,7 +20734,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>64</v>
       </c>
@@ -20732,7 +20754,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>64</v>
       </c>
@@ -20752,7 +20774,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>64</v>
       </c>
@@ -20772,7 +20794,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>64</v>
       </c>
@@ -20792,7 +20814,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>64</v>
       </c>
@@ -20812,7 +20834,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>64</v>
       </c>
@@ -20832,7 +20854,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>64</v>
       </c>
@@ -20852,7 +20874,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
         <v>64</v>
       </c>
@@ -20872,7 +20894,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>64</v>
       </c>
@@ -20892,7 +20914,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>64</v>
       </c>
@@ -20912,7 +20934,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
         <v>64</v>
       </c>
@@ -20932,7 +20954,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
         <v>64</v>
       </c>
@@ -20952,7 +20974,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>64</v>
       </c>
@@ -20972,7 +20994,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>64</v>
       </c>
@@ -20992,7 +21014,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>64</v>
       </c>
@@ -21012,7 +21034,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>64</v>
       </c>
@@ -21032,7 +21054,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>64</v>
       </c>
@@ -21052,7 +21074,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>64</v>
       </c>
@@ -21072,7 +21094,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
         <v>64</v>
       </c>
@@ -21092,7 +21114,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>64</v>
       </c>
@@ -21112,7 +21134,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>64</v>
       </c>
@@ -21132,7 +21154,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>64</v>
       </c>
@@ -21152,7 +21174,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>64</v>
       </c>
@@ -21172,7 +21194,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>64</v>
       </c>
@@ -21192,7 +21214,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
         <v>64</v>
       </c>
@@ -21212,7 +21234,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>64</v>
       </c>
@@ -21232,7 +21254,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>64</v>
       </c>
@@ -21252,7 +21274,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>64</v>
       </c>
@@ -21272,7 +21294,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>64</v>
       </c>
@@ -21292,7 +21314,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
         <v>64</v>
       </c>
@@ -21312,7 +21334,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>64</v>
       </c>
@@ -21332,7 +21354,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>64</v>
       </c>
@@ -21352,7 +21374,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>64</v>
       </c>
@@ -21372,7 +21394,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>64</v>
       </c>
@@ -21392,7 +21414,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
         <v>64</v>
       </c>
@@ -21412,7 +21434,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>64</v>
       </c>
@@ -21432,7 +21454,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>64</v>
       </c>
@@ -21452,7 +21474,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>64</v>
       </c>
@@ -21472,7 +21494,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>64</v>
       </c>
@@ -21492,7 +21514,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>64</v>
       </c>
@@ -21512,7 +21534,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>64</v>
       </c>
@@ -21532,7 +21554,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>64</v>
       </c>
@@ -21552,7 +21574,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>64</v>
       </c>
@@ -21572,7 +21594,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
         <v>64</v>
       </c>
@@ -21592,7 +21614,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>64</v>
       </c>
@@ -21612,7 +21634,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>64</v>
       </c>
@@ -21632,7 +21654,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>64</v>
       </c>
@@ -21652,7 +21674,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
         <v>64</v>
       </c>
@@ -21672,7 +21694,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
         <v>64</v>
       </c>
@@ -21692,7 +21714,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>64</v>
       </c>
@@ -21712,7 +21734,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>64</v>
       </c>
@@ -21732,7 +21754,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>64</v>
       </c>
@@ -21752,7 +21774,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
         <v>64</v>
       </c>
@@ -21772,7 +21794,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>64</v>
       </c>
@@ -21792,7 +21814,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>64</v>
       </c>
@@ -21812,7 +21834,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>64</v>
       </c>
@@ -21832,7 +21854,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>64</v>
       </c>
@@ -21852,7 +21874,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>64</v>
       </c>
@@ -21872,7 +21894,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>64</v>
       </c>
@@ -21892,7 +21914,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>64</v>
       </c>
@@ -21912,7 +21934,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>64</v>
       </c>
@@ -21932,7 +21954,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>64</v>
       </c>
@@ -21952,7 +21974,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>64</v>
       </c>
@@ -21972,7 +21994,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>64</v>
       </c>
@@ -21992,7 +22014,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
         <v>64</v>
       </c>
@@ -22012,7 +22034,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>64</v>
       </c>
@@ -22032,7 +22054,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>64</v>
       </c>
@@ -22052,7 +22074,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>64</v>
       </c>
@@ -22072,7 +22094,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>64</v>
       </c>
@@ -22092,7 +22114,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>64</v>
       </c>
@@ -22112,7 +22134,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>64</v>
       </c>
@@ -22135,7 +22157,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>64</v>
       </c>
@@ -22155,7 +22177,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
         <v>64</v>
       </c>
@@ -22175,7 +22197,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
         <v>64</v>
       </c>
@@ -22198,7 +22220,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A869" t="s">
         <v>64</v>
       </c>
@@ -22218,7 +22240,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
         <v>64</v>
       </c>
@@ -22238,7 +22260,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
         <v>64</v>
       </c>
@@ -22258,7 +22280,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
         <v>64</v>
       </c>
@@ -22278,7 +22300,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
         <v>64</v>
       </c>
@@ -22298,7 +22320,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
         <v>64</v>
       </c>
@@ -22318,7 +22340,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A875" t="s">
         <v>64</v>
       </c>
@@ -22338,7 +22360,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
         <v>65</v>
       </c>
@@ -22358,7 +22380,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
         <v>65</v>
       </c>
@@ -22381,7 +22403,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
         <v>65</v>
       </c>
@@ -22401,7 +22423,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A879" t="s">
         <v>65</v>
       </c>
@@ -22424,7 +22446,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
         <v>65</v>
       </c>
@@ -22444,7 +22466,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
         <v>65</v>
       </c>
@@ -22464,7 +22486,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
         <v>65</v>
       </c>
@@ -22484,7 +22506,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A883" t="s">
         <v>65</v>
       </c>
@@ -22504,7 +22526,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
         <v>66</v>
       </c>
@@ -22524,7 +22546,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
         <v>66</v>
       </c>
@@ -22544,7 +22566,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
         <v>67</v>
       </c>
@@ -22567,7 +22589,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A887" t="s">
         <v>67</v>
       </c>
@@ -22587,7 +22609,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
         <v>67</v>
       </c>
@@ -22607,7 +22629,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>67</v>
       </c>
@@ -22630,7 +22652,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
         <v>67</v>
       </c>
@@ -22653,7 +22675,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A891" t="s">
         <v>67</v>
       </c>
@@ -22676,7 +22698,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A892" t="s">
         <v>67</v>
       </c>
@@ -22696,7 +22718,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
         <v>67</v>
       </c>
@@ -22716,7 +22738,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
         <v>67</v>
       </c>
@@ -22736,7 +22758,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A895" t="s">
         <v>67</v>
       </c>
@@ -22759,7 +22781,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A896" t="s">
         <v>67</v>
       </c>
@@ -22779,7 +22801,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="897" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A897" t="s">
         <v>67</v>
       </c>
@@ -22799,7 +22821,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A898" t="s">
         <v>67</v>
       </c>
@@ -22822,7 +22844,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A899" t="s">
         <v>67</v>
       </c>
@@ -22845,7 +22867,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A900" t="s">
         <v>67</v>
       </c>
@@ -22865,7 +22887,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A901" t="s">
         <v>67</v>
       </c>
@@ -22885,7 +22907,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A902" t="s">
         <v>67</v>
       </c>
@@ -22908,7 +22930,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A903" t="s">
         <v>67</v>
       </c>
@@ -22928,7 +22950,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A904" t="s">
         <v>67</v>
       </c>
@@ -22948,7 +22970,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A905" t="s">
         <v>67</v>
       </c>
@@ -22968,7 +22990,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A906" t="s">
         <v>67</v>
       </c>
@@ -22991,7 +23013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A907" t="s">
         <v>67</v>
       </c>
@@ -23014,7 +23036,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A908" t="s">
         <v>67</v>
       </c>
@@ -23034,7 +23056,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A909" t="s">
         <v>67</v>
       </c>
@@ -23054,7 +23076,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A910" t="s">
         <v>67</v>
       </c>
@@ -23077,7 +23099,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="911" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A911" t="s">
         <v>67</v>
       </c>
@@ -23100,7 +23122,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="912" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A912" t="s">
         <v>67</v>
       </c>
@@ -23123,7 +23145,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="913" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A913" t="s">
         <v>67</v>
       </c>
@@ -23143,7 +23165,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="914" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A914" t="s">
         <v>67</v>
       </c>
@@ -23163,7 +23185,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="915" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A915" t="s">
         <v>68</v>
       </c>
@@ -23183,7 +23205,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="916" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A916" t="s">
         <v>68</v>
       </c>
@@ -23206,7 +23228,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="917" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A917" t="s">
         <v>68</v>
       </c>
@@ -23226,7 +23248,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="918" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A918" t="s">
         <v>68</v>
       </c>
@@ -23246,7 +23268,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="919" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A919" t="s">
         <v>68</v>
       </c>
@@ -23266,7 +23288,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="920" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A920" t="s">
         <v>68</v>
       </c>
@@ -23289,7 +23311,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="921" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A921" t="s">
         <v>68</v>
       </c>
@@ -23312,7 +23334,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="922" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A922" t="s">
         <v>68</v>
       </c>
@@ -23332,7 +23354,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="923" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A923" t="s">
         <v>68</v>
       </c>
@@ -23355,7 +23377,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="924" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A924" t="s">
         <v>68</v>
       </c>
@@ -23378,7 +23400,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="925" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A925" t="s">
         <v>68</v>
       </c>
@@ -23401,7 +23423,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="926" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A926" t="s">
         <v>68</v>
       </c>
@@ -23421,7 +23443,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="927" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A927" t="s">
         <v>68</v>
       </c>
@@ -23441,7 +23463,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="928" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A928" t="s">
         <v>68</v>
       </c>
@@ -23461,7 +23483,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="929" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A929" t="s">
         <v>68</v>
       </c>
@@ -23484,7 +23506,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="930" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A930" t="s">
         <v>68</v>
       </c>
@@ -23504,7 +23526,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="931" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A931" t="s">
         <v>68</v>
       </c>
@@ -23524,7 +23546,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="932" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A932" t="s">
         <v>68</v>
       </c>
@@ -23544,7 +23566,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="933" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A933" t="s">
         <v>68</v>
       </c>
@@ -23567,7 +23589,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="934" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A934" t="s">
         <v>68</v>
       </c>
@@ -23587,7 +23609,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="935" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A935" t="s">
         <v>68</v>
       </c>
@@ -23607,7 +23629,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="936" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A936" t="s">
         <v>68</v>
       </c>
@@ -23630,7 +23652,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="937" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A937" t="s">
         <v>68</v>
       </c>
@@ -23653,7 +23675,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="938" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A938" t="s">
         <v>68</v>
       </c>
@@ -23676,7 +23698,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="939" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A939" t="s">
         <v>68</v>
       </c>
@@ -23699,7 +23721,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="940" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A940" t="s">
         <v>68</v>
       </c>
@@ -23719,7 +23741,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="941" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A941" t="s">
         <v>68</v>
       </c>
@@ -23742,7 +23764,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="942" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A942" t="s">
         <v>68</v>
       </c>
@@ -23762,7 +23784,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="943" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A943" t="s">
         <v>68</v>
       </c>
@@ -23782,7 +23804,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="944" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A944" t="s">
         <v>68</v>
       </c>
@@ -23802,7 +23824,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="945" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A945" t="s">
         <v>69</v>
       </c>
@@ -23822,7 +23844,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="946" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A946" t="s">
         <v>69</v>
       </c>
@@ -23845,7 +23867,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="947" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A947" t="s">
         <v>69</v>
       </c>
@@ -23865,7 +23887,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="948" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A948" t="s">
         <v>69</v>
       </c>
@@ -23885,7 +23907,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="949" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A949" t="s">
         <v>69</v>
       </c>
@@ -23905,7 +23927,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="950" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A950" t="s">
         <v>69</v>
       </c>
@@ -23928,7 +23950,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="951" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A951" t="s">
         <v>69</v>
       </c>
@@ -23948,7 +23970,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="952" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A952" t="s">
         <v>69</v>
       </c>
@@ -23968,7 +23990,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="953" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A953" t="s">
         <v>70</v>
       </c>
@@ -23988,7 +24010,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="954" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A954" t="s">
         <v>70</v>
       </c>
@@ -24011,7 +24033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="955" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A955" t="s">
         <v>70</v>
       </c>
@@ -24034,7 +24056,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="956" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A956" t="s">
         <v>70</v>
       </c>
@@ -24054,7 +24076,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="957" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A957" t="s">
         <v>70</v>
       </c>
@@ -24077,7 +24099,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="958" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A958" t="s">
         <v>70</v>
       </c>
@@ -24097,7 +24119,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="959" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A959" t="s">
         <v>70</v>
       </c>
@@ -24117,7 +24139,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="960" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A960" t="s">
         <v>70</v>
       </c>
@@ -24140,7 +24162,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="961" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A961" t="s">
         <v>70</v>
       </c>
@@ -24160,7 +24182,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="962" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A962" t="s">
         <v>70</v>
       </c>
@@ -24180,7 +24202,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="963" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A963" t="s">
         <v>70</v>
       </c>
@@ -24203,7 +24225,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="964" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A964" t="s">
         <v>70</v>
       </c>
@@ -24223,7 +24245,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="965" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A965" t="s">
         <v>70</v>
       </c>
@@ -24246,7 +24268,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="966" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A966" t="s">
         <v>70</v>
       </c>
@@ -24269,7 +24291,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="967" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A967" t="s">
         <v>70</v>
       </c>
@@ -24292,7 +24314,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="968" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A968" t="s">
         <v>70</v>
       </c>
@@ -24312,7 +24334,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="969" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
         <v>70</v>
       </c>
@@ -24332,7 +24354,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="970" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A970" t="s">
         <v>70</v>
       </c>
@@ -24352,7 +24374,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="971" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A971" t="s">
         <v>70</v>
       </c>
@@ -24375,7 +24397,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A972" t="s">
         <v>70</v>
       </c>
@@ -24395,7 +24417,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="973" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A973" t="s">
         <v>70</v>
       </c>
@@ -24418,7 +24440,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A974" t="s">
         <v>70</v>
       </c>
@@ -24438,7 +24460,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="975" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A975" t="s">
         <v>70</v>
       </c>
@@ -24461,7 +24483,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A976" t="s">
         <v>70</v>
       </c>
@@ -24481,7 +24503,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="977" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A977" t="s">
         <v>70</v>
       </c>
@@ -24501,7 +24523,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A978" t="s">
         <v>70</v>
       </c>
@@ -24521,7 +24543,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A979" t="s">
         <v>70</v>
       </c>
@@ -24544,7 +24566,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A980" t="s">
         <v>71</v>
       </c>
@@ -24564,7 +24586,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="981" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A981" t="s">
         <v>71</v>
       </c>
@@ -24584,7 +24606,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="982" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A982" t="s">
         <v>71</v>
       </c>
@@ -24604,7 +24626,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="983" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A983" t="s">
         <v>71</v>
       </c>
@@ -24624,7 +24646,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="984" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A984" t="s">
         <v>71</v>
       </c>
@@ -24647,7 +24669,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="985" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A985" t="s">
         <v>71</v>
       </c>
@@ -24667,7 +24689,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="986" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A986" t="s">
         <v>71</v>
       </c>
@@ -24687,7 +24709,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="987" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A987" t="s">
         <v>71</v>
       </c>
@@ -24707,7 +24729,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="988" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A988" t="s">
         <v>71</v>
       </c>
@@ -24727,7 +24749,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="989" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A989" t="s">
         <v>71</v>
       </c>
@@ -24747,7 +24769,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="990" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
         <v>72</v>
       </c>
@@ -24767,7 +24789,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
         <v>72</v>
       </c>
@@ -24790,7 +24812,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="992" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
         <v>72</v>
       </c>
@@ -24810,7 +24832,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="993" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
         <v>72</v>
       </c>
@@ -24833,7 +24855,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="994" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A994" t="s">
         <v>72</v>
       </c>
@@ -24856,7 +24878,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="995" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
         <v>72</v>
       </c>
@@ -24876,7 +24898,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="996" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
         <v>72</v>
       </c>
@@ -24896,7 +24918,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="997" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
         <v>72</v>
       </c>
@@ -24916,7 +24938,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="998" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
         <v>72</v>
       </c>
@@ -24936,7 +24958,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="999" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A999" t="s">
         <v>72</v>
       </c>
@@ -24956,7 +24978,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1000" t="s">
         <v>73</v>
       </c>
@@ -24976,7 +24998,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1001" t="s">
         <v>73</v>
       </c>
@@ -24996,7 +25018,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1002" t="s">
         <v>74</v>
       </c>
@@ -25016,7 +25038,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1003" t="s">
         <v>74</v>
       </c>
@@ -25036,7 +25058,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1004" t="s">
         <v>74</v>
       </c>
@@ -25056,7 +25078,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1005" t="s">
         <v>75</v>
       </c>
@@ -25076,7 +25098,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1006" t="s">
         <v>75</v>
       </c>
@@ -25096,7 +25118,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1007" t="s">
         <v>75</v>
       </c>
@@ -25116,7 +25138,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1008" t="s">
         <v>75</v>
       </c>
@@ -25136,7 +25158,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1009" t="s">
         <v>75</v>
       </c>
@@ -25157,7 +25179,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1009" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:J1009" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6128C858-0376-FD47-99E3-379F9FAAE810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B194E42-7442-4446-B05A-2117B636F19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="1820" windowWidth="32060" windowHeight="16700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4445,7 +4445,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J1009"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4493,7 +4492,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4513,7 +4512,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4533,7 +4532,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4553,7 +4552,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4573,7 +4572,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4593,7 +4592,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4633,7 +4632,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -4656,7 +4655,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -4679,7 +4678,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -4699,7 +4698,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -4722,7 +4721,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4742,7 +4741,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -4762,7 +4761,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -4782,7 +4781,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -4805,7 +4804,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -4828,7 +4827,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -4851,7 +4850,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -4871,7 +4870,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -4894,7 +4893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -4914,7 +4913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -4937,7 +4936,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -4960,7 +4959,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -4980,7 +4979,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -5003,7 +5002,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -5023,7 +5022,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -5046,7 +5045,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -5069,7 +5068,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -5115,7 +5114,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -5138,7 +5137,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -5161,7 +5160,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -5204,7 +5203,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -5227,7 +5226,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -5250,7 +5249,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -5270,7 +5269,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -5290,7 +5289,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -5310,7 +5309,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -5330,7 +5329,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -5353,7 +5352,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -5376,7 +5375,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -5419,7 +5418,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -5442,7 +5441,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -5465,7 +5464,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -5485,7 +5484,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -5505,7 +5504,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -5528,7 +5527,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -5548,7 +5547,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -5571,7 +5570,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -5591,7 +5590,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -5611,7 +5610,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -5631,7 +5630,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -5657,7 +5656,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -5677,7 +5676,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -5720,7 +5719,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -5740,7 +5739,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -5760,7 +5759,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -5780,7 +5779,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -5803,7 +5802,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -5823,7 +5822,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -5843,7 +5842,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -5863,7 +5862,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -5883,7 +5882,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -5903,7 +5902,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -5923,7 +5922,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -5943,7 +5942,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -5963,7 +5962,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -5983,7 +5982,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -6003,7 +6002,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -6029,7 +6028,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -6049,7 +6048,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -6072,7 +6071,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -6092,7 +6091,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -6115,7 +6114,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -6135,7 +6134,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -6158,7 +6157,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -6181,7 +6180,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -6201,7 +6200,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -6221,7 +6220,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -6241,7 +6240,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>7</v>
       </c>
@@ -6261,7 +6260,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -6281,7 +6280,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>7</v>
       </c>
@@ -6301,7 +6300,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -6321,7 +6320,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -6341,7 +6340,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -6361,7 +6360,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -6381,7 +6380,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -6401,7 +6400,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -6424,7 +6423,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -6444,7 +6443,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -6464,7 +6463,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -6487,7 +6486,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -6507,7 +6506,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -6527,7 +6526,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -6547,7 +6546,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -6567,7 +6566,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -6587,7 +6586,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -6610,7 +6609,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -6630,7 +6629,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -6650,7 +6649,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>7</v>
       </c>
@@ -6670,7 +6669,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>7</v>
       </c>
@@ -6693,7 +6692,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -6713,7 +6712,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -6733,7 +6732,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -6759,7 +6758,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -6779,7 +6778,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -6802,7 +6801,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -6822,7 +6821,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -6842,7 +6841,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -6865,7 +6864,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -6888,7 +6887,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -6908,7 +6907,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -6928,7 +6927,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -6948,7 +6947,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>8</v>
       </c>
@@ -6988,7 +6987,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -7008,7 +7007,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -7028,7 +7027,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -7068,7 +7067,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -7088,7 +7087,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -7108,7 +7107,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -7128,7 +7127,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -7148,7 +7147,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>9</v>
       </c>
@@ -7168,7 +7167,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -7188,7 +7187,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -7208,7 +7207,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -7228,7 +7227,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -7271,7 +7270,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -7297,7 +7296,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -7317,7 +7316,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -7337,7 +7336,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -7357,7 +7356,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -7377,7 +7376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -7420,7 +7419,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -7440,7 +7439,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -7457,7 +7456,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -7477,7 +7476,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -7497,7 +7496,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -7517,7 +7516,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -7537,7 +7536,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -7560,7 +7559,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -7577,7 +7576,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -7597,7 +7596,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -7617,7 +7616,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -7637,7 +7636,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -7654,7 +7653,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>10</v>
       </c>
@@ -7674,7 +7673,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -7697,7 +7696,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>10</v>
       </c>
@@ -7717,7 +7716,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -7734,7 +7733,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -7754,7 +7753,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -7774,7 +7773,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -7791,7 +7790,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -7811,7 +7810,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>10</v>
       </c>
@@ -7831,7 +7830,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>10</v>
       </c>
@@ -7851,7 +7850,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>10</v>
       </c>
@@ -7871,7 +7870,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>10</v>
       </c>
@@ -7891,7 +7890,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>10</v>
       </c>
@@ -7911,7 +7910,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -7931,7 +7930,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>10</v>
       </c>
@@ -7951,7 +7950,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -7971,7 +7970,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>10</v>
       </c>
@@ -7991,7 +7990,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -8011,7 +8010,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -8028,7 +8027,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>10</v>
       </c>
@@ -8054,7 +8053,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>10</v>
       </c>
@@ -8074,7 +8073,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -8094,7 +8093,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>10</v>
       </c>
@@ -8114,7 +8113,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>10</v>
       </c>
@@ -8134,7 +8133,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>10</v>
       </c>
@@ -8157,7 +8156,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -8177,7 +8176,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -8197,7 +8196,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>11</v>
       </c>
@@ -8217,7 +8216,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -8237,7 +8236,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -8260,7 +8259,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -8283,7 +8282,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -8303,7 +8302,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -8326,7 +8325,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -8346,7 +8345,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -8366,7 +8365,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -8389,7 +8388,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -8409,7 +8408,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -8429,7 +8428,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -8452,7 +8451,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -8472,7 +8471,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -8495,7 +8494,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -8518,7 +8517,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>13</v>
       </c>
@@ -8541,7 +8540,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -8564,7 +8563,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -8587,7 +8586,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>13</v>
       </c>
@@ -8610,7 +8609,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -8633,7 +8632,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -8656,7 +8655,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>13</v>
       </c>
@@ -8679,7 +8678,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -8702,7 +8701,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -8725,7 +8724,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -8748,7 +8747,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -8771,7 +8770,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -8794,7 +8793,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -8814,7 +8813,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -8837,7 +8836,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -8860,7 +8859,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -8883,7 +8882,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>14</v>
       </c>
@@ -8903,7 +8902,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>14</v>
       </c>
@@ -8923,7 +8922,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>15</v>
       </c>
@@ -8943,7 +8942,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>15</v>
       </c>
@@ -8963,7 +8962,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>15</v>
       </c>
@@ -8983,7 +8982,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>15</v>
       </c>
@@ -9003,7 +9002,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -9023,7 +9022,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>15</v>
       </c>
@@ -9043,7 +9042,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -9069,7 +9068,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -9089,7 +9088,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -9109,7 +9108,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -9129,7 +9128,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -9149,7 +9148,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -9169,7 +9168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -9189,7 +9188,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -9209,7 +9208,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -9229,7 +9228,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -9249,7 +9248,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -9269,7 +9268,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -9289,7 +9288,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -9312,7 +9311,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>17</v>
       </c>
@@ -9332,7 +9331,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>17</v>
       </c>
@@ -9358,7 +9357,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -9378,7 +9377,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -9398,7 +9397,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>19</v>
       </c>
@@ -9418,7 +9417,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>19</v>
       </c>
@@ -9438,7 +9437,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -9458,7 +9457,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>19</v>
       </c>
@@ -9478,7 +9477,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -9498,7 +9497,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>19</v>
       </c>
@@ -9518,7 +9517,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>19</v>
       </c>
@@ -9538,7 +9537,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>19</v>
       </c>
@@ -9558,7 +9557,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>19</v>
       </c>
@@ -9578,7 +9577,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>19</v>
       </c>
@@ -9601,7 +9600,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>19</v>
       </c>
@@ -9621,7 +9620,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>19</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>19</v>
       </c>
@@ -9661,7 +9660,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>19</v>
       </c>
@@ -9681,7 +9680,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>19</v>
       </c>
@@ -9701,7 +9700,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>19</v>
       </c>
@@ -9724,7 +9723,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>19</v>
       </c>
@@ -9744,7 +9743,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>19</v>
       </c>
@@ -9764,7 +9763,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>19</v>
       </c>
@@ -9784,7 +9783,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>19</v>
       </c>
@@ -9807,7 +9806,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>19</v>
       </c>
@@ -9827,7 +9826,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>19</v>
       </c>
@@ -9847,7 +9846,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -9867,7 +9866,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>19</v>
       </c>
@@ -9887,7 +9886,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>19</v>
       </c>
@@ -9907,7 +9906,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>19</v>
       </c>
@@ -9927,7 +9926,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>19</v>
       </c>
@@ -9947,7 +9946,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>19</v>
       </c>
@@ -9967,7 +9966,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>19</v>
       </c>
@@ -9987,7 +9986,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>19</v>
       </c>
@@ -10010,7 +10009,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>19</v>
       </c>
@@ -10030,7 +10029,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -10050,7 +10049,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>20</v>
       </c>
@@ -10070,7 +10069,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>20</v>
       </c>
@@ -10090,7 +10089,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>20</v>
       </c>
@@ -10110,7 +10109,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>21</v>
       </c>
@@ -10130,7 +10129,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>22</v>
       </c>
@@ -10150,7 +10149,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>22</v>
       </c>
@@ -10170,7 +10169,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>22</v>
       </c>
@@ -10190,7 +10189,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>22</v>
       </c>
@@ -10210,7 +10209,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>23</v>
       </c>
@@ -10230,7 +10229,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -10250,7 +10249,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>23</v>
       </c>
@@ -10270,7 +10269,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>24</v>
       </c>
@@ -10290,7 +10289,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>25</v>
       </c>
@@ -10310,7 +10309,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>25</v>
       </c>
@@ -10330,7 +10329,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>25</v>
       </c>
@@ -10350,7 +10349,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>25</v>
       </c>
@@ -10376,7 +10375,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>26</v>
       </c>
@@ -10396,7 +10395,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>26</v>
       </c>
@@ -10416,7 +10415,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>26</v>
       </c>
@@ -10436,7 +10435,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>26</v>
       </c>
@@ -10456,7 +10455,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>26</v>
       </c>
@@ -10482,7 +10481,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>27</v>
       </c>
@@ -10502,7 +10501,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>28</v>
       </c>
@@ -10522,7 +10521,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>29</v>
       </c>
@@ -10545,7 +10544,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>29</v>
       </c>
@@ -10565,7 +10564,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>29</v>
       </c>
@@ -10585,7 +10584,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>30</v>
       </c>
@@ -10608,7 +10607,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>30</v>
       </c>
@@ -10628,7 +10627,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>30</v>
       </c>
@@ -10648,7 +10647,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>31</v>
       </c>
@@ -10668,7 +10667,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>31</v>
       </c>
@@ -10688,7 +10687,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>32</v>
       </c>
@@ -10708,7 +10707,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>32</v>
       </c>
@@ -10728,7 +10727,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>32</v>
       </c>
@@ -10748,7 +10747,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>33</v>
       </c>
@@ -10768,7 +10767,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>34</v>
       </c>
@@ -10791,7 +10790,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>34</v>
       </c>
@@ -10811,7 +10810,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>34</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>34</v>
       </c>
@@ -10854,7 +10853,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>34</v>
       </c>
@@ -10874,7 +10873,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>34</v>
       </c>
@@ -10894,7 +10893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>34</v>
       </c>
@@ -10914,7 +10913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>34</v>
       </c>
@@ -10934,7 +10933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>34</v>
       </c>
@@ -10954,7 +10953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>34</v>
       </c>
@@ -10974,7 +10973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>34</v>
       </c>
@@ -10994,7 +10993,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>34</v>
       </c>
@@ -11014,7 +11013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>34</v>
       </c>
@@ -11034,7 +11033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>34</v>
       </c>
@@ -11057,7 +11056,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>34</v>
       </c>
@@ -11077,7 +11076,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>34</v>
       </c>
@@ -11097,7 +11096,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>35</v>
       </c>
@@ -11117,7 +11116,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>35</v>
       </c>
@@ -11137,7 +11136,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>35</v>
       </c>
@@ -11157,7 +11156,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>36</v>
       </c>
@@ -11177,7 +11176,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>36</v>
       </c>
@@ -11197,7 +11196,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>37</v>
       </c>
@@ -11217,7 +11216,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>38</v>
       </c>
@@ -11237,7 +11236,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>38</v>
       </c>
@@ -11257,7 +11256,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>38</v>
       </c>
@@ -11277,7 +11276,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>38</v>
       </c>
@@ -11297,7 +11296,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>39</v>
       </c>
@@ -11317,7 +11316,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>39</v>
       </c>
@@ -11337,7 +11336,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>39</v>
       </c>
@@ -11357,7 +11356,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>39</v>
       </c>
@@ -11377,7 +11376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>39</v>
       </c>
@@ -11397,7 +11396,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>39</v>
       </c>
@@ -11417,7 +11416,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>39</v>
       </c>
@@ -11437,7 +11436,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>39</v>
       </c>
@@ -11457,7 +11456,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>39</v>
       </c>
@@ -11477,7 +11476,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>39</v>
       </c>
@@ -11497,7 +11496,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -11517,7 +11516,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -11537,7 +11536,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>40</v>
       </c>
@@ -11557,7 +11556,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>41</v>
       </c>
@@ -11580,7 +11579,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -11600,7 +11599,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>41</v>
       </c>
@@ -11620,7 +11619,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>41</v>
       </c>
@@ -11643,7 +11642,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>41</v>
       </c>
@@ -11663,7 +11662,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>42</v>
       </c>
@@ -11686,7 +11685,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>42</v>
       </c>
@@ -11706,7 +11705,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>42</v>
       </c>
@@ -11729,7 +11728,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>42</v>
       </c>
@@ -11752,7 +11751,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>42</v>
       </c>
@@ -11772,7 +11771,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>42</v>
       </c>
@@ -11795,7 +11794,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>43</v>
       </c>
@@ -11815,7 +11814,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>43</v>
       </c>
@@ -11835,7 +11834,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>43</v>
       </c>
@@ -11855,7 +11854,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>43</v>
       </c>
@@ -11878,7 +11877,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>43</v>
       </c>
@@ -11898,7 +11897,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>44</v>
       </c>
@@ -11918,7 +11917,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>44</v>
       </c>
@@ -11938,7 +11937,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>44</v>
       </c>
@@ -11961,7 +11960,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>44</v>
       </c>
@@ -11981,7 +11980,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>45</v>
       </c>
@@ -12001,7 +12000,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>46</v>
       </c>
@@ -12021,7 +12020,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>46</v>
       </c>
@@ -12041,7 +12040,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>46</v>
       </c>
@@ -12061,7 +12060,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>46</v>
       </c>
@@ -12081,7 +12080,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>46</v>
       </c>
@@ -12101,7 +12100,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>46</v>
       </c>
@@ -12121,7 +12120,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>46</v>
       </c>
@@ -12141,7 +12140,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>46</v>
       </c>
@@ -12161,7 +12160,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>46</v>
       </c>
@@ -12181,7 +12180,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>46</v>
       </c>
@@ -12201,7 +12200,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>46</v>
       </c>
@@ -12221,7 +12220,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>46</v>
       </c>
@@ -12241,7 +12240,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>46</v>
       </c>
@@ -12261,7 +12260,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>46</v>
       </c>
@@ -12281,7 +12280,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>46</v>
       </c>
@@ -12301,7 +12300,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>46</v>
       </c>
@@ -12321,7 +12320,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>46</v>
       </c>
@@ -12341,7 +12340,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>46</v>
       </c>
@@ -12361,7 +12360,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>46</v>
       </c>
@@ -12381,7 +12380,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>46</v>
       </c>
@@ -12401,7 +12400,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>46</v>
       </c>
@@ -12421,7 +12420,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>46</v>
       </c>
@@ -12441,7 +12440,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>47</v>
       </c>
@@ -12461,7 +12460,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>47</v>
       </c>
@@ -12481,7 +12480,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>47</v>
       </c>
@@ -12501,7 +12500,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>47</v>
       </c>
@@ -12521,7 +12520,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>47</v>
       </c>
@@ -12541,7 +12540,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>47</v>
       </c>
@@ -12561,7 +12560,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>47</v>
       </c>
@@ -12581,7 +12580,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>47</v>
       </c>
@@ -12601,7 +12600,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>48</v>
       </c>
@@ -12627,7 +12626,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>48</v>
       </c>
@@ -12647,7 +12646,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>48</v>
       </c>
@@ -12670,7 +12669,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>48</v>
       </c>
@@ -12690,7 +12689,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>48</v>
       </c>
@@ -12710,7 +12709,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>49</v>
       </c>
@@ -12730,7 +12729,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>49</v>
       </c>
@@ -12750,7 +12749,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>49</v>
       </c>
@@ -12770,7 +12769,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>49</v>
       </c>
@@ -12790,7 +12789,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>49</v>
       </c>
@@ -12810,7 +12809,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>49</v>
       </c>
@@ -12833,7 +12832,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>49</v>
       </c>
@@ -12853,7 +12852,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>49</v>
       </c>
@@ -12873,7 +12872,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>49</v>
       </c>
@@ -12893,7 +12892,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>49</v>
       </c>
@@ -12913,7 +12912,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>49</v>
       </c>
@@ -12933,7 +12932,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>49</v>
       </c>
@@ -12953,7 +12952,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>49</v>
       </c>
@@ -12973,7 +12972,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>49</v>
       </c>
@@ -12993,7 +12992,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>49</v>
       </c>
@@ -13013,7 +13012,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>49</v>
       </c>
@@ -13033,7 +13032,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>49</v>
       </c>
@@ -13053,7 +13052,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>49</v>
       </c>
@@ -13073,7 +13072,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>49</v>
       </c>
@@ -13093,7 +13092,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>49</v>
       </c>
@@ -13113,7 +13112,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>49</v>
       </c>
@@ -13133,7 +13132,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>49</v>
       </c>
@@ -13153,7 +13152,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>49</v>
       </c>
@@ -13173,7 +13172,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>49</v>
       </c>
@@ -13196,7 +13195,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>49</v>
       </c>
@@ -13216,7 +13215,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>49</v>
       </c>
@@ -13236,7 +13235,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>49</v>
       </c>
@@ -13256,7 +13255,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>49</v>
       </c>
@@ -13276,7 +13275,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>49</v>
       </c>
@@ -13296,7 +13295,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>50</v>
       </c>
@@ -13316,7 +13315,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>50</v>
       </c>
@@ -13336,7 +13335,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>50</v>
       </c>
@@ -13356,7 +13355,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>50</v>
       </c>
@@ -13376,7 +13375,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>50</v>
       </c>
@@ -13396,7 +13395,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>50</v>
       </c>
@@ -13416,7 +13415,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>51</v>
       </c>
@@ -13436,7 +13435,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>52</v>
       </c>
@@ -13456,7 +13455,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>52</v>
       </c>
@@ -13476,7 +13475,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>52</v>
       </c>
@@ -13499,7 +13498,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>52</v>
       </c>
@@ -13519,7 +13518,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>52</v>
       </c>
@@ -13539,7 +13538,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>52</v>
       </c>
@@ -13559,7 +13558,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>52</v>
       </c>
@@ -13579,7 +13578,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>52</v>
       </c>
@@ -13599,7 +13598,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>52</v>
       </c>
@@ -13619,7 +13618,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>52</v>
       </c>
@@ -13639,7 +13638,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>52</v>
       </c>
@@ -13659,7 +13658,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>52</v>
       </c>
@@ -13679,7 +13678,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>52</v>
       </c>
@@ -13699,7 +13698,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>52</v>
       </c>
@@ -13719,7 +13718,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>52</v>
       </c>
@@ -13739,7 +13738,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>52</v>
       </c>
@@ -13759,7 +13758,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>52</v>
       </c>
@@ -13779,7 +13778,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>52</v>
       </c>
@@ -13799,7 +13798,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>52</v>
       </c>
@@ -13819,7 +13818,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>52</v>
       </c>
@@ -13842,7 +13841,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>52</v>
       </c>
@@ -13865,7 +13864,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>52</v>
       </c>
@@ -13885,7 +13884,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>52</v>
       </c>
@@ -13908,7 +13907,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>52</v>
       </c>
@@ -13934,7 +13933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>52</v>
       </c>
@@ -13954,7 +13953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>52</v>
       </c>
@@ -13974,7 +13973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>52</v>
       </c>
@@ -13997,7 +13996,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>52</v>
       </c>
@@ -14017,7 +14016,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>53</v>
       </c>
@@ -14040,7 +14039,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>53</v>
       </c>
@@ -14060,7 +14059,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>53</v>
       </c>
@@ -14083,7 +14082,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>53</v>
       </c>
@@ -14103,7 +14102,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>53</v>
       </c>
@@ -14129,7 +14128,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>53</v>
       </c>
@@ -14149,7 +14148,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>53</v>
       </c>
@@ -14169,7 +14168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>53</v>
       </c>
@@ -14189,7 +14188,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>53</v>
       </c>
@@ -14209,7 +14208,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>53</v>
       </c>
@@ -14229,7 +14228,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>53</v>
       </c>
@@ -14249,7 +14248,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>53</v>
       </c>
@@ -14269,7 +14268,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>54</v>
       </c>
@@ -14289,7 +14288,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>54</v>
       </c>
@@ -14309,7 +14308,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>55</v>
       </c>
@@ -14329,7 +14328,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>55</v>
       </c>
@@ -14349,7 +14348,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>55</v>
       </c>
@@ -14369,7 +14368,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>55</v>
       </c>
@@ -14389,7 +14388,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>55</v>
       </c>
@@ -14409,7 +14408,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>56</v>
       </c>
@@ -14429,7 +14428,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>56</v>
       </c>
@@ -14449,7 +14448,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>56</v>
       </c>
@@ -14469,7 +14468,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>56</v>
       </c>
@@ -14489,7 +14488,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>56</v>
       </c>
@@ -14512,7 +14511,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>56</v>
       </c>
@@ -14532,7 +14531,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>56</v>
       </c>
@@ -14555,7 +14554,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>56</v>
       </c>
@@ -14575,7 +14574,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>56</v>
       </c>
@@ -14598,7 +14597,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>56</v>
       </c>
@@ -14618,7 +14617,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>56</v>
       </c>
@@ -14638,7 +14637,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>56</v>
       </c>
@@ -14658,7 +14657,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>56</v>
       </c>
@@ -14681,7 +14680,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>56</v>
       </c>
@@ -14701,7 +14700,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>56</v>
       </c>
@@ -14721,7 +14720,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>56</v>
       </c>
@@ -14741,7 +14740,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>56</v>
       </c>
@@ -14761,7 +14760,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>56</v>
       </c>
@@ -14781,7 +14780,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>56</v>
       </c>
@@ -14801,7 +14800,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>56</v>
       </c>
@@ -14821,7 +14820,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>56</v>
       </c>
@@ -14841,7 +14840,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>56</v>
       </c>
@@ -14861,7 +14860,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>56</v>
       </c>
@@ -14884,7 +14883,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>56</v>
       </c>
@@ -14904,7 +14903,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>56</v>
       </c>
@@ -14924,7 +14923,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>56</v>
       </c>
@@ -14944,7 +14943,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>56</v>
       </c>
@@ -14964,7 +14963,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>56</v>
       </c>
@@ -14984,7 +14983,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>56</v>
       </c>
@@ -15004,7 +15003,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>56</v>
       </c>
@@ -15024,7 +15023,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>56</v>
       </c>
@@ -15044,7 +15043,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>56</v>
       </c>
@@ -15064,7 +15063,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>56</v>
       </c>
@@ -15084,7 +15083,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>56</v>
       </c>
@@ -15107,7 +15106,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>56</v>
       </c>
@@ -15127,7 +15126,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>56</v>
       </c>
@@ -15147,7 +15146,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>56</v>
       </c>
@@ -15167,7 +15166,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>56</v>
       </c>
@@ -15187,7 +15186,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>56</v>
       </c>
@@ -15210,7 +15209,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>56</v>
       </c>
@@ -15233,7 +15232,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>57</v>
       </c>
@@ -15253,7 +15252,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>57</v>
       </c>
@@ -15273,7 +15272,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>57</v>
       </c>
@@ -15293,7 +15292,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>58</v>
       </c>
@@ -15313,7 +15312,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>58</v>
       </c>
@@ -15333,7 +15332,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>58</v>
       </c>
@@ -15353,7 +15352,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>59</v>
       </c>
@@ -15373,7 +15372,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>59</v>
       </c>
@@ -15393,7 +15392,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>60</v>
       </c>
@@ -15413,7 +15412,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>60</v>
       </c>
@@ -15433,7 +15432,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>61</v>
       </c>
@@ -15453,7 +15452,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>61</v>
       </c>
@@ -15473,7 +15472,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>61</v>
       </c>
@@ -15493,7 +15492,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>62</v>
       </c>
@@ -15513,7 +15512,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>62</v>
       </c>
@@ -15533,7 +15532,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>62</v>
       </c>
@@ -15553,7 +15552,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>62</v>
       </c>
@@ -15573,7 +15572,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>62</v>
       </c>
@@ -15593,7 +15592,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>62</v>
       </c>
@@ -15613,7 +15612,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>62</v>
       </c>
@@ -15633,7 +15632,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>62</v>
       </c>
@@ -15653,7 +15652,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>62</v>
       </c>
@@ -15673,7 +15672,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>62</v>
       </c>
@@ -15693,7 +15692,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>62</v>
       </c>
@@ -15713,7 +15712,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>62</v>
       </c>
@@ -15733,7 +15732,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>62</v>
       </c>
@@ -15753,7 +15752,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>62</v>
       </c>
@@ -15773,7 +15772,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>62</v>
       </c>
@@ -15793,7 +15792,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>62</v>
       </c>
@@ -15813,7 +15812,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>62</v>
       </c>
@@ -15833,7 +15832,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>62</v>
       </c>
@@ -15853,7 +15852,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>62</v>
       </c>
@@ -15873,7 +15872,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>62</v>
       </c>
@@ -15893,7 +15892,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>62</v>
       </c>
@@ -15913,7 +15912,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>62</v>
       </c>
@@ -15933,7 +15932,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>62</v>
       </c>
@@ -15953,7 +15952,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>62</v>
       </c>
@@ -15973,7 +15972,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>62</v>
       </c>
@@ -15993,7 +15992,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>62</v>
       </c>
@@ -16013,7 +16012,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>62</v>
       </c>
@@ -16033,7 +16032,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>62</v>
       </c>
@@ -16053,7 +16052,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>62</v>
       </c>
@@ -16073,7 +16072,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>62</v>
       </c>
@@ -16093,7 +16092,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>62</v>
       </c>
@@ -16113,7 +16112,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>62</v>
       </c>
@@ -16133,7 +16132,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>62</v>
       </c>
@@ -16153,7 +16152,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>62</v>
       </c>
@@ -16176,7 +16175,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>62</v>
       </c>
@@ -16196,7 +16195,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>62</v>
       </c>
@@ -16216,7 +16215,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>62</v>
       </c>
@@ -16236,7 +16235,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>62</v>
       </c>
@@ -16256,7 +16255,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>62</v>
       </c>
@@ -16276,7 +16275,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>62</v>
       </c>
@@ -16296,7 +16295,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>62</v>
       </c>
@@ -16316,7 +16315,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>62</v>
       </c>
@@ -16336,7 +16335,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>62</v>
       </c>
@@ -16356,7 +16355,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>62</v>
       </c>
@@ -16376,7 +16375,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>62</v>
       </c>
@@ -16396,7 +16395,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>62</v>
       </c>
@@ -16416,7 +16415,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>62</v>
       </c>
@@ -16436,7 +16435,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>62</v>
       </c>
@@ -16456,7 +16455,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>62</v>
       </c>
@@ -16476,7 +16475,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>62</v>
       </c>
@@ -16496,7 +16495,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>62</v>
       </c>
@@ -16516,7 +16515,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>62</v>
       </c>
@@ -16536,7 +16535,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>62</v>
       </c>
@@ -16556,7 +16555,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>62</v>
       </c>
@@ -16576,7 +16575,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>62</v>
       </c>
@@ -16596,7 +16595,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>62</v>
       </c>
@@ -16616,7 +16615,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>62</v>
       </c>
@@ -16636,7 +16635,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>62</v>
       </c>
@@ -16656,7 +16655,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>62</v>
       </c>
@@ -16676,7 +16675,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>62</v>
       </c>
@@ -16696,7 +16695,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>62</v>
       </c>
@@ -16716,7 +16715,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>62</v>
       </c>
@@ -16736,7 +16735,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>62</v>
       </c>
@@ -16756,7 +16755,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>62</v>
       </c>
@@ -16776,7 +16775,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>62</v>
       </c>
@@ -16796,7 +16795,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>62</v>
       </c>
@@ -16816,7 +16815,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>62</v>
       </c>
@@ -16836,7 +16835,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>62</v>
       </c>
@@ -16856,7 +16855,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>62</v>
       </c>
@@ -16876,7 +16875,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>62</v>
       </c>
@@ -16896,7 +16895,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>62</v>
       </c>
@@ -16916,7 +16915,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>62</v>
       </c>
@@ -16936,7 +16935,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>62</v>
       </c>
@@ -16956,7 +16955,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>62</v>
       </c>
@@ -16976,7 +16975,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>62</v>
       </c>
@@ -16996,7 +16995,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>62</v>
       </c>
@@ -17016,7 +17015,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>62</v>
       </c>
@@ -17036,7 +17035,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>62</v>
       </c>
@@ -17056,7 +17055,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>62</v>
       </c>
@@ -17076,7 +17075,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>62</v>
       </c>
@@ -17096,7 +17095,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>62</v>
       </c>
@@ -17116,7 +17115,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>62</v>
       </c>
@@ -17136,7 +17135,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>62</v>
       </c>
@@ -17156,7 +17155,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>62</v>
       </c>
@@ -17176,7 +17175,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>62</v>
       </c>
@@ -17196,7 +17195,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>62</v>
       </c>
@@ -17216,7 +17215,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>62</v>
       </c>
@@ -17236,7 +17235,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>62</v>
       </c>
@@ -17256,7 +17255,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>62</v>
       </c>
@@ -17276,7 +17275,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>62</v>
       </c>
@@ -17296,7 +17295,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>62</v>
       </c>
@@ -17316,7 +17315,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>62</v>
       </c>
@@ -17336,7 +17335,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>62</v>
       </c>
@@ -17356,7 +17355,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>62</v>
       </c>
@@ -17376,7 +17375,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>62</v>
       </c>
@@ -17396,7 +17395,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>62</v>
       </c>
@@ -17416,7 +17415,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>62</v>
       </c>
@@ -17436,7 +17435,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>62</v>
       </c>
@@ -17456,7 +17455,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>62</v>
       </c>
@@ -17476,7 +17475,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>62</v>
       </c>
@@ -17496,7 +17495,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>62</v>
       </c>
@@ -17516,7 +17515,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>62</v>
       </c>
@@ -17536,7 +17535,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>62</v>
       </c>
@@ -17556,7 +17555,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>62</v>
       </c>
@@ -17576,7 +17575,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>62</v>
       </c>
@@ -17596,7 +17595,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>62</v>
       </c>
@@ -17619,7 +17618,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>62</v>
       </c>
@@ -17639,7 +17638,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>62</v>
       </c>
@@ -17659,7 +17658,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>62</v>
       </c>
@@ -17679,7 +17678,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>62</v>
       </c>
@@ -17699,7 +17698,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>62</v>
       </c>
@@ -17719,7 +17718,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>62</v>
       </c>
@@ -17739,7 +17738,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>62</v>
       </c>
@@ -17759,7 +17758,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>62</v>
       </c>
@@ -17779,7 +17778,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>62</v>
       </c>
@@ -17799,7 +17798,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>62</v>
       </c>
@@ -17819,7 +17818,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>62</v>
       </c>
@@ -17839,7 +17838,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>62</v>
       </c>
@@ -17859,7 +17858,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>62</v>
       </c>
@@ -17879,7 +17878,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>62</v>
       </c>
@@ -17899,7 +17898,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>62</v>
       </c>
@@ -17919,7 +17918,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>62</v>
       </c>
@@ -17939,7 +17938,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>62</v>
       </c>
@@ -17959,7 +17958,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>62</v>
       </c>
@@ -17979,7 +17978,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>62</v>
       </c>
@@ -17999,7 +17998,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>62</v>
       </c>
@@ -18019,7 +18018,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>62</v>
       </c>
@@ -18039,7 +18038,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>62</v>
       </c>
@@ -18059,7 +18058,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>62</v>
       </c>
@@ -18082,7 +18081,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>62</v>
       </c>
@@ -18102,7 +18101,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>62</v>
       </c>
@@ -18122,7 +18121,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>62</v>
       </c>
@@ -18142,7 +18141,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>62</v>
       </c>
@@ -18162,7 +18161,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>62</v>
       </c>
@@ -18182,7 +18181,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>62</v>
       </c>
@@ -18202,7 +18201,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>62</v>
       </c>
@@ -18222,7 +18221,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>62</v>
       </c>
@@ -18242,7 +18241,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>62</v>
       </c>
@@ -18262,7 +18261,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>62</v>
       </c>
@@ -18282,7 +18281,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>62</v>
       </c>
@@ -18302,7 +18301,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>62</v>
       </c>
@@ -18322,7 +18321,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>62</v>
       </c>
@@ -18342,7 +18341,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>62</v>
       </c>
@@ -18362,7 +18361,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>62</v>
       </c>
@@ -18382,7 +18381,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>62</v>
       </c>
@@ -18402,7 +18401,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>62</v>
       </c>
@@ -18422,7 +18421,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>62</v>
       </c>
@@ -18442,7 +18441,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>62</v>
       </c>
@@ -18462,7 +18461,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>62</v>
       </c>
@@ -18482,7 +18481,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>62</v>
       </c>
@@ -18502,7 +18501,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>62</v>
       </c>
@@ -18522,7 +18521,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>62</v>
       </c>
@@ -18542,7 +18541,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>62</v>
       </c>
@@ -18562,7 +18561,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>62</v>
       </c>
@@ -18582,7 +18581,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>62</v>
       </c>
@@ -18602,7 +18601,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>62</v>
       </c>
@@ -18622,7 +18621,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>62</v>
       </c>
@@ -18642,7 +18641,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>62</v>
       </c>
@@ -18662,7 +18661,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>62</v>
       </c>
@@ -18682,7 +18681,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>62</v>
       </c>
@@ -18702,7 +18701,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>62</v>
       </c>
@@ -18725,7 +18724,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>62</v>
       </c>
@@ -18745,7 +18744,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>62</v>
       </c>
@@ -18765,7 +18764,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>62</v>
       </c>
@@ -18785,7 +18784,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>63</v>
       </c>
@@ -18805,7 +18804,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>63</v>
       </c>
@@ -18825,7 +18824,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>63</v>
       </c>
@@ -18848,7 +18847,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>63</v>
       </c>
@@ -18868,7 +18867,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>63</v>
       </c>
@@ -18888,7 +18887,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
         <v>63</v>
       </c>
@@ -18908,7 +18907,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>63</v>
       </c>
@@ -18928,7 +18927,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>63</v>
       </c>
@@ -18948,7 +18947,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>63</v>
       </c>
@@ -18968,7 +18967,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
         <v>63</v>
       </c>
@@ -18988,7 +18987,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>63</v>
       </c>
@@ -19008,7 +19007,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>63</v>
       </c>
@@ -19028,7 +19027,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>63</v>
       </c>
@@ -19048,7 +19047,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>63</v>
       </c>
@@ -19068,7 +19067,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>63</v>
       </c>
@@ -19088,7 +19087,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>63</v>
       </c>
@@ -19108,7 +19107,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>64</v>
       </c>
@@ -19128,7 +19127,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>64</v>
       </c>
@@ -19148,7 +19147,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
         <v>64</v>
       </c>
@@ -19168,7 +19167,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>64</v>
       </c>
@@ -19188,7 +19187,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>64</v>
       </c>
@@ -19208,7 +19207,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
         <v>64</v>
       </c>
@@ -19228,7 +19227,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>64</v>
       </c>
@@ -19248,7 +19247,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
         <v>64</v>
       </c>
@@ -19268,7 +19267,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>64</v>
       </c>
@@ -19291,7 +19290,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>64</v>
       </c>
@@ -19311,7 +19310,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>64</v>
       </c>
@@ -19331,7 +19330,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
         <v>64</v>
       </c>
@@ -19351,7 +19350,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>64</v>
       </c>
@@ -19371,7 +19370,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>64</v>
       </c>
@@ -19391,7 +19390,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>64</v>
       </c>
@@ -19411,7 +19410,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>64</v>
       </c>
@@ -19431,7 +19430,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
         <v>64</v>
       </c>
@@ -19451,7 +19450,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>64</v>
       </c>
@@ -19471,7 +19470,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>64</v>
       </c>
@@ -19494,7 +19493,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>64</v>
       </c>
@@ -19514,7 +19513,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>64</v>
       </c>
@@ -19534,7 +19533,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>64</v>
       </c>
@@ -19554,7 +19553,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>64</v>
       </c>
@@ -19574,7 +19573,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>64</v>
       </c>
@@ -19594,7 +19593,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>64</v>
       </c>
@@ -19614,7 +19613,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>64</v>
       </c>
@@ -19634,7 +19633,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>64</v>
       </c>
@@ -19654,7 +19653,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>64</v>
       </c>
@@ -19674,7 +19673,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
         <v>64</v>
       </c>
@@ -19694,7 +19693,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>64</v>
       </c>
@@ -19714,7 +19713,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>64</v>
       </c>
@@ -19734,7 +19733,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>64</v>
       </c>
@@ -19754,7 +19753,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>64</v>
       </c>
@@ -19774,7 +19773,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>64</v>
       </c>
@@ -19794,7 +19793,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
         <v>64</v>
       </c>
@@ -19814,7 +19813,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>64</v>
       </c>
@@ -19834,7 +19833,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>64</v>
       </c>
@@ -19854,7 +19853,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>64</v>
       </c>
@@ -19874,7 +19873,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>64</v>
       </c>
@@ -19894,7 +19893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
         <v>64</v>
       </c>
@@ -19914,7 +19913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>64</v>
       </c>
@@ -19934,7 +19933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
         <v>64</v>
       </c>
@@ -19954,7 +19953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>64</v>
       </c>
@@ -19974,7 +19973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>64</v>
       </c>
@@ -19994,7 +19993,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>64</v>
       </c>
@@ -20014,7 +20013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>64</v>
       </c>
@@ -20034,7 +20033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>64</v>
       </c>
@@ -20054,7 +20053,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
         <v>64</v>
       </c>
@@ -20074,7 +20073,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
         <v>64</v>
       </c>
@@ -20094,7 +20093,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>64</v>
       </c>
@@ -20114,7 +20113,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
         <v>64</v>
       </c>
@@ -20134,7 +20133,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
         <v>64</v>
       </c>
@@ -20154,7 +20153,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
         <v>64</v>
       </c>
@@ -20174,7 +20173,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
         <v>64</v>
       </c>
@@ -20194,7 +20193,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
         <v>64</v>
       </c>
@@ -20214,7 +20213,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>64</v>
       </c>
@@ -20234,7 +20233,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
         <v>64</v>
       </c>
@@ -20254,7 +20253,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>64</v>
       </c>
@@ -20274,7 +20273,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>64</v>
       </c>
@@ -20294,7 +20293,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>64</v>
       </c>
@@ -20314,7 +20313,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
         <v>64</v>
       </c>
@@ -20334,7 +20333,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
         <v>64</v>
       </c>
@@ -20354,7 +20353,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>64</v>
       </c>
@@ -20374,7 +20373,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
         <v>64</v>
       </c>
@@ -20394,7 +20393,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>64</v>
       </c>
@@ -20414,7 +20413,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>64</v>
       </c>
@@ -20434,7 +20433,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>64</v>
       </c>
@@ -20454,7 +20453,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>64</v>
       </c>
@@ -20474,7 +20473,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>64</v>
       </c>
@@ -20494,7 +20493,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>64</v>
       </c>
@@ -20514,7 +20513,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>64</v>
       </c>
@@ -20534,7 +20533,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>64</v>
       </c>
@@ -20554,7 +20553,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>64</v>
       </c>
@@ -20574,7 +20573,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>64</v>
       </c>
@@ -20594,7 +20593,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
         <v>64</v>
       </c>
@@ -20614,7 +20613,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>64</v>
       </c>
@@ -20634,7 +20633,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>64</v>
       </c>
@@ -20654,7 +20653,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>64</v>
       </c>
@@ -20674,7 +20673,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
         <v>64</v>
       </c>
@@ -20694,7 +20693,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
         <v>64</v>
       </c>
@@ -20714,7 +20713,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>64</v>
       </c>
@@ -20734,7 +20733,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>64</v>
       </c>
@@ -20754,7 +20753,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>64</v>
       </c>
@@ -20774,7 +20773,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>64</v>
       </c>
@@ -20794,7 +20793,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>64</v>
       </c>
@@ -20814,7 +20813,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>64</v>
       </c>
@@ -20834,7 +20833,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>64</v>
       </c>
@@ -20854,7 +20853,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>64</v>
       </c>
@@ -20874,7 +20873,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
         <v>64</v>
       </c>
@@ -20894,7 +20893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>64</v>
       </c>
@@ -20914,7 +20913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>64</v>
       </c>
@@ -20934,7 +20933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
         <v>64</v>
       </c>
@@ -20954,7 +20953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
         <v>64</v>
       </c>
@@ -20974,7 +20973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>64</v>
       </c>
@@ -20994,7 +20993,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>64</v>
       </c>
@@ -21014,7 +21013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>64</v>
       </c>
@@ -21034,7 +21033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>64</v>
       </c>
@@ -21054,7 +21053,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>64</v>
       </c>
@@ -21074,7 +21073,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>64</v>
       </c>
@@ -21094,7 +21093,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
         <v>64</v>
       </c>
@@ -21114,7 +21113,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>64</v>
       </c>
@@ -21134,7 +21133,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>64</v>
       </c>
@@ -21154,7 +21153,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>64</v>
       </c>
@@ -21174,7 +21173,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>64</v>
       </c>
@@ -21194,7 +21193,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>64</v>
       </c>
@@ -21214,7 +21213,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
         <v>64</v>
       </c>
@@ -21234,7 +21233,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>64</v>
       </c>
@@ -21254,7 +21253,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>64</v>
       </c>
@@ -21274,7 +21273,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>64</v>
       </c>
@@ -21294,7 +21293,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>64</v>
       </c>
@@ -21314,7 +21313,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
         <v>64</v>
       </c>
@@ -21334,7 +21333,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>64</v>
       </c>
@@ -21354,7 +21353,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>64</v>
       </c>
@@ -21374,7 +21373,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>64</v>
       </c>
@@ -21394,7 +21393,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>64</v>
       </c>
@@ -21414,7 +21413,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
         <v>64</v>
       </c>
@@ -21434,7 +21433,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>64</v>
       </c>
@@ -21454,7 +21453,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>64</v>
       </c>
@@ -21474,7 +21473,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>64</v>
       </c>
@@ -21494,7 +21493,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>64</v>
       </c>
@@ -21514,7 +21513,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>64</v>
       </c>
@@ -21534,7 +21533,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>64</v>
       </c>
@@ -21554,7 +21553,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>64</v>
       </c>
@@ -21574,7 +21573,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>64</v>
       </c>
@@ -21594,7 +21593,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
         <v>64</v>
       </c>
@@ -21614,7 +21613,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>64</v>
       </c>
@@ -21634,7 +21633,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>64</v>
       </c>
@@ -21654,7 +21653,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>64</v>
       </c>
@@ -21674,7 +21673,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
         <v>64</v>
       </c>
@@ -21694,7 +21693,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
         <v>64</v>
       </c>
@@ -21714,7 +21713,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>64</v>
       </c>
@@ -21734,7 +21733,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>64</v>
       </c>
@@ -21754,7 +21753,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>64</v>
       </c>
@@ -21774,7 +21773,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
         <v>64</v>
       </c>
@@ -21794,7 +21793,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>64</v>
       </c>
@@ -21814,7 +21813,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>64</v>
       </c>
@@ -21834,7 +21833,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>64</v>
       </c>
@@ -21854,7 +21853,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>64</v>
       </c>
@@ -21874,7 +21873,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>64</v>
       </c>
@@ -21894,7 +21893,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>64</v>
       </c>
@@ -21914,7 +21913,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>64</v>
       </c>
@@ -21934,7 +21933,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>64</v>
       </c>
@@ -21954,7 +21953,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>64</v>
       </c>
@@ -21974,7 +21973,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>64</v>
       </c>
@@ -21994,7 +21993,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>64</v>
       </c>
@@ -22014,7 +22013,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
         <v>64</v>
       </c>
@@ -22034,7 +22033,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>64</v>
       </c>
@@ -22054,7 +22053,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>64</v>
       </c>
@@ -22074,7 +22073,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>64</v>
       </c>
@@ -22094,7 +22093,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>64</v>
       </c>
@@ -22114,7 +22113,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>64</v>
       </c>
@@ -22134,7 +22133,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>64</v>
       </c>
@@ -22157,7 +22156,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>64</v>
       </c>
@@ -22177,7 +22176,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
         <v>64</v>
       </c>
@@ -22197,7 +22196,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
         <v>64</v>
       </c>
@@ -22220,7 +22219,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A869" t="s">
         <v>64</v>
       </c>
@@ -22240,7 +22239,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
         <v>64</v>
       </c>
@@ -22260,7 +22259,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
         <v>64</v>
       </c>
@@ -22280,7 +22279,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
         <v>64</v>
       </c>
@@ -22300,7 +22299,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
         <v>64</v>
       </c>
@@ -22320,7 +22319,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
         <v>64</v>
       </c>
@@ -22340,7 +22339,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A875" t="s">
         <v>64</v>
       </c>
@@ -22360,7 +22359,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
         <v>65</v>
       </c>
@@ -22380,7 +22379,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
         <v>65</v>
       </c>
@@ -22403,7 +22402,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
         <v>65</v>
       </c>
@@ -22423,7 +22422,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A879" t="s">
         <v>65</v>
       </c>
@@ -22446,7 +22445,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
         <v>65</v>
       </c>
@@ -22466,7 +22465,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="881" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
         <v>65</v>
       </c>
@@ -22486,7 +22485,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
         <v>65</v>
       </c>
@@ -22506,7 +22505,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A883" t="s">
         <v>65</v>
       </c>
@@ -22526,7 +22525,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
         <v>66</v>
       </c>
@@ -22546,7 +22545,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="885" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
         <v>66</v>
       </c>
@@ -22566,7 +22565,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="886" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
         <v>67</v>
       </c>
@@ -22589,7 +22588,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A887" t="s">
         <v>67</v>
       </c>
@@ -22609,7 +22608,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="888" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
         <v>67</v>
       </c>
@@ -22629,7 +22628,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="889" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>67</v>
       </c>
@@ -22652,7 +22651,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="890" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
         <v>67</v>
       </c>
@@ -22675,7 +22674,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="891" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A891" t="s">
         <v>67</v>
       </c>
@@ -22698,7 +22697,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="892" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A892" t="s">
         <v>67</v>
       </c>
@@ -22718,7 +22717,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="893" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
         <v>67</v>
       </c>
@@ -22738,7 +22737,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="894" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
         <v>67</v>
       </c>
@@ -22758,7 +22757,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="895" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A895" t="s">
         <v>67</v>
       </c>
@@ -22781,7 +22780,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A896" t="s">
         <v>67</v>
       </c>
@@ -22801,7 +22800,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="897" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A897" t="s">
         <v>67</v>
       </c>
@@ -22821,7 +22820,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A898" t="s">
         <v>67</v>
       </c>
@@ -22844,7 +22843,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A899" t="s">
         <v>67</v>
       </c>
@@ -22867,7 +22866,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A900" t="s">
         <v>67</v>
       </c>
@@ -22887,7 +22886,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A901" t="s">
         <v>67</v>
       </c>
@@ -22907,7 +22906,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A902" t="s">
         <v>67</v>
       </c>
@@ -22930,7 +22929,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A903" t="s">
         <v>67</v>
       </c>
@@ -22950,7 +22949,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A904" t="s">
         <v>67</v>
       </c>
@@ -22970,7 +22969,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A905" t="s">
         <v>67</v>
       </c>
@@ -22990,7 +22989,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A906" t="s">
         <v>67</v>
       </c>
@@ -23013,7 +23012,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A907" t="s">
         <v>67</v>
       </c>
@@ -23036,7 +23035,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A908" t="s">
         <v>67</v>
       </c>
@@ -23056,7 +23055,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A909" t="s">
         <v>67</v>
       </c>
@@ -23076,7 +23075,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A910" t="s">
         <v>67</v>
       </c>
@@ -23099,7 +23098,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A911" t="s">
         <v>67</v>
       </c>
@@ -23122,7 +23121,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A912" t="s">
         <v>67</v>
       </c>
@@ -23145,7 +23144,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A913" t="s">
         <v>67</v>
       </c>
@@ -23165,7 +23164,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="914" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A914" t="s">
         <v>67</v>
       </c>
@@ -23185,7 +23184,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="915" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A915" t="s">
         <v>68</v>
       </c>
@@ -23205,7 +23204,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="916" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A916" t="s">
         <v>68</v>
       </c>
@@ -23228,7 +23227,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="917" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A917" t="s">
         <v>68</v>
       </c>
@@ -23248,7 +23247,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="918" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A918" t="s">
         <v>68</v>
       </c>
@@ -23268,7 +23267,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="919" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A919" t="s">
         <v>68</v>
       </c>
@@ -23288,7 +23287,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="920" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A920" t="s">
         <v>68</v>
       </c>
@@ -23311,7 +23310,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="921" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A921" t="s">
         <v>68</v>
       </c>
@@ -23334,7 +23333,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="922" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A922" t="s">
         <v>68</v>
       </c>
@@ -23354,7 +23353,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="923" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A923" t="s">
         <v>68</v>
       </c>
@@ -23377,7 +23376,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="924" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A924" t="s">
         <v>68</v>
       </c>
@@ -23400,7 +23399,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="925" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A925" t="s">
         <v>68</v>
       </c>
@@ -23423,7 +23422,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="926" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A926" t="s">
         <v>68</v>
       </c>
@@ -23443,7 +23442,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="927" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A927" t="s">
         <v>68</v>
       </c>
@@ -23463,7 +23462,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="928" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A928" t="s">
         <v>68</v>
       </c>
@@ -23483,7 +23482,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="929" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A929" t="s">
         <v>68</v>
       </c>
@@ -23506,7 +23505,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="930" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A930" t="s">
         <v>68</v>
       </c>
@@ -23526,7 +23525,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="931" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A931" t="s">
         <v>68</v>
       </c>
@@ -23546,7 +23545,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="932" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A932" t="s">
         <v>68</v>
       </c>
@@ -23566,7 +23565,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A933" t="s">
         <v>68</v>
       </c>
@@ -23589,7 +23588,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A934" t="s">
         <v>68</v>
       </c>
@@ -23609,7 +23608,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A935" t="s">
         <v>68</v>
       </c>
@@ -23629,7 +23628,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A936" t="s">
         <v>68</v>
       </c>
@@ -23652,7 +23651,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A937" t="s">
         <v>68</v>
       </c>
@@ -23675,7 +23674,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A938" t="s">
         <v>68</v>
       </c>
@@ -23698,7 +23697,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A939" t="s">
         <v>68</v>
       </c>
@@ -23721,7 +23720,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A940" t="s">
         <v>68</v>
       </c>
@@ -23741,7 +23740,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="941" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A941" t="s">
         <v>68</v>
       </c>
@@ -23764,7 +23763,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="942" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A942" t="s">
         <v>68</v>
       </c>
@@ -23784,7 +23783,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A943" t="s">
         <v>68</v>
       </c>
@@ -23804,7 +23803,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="944" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A944" t="s">
         <v>68</v>
       </c>
@@ -23824,7 +23823,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="945" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A945" t="s">
         <v>69</v>
       </c>
@@ -23844,7 +23843,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A946" t="s">
         <v>69</v>
       </c>
@@ -23867,7 +23866,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A947" t="s">
         <v>69</v>
       </c>
@@ -23887,7 +23886,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A948" t="s">
         <v>69</v>
       </c>
@@ -23907,7 +23906,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A949" t="s">
         <v>69</v>
       </c>
@@ -23927,7 +23926,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A950" t="s">
         <v>69</v>
       </c>
@@ -23950,7 +23949,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="951" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A951" t="s">
         <v>69</v>
       </c>
@@ -23970,7 +23969,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A952" t="s">
         <v>69</v>
       </c>
@@ -23990,7 +23989,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A953" t="s">
         <v>70</v>
       </c>
@@ -24010,7 +24009,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="954" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A954" t="s">
         <v>70</v>
       </c>
@@ -24033,7 +24032,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="955" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A955" t="s">
         <v>70</v>
       </c>
@@ -24056,7 +24055,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A956" t="s">
         <v>70</v>
       </c>
@@ -24076,7 +24075,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A957" t="s">
         <v>70</v>
       </c>
@@ -24099,7 +24098,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A958" t="s">
         <v>70</v>
       </c>
@@ -24119,7 +24118,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A959" t="s">
         <v>70</v>
       </c>
@@ -24139,7 +24138,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A960" t="s">
         <v>70</v>
       </c>
@@ -24162,7 +24161,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="961" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A961" t="s">
         <v>70</v>
       </c>
@@ -24182,7 +24181,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="962" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A962" t="s">
         <v>70</v>
       </c>
@@ -24202,7 +24201,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="963" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A963" t="s">
         <v>70</v>
       </c>
@@ -24225,7 +24224,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A964" t="s">
         <v>70</v>
       </c>
@@ -24245,7 +24244,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A965" t="s">
         <v>70</v>
       </c>
@@ -24268,7 +24267,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="966" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A966" t="s">
         <v>70</v>
       </c>
@@ -24291,7 +24290,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="967" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A967" t="s">
         <v>70</v>
       </c>
@@ -24314,7 +24313,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="968" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A968" t="s">
         <v>70</v>
       </c>
@@ -24334,7 +24333,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
         <v>70</v>
       </c>
@@ -24354,7 +24353,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A970" t="s">
         <v>70</v>
       </c>
@@ -24374,7 +24373,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A971" t="s">
         <v>70</v>
       </c>
@@ -24397,7 +24396,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A972" t="s">
         <v>70</v>
       </c>
@@ -24417,7 +24416,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A973" t="s">
         <v>70</v>
       </c>
@@ -24440,7 +24439,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A974" t="s">
         <v>70</v>
       </c>
@@ -24460,7 +24459,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A975" t="s">
         <v>70</v>
       </c>
@@ -24483,7 +24482,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A976" t="s">
         <v>70</v>
       </c>
@@ -24503,7 +24502,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A977" t="s">
         <v>70</v>
       </c>
@@ -24523,7 +24522,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A978" t="s">
         <v>70</v>
       </c>
@@ -24543,7 +24542,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="979" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A979" t="s">
         <v>70</v>
       </c>
@@ -24566,7 +24565,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="980" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A980" t="s">
         <v>71</v>
       </c>
@@ -24586,7 +24585,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="981" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A981" t="s">
         <v>71</v>
       </c>
@@ -24606,7 +24605,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="982" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A982" t="s">
         <v>71</v>
       </c>
@@ -24626,7 +24625,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="983" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A983" t="s">
         <v>71</v>
       </c>
@@ -24646,7 +24645,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="984" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A984" t="s">
         <v>71</v>
       </c>
@@ -24669,7 +24668,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="985" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A985" t="s">
         <v>71</v>
       </c>
@@ -24689,7 +24688,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="986" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A986" t="s">
         <v>71</v>
       </c>
@@ -24709,7 +24708,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="987" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A987" t="s">
         <v>71</v>
       </c>
@@ -24729,7 +24728,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="988" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A988" t="s">
         <v>71</v>
       </c>
@@ -24749,7 +24748,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="989" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A989" t="s">
         <v>71</v>
       </c>
@@ -24769,7 +24768,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="990" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
         <v>72</v>
       </c>
@@ -24789,7 +24788,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="991" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
         <v>72</v>
       </c>
@@ -24812,7 +24811,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="992" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
         <v>72</v>
       </c>
@@ -24832,7 +24831,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="993" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
         <v>72</v>
       </c>
@@ -24855,7 +24854,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="994" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A994" t="s">
         <v>72</v>
       </c>
@@ -24878,7 +24877,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="995" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
         <v>72</v>
       </c>
@@ -24898,7 +24897,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="996" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
         <v>72</v>
       </c>
@@ -24918,7 +24917,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="997" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
         <v>72</v>
       </c>
@@ -24938,7 +24937,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="998" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
         <v>72</v>
       </c>
@@ -24958,7 +24957,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="999" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A999" t="s">
         <v>72</v>
       </c>
@@ -24978,7 +24977,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1000" t="s">
         <v>73</v>
       </c>
@@ -24998,7 +24997,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1001" t="s">
         <v>73</v>
       </c>
@@ -25018,7 +25017,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1002" t="s">
         <v>74</v>
       </c>
@@ -25038,7 +25037,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1003" t="s">
         <v>74</v>
       </c>
@@ -25058,7 +25057,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1004" t="s">
         <v>74</v>
       </c>
@@ -25078,7 +25077,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1005" t="s">
         <v>75</v>
       </c>
@@ -25098,7 +25097,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1006" t="s">
         <v>75</v>
       </c>
@@ -25118,7 +25117,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1007" t="s">
         <v>75</v>
       </c>
@@ -25138,7 +25137,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1008" t="s">
         <v>75</v>
       </c>
@@ -25158,7 +25157,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1009" t="s">
         <v>75</v>
       </c>
@@ -25179,13 +25178,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1009" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J1009" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76675445-7905-4C4B-9268-2AD33BD61849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7D9EA3-4D75-1B4C-BF2D-A9A4F02D4CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608A48B2-363E-3147-A1EB-4A3DC06AFDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43160542-1978-044F-B21D-DBF3FBC5340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="31980" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9295,7 +9295,7 @@
         <v>58</v>
       </c>
       <c r="E341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I341" t="s">
         <v>11</v>
@@ -9332,7 +9332,7 @@
         <v>37</v>
       </c>
       <c r="D343" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E343" t="b">
         <v>0</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43160542-1978-044F-B21D-DBF3FBC5340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615A734B-D3C6-2348-938D-BF65D15F1327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="31980" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9295,7 +9295,7 @@
         <v>58</v>
       </c>
       <c r="E341" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I341" t="s">
         <v>11</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15ACD5B8-D68E-8849-A987-C9A3C752E579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F8945F-0B71-8D40-90AC-26FB67AE523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="700" windowWidth="33720" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="700" windowWidth="33720" windowHeight="19740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="628">
   <si>
     <t>Table Name</t>
   </si>
@@ -1811,6 +1811,105 @@
   </si>
   <si>
     <t>Agg Time Dimension</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>ACQUIRING</t>
+  </si>
+  <si>
+    <t>SPAN</t>
+  </si>
+  <si>
+    <t>WONDR</t>
+  </si>
+  <si>
+    <t>TELLER</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>OTHERS</t>
+  </si>
+  <si>
+    <t>BOP</t>
+  </si>
+  <si>
+    <t>AUTODEBET</t>
+  </si>
+  <si>
+    <t>EDC_NON_BNI</t>
+  </si>
+  <si>
+    <t>NEW_MOB</t>
+  </si>
+  <si>
+    <t>REMITTANCE</t>
+  </si>
+  <si>
+    <t>AGEN_TRX</t>
+  </si>
+  <si>
+    <t>BNIDIRECT</t>
+  </si>
+  <si>
+    <t>ATM</t>
+  </si>
+  <si>
+    <t>NON API</t>
+  </si>
+  <si>
+    <t>Transaksi via Teller</t>
+  </si>
+  <si>
+    <t>Transaksi via Wonder / WONDR</t>
+  </si>
+  <si>
+    <t>Transaksi via SMS</t>
+  </si>
+  <si>
+    <t>Transaksi lainnya</t>
+  </si>
+  <si>
+    <t>Transaksi via Autodebet</t>
+  </si>
+  <si>
+    <t>Transaksi via EDC Non BNI (EDC Bank Lain)</t>
+  </si>
+  <si>
+    <t>Transaksi Remittance</t>
+  </si>
+  <si>
+    <t>Transaksi via Agen</t>
+  </si>
+  <si>
+    <t>Transaksi via BNI Direct</t>
+  </si>
+  <si>
+    <t>Transaksi Non API</t>
+  </si>
+  <si>
+    <t>Transaksi via ATM</t>
+  </si>
+  <si>
+    <t>Transaksi API</t>
+  </si>
+  <si>
+    <t>Transaksi Acquiring</t>
+  </si>
+  <si>
+    <t>Transaksi SPAN</t>
+  </si>
+  <si>
+    <t>Transaksi BOP</t>
+  </si>
+  <si>
+    <t>Transaksi New MOB</t>
+  </si>
+  <si>
+    <t>Wonder</t>
   </si>
 </sst>
 </file>
@@ -2647,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>10</v>
+        <v>593</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>348</v>
@@ -9349,14 +9448,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -9388,6 +9487,233 @@
       </c>
       <c r="D2" t="s">
         <v>592</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E5" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>598</v>
+      </c>
+      <c r="D6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>599</v>
+      </c>
+      <c r="E7" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>600</v>
+      </c>
+      <c r="E8" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>601</v>
+      </c>
+      <c r="E9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>602</v>
+      </c>
+      <c r="E10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>603</v>
+      </c>
+      <c r="E11" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>604</v>
+      </c>
+      <c r="E12" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>605</v>
+      </c>
+      <c r="E13" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>606</v>
+      </c>
+      <c r="E14" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>607</v>
+      </c>
+      <c r="E15" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>608</v>
+      </c>
+      <c r="E16" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>610</v>
+      </c>
+      <c r="E17" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>609</v>
+      </c>
+      <c r="E18" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F8945F-0B71-8D40-90AC-26FB67AE523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E0F96A-74B0-7B4F-8481-A29AA6D275EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="700" windowWidth="33720" windowHeight="19740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="700" windowWidth="33720" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="629">
   <si>
     <t>Table Name</t>
   </si>
@@ -1910,6 +1910,9 @@
   </si>
   <si>
     <t>Wonder</t>
+  </si>
+  <si>
+    <t>Tampilkan cash out</t>
   </si>
 </sst>
 </file>
@@ -9723,7 +9726,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30159596-74E1-AB4A-8605-D929B81467D2}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.1640625" bestFit="1" customWidth="1"/>
@@ -9752,6 +9755,11 @@
         <v>21</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>628</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E0F96A-74B0-7B4F-8481-A29AA6D275EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E7EE77-5D8C-834B-B59D-13A2D31AD240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="700" windowWidth="33720" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -1027,9 +1027,6 @@
     <t>group_principal</t>
   </si>
   <si>
-    <t>Tanggal Data</t>
-  </si>
-  <si>
     <t>Waktu Transaksi</t>
   </si>
   <si>
@@ -1069,9 +1066,6 @@
     <t>No Jurnal Transaksi</t>
   </si>
   <si>
-    <t>Nilai Transaksi</t>
-  </si>
-  <si>
     <t>Channel Transaksi</t>
   </si>
   <si>
@@ -1913,6 +1907,12 @@
   </si>
   <si>
     <t>Tampilkan cash out</t>
+  </si>
+  <si>
+    <t>Nilai Transaksi / Amount</t>
+  </si>
+  <si>
+    <t>Tanggal Transaksi Data, digunakan untuk filter tanggal, bulan, tahun</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2329,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2340,7 +2340,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2351,18 +2351,18 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -2402,7 +2402,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
@@ -2440,7 +2440,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>333</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2460,7 +2460,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2477,13 +2477,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -2500,13 +2500,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2526,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2546,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2566,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2586,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2606,7 +2606,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2626,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2646,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2666,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2686,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2732,7 +2732,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>347</v>
+        <v>627</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2749,10 +2749,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2772,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2792,7 +2792,7 @@
         <v>10</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2812,7 +2812,7 @@
         <v>10</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2832,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2852,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2872,7 +2872,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2892,7 +2892,7 @@
         <v>10</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2912,7 +2912,7 @@
         <v>10</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2932,7 +2932,7 @@
         <v>10</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2952,7 +2952,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2972,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2989,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -3012,13 +3012,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3038,7 +3038,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3058,7 +3058,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3078,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3098,7 +3098,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3138,7 +3138,7 @@
         <v>10</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3158,7 +3158,7 @@
         <v>10</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3178,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3201,7 +3201,7 @@
         <v>10</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3221,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3241,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3261,7 +3261,7 @@
         <v>10</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3281,7 +3281,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3301,7 +3301,7 @@
         <v>10</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3321,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3344,7 +3344,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3364,7 +3364,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3384,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3404,7 +3404,7 @@
         <v>10</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3424,7 +3424,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3444,7 +3444,7 @@
         <v>10</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3461,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3487,7 +3487,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3507,7 +3507,7 @@
         <v>10</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3527,7 +3527,7 @@
         <v>10</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3547,7 +3547,7 @@
         <v>10</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3567,7 +3567,7 @@
         <v>10</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3587,7 +3587,7 @@
         <v>10</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3607,7 +3607,7 @@
         <v>10</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3627,7 +3627,7 @@
         <v>10</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3647,7 +3647,7 @@
         <v>10</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3667,7 +3667,7 @@
         <v>10</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3687,7 +3687,7 @@
         <v>10</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3707,7 +3707,7 @@
         <v>10</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3727,7 +3727,7 @@
         <v>10</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3747,7 +3747,7 @@
         <v>10</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3770,7 +3770,7 @@
         <v>10</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3790,7 +3790,7 @@
         <v>10</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3810,7 +3810,7 @@
         <v>10</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3830,7 +3830,7 @@
         <v>10</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3850,7 +3850,7 @@
         <v>10</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3870,7 +3870,7 @@
         <v>10</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3890,7 +3890,7 @@
         <v>10</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3910,7 +3910,7 @@
         <v>10</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3930,7 +3930,7 @@
         <v>10</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3950,7 +3950,7 @@
         <v>10</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3970,7 +3970,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3990,7 +3990,7 @@
         <v>10</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4010,7 +4010,7 @@
         <v>10</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4030,7 +4030,7 @@
         <v>10</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4050,7 +4050,7 @@
         <v>10</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4104,7 +4104,7 @@
         <v>10</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4175,7 +4175,7 @@
         <v>10</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4195,7 +4195,7 @@
         <v>10</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4215,7 +4215,7 @@
         <v>10</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4235,7 +4235,7 @@
         <v>10</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4255,7 +4255,7 @@
         <v>10</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4275,7 +4275,7 @@
         <v>10</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4295,7 +4295,7 @@
         <v>10</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4315,7 +4315,7 @@
         <v>10</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4335,7 +4335,7 @@
         <v>10</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4355,7 +4355,7 @@
         <v>10</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4375,7 +4375,7 @@
         <v>10</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4395,7 +4395,7 @@
         <v>10</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4415,7 +4415,7 @@
         <v>10</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4452,7 +4452,7 @@
         <v>10</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4472,7 +4472,7 @@
         <v>10</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4495,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4555,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4609,7 +4609,7 @@
         <v>10</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4629,7 +4629,7 @@
         <v>10</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4649,7 +4649,7 @@
         <v>10</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4669,7 +4669,7 @@
         <v>10</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4689,7 +4689,7 @@
         <v>10</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4709,7 +4709,7 @@
         <v>10</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4729,7 +4729,7 @@
         <v>10</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4749,7 +4749,7 @@
         <v>10</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4769,7 +4769,7 @@
         <v>10</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4789,7 +4789,7 @@
         <v>10</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4809,7 +4809,7 @@
         <v>10</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4829,7 +4829,7 @@
         <v>10</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4849,7 +4849,7 @@
         <v>10</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4869,7 +4869,7 @@
         <v>10</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4889,7 +4889,7 @@
         <v>10</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4909,7 +4909,7 @@
         <v>10</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4929,7 +4929,7 @@
         <v>10</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4949,7 +4949,7 @@
         <v>10</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4969,7 +4969,7 @@
         <v>10</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4989,7 +4989,7 @@
         <v>10</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5029,7 +5029,7 @@
         <v>10</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5049,7 +5049,7 @@
         <v>10</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5069,7 +5069,7 @@
         <v>10</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5089,7 +5089,7 @@
         <v>10</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5109,7 +5109,7 @@
         <v>10</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5129,7 +5129,7 @@
         <v>10</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5149,7 +5149,7 @@
         <v>10</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5169,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5189,7 +5189,7 @@
         <v>10</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5209,7 +5209,7 @@
         <v>10</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5226,13 +5226,13 @@
         <v>0</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5252,7 +5252,7 @@
         <v>10</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5272,7 +5272,7 @@
         <v>10</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5292,7 +5292,7 @@
         <v>10</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5312,7 +5312,7 @@
         <v>10</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5332,7 +5332,7 @@
         <v>10</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5352,7 +5352,7 @@
         <v>10</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5372,7 +5372,7 @@
         <v>10</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5392,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5412,7 +5412,7 @@
         <v>10</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5432,7 +5432,7 @@
         <v>10</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5452,7 +5452,7 @@
         <v>10</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5472,7 +5472,7 @@
         <v>10</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5492,7 +5492,7 @@
         <v>10</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5512,7 +5512,7 @@
         <v>10</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5532,7 +5532,7 @@
         <v>10</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5552,7 +5552,7 @@
         <v>10</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5572,7 +5572,7 @@
         <v>10</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5592,7 +5592,7 @@
         <v>10</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5612,7 +5612,7 @@
         <v>10</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5632,7 +5632,7 @@
         <v>10</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5672,7 +5672,7 @@
         <v>10</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5692,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5712,7 +5712,7 @@
         <v>10</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5732,7 +5732,7 @@
         <v>10</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5755,7 +5755,7 @@
         <v>10</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5775,7 +5775,7 @@
         <v>10</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5795,7 +5795,7 @@
         <v>10</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5815,7 +5815,7 @@
         <v>10</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5835,7 +5835,7 @@
         <v>10</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5855,7 +5855,7 @@
         <v>10</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5875,7 +5875,7 @@
         <v>10</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5895,7 +5895,7 @@
         <v>10</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5915,7 +5915,7 @@
         <v>10</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5935,7 +5935,7 @@
         <v>10</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5955,7 +5955,7 @@
         <v>10</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5975,7 +5975,7 @@
         <v>10</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5998,7 +5998,7 @@
         <v>10</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6021,7 +6021,7 @@
         <v>10</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6044,7 +6044,7 @@
         <v>10</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6067,7 +6067,7 @@
         <v>10</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6090,7 +6090,7 @@
         <v>10</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6110,7 +6110,7 @@
         <v>10</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6130,7 +6130,7 @@
         <v>10</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6150,7 +6150,7 @@
         <v>10</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6170,7 +6170,7 @@
         <v>10</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6190,7 +6190,7 @@
         <v>10</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6210,7 +6210,7 @@
         <v>10</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6230,7 +6230,7 @@
         <v>10</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6250,7 +6250,7 @@
         <v>10</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6270,7 +6270,7 @@
         <v>10</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6290,7 +6290,7 @@
         <v>10</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6310,7 +6310,7 @@
         <v>10</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6330,7 +6330,7 @@
         <v>10</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6350,7 +6350,7 @@
         <v>10</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6370,7 +6370,7 @@
         <v>10</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6390,7 +6390,7 @@
         <v>10</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6410,7 +6410,7 @@
         <v>10</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6430,7 +6430,7 @@
         <v>10</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6450,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6473,7 +6473,7 @@
         <v>10</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6496,7 +6496,7 @@
         <v>10</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6542,7 +6542,7 @@
         <v>10</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6565,7 +6565,7 @@
         <v>10</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6588,7 +6588,7 @@
         <v>10</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6611,7 +6611,7 @@
         <v>10</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6634,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6657,7 +6657,7 @@
         <v>10</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6680,7 +6680,7 @@
         <v>10</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6700,7 +6700,7 @@
         <v>10</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6720,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6763,7 +6763,7 @@
         <v>10</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6786,7 +6786,7 @@
         <v>10</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6809,7 +6809,7 @@
         <v>10</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6829,7 +6829,7 @@
         <v>10</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6849,7 +6849,7 @@
         <v>10</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6869,7 +6869,7 @@
         <v>10</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6889,7 +6889,7 @@
         <v>10</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6909,7 +6909,7 @@
         <v>10</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6929,7 +6929,7 @@
         <v>10</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6949,7 +6949,7 @@
         <v>10</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6969,7 +6969,7 @@
         <v>10</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6989,7 +6989,7 @@
         <v>10</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7009,7 +7009,7 @@
         <v>10</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7029,7 +7029,7 @@
         <v>10</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7052,7 +7052,7 @@
         <v>10</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7075,7 +7075,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7098,7 +7098,7 @@
         <v>10</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7121,7 +7121,7 @@
         <v>10</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7144,7 +7144,7 @@
         <v>10</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7167,7 +7167,7 @@
         <v>10</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7190,7 +7190,7 @@
         <v>10</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7213,7 +7213,7 @@
         <v>10</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7256,7 +7256,7 @@
         <v>10</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7276,7 +7276,7 @@
         <v>10</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7299,7 +7299,7 @@
         <v>10</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7319,7 +7319,7 @@
         <v>10</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7339,7 +7339,7 @@
         <v>10</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7382,7 +7382,7 @@
         <v>10</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7402,7 +7402,7 @@
         <v>10</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7422,7 +7422,7 @@
         <v>10</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7442,7 +7442,7 @@
         <v>10</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7462,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7482,7 +7482,7 @@
         <v>10</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7502,7 +7502,7 @@
         <v>10</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7542,7 +7542,7 @@
         <v>10</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7562,7 +7562,7 @@
         <v>10</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7582,7 +7582,7 @@
         <v>10</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7602,7 +7602,7 @@
         <v>10</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7622,7 +7622,7 @@
         <v>10</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7642,7 +7642,7 @@
         <v>10</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7662,7 +7662,7 @@
         <v>10</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7682,7 +7682,7 @@
         <v>10</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7702,7 +7702,7 @@
         <v>10</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7722,7 +7722,7 @@
         <v>10</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7742,7 +7742,7 @@
         <v>10</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7762,7 +7762,7 @@
         <v>10</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7782,7 +7782,7 @@
         <v>10</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7802,7 +7802,7 @@
         <v>10</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7822,7 +7822,7 @@
         <v>10</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7842,7 +7842,7 @@
         <v>10</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7862,7 +7862,7 @@
         <v>10</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7882,7 +7882,7 @@
         <v>10</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7902,7 +7902,7 @@
         <v>10</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7922,7 +7922,7 @@
         <v>10</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7942,7 +7942,7 @@
         <v>10</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7962,7 +7962,7 @@
         <v>10</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7982,7 +7982,7 @@
         <v>10</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8002,7 +8002,7 @@
         <v>10</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8022,7 +8022,7 @@
         <v>10</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8042,7 +8042,7 @@
         <v>10</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8062,7 +8062,7 @@
         <v>10</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8082,7 +8082,7 @@
         <v>10</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8102,7 +8102,7 @@
         <v>10</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8122,7 +8122,7 @@
         <v>10</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8142,7 +8142,7 @@
         <v>10</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8162,7 +8162,7 @@
         <v>10</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8182,7 +8182,7 @@
         <v>10</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8202,7 +8202,7 @@
         <v>10</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8222,7 +8222,7 @@
         <v>10</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8242,7 +8242,7 @@
         <v>10</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8262,7 +8262,7 @@
         <v>10</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8282,7 +8282,7 @@
         <v>10</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8302,7 +8302,7 @@
         <v>10</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8322,7 +8322,7 @@
         <v>10</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8342,7 +8342,7 @@
         <v>10</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8362,7 +8362,7 @@
         <v>10</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8382,7 +8382,7 @@
         <v>10</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8402,7 +8402,7 @@
         <v>10</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8422,7 +8422,7 @@
         <v>10</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8445,7 +8445,7 @@
         <v>10</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8468,7 +8468,7 @@
         <v>10</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8491,7 +8491,7 @@
         <v>10</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8514,7 +8514,7 @@
         <v>10</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8537,7 +8537,7 @@
         <v>10</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8560,7 +8560,7 @@
         <v>10</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8583,7 +8583,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8606,7 +8606,7 @@
         <v>10</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8629,7 +8629,7 @@
         <v>10</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8652,7 +8652,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8675,7 +8675,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8698,7 +8698,7 @@
         <v>10</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8721,7 +8721,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8744,7 +8744,7 @@
         <v>10</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8767,7 +8767,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8790,7 +8790,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8813,7 +8813,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8833,7 +8833,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8853,7 +8853,7 @@
         <v>10</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8873,7 +8873,7 @@
         <v>10</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8893,7 +8893,7 @@
         <v>10</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8913,7 +8913,7 @@
         <v>10</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8933,7 +8933,7 @@
         <v>10</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8953,7 +8953,7 @@
         <v>10</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8973,7 +8973,7 @@
         <v>10</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8993,7 +8993,7 @@
         <v>10</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9013,7 +9013,7 @@
         <v>10</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9033,7 +9033,7 @@
         <v>10</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9056,7 +9056,7 @@
         <v>10</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9079,7 +9079,7 @@
         <v>10</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9102,7 +9102,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9122,7 +9122,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9142,7 +9142,7 @@
         <v>10</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9162,7 +9162,7 @@
         <v>10</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9182,7 +9182,7 @@
         <v>10</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9202,7 +9202,7 @@
         <v>10</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9225,7 +9225,7 @@
         <v>10</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9248,7 +9248,7 @@
         <v>10</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9268,7 +9268,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9288,7 +9288,7 @@
         <v>10</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9311,7 +9311,7 @@
         <v>10</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9334,7 +9334,7 @@
         <v>10</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9354,12 +9354,12 @@
         <v>10</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B340" s="4" t="s">
         <v>331</v>
@@ -9371,18 +9371,18 @@
         <v>0</v>
       </c>
       <c r="F340" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H340" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B341" s="4" t="s">
         <v>332</v>
@@ -9397,12 +9397,12 @@
         <v>10</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B342" s="4" t="s">
         <v>149</v>
@@ -9417,12 +9417,12 @@
         <v>10</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B343" s="4" t="s">
         <v>31</v>
@@ -9440,7 +9440,7 @@
         <v>10</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -9486,10 +9486,10 @@
         <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9500,10 +9500,10 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9514,10 +9514,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9528,10 +9528,10 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9542,13 +9542,13 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9559,10 +9559,10 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E7" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9573,10 +9573,10 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E8" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9587,10 +9587,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E9" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9601,10 +9601,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E10" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9615,10 +9615,10 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E11" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9629,10 +9629,10 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9643,10 +9643,10 @@
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E13" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9657,10 +9657,10 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E14" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9671,10 +9671,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E15" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9685,10 +9685,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E16" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9699,10 +9699,10 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E17" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9713,10 +9713,10 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E18" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -9746,10 +9746,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -9757,7 +9757,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E7EE77-5D8C-834B-B59D-13A2D31AD240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8015EDF6-7CB3-0545-AFD1-C2D035F9EFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8015EDF6-7CB3-0545-AFD1-C2D035F9EFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323B8465-1134-9A42-8797-5ED527459615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="630">
   <si>
     <t>Table Name</t>
   </si>
@@ -1906,13 +1906,16 @@
     <t>Wonder</t>
   </si>
   <si>
-    <t>Tampilkan cash out</t>
-  </si>
-  <si>
     <t>Nilai Transaksi / Amount</t>
   </si>
   <si>
     <t>Tanggal Transaksi Data, digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>Aktivitas Cash out</t>
+  </si>
+  <si>
+    <t>SELECT * FROM dm_transaction.trxchannel WHERE destination_bankname &lt;&gt; 'BANK NEGARA INDONESIA';</t>
   </si>
 </sst>
 </file>
@@ -2440,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2732,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9755,9 +9758,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>626</v>
+        <v>628</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323B8465-1134-9A42-8797-5ED527459615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79458033-870F-9147-A2CA-A0DAE6540A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="630">
   <si>
     <t>Table Name</t>
   </si>
@@ -1105,12 +1105,6 @@
     <t>CIF Penerima</t>
   </si>
   <si>
-    <t>No Rek Penerima</t>
-  </si>
-  <si>
-    <t>Bank Penerima</t>
-  </si>
-  <si>
     <t>Nama Penerima</t>
   </si>
   <si>
@@ -1771,9 +1765,6 @@
     <t>SELECT * FROM dm_customer.customer_icons WHERE cust_status = 'AKTIF';</t>
   </si>
   <si>
-    <t>Tampilkan nasabah aktif</t>
-  </si>
-  <si>
     <t>prd_db_sbx_ind</t>
   </si>
   <si>
@@ -1912,10 +1903,19 @@
     <t>Tanggal Transaksi Data, digunakan untuk filter tanggal, bulan, tahun</t>
   </si>
   <si>
-    <t>Aktivitas Cash out</t>
-  </si>
-  <si>
     <t>SELECT * FROM dm_transaction.trxchannel WHERE destination_bankname &lt;&gt; 'BANK NEGARA INDONESIA';</t>
+  </si>
+  <si>
+    <t>Aktivitas cashout / cash out</t>
+  </si>
+  <si>
+    <t>Nasabah aktif</t>
+  </si>
+  <si>
+    <t>Nama Bank Penerima / Nama Bank Tujuan</t>
+  </si>
+  <si>
+    <t>Nomor Rekening Penerima</t>
   </si>
 </sst>
 </file>
@@ -2332,7 +2332,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2343,7 +2343,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2354,18 +2354,18 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B6" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>10</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>10</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>10</v>
@@ -2735,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>346</v>
@@ -2992,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>10</v>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>359</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3041,7 +3041,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>360</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3061,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3081,7 +3081,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3101,7 +3101,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3121,7 +3121,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3141,7 +3141,7 @@
         <v>10</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3161,7 +3161,7 @@
         <v>10</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3181,7 +3181,7 @@
         <v>10</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3204,7 +3204,7 @@
         <v>10</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3220,11 +3220,14 @@
       <c r="D40" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G40" s="4" t="s">
+        <v>585</v>
+      </c>
       <c r="H40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3244,7 +3247,7 @@
         <v>10</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3284,7 +3287,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3304,7 +3307,7 @@
         <v>10</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3324,7 +3327,7 @@
         <v>10</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3347,7 +3350,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3367,7 +3370,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3387,7 +3390,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3407,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3427,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3447,7 +3450,7 @@
         <v>10</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3464,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3490,7 +3493,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3510,7 +3513,7 @@
         <v>10</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3530,7 +3533,7 @@
         <v>10</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3550,7 +3553,7 @@
         <v>10</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3570,7 +3573,7 @@
         <v>10</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3590,7 +3593,7 @@
         <v>10</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3610,7 +3613,7 @@
         <v>10</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3630,7 +3633,7 @@
         <v>10</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3650,7 +3653,7 @@
         <v>10</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3670,7 +3673,7 @@
         <v>10</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3690,7 +3693,7 @@
         <v>10</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3710,7 +3713,7 @@
         <v>10</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3730,7 +3733,7 @@
         <v>10</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3750,7 +3753,7 @@
         <v>10</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3773,7 +3776,7 @@
         <v>10</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3793,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3813,7 +3816,7 @@
         <v>10</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3833,7 +3836,7 @@
         <v>10</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3853,7 +3856,7 @@
         <v>10</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3873,7 +3876,7 @@
         <v>10</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3893,7 +3896,7 @@
         <v>10</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3913,7 +3916,7 @@
         <v>10</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3933,7 +3936,7 @@
         <v>10</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3953,7 +3956,7 @@
         <v>10</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3973,7 +3976,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3993,7 +3996,7 @@
         <v>10</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4013,7 +4016,7 @@
         <v>10</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4033,7 +4036,7 @@
         <v>10</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4053,7 +4056,7 @@
         <v>10</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4107,7 +4110,7 @@
         <v>10</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4178,7 +4181,7 @@
         <v>10</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4198,7 +4201,7 @@
         <v>10</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4218,7 +4221,7 @@
         <v>10</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4238,7 +4241,7 @@
         <v>10</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4258,7 +4261,7 @@
         <v>10</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4278,7 +4281,7 @@
         <v>10</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4298,7 +4301,7 @@
         <v>10</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4318,7 +4321,7 @@
         <v>10</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4338,7 +4341,7 @@
         <v>10</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4358,7 +4361,7 @@
         <v>10</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4378,7 +4381,7 @@
         <v>10</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4398,7 +4401,7 @@
         <v>10</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4418,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4455,7 +4458,7 @@
         <v>10</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4475,7 +4478,7 @@
         <v>10</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4498,7 +4501,7 @@
         <v>10</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4558,7 +4561,7 @@
         <v>10</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4612,7 +4615,7 @@
         <v>10</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4632,7 +4635,7 @@
         <v>10</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4652,7 +4655,7 @@
         <v>10</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4672,7 +4675,7 @@
         <v>10</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4692,7 +4695,7 @@
         <v>10</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4712,7 +4715,7 @@
         <v>10</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4732,7 +4735,7 @@
         <v>10</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4752,7 +4755,7 @@
         <v>10</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4772,7 +4775,7 @@
         <v>10</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4792,7 +4795,7 @@
         <v>10</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4812,7 +4815,7 @@
         <v>10</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4832,7 +4835,7 @@
         <v>10</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4852,7 +4855,7 @@
         <v>10</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4872,7 +4875,7 @@
         <v>10</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4892,7 +4895,7 @@
         <v>10</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4912,7 +4915,7 @@
         <v>10</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4932,7 +4935,7 @@
         <v>10</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4952,7 +4955,7 @@
         <v>10</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4972,7 +4975,7 @@
         <v>10</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4992,7 +4995,7 @@
         <v>10</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5012,7 +5015,7 @@
         <v>10</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5032,7 +5035,7 @@
         <v>10</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5052,7 +5055,7 @@
         <v>10</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5072,7 +5075,7 @@
         <v>10</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5092,7 +5095,7 @@
         <v>10</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5112,7 +5115,7 @@
         <v>10</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5132,7 +5135,7 @@
         <v>10</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5152,7 +5155,7 @@
         <v>10</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5172,7 +5175,7 @@
         <v>10</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5192,7 +5195,7 @@
         <v>10</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5212,7 +5215,7 @@
         <v>10</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5229,13 +5232,13 @@
         <v>0</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5255,7 +5258,7 @@
         <v>10</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5275,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5295,7 +5298,7 @@
         <v>10</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5315,7 +5318,7 @@
         <v>10</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5335,7 +5338,7 @@
         <v>10</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5355,7 +5358,7 @@
         <v>10</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5375,7 +5378,7 @@
         <v>10</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5395,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5415,7 +5418,7 @@
         <v>10</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5435,7 +5438,7 @@
         <v>10</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5455,7 +5458,7 @@
         <v>10</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5475,7 +5478,7 @@
         <v>10</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5495,7 +5498,7 @@
         <v>10</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5515,7 +5518,7 @@
         <v>10</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5535,7 +5538,7 @@
         <v>10</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5555,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5575,7 +5578,7 @@
         <v>10</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5595,7 +5598,7 @@
         <v>10</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5615,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5635,7 +5638,7 @@
         <v>10</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5655,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5675,7 +5678,7 @@
         <v>10</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5695,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5715,7 +5718,7 @@
         <v>10</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5735,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5758,7 +5761,7 @@
         <v>10</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5778,7 +5781,7 @@
         <v>10</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5798,7 +5801,7 @@
         <v>10</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5818,7 +5821,7 @@
         <v>10</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5838,7 +5841,7 @@
         <v>10</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5858,7 +5861,7 @@
         <v>10</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5878,7 +5881,7 @@
         <v>10</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5898,7 +5901,7 @@
         <v>10</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5918,7 +5921,7 @@
         <v>10</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5938,7 +5941,7 @@
         <v>10</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5958,7 +5961,7 @@
         <v>10</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5978,7 +5981,7 @@
         <v>10</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6001,7 +6004,7 @@
         <v>10</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6024,7 +6027,7 @@
         <v>10</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6047,7 +6050,7 @@
         <v>10</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6070,7 +6073,7 @@
         <v>10</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6093,7 +6096,7 @@
         <v>10</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6113,7 +6116,7 @@
         <v>10</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6133,7 +6136,7 @@
         <v>10</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6153,7 +6156,7 @@
         <v>10</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6173,7 +6176,7 @@
         <v>10</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6193,7 +6196,7 @@
         <v>10</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6213,7 +6216,7 @@
         <v>10</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6233,7 +6236,7 @@
         <v>10</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6253,7 +6256,7 @@
         <v>10</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6273,7 +6276,7 @@
         <v>10</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6293,7 +6296,7 @@
         <v>10</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6313,7 +6316,7 @@
         <v>10</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6333,7 +6336,7 @@
         <v>10</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6353,7 +6356,7 @@
         <v>10</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6373,7 +6376,7 @@
         <v>10</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6393,7 +6396,7 @@
         <v>10</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6413,7 +6416,7 @@
         <v>10</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6433,7 +6436,7 @@
         <v>10</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6453,7 +6456,7 @@
         <v>10</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6476,7 +6479,7 @@
         <v>10</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6499,7 +6502,7 @@
         <v>10</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6522,7 +6525,7 @@
         <v>10</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6545,7 +6548,7 @@
         <v>10</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6568,7 +6571,7 @@
         <v>10</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6591,7 +6594,7 @@
         <v>10</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6614,7 +6617,7 @@
         <v>10</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6637,7 +6640,7 @@
         <v>10</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6660,7 +6663,7 @@
         <v>10</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6683,7 +6686,7 @@
         <v>10</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6703,7 +6706,7 @@
         <v>10</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6723,7 +6726,7 @@
         <v>10</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6743,7 +6746,7 @@
         <v>10</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6766,7 +6769,7 @@
         <v>10</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6789,7 +6792,7 @@
         <v>10</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6812,7 +6815,7 @@
         <v>10</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6832,7 +6835,7 @@
         <v>10</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6852,7 +6855,7 @@
         <v>10</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6872,7 +6875,7 @@
         <v>10</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6892,7 +6895,7 @@
         <v>10</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6912,7 +6915,7 @@
         <v>10</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6932,7 +6935,7 @@
         <v>10</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6952,7 +6955,7 @@
         <v>10</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6972,7 +6975,7 @@
         <v>10</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6992,7 +6995,7 @@
         <v>10</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7012,7 +7015,7 @@
         <v>10</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7032,7 +7035,7 @@
         <v>10</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7055,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7078,7 +7081,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7101,7 +7104,7 @@
         <v>10</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7124,7 +7127,7 @@
         <v>10</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7147,7 +7150,7 @@
         <v>10</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7170,7 +7173,7 @@
         <v>10</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7193,7 +7196,7 @@
         <v>10</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7216,7 +7219,7 @@
         <v>10</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7236,7 +7239,7 @@
         <v>10</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7259,7 +7262,7 @@
         <v>10</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7279,7 +7282,7 @@
         <v>10</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7302,7 +7305,7 @@
         <v>10</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7322,7 +7325,7 @@
         <v>10</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7342,7 +7345,7 @@
         <v>10</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7359,13 +7362,13 @@
         <v>0</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7385,7 +7388,7 @@
         <v>10</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7405,7 +7408,7 @@
         <v>10</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7425,7 +7428,7 @@
         <v>10</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7445,7 +7448,7 @@
         <v>10</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7465,7 +7468,7 @@
         <v>10</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7485,7 +7488,7 @@
         <v>10</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7505,7 +7508,7 @@
         <v>10</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7525,7 +7528,7 @@
         <v>10</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7545,7 +7548,7 @@
         <v>10</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7565,7 +7568,7 @@
         <v>10</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7585,7 +7588,7 @@
         <v>10</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7605,7 +7608,7 @@
         <v>10</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7625,7 +7628,7 @@
         <v>10</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7645,7 +7648,7 @@
         <v>10</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7665,7 +7668,7 @@
         <v>10</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7685,7 +7688,7 @@
         <v>10</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7705,7 +7708,7 @@
         <v>10</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7725,7 +7728,7 @@
         <v>10</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7745,7 +7748,7 @@
         <v>10</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7765,7 +7768,7 @@
         <v>10</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7785,7 +7788,7 @@
         <v>10</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7805,7 +7808,7 @@
         <v>10</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7825,7 +7828,7 @@
         <v>10</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7845,7 +7848,7 @@
         <v>10</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7865,7 +7868,7 @@
         <v>10</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7885,7 +7888,7 @@
         <v>10</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7905,7 +7908,7 @@
         <v>10</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7925,7 +7928,7 @@
         <v>10</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7945,7 +7948,7 @@
         <v>10</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7965,7 +7968,7 @@
         <v>10</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7985,7 +7988,7 @@
         <v>10</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8005,7 +8008,7 @@
         <v>10</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8025,7 +8028,7 @@
         <v>10</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8045,7 +8048,7 @@
         <v>10</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8065,7 +8068,7 @@
         <v>10</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8085,7 +8088,7 @@
         <v>10</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8105,7 +8108,7 @@
         <v>10</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8125,7 +8128,7 @@
         <v>10</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8145,7 +8148,7 @@
         <v>10</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8165,7 +8168,7 @@
         <v>10</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8185,7 +8188,7 @@
         <v>10</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8205,7 +8208,7 @@
         <v>10</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8225,7 +8228,7 @@
         <v>10</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8245,7 +8248,7 @@
         <v>10</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8265,7 +8268,7 @@
         <v>10</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8285,7 +8288,7 @@
         <v>10</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8305,7 +8308,7 @@
         <v>10</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8325,7 +8328,7 @@
         <v>10</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8345,7 +8348,7 @@
         <v>10</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8365,7 +8368,7 @@
         <v>10</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8385,7 +8388,7 @@
         <v>10</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8405,7 +8408,7 @@
         <v>10</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8425,7 +8428,7 @@
         <v>10</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8448,7 +8451,7 @@
         <v>10</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8471,7 +8474,7 @@
         <v>10</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8494,7 +8497,7 @@
         <v>10</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8517,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8540,7 +8543,7 @@
         <v>10</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8563,7 +8566,7 @@
         <v>10</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8586,7 +8589,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8609,7 +8612,7 @@
         <v>10</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8632,7 +8635,7 @@
         <v>10</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8655,7 +8658,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8678,7 +8681,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8701,7 +8704,7 @@
         <v>10</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8724,7 +8727,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8747,7 +8750,7 @@
         <v>10</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8770,7 +8773,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8793,7 +8796,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8816,7 +8819,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8836,7 +8839,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8856,7 +8859,7 @@
         <v>10</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8876,7 +8879,7 @@
         <v>10</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8896,7 +8899,7 @@
         <v>10</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8916,7 +8919,7 @@
         <v>10</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8936,7 +8939,7 @@
         <v>10</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8956,7 +8959,7 @@
         <v>10</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8976,7 +8979,7 @@
         <v>10</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8996,7 +8999,7 @@
         <v>10</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9016,7 +9019,7 @@
         <v>10</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9036,7 +9039,7 @@
         <v>10</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9059,7 +9062,7 @@
         <v>10</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9082,7 +9085,7 @@
         <v>10</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9105,7 +9108,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9125,7 +9128,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9145,7 +9148,7 @@
         <v>10</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9165,7 +9168,7 @@
         <v>10</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9185,7 +9188,7 @@
         <v>10</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9205,7 +9208,7 @@
         <v>10</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9228,7 +9231,7 @@
         <v>10</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9251,7 +9254,7 @@
         <v>10</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9271,7 +9274,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9291,7 +9294,7 @@
         <v>10</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9314,7 +9317,7 @@
         <v>10</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9337,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9357,12 +9360,12 @@
         <v>10</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B340" s="4" t="s">
         <v>331</v>
@@ -9374,18 +9377,18 @@
         <v>0</v>
       </c>
       <c r="F340" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H340" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B341" s="4" t="s">
         <v>332</v>
@@ -9400,12 +9403,12 @@
         <v>10</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B342" s="4" t="s">
         <v>149</v>
@@ -9420,12 +9423,12 @@
         <v>10</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B343" s="4" t="s">
         <v>31</v>
@@ -9443,7 +9446,7 @@
         <v>10</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -9489,10 +9492,10 @@
         <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9503,10 +9506,10 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9517,10 +9520,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E4" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9531,10 +9534,10 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9545,13 +9548,13 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9562,10 +9565,10 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9576,10 +9579,10 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E8" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9590,10 +9593,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E9" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9604,10 +9607,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E10" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9618,10 +9621,10 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E11" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9632,10 +9635,10 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E12" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9646,10 +9649,10 @@
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E13" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9660,10 +9663,10 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E14" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9674,10 +9677,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E15" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9688,10 +9691,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E16" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9702,10 +9705,10 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E17" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9716,10 +9719,10 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E18" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -9749,10 +9752,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>581</v>
+        <v>627</v>
       </c>
       <c r="B2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -9760,10 +9763,10 @@
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79458033-870F-9147-A2CA-A0DAE6540A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79458033-870F-9147-A2CA-A0DAE6540A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F448F407-F0F7-414C-AF7C-83BC65D9BE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="33720" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="Golden_Queries" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$J$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$J$344</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="704">
   <si>
     <t>Table Name</t>
   </si>
@@ -1030,12 +1030,6 @@
     <t>Waktu Transaksi</t>
   </si>
   <si>
-    <t>CIF Key nasabah (ID Nasabah)</t>
-  </si>
-  <si>
-    <t>No rekening Nasabah</t>
-  </si>
-  <si>
     <t>Bank Pengirim</t>
   </si>
   <si>
@@ -1195,33 +1189,12 @@
     <t>Flag Emerald</t>
   </si>
   <si>
-    <t>Kode Kelamin Nasabah</t>
-  </si>
-  <si>
-    <t>Tempat Lahir Nasabah</t>
-  </si>
-  <si>
-    <t>Tanggal Lahir Nasabah</t>
-  </si>
-  <si>
-    <t>Umur Nasabah</t>
-  </si>
-  <si>
-    <t>Agama Nasabah</t>
-  </si>
-  <si>
-    <t>Kode Negara Nasabah</t>
-  </si>
-  <si>
     <t>Kode Domisili</t>
   </si>
   <si>
     <t>Type ID</t>
   </si>
   <si>
-    <t>Nomor KTP Nasabah</t>
-  </si>
-  <si>
     <t>Tanggal Pengeluaran KTP</t>
   </si>
   <si>
@@ -1234,57 +1207,9 @@
     <t>Nama Gadis Ibu Kandung</t>
   </si>
   <si>
-    <t>Segment Nasabah</t>
-  </si>
-  <si>
-    <t>Kode Menikah Nasabah</t>
-  </si>
-  <si>
-    <t>Edukasi Nasabah</t>
-  </si>
-  <si>
-    <t>Hobby Nasabah</t>
-  </si>
-  <si>
-    <t>Email Nasabah</t>
-  </si>
-  <si>
-    <t>No Fax Nasabah</t>
-  </si>
-  <si>
-    <t>Alamat Nasabah (Jalan)</t>
-  </si>
-  <si>
-    <t>Alamat Nasabah (RT/RW)</t>
-  </si>
-  <si>
-    <t>Alamat Nasabah (Keluarahan)</t>
-  </si>
-  <si>
-    <t>Alamat Nasabah (Kecamatan)</t>
-  </si>
-  <si>
-    <t>Kode Pos Nasabah</t>
-  </si>
-  <si>
-    <t>Kota Nasabah</t>
-  </si>
-  <si>
-    <t>Alamat Kantor 1 Nasabah</t>
-  </si>
-  <si>
-    <t>Alamat Kantor 2 Nasabah</t>
-  </si>
-  <si>
     <t>Kode Pos Kantor</t>
   </si>
   <si>
-    <t>Pekerjaan Nasabah</t>
-  </si>
-  <si>
-    <t>Tempat Bekerja Nasabah</t>
-  </si>
-  <si>
     <t>Flag Pembisnis</t>
   </si>
   <si>
@@ -1303,459 +1228,15 @@
     <t>Channel Pembuka CIF</t>
   </si>
   <si>
-    <t>Segment Nasabah ( Divisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Sub Segment Nasabah</t>
-  </si>
-  <si>
-    <t>Dir Owner Nasabah</t>
-  </si>
-  <si>
-    <t>Nasabah</t>
-  </si>
-  <si>
-    <t>Sentra Code Nasabah</t>
-  </si>
-  <si>
-    <t>Channel Type Nasabah</t>
-  </si>
-  <si>
-    <t>Segment Maverick Nasabah</t>
-  </si>
-  <si>
-    <t>Ntb Nasabah ( Etbisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Rm Nasabah ( Danaisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Rm Nasabah ( Kreditisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Relation Nasabah ( Withisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Bi Nasabah ( Ownerisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Corp Nasabah ( Groupisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cif Nasabah ( Rmisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Terrorism Nasabah ( Relatedisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Campaign Flag Nasabah</t>
-  </si>
-  <si>
-    <t>Share Nasabah ( Dataisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Esg Flag Nasabah</t>
-  </si>
-  <si>
-    <t>Xpora Location Nasabah</t>
-  </si>
-  <si>
-    <t>Exporter Type Nasabah</t>
-  </si>
-  <si>
-    <t>Cust Nasabah ( User_Defineisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Sector Economi Nasabah</t>
-  </si>
-  <si>
-    <t>Consent Marketing Nasabah</t>
-  </si>
-  <si>
-    <t>Consent Nasabah ( Dataisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cust Nasabah ( Statusisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Consent Nasabah ( Marketingisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Consent Nasabah ( Data_Sharingisi Pemegang Nasabah)</t>
-  </si>
-  <si>
     <t>Channel Nasabah ( Consentisi Pemegang Nasabah)</t>
   </si>
   <si>
     <t>Channel Nasabah ( Consent_Nameisi Pemegang Nasabah)</t>
   </si>
   <si>
-    <t>Consent Date Nasabah</t>
-  </si>
-  <si>
-    <t>Account Number Nasabah</t>
-  </si>
-  <si>
     <t>Cif Key Nasabah</t>
   </si>
   <si>
-    <t>Cust Nasabah ( Typeisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cust Type Nasabah</t>
-  </si>
-  <si>
-    <t>Cif Nasabah ( Open_Regionisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cif Nasabah ( Openisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cif Nasabah ( Open_Branchisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Nama Nasabah Nasabah</t>
-  </si>
-  <si>
-    <t>Company Name Nasabah</t>
-  </si>
-  <si>
-    <t>Flag Nasabah ( Custisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Flag Nasabah ( Cifisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Pekerjaan Nasabah ( Pekisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Account Type Nasabah</t>
-  </si>
-  <si>
-    <t>Sub Category Nasabah</t>
-  </si>
-  <si>
-    <t>Product Name Nasabah</t>
-  </si>
-  <si>
-    <t>Currency Type Nasabah</t>
-  </si>
-  <si>
-    <t>Acct Nasabah ( Open_Regionisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Acct Nasabah ( Openisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Acct Nasabah ( Open_Branchisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Acct Nasabah ( Open_Subbranchisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Acct Nasabah ( Renewalisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Acct Nasabah ( Closeisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Gl Nasabah ( Accountisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Gl Description Nasabah</t>
-  </si>
-  <si>
-    <t>Market Nasabah ( Segmentisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Account Status Nasabah</t>
-  </si>
-  <si>
-    <t>Account Nasabah ( Statusisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Org Term Nasabah</t>
-  </si>
-  <si>
-    <t>Org Nasabah ( Termisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Maturity Date Nasabah</t>
-  </si>
-  <si>
-    <t>Flag Rate Nasabah</t>
-  </si>
-  <si>
-    <t>Cur Nasabah ( Bookisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cur Nasabah ( Book_Balisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Amortisi Idr Nasabah</t>
-  </si>
-  <si>
-    <t>Ending Balance Nasabah</t>
-  </si>
-  <si>
-    <t>Affiliated Nasabah ( Acctisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Open Nasabah ( Acctisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Src Nasabah ( Ofisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Debtor Flag Nasabah</t>
-  </si>
-  <si>
-    <t>Flag Nasabah ( Acctisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Dhe Flag Nasabah</t>
-  </si>
-  <si>
-    <t>Flag Kategori Nasabah</t>
-  </si>
-  <si>
-    <t>Flag Nasabah ( Kategoriisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Flag Product Nasabah</t>
-  </si>
-  <si>
-    <t>Group Product Nasabah</t>
-  </si>
-  <si>
-    <t>Channel Nasabah ( Ownerisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Product Nasabah ( Divisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cab Sentra Nasabah</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Book_Balisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Book_Bal_Mtdisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Book_Bal_Ytdisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cur Nasabah ( Book_Bal_Idrisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Flag Nasabah ( Rekeningisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Flag Nasabah ( Tabungan_Regulerisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Source Data Nasabah</t>
-  </si>
-  <si>
-    <t>Ie Daily Nasabah</t>
-  </si>
-  <si>
-    <t>Ie Mtd Nasabah</t>
-  </si>
-  <si>
-    <t>Ie Nasabah ( Pmsisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Teller Id Nasabah</t>
-  </si>
-  <si>
-    <t>Teller Name Nasabah</t>
-  </si>
-  <si>
-    <t>Rm Nasabah ( Fundingisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>User Nasabah ( Defineisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Product Nasabah ( Dpkisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Channel Nasabah ( Openisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Jenis Nasabah ( Badanisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Ending Nasabah ( Balanceisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Ending Nasabah ( Balance_Idrisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Saldo Dsra Nasabah</t>
-  </si>
-  <si>
-    <t>Saldo Dspa Nasabah</t>
-  </si>
-  <si>
-    <t>Lt Nasabah ( Trxisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Blocked Balance Nasabah</t>
-  </si>
-  <si>
-    <t>As Nasabah ( Ofisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Mdm Id Nasabah</t>
-  </si>
-  <si>
-    <t>Account Nasabah ( Numberisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Sentra Name Nasabah</t>
-  </si>
-  <si>
-    <t>Remap Sentra Nasabah</t>
-  </si>
-  <si>
-    <t>Loan Nasabah ( Purposeisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Economic Nasabah ( Sectorisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Pk Nasabah ( Akhirisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Pk Nasabah ( Awalisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Lst Nasabah ( Mntisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Restructuring Cd Nasabah</t>
-  </si>
-  <si>
-    <t>Grace Nasabah ( Periodeisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Credit Nasabah ( Applicationisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Approve Date Nasabah</t>
-  </si>
-  <si>
-    <t>Loan Nasabah ( Approvalisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Funding Type Nasabah</t>
-  </si>
-  <si>
-    <t>Next Nasabah ( Loan_Reviewisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Settlement Date Nasabah</t>
-  </si>
-  <si>
-    <t>Rm Code Nasabah</t>
-  </si>
-  <si>
-    <t>Loan Nasabah ( Principalisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Baki Debet Nasabah</t>
-  </si>
-  <si>
-    <t>Psak Nasabah ( Adjisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Loan_Principal_Psakisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Max Credit Nasabah</t>
-  </si>
-  <si>
-    <t>Commitment Bal Nasabah</t>
-  </si>
-  <si>
-    <t>Commitment Nasabah ( Balisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Org Nasabah ( Creditisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Add Nasabah ( Creditisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Loan_Principalisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Loan_Principal_Ytdisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Avg Nasabah ( Loan_Principal_Mtdisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Angsuran Bunga Nasabah</t>
-  </si>
-  <si>
-    <t>Angsuran Pokok Nasabah</t>
-  </si>
-  <si>
-    <t>Del Nasabah ( Curisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Last Nasabah ( Arrearsisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Worst Collectibility Nasabah</t>
-  </si>
-  <si>
-    <t>Collectibility Nasabah ( Bilisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Written Nasabah ( Offisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Business Nasabah ( Divisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Output L Nasabah</t>
-  </si>
-  <si>
-    <t>Lst Nasabah ( Worstisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Outstanding Nasabah ( Ingisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Channel Nasabah ( Typeisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Dspa Balance Nasabah</t>
-  </si>
-  <si>
-    <t>Dsra Balance Nasabah</t>
-  </si>
-  <si>
-    <t>Ii Daily Nasabah</t>
-  </si>
-  <si>
-    <t>Ii Monthly Nasabah</t>
-  </si>
-  <si>
-    <t>Short Name Nasabah</t>
-  </si>
-  <si>
-    <t>Cif Principal Nasabah</t>
-  </si>
-  <si>
-    <t>Group Principal Nasabah</t>
-  </si>
-  <si>
     <t>customer_icons.cif_key</t>
   </si>
   <si>
@@ -1897,9 +1378,6 @@
     <t>Wonder</t>
   </si>
   <si>
-    <t>Nilai Transaksi / Amount</t>
-  </si>
-  <si>
     <t>Tanggal Transaksi Data, digunakan untuk filter tanggal, bulan, tahun</t>
   </si>
   <si>
@@ -1912,10 +1390,754 @@
     <t>Nasabah aktif</t>
   </si>
   <si>
-    <t>Nama Bank Penerima / Nama Bank Tujuan</t>
-  </si>
-  <si>
-    <t>Nomor Rekening Penerima</t>
+    <t>Nilai Transaksi</t>
+  </si>
+  <si>
+    <t>No Rek Penerima</t>
+  </si>
+  <si>
+    <t>Bank Penerima</t>
+  </si>
+  <si>
+    <t>Account Opening Region Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Opening Region </t>
+  </si>
+  <si>
+    <t>Account Opening Branch Code</t>
+  </si>
+  <si>
+    <t>Account Opening Branch</t>
+  </si>
+  <si>
+    <t>Account Opening Subbranch Code</t>
+  </si>
+  <si>
+    <t>Acoount Opening Subbranch</t>
+  </si>
+  <si>
+    <t>Account Open Date</t>
+  </si>
+  <si>
+    <t>Account Renewal Date</t>
+  </si>
+  <si>
+    <t>Tanggal penutupan account</t>
+  </si>
+  <si>
+    <t>Flag Burekol</t>
+  </si>
+  <si>
+    <t>CUR BOOK BAL MTD</t>
+  </si>
+  <si>
+    <t>CUR Book bal idr MTD</t>
+  </si>
+  <si>
+    <t>Saldo buku berjalan untuk periode Year-to-Date (YTD).</t>
+  </si>
+  <si>
+    <t>Saldo buku YTD yang telah dikonversi ke Rupiah (IDR).</t>
+  </si>
+  <si>
+    <t>Saldo buku untuk periode/perbandingan Year-on-Year (YoY).</t>
+  </si>
+  <si>
+    <t>Saldo buku YoY yang telah dikonversi ke Rupiah.</t>
+  </si>
+  <si>
+    <t>Penanda apakah rekening termasuk rekening bantuan sosial (bansos).</t>
+  </si>
+  <si>
+    <t>Penanda apakah rekening termasuk tabungan reguler berbayar.</t>
+  </si>
+  <si>
+    <t>Sumber atau sistem asal data.</t>
+  </si>
+  <si>
+    <t>Interest Expense atau beban bunga harian.</t>
+  </si>
+  <si>
+    <t>Interest Expense kumulatif Month-to-Date (MTD).</t>
+  </si>
+  <si>
+    <t>Interest Expense berdasarkan proses/sistem PMS pada posisi End-of-Month (EOM).</t>
+  </si>
+  <si>
+    <t>ID teller yang terkait dengan rekening/transaksi.</t>
+  </si>
+  <si>
+    <t>Nama teller yang terkait dengan rekening/transaksi.</t>
+  </si>
+  <si>
+    <t>Kode Relationship Manager yang menangani funding.</t>
+  </si>
+  <si>
+    <t>Nama Relationship Manager yang menangani funding.</t>
+  </si>
+  <si>
+    <t>Kode klasifikasi tambahan yang didefinisikan oleh user/sistem.</t>
+  </si>
+  <si>
+    <t>Klasifikasi produk Dana Pihak Ketiga (DPK) level 1.</t>
+  </si>
+  <si>
+    <t>Klasifikasi produk DPK level 2.</t>
+  </si>
+  <si>
+    <t>Klasifikasi produk DPK level 3.</t>
+  </si>
+  <si>
+    <t>Alasan penutupan rekening.</t>
+  </si>
+  <si>
+    <t>Channel yang digunakan untuk membuka rekening.</t>
+  </si>
+  <si>
+    <t>Jenis atau bentuk badan hukum nasabah/perusahaan.</t>
+  </si>
+  <si>
+    <t>Saldo akhir untuk periode Month-to-Date.</t>
+  </si>
+  <si>
+    <t>Saldo akhir MTD yang telah dikonversi ke Rupiah.</t>
+  </si>
+  <si>
+    <t>Saldo akhir untuk periode Year-to-Date.</t>
+  </si>
+  <si>
+    <t>Saldo akhir YTD yang telah dikonversi ke Rupiah.</t>
+  </si>
+  <si>
+    <t>Saldo akhir untuk periode/perbandingan Year-on-Year.</t>
+  </si>
+  <si>
+    <t>Saldo akhir YoY yang telah dikonversi ke Rupiah.</t>
+  </si>
+  <si>
+    <t>Saldo Debt Service Reserve Account (DSRA) atau rekening cadangan pembayaran kewajiban utang.</t>
+  </si>
+  <si>
+    <t>Saldo DSPA sesuai definisi rekening/internal sistem bank.</t>
+  </si>
+  <si>
+    <t>Tanggal transaksi terakhir (last transaction date).</t>
+  </si>
+  <si>
+    <t>Nilai saldo yang diblokir atau tidak dapat digunakan.</t>
+  </si>
+  <si>
+    <t>Hasil mapping/mirror dari pemilik channel.</t>
+  </si>
+  <si>
+    <t>Tanggal posisi atau snapshot data.</t>
+  </si>
+  <si>
+    <t>ID nasabah/entity pada sistem Master Data Management.</t>
+  </si>
+  <si>
+    <t>Nomor rekening.</t>
+  </si>
+  <si>
+    <t>Kunci/identifier Customer Information File (CIF).</t>
+  </si>
+  <si>
+    <t>Kode jenis nasabah.</t>
+  </si>
+  <si>
+    <t>Deskripsi jenis nasabah, misalnya individu atau badan usaha.</t>
+  </si>
+  <si>
+    <t>Kode region tempat CIF dibuka.</t>
+  </si>
+  <si>
+    <t>Nama region tempat CIF dibuka.</t>
+  </si>
+  <si>
+    <t>Kode cabang tempat CIF dibuka.</t>
+  </si>
+  <si>
+    <t>Nama cabang tempat CIF dibuka.</t>
+  </si>
+  <si>
+    <t>Tanggal CIF dibuat atau dibuka.</t>
+  </si>
+  <si>
+    <t>Nama nasabah.</t>
+  </si>
+  <si>
+    <t>Penanda apakah CIF terkait proses/produk Burekol atau buka rekening kolektif.</t>
+  </si>
+  <si>
+    <t>Jenis atau tipe rekening.</t>
+  </si>
+  <si>
+    <t>Subkategori produk/rekening.</t>
+  </si>
+  <si>
+    <t>Nama produk perbankan.</t>
+  </si>
+  <si>
+    <t>Mata uang rekening, misalnya IDR, USD, SGD, dan lainnya.</t>
+  </si>
+  <si>
+    <t>Jenis/kelompok mata uang, misalnya lokal dan valuta asing.</t>
+  </si>
+  <si>
+    <t>Kode region tempat rekening dibuka.</t>
+  </si>
+  <si>
+    <t>Nama region tempat rekening dibuka.</t>
+  </si>
+  <si>
+    <t>Kode cabang tempat rekening dibuka.</t>
+  </si>
+  <si>
+    <t>Nama cabang tempat rekening dibuka.</t>
+  </si>
+  <si>
+    <t>Kode sub-branch/unit tempat rekening dibuka.</t>
+  </si>
+  <si>
+    <t>Nama sub-branch/unit tempat rekening dibuka.</t>
+  </si>
+  <si>
+    <t>Tanggal pembukaan rekening.</t>
+  </si>
+  <si>
+    <t>Tanggal penutupan rekening.</t>
+  </si>
+  <si>
+    <t>Kode atau ID General Ledger yang terkait dengan rekening.</t>
+  </si>
+  <si>
+    <t>Deskripsi akun General Ledger.</t>
+  </si>
+  <si>
+    <t>Kode status rekening.</t>
+  </si>
+  <si>
+    <t>Deskripsi status rekening, seperti aktif, tutup, dormant, dan sebagainya.</t>
+  </si>
+  <si>
+    <t>Kode sentra atau unit bisnis.</t>
+  </si>
+  <si>
+    <t>Hasil pemetaan ulang sentra ke struktur/klasifikasi tertentu.</t>
+  </si>
+  <si>
+    <t>Kode tujuan penggunaan kredit/pinjaman.</t>
+  </si>
+  <si>
+    <t>Tanggal akhir Perjanjian Kredit (PK).</t>
+  </si>
+  <si>
+    <t>Tanggal awal Perjanjian Kredit (PK).</t>
+  </si>
+  <si>
+    <t>Tanggal maintenance/perubahan terakhir sesuai sistem sumber.</t>
+  </si>
+  <si>
+    <t>Kode yang menunjukkan status atau jenis restrukturisasi kredit.</t>
+  </si>
+  <si>
+    <t>Jangka waktu masa tenggang (grace period) kredit.</t>
+  </si>
+  <si>
+    <t>Nomor aplikasi/pengajuan kredit.</t>
+  </si>
+  <si>
+    <t>Tanggal persetujuan kredit.</t>
+  </si>
+  <si>
+    <t>Nomor persetujuan kredit.</t>
+  </si>
+  <si>
+    <t>Jenis atau kategori sumber dana/funding.</t>
+  </si>
+  <si>
+    <t>Tanggal review kredit berikutnya.</t>
+  </si>
+  <si>
+    <t>Tanggal penyelesaian atau pelunasan fasilitas/kewajiban.</t>
+  </si>
+  <si>
+    <t>Tanggal jatuh tempo fasilitas kredit/rekening.</t>
+  </si>
+  <si>
+    <t>Jangka waktu awal/original term fasilitas kredit.</t>
+  </si>
+  <si>
+    <t>Satuan atau multiplier yang digunakan pada original term, misalnya hari/bulan/tahun.</t>
+  </si>
+  <si>
+    <t>Nilai pokok pinjaman dalam Rupiah.</t>
+  </si>
+  <si>
+    <t>Saldo pokok kredit yang masih terutang/outstanding.</t>
+  </si>
+  <si>
+    <t>Nilai penyesuaian PSAK dengan kategori/komponen DMA sesuai definisi internal.</t>
+  </si>
+  <si>
+    <t>Nilai penyesuaian PSAK dengan kategori/komponen ACC sesuai definisi internal.</t>
+  </si>
+  <si>
+    <t>Rata-rata pokok pinjaman berdasarkan PSAK untuk periode Month-to-Date.</t>
+  </si>
+  <si>
+    <t>Rata-rata pokok pinjaman berdasarkan PSAK untuk periode Year-to-Date.</t>
+  </si>
+  <si>
+    <t>Batas/nilai maksimum kredit yang diberikan.</t>
+  </si>
+  <si>
+    <t>Saldo komitmen fasilitas kredit dalam mata uang asli.</t>
+  </si>
+  <si>
+    <t>Saldo komitmen fasilitas kredit yang dikonversi ke Rupiah.</t>
+  </si>
+  <si>
+    <t>Limit kredit awal/original credit limit.</t>
+  </si>
+  <si>
+    <t>Tambahan limit kredit yang diberikan.</t>
+  </si>
+  <si>
+    <t>Rata-rata saldo pokok pinjaman Year-to-Date dalam mata uang asli.</t>
+  </si>
+  <si>
+    <t>Rata-rata saldo pokok pinjaman YTD dalam Rupiah.</t>
+  </si>
+  <si>
+    <t>Rata-rata saldo pokok pinjaman Month-to-Date dalam mata uang asli.</t>
+  </si>
+  <si>
+    <t>Rata-rata saldo pokok pinjaman MTD dalam Rupiah.</t>
+  </si>
+  <si>
+    <t>Nilai angsuran atau pembayaran bunga.</t>
+  </si>
+  <si>
+    <t>Nilai angsuran atau pembayaran pokok pinjaman.</t>
+  </si>
+  <si>
+    <t>Jumlah hari keterlambatan/delinquency saat ini.</t>
+  </si>
+  <si>
+    <t>Tanggal tunggakan terakhir.</t>
+  </si>
+  <si>
+    <t>Kolektibilitas terburuk yang pernah tercatat pada periode tertentu.</t>
+  </si>
+  <si>
+    <t>Status kolektibilitas kredit saat ini.</t>
+  </si>
+  <si>
+    <t>Tanggal kredit dihapus buku/write-off.</t>
+  </si>
+  <si>
+    <t>Divisi yang menjadi pemilik produk.</t>
+  </si>
+  <si>
+    <t>Divisi bisnis yang menjadi pemilik/penanggung jawab account.</t>
+  </si>
+  <si>
+    <t>Hasil klasifikasi/output bisnis level 1.</t>
+  </si>
+  <si>
+    <t>Hasil klasifikasi/output bisnis level 2.</t>
+  </si>
+  <si>
+    <t>Hasil klasifikasi/output bisnis level 3.</t>
+  </si>
+  <si>
+    <t>Kolektibilitas terburuk terakhir yang tercatat.</t>
+  </si>
+  <si>
+    <t>Saldo buku berjalan/current book balance dalam Rupiah.</t>
+  </si>
+  <si>
+    <t>Saldo buku berjalan/current book balance dalam mata uang asli.</t>
+  </si>
+  <si>
+    <t>Nilai outstanding/exposure yang masih berjalan.</t>
+  </si>
+  <si>
+    <t>Klasifikasi pemilik channel level 1.</t>
+  </si>
+  <si>
+    <t>Klasifikasi pemilik channel level 2.</t>
+  </si>
+  <si>
+    <t>Klasifikasi pemilik channel level 3.</t>
+  </si>
+  <si>
+    <t>Hasil mapping/mirror pemilik channel.</t>
+  </si>
+  <si>
+    <t>Hasil mapping/mirror jenis channel.</t>
+  </si>
+  <si>
+    <t>Saldo DSPA sesuai definisi internal bank.</t>
+  </si>
+  <si>
+    <t>Saldo Debt Service Reserve Account (DSRA).</t>
+  </si>
+  <si>
+    <t>Deskripsi tujuan penggunaan kredit.</t>
+  </si>
+  <si>
+    <t>Interest Income atau pendapatan bunga harian.</t>
+  </si>
+  <si>
+    <t>Interest Income atau pendapatan bunga bulanan.</t>
+  </si>
+  <si>
+    <t>CIF utama/principal apabila nasabah memiliki beberapa CIF terkait.</t>
+  </si>
+  <si>
+    <t>Nasabah/perusahaan utama dalam satu kelompok usaha atau grup.</t>
+  </si>
+  <si>
+    <t>Tanggal posisi/snapshot data.</t>
+  </si>
+  <si>
+    <t>CIF Key Nasabah (ID Nasabah)</t>
+  </si>
+  <si>
+    <t>Nomor Rekening</t>
+  </si>
+  <si>
+    <t>Nama Lengkap</t>
+  </si>
+  <si>
+    <t>Kode Kelamin</t>
+  </si>
+  <si>
+    <t>Tempat Lahir</t>
+  </si>
+  <si>
+    <t>Tanggal Lahir</t>
+  </si>
+  <si>
+    <t>Umur</t>
+  </si>
+  <si>
+    <t>Agama</t>
+  </si>
+  <si>
+    <t>Kode Negara</t>
+  </si>
+  <si>
+    <t>Nomor KTP / Kartu Tanda Penduduk</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Kode Menikah</t>
+  </si>
+  <si>
+    <t>Hobby / Hobi</t>
+  </si>
+  <si>
+    <t>Edukasi / Education</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Nomor Fax</t>
+  </si>
+  <si>
+    <t>Alamat (Jalan)</t>
+  </si>
+  <si>
+    <t>Alamat (RT/RW)</t>
+  </si>
+  <si>
+    <t>Alamat (Keluarahan)</t>
+  </si>
+  <si>
+    <t>Alamat (Kecamatan)</t>
+  </si>
+  <si>
+    <t>Kode Pos</t>
+  </si>
+  <si>
+    <t>Kota</t>
+  </si>
+  <si>
+    <t>Alamat Kantor 1</t>
+  </si>
+  <si>
+    <t>Alamat Kantor 2</t>
+  </si>
+  <si>
+    <t>Pekerjaan</t>
+  </si>
+  <si>
+    <t>Tempat Bekerja</t>
+  </si>
+  <si>
+    <t>Sub Segment</t>
+  </si>
+  <si>
+    <t>Dir Owner</t>
+  </si>
+  <si>
+    <t>Segment Div Owner</t>
+  </si>
+  <si>
+    <t>Sentra Code</t>
+  </si>
+  <si>
+    <t>Channel Type / Tipe Channel</t>
+  </si>
+  <si>
+    <t>Segment Maverick</t>
+  </si>
+  <si>
+    <t>Ntb / Etb</t>
+  </si>
+  <si>
+    <t>Rm (Dana)</t>
+  </si>
+  <si>
+    <t>Rm (Kredit)</t>
+  </si>
+  <si>
+    <t>Relation dengan Bank</t>
+  </si>
+  <si>
+    <t>CIF RM</t>
+  </si>
+  <si>
+    <t>Kode Corp (Group)</t>
+  </si>
+  <si>
+    <t>Kode BI Owner</t>
+  </si>
+  <si>
+    <t>Penanda Terrorism (Related)</t>
+  </si>
+  <si>
+    <t>Campaign Flag</t>
+  </si>
+  <si>
+    <t>Mata uang</t>
+  </si>
+  <si>
+    <t>Tipe mata uang</t>
+  </si>
+  <si>
+    <t>ID Account / Akun GL</t>
+  </si>
+  <si>
+    <t>Deskripsi Account / Akun GL</t>
+  </si>
+  <si>
+    <t>Nama Produk</t>
+  </si>
+  <si>
+    <t>Sub Category</t>
+  </si>
+  <si>
+    <t>Account Type / Tipe Akun</t>
+  </si>
+  <si>
+    <t>Penanda Share / Sharing data</t>
+  </si>
+  <si>
+    <t>Penanda ESG / ESG Flag</t>
+  </si>
+  <si>
+    <t>Xpora Location / Lokasi Xpora</t>
+  </si>
+  <si>
+    <t>Exporter Type / Tipe exporter</t>
+  </si>
+  <si>
+    <t>User Define Code / Kode User Definisi</t>
+  </si>
+  <si>
+    <t>Sektor Ekonomi</t>
+  </si>
+  <si>
+    <t>Marketing Consent</t>
+  </si>
+  <si>
+    <t>Data Sharing Consent</t>
+  </si>
+  <si>
+    <t>Status Bisnis</t>
+  </si>
+  <si>
+    <t>Data Sharing Consent (Sebelum)</t>
+  </si>
+  <si>
+    <t>Marketing Consent / (Sebelum)</t>
+  </si>
+  <si>
+    <t>Consent Date</t>
+  </si>
+  <si>
+    <t>Account Number / Nomor Akun</t>
+  </si>
+  <si>
+    <t>Tipe nasabah</t>
+  </si>
+  <si>
+    <t>Kode tipe nasabah</t>
+  </si>
+  <si>
+    <t>Kode Region pembukaan CIF</t>
+  </si>
+  <si>
+    <t>Region pembukaan CIF</t>
+  </si>
+  <si>
+    <t>Kode cabang pembukaan CIF</t>
+  </si>
+  <si>
+    <t>Tanggal pembukaan CIF</t>
+  </si>
+  <si>
+    <t>Cabang pembukaan CIF</t>
+  </si>
+  <si>
+    <t>Kode Segmen Market</t>
+  </si>
+  <si>
+    <t>Status Akun</t>
+  </si>
+  <si>
+    <t>Deskripsi status akun</t>
+  </si>
+  <si>
+    <t>Term Organisasi</t>
+  </si>
+  <si>
+    <t>Tanggal maturity</t>
+  </si>
+  <si>
+    <t>Flag Rate</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Balance Saat Ini</t>
+  </si>
+  <si>
+    <t>Balance IDR Saat ini</t>
+  </si>
+  <si>
+    <t>Amortisi dalam IDR</t>
+  </si>
+  <si>
+    <t>Ending Balance</t>
+  </si>
+  <si>
+    <t>Akun Afiliasi</t>
+  </si>
+  <si>
+    <t>Open Account</t>
+  </si>
+  <si>
+    <t>Sumber Dana</t>
+  </si>
+  <si>
+    <t>DHE Flag</t>
+  </si>
+  <si>
+    <t>Flag Kategori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag Kategori Akun </t>
+  </si>
+  <si>
+    <t>Flag Produk</t>
+  </si>
+  <si>
+    <t>Group Product / Produk Grup</t>
+  </si>
+  <si>
+    <t>Sentra Code / Kode Sentra</t>
+  </si>
+  <si>
+    <t>Channel Owner L1</t>
+  </si>
+  <si>
+    <t>Channel Owner L2</t>
+  </si>
+  <si>
+    <t>Channel Owner L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produk Divisi Owner </t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Cabang Sentra</t>
+  </si>
+  <si>
+    <t>Rata-rata book balance MTD</t>
+  </si>
+  <si>
+    <t>Rata-rata book balance MTD dalam IDR</t>
+  </si>
+  <si>
+    <t>Rata-rata book balance YTD</t>
+  </si>
+  <si>
+    <t>Rata-rata book balance YTD dalam IDR</t>
+  </si>
+  <si>
+    <t>Nomor rekening yang memiliki hubungan atau afiliasi dengan rekening utama.</t>
+  </si>
+  <si>
+    <t>Nama perusahaan/badan usaha.</t>
+  </si>
+  <si>
+    <t>Penanda apakah terkait atau merupakan penerima program bansos.</t>
+  </si>
+  <si>
+    <t>Informasi pekerjaan/profesi.</t>
+  </si>
+  <si>
+    <t>Divisi yang menjadi pemilik segmen.</t>
+  </si>
+  <si>
+    <t>Sub segmen nasabah.</t>
+  </si>
+  <si>
+    <t>Nama sentra atau unit bisnis yang menangani rekening</t>
+  </si>
+  <si>
+    <t>Segmen bisnis.</t>
+  </si>
+  <si>
+    <t>Kode sektor ekonomi.</t>
+  </si>
+  <si>
+    <t>Kode Relationship Manager.</t>
+  </si>
+  <si>
+    <t>Deskripsi market segment.</t>
+  </si>
+  <si>
+    <t>Nama singkat.</t>
+  </si>
+  <si>
+    <t>Divisi pemilik segmen.</t>
+  </si>
+  <si>
+    <t>Tanggal snapshot customer, digunakan untuk filter tanggal, bulan, tahun</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +2202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1991,6 +2213,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2332,7 +2557,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>581</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2343,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>583</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2354,18 +2579,18 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>582</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>579</v>
+        <v>406</v>
       </c>
       <c r="B6" t="s">
-        <v>580</v>
+        <v>407</v>
       </c>
       <c r="C6" t="s">
-        <v>584</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +2600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" style="4" customWidth="1"/>
@@ -2387,7 +2612,7 @@
     <col min="7" max="7" width="24.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="91.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5" style="4" customWidth="1"/>
     <col min="11" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -2405,7 +2630,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>589</v>
+        <v>416</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
@@ -2423,7 +2648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -2443,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>624</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2462,7 +2687,7 @@
       <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" t="s">
         <v>333</v>
       </c>
     </row>
@@ -2480,13 +2705,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>576</v>
+        <v>403</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>334</v>
+      <c r="J4" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -2503,13 +2728,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>577</v>
+        <v>404</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>335</v>
+      <c r="J5" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2528,8 +2753,8 @@
       <c r="H6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>336</v>
+      <c r="J6" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2548,8 +2773,8 @@
       <c r="H7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>337</v>
+      <c r="J7" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2568,8 +2793,8 @@
       <c r="H8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>338</v>
+      <c r="J8" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2588,8 +2813,8 @@
       <c r="H9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>339</v>
+      <c r="J9" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2608,8 +2833,8 @@
       <c r="H10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>340</v>
+      <c r="J10" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2628,8 +2853,8 @@
       <c r="H11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>341</v>
+      <c r="J11" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2648,8 +2873,8 @@
       <c r="H12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>342</v>
+      <c r="J12" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2668,8 +2893,8 @@
       <c r="H13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>343</v>
+      <c r="J13" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2688,8 +2913,8 @@
       <c r="H14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>344</v>
+      <c r="J14" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2706,13 +2931,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>585</v>
+        <v>412</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>345</v>
+      <c r="J15" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2734,8 +2959,8 @@
       <c r="H16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>623</v>
+      <c r="J16" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2752,10 +2977,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>346</v>
+        <v>415</v>
+      </c>
+      <c r="J17" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2774,8 +2999,8 @@
       <c r="H18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>347</v>
+      <c r="J18" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2794,8 +3019,8 @@
       <c r="H19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>348</v>
+      <c r="J19" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2814,8 +3039,8 @@
       <c r="H20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>349</v>
+      <c r="J20" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2834,8 +3059,8 @@
       <c r="H21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>350</v>
+      <c r="J21" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2854,8 +3079,8 @@
       <c r="H22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>351</v>
+      <c r="J22" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2874,8 +3099,8 @@
       <c r="H23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>352</v>
+      <c r="J23" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2894,8 +3119,8 @@
       <c r="H24" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>353</v>
+      <c r="J24" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2914,8 +3139,8 @@
       <c r="H25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>354</v>
+      <c r="J25" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2934,8 +3159,8 @@
       <c r="H26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>355</v>
+      <c r="J26" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2954,8 +3179,8 @@
       <c r="H27" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>356</v>
+      <c r="J27" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2974,8 +3199,8 @@
       <c r="H28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>357</v>
+      <c r="J28" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2992,13 +3217,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>576</v>
+        <v>403</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J29" s="4" t="s">
-        <v>358</v>
+      <c r="J29" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -3015,13 +3240,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>577</v>
+        <v>404</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>629</v>
+      <c r="J30" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3040,8 +3265,8 @@
       <c r="H31" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>628</v>
+      <c r="J31" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3060,8 +3285,8 @@
       <c r="H32" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="4" t="s">
-        <v>359</v>
+      <c r="J32" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3080,8 +3305,8 @@
       <c r="H33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>360</v>
+      <c r="J33" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3100,8 +3325,8 @@
       <c r="H34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J34" s="4" t="s">
-        <v>361</v>
+      <c r="J34" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3120,8 +3345,8 @@
       <c r="H35" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>362</v>
+      <c r="J35" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3140,8 +3365,8 @@
       <c r="H36" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J36" s="4" t="s">
-        <v>363</v>
+      <c r="J36" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3160,8 +3385,8 @@
       <c r="H37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J37" s="4" t="s">
-        <v>364</v>
+      <c r="J37" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3180,8 +3405,8 @@
       <c r="H38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J38" s="4" t="s">
-        <v>365</v>
+      <c r="J38" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3203,31 +3428,31 @@
       <c r="H39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J39" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D40" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>585</v>
+      <c r="E40" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>367</v>
+        <v>703</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3235,19 +3460,22 @@
         <v>23</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D41" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>412</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J41" s="4" t="s">
-        <v>368</v>
+      <c r="J41" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3255,19 +3483,19 @@
         <v>23</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D42" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>356</v>
+      <c r="J42" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3275,7 +3503,7 @@
         <v>23</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>38</v>
@@ -3286,8 +3514,8 @@
       <c r="H43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>369</v>
+      <c r="J43" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3295,10 +3523,10 @@
         <v>23</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D44" s="4" t="b">
         <v>0</v>
@@ -3306,8 +3534,8 @@
       <c r="H44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>370</v>
+      <c r="J44" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3315,10 +3543,10 @@
         <v>23</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D45" s="4" t="b">
         <v>0</v>
@@ -3326,8 +3554,8 @@
       <c r="H45" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>371</v>
+      <c r="J45" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3335,22 +3563,19 @@
         <v>23</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D46" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E46" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>372</v>
+      <c r="J46" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3358,19 +3583,22 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D47" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="E47" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="H47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>373</v>
+      <c r="J47" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3378,10 +3606,10 @@
         <v>23</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D48" s="4" t="b">
         <v>0</v>
@@ -3389,8 +3617,8 @@
       <c r="H48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>373</v>
+      <c r="J48" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3398,10 +3626,10 @@
         <v>23</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D49" s="4" t="b">
         <v>0</v>
@@ -3409,8 +3637,8 @@
       <c r="H49" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>374</v>
+      <c r="J49" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3418,10 +3646,10 @@
         <v>23</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D50" s="4" t="b">
         <v>0</v>
@@ -3429,8 +3657,8 @@
       <c r="H50" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J50" s="4" t="s">
-        <v>375</v>
+      <c r="J50" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3438,7 +3666,7 @@
         <v>23</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>38</v>
@@ -3449,8 +3677,8 @@
       <c r="H51" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>376</v>
+      <c r="J51" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3458,22 +3686,19 @@
         <v>23</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D52" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>377</v>
+        <v>10</v>
+      </c>
+      <c r="J52" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3481,19 +3706,22 @@
         <v>23</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D53" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>378</v>
+        <v>415</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J53" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3501,7 +3729,7 @@
         <v>23</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>38</v>
@@ -3512,8 +3740,8 @@
       <c r="H54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J54" s="4" t="s">
-        <v>379</v>
+      <c r="J54" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3521,7 +3749,7 @@
         <v>23</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>38</v>
@@ -3532,8 +3760,8 @@
       <c r="H55" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J55" s="4" t="s">
-        <v>380</v>
+      <c r="J55" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3541,7 +3769,7 @@
         <v>23</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>38</v>
@@ -3552,8 +3780,8 @@
       <c r="H56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J56" s="4" t="s">
-        <v>381</v>
+      <c r="J56" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3561,7 +3789,7 @@
         <v>23</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>38</v>
@@ -3572,8 +3800,8 @@
       <c r="H57" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J57" s="4" t="s">
-        <v>382</v>
+      <c r="J57" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3581,7 +3809,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>38</v>
@@ -3592,8 +3820,8 @@
       <c r="H58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J58" s="4" t="s">
-        <v>383</v>
+      <c r="J58" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3601,7 +3829,7 @@
         <v>23</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>38</v>
@@ -3612,8 +3840,8 @@
       <c r="H59" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J59" s="4" t="s">
-        <v>384</v>
+      <c r="J59" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3621,7 +3849,7 @@
         <v>23</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>38</v>
@@ -3632,8 +3860,8 @@
       <c r="H60" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>385</v>
+      <c r="J60" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3641,7 +3869,7 @@
         <v>23</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>38</v>
@@ -3652,8 +3880,8 @@
       <c r="H61" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J61" s="4" t="s">
-        <v>386</v>
+      <c r="J61" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3661,7 +3889,7 @@
         <v>23</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>38</v>
@@ -3672,8 +3900,8 @@
       <c r="H62" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J62" s="4" t="s">
-        <v>387</v>
+      <c r="J62" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3681,7 +3909,7 @@
         <v>23</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>38</v>
@@ -3692,8 +3920,8 @@
       <c r="H63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>388</v>
+      <c r="J63" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3701,7 +3929,7 @@
         <v>23</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>38</v>
@@ -3712,8 +3940,8 @@
       <c r="H64" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J64" s="4" t="s">
-        <v>389</v>
+      <c r="J64" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3721,7 +3949,7 @@
         <v>23</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>38</v>
@@ -3732,8 +3960,8 @@
       <c r="H65" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J65" s="4" t="s">
-        <v>390</v>
+      <c r="J65" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3741,10 +3969,10 @@
         <v>23</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D66" s="4" t="b">
         <v>0</v>
@@ -3752,8 +3980,8 @@
       <c r="H66" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>391</v>
+      <c r="J66" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3761,22 +3989,19 @@
         <v>23</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="D67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H67" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J67" s="4" t="s">
-        <v>392</v>
+      <c r="J67" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3784,19 +4009,22 @@
         <v>23</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="D68" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G68" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H68" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>393</v>
+      <c r="J68" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3804,7 +4032,7 @@
         <v>23</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>38</v>
@@ -3815,8 +4043,8 @@
       <c r="H69" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J69" s="4" t="s">
-        <v>394</v>
+      <c r="J69" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3824,7 +4052,7 @@
         <v>23</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>38</v>
@@ -3835,8 +4063,8 @@
       <c r="H70" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J70" s="4" t="s">
-        <v>395</v>
+      <c r="J70" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3844,7 +4072,7 @@
         <v>23</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>38</v>
@@ -3855,8 +4083,8 @@
       <c r="H71" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J71" s="4" t="s">
-        <v>396</v>
+      <c r="J71" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3864,7 +4092,7 @@
         <v>23</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>38</v>
@@ -3875,8 +4103,8 @@
       <c r="H72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J72" s="4" t="s">
-        <v>397</v>
+      <c r="J72" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3884,10 +4112,10 @@
         <v>23</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D73" s="4" t="b">
         <v>0</v>
@@ -3895,8 +4123,8 @@
       <c r="H73" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J73" s="4" t="s">
-        <v>398</v>
+      <c r="J73" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3904,10 +4132,10 @@
         <v>23</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D74" s="4" t="b">
         <v>0</v>
@@ -3915,8 +4143,8 @@
       <c r="H74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>399</v>
+      <c r="J74" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3924,7 +4152,7 @@
         <v>23</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>38</v>
@@ -3935,8 +4163,8 @@
       <c r="H75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J75" s="4" t="s">
-        <v>400</v>
+      <c r="J75" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3944,7 +4172,7 @@
         <v>23</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>38</v>
@@ -3955,8 +4183,8 @@
       <c r="H76" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J76" s="4" t="s">
-        <v>401</v>
+      <c r="J76" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3964,7 +4192,7 @@
         <v>23</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>38</v>
@@ -3975,8 +4203,8 @@
       <c r="H77" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J77" s="4" t="s">
-        <v>402</v>
+      <c r="J77" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3984,7 +4212,7 @@
         <v>23</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>38</v>
@@ -3995,8 +4223,8 @@
       <c r="H78" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J78" s="4" t="s">
-        <v>403</v>
+      <c r="J78" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4004,7 +4232,7 @@
         <v>23</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>38</v>
@@ -4015,8 +4243,8 @@
       <c r="H79" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J79" s="4" t="s">
-        <v>404</v>
+      <c r="J79" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4024,7 +4252,7 @@
         <v>23</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>38</v>
@@ -4035,8 +4263,8 @@
       <c r="H80" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>405</v>
+      <c r="J80" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4044,7 +4272,7 @@
         <v>23</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>38</v>
@@ -4055,8 +4283,8 @@
       <c r="H81" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J81" s="4" t="s">
-        <v>406</v>
+      <c r="J81" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4064,7 +4292,7 @@
         <v>23</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>38</v>
@@ -4074,6 +4302,9 @@
       </c>
       <c r="H82" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="J82" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4081,7 +4312,7 @@
         <v>23</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>38</v>
@@ -4092,13 +4323,14 @@
       <c r="H83" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J83"/>
     </row>
     <row r="84" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>38</v>
@@ -4109,16 +4341,14 @@
       <c r="H84" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J84" s="4" t="s">
-        <v>407</v>
-      </c>
+      <c r="J84"/>
     </row>
     <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>38</v>
@@ -4128,6 +4358,9 @@
       </c>
       <c r="H85" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="J85" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4135,7 +4368,7 @@
         <v>23</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>38</v>
@@ -4146,13 +4379,14 @@
       <c r="H86" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J86"/>
     </row>
     <row r="87" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>38</v>
@@ -4163,13 +4397,14 @@
       <c r="H87" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J87"/>
     </row>
     <row r="88" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>38</v>
@@ -4180,16 +4415,14 @@
       <c r="H88" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J88" s="4" t="s">
-        <v>408</v>
-      </c>
+      <c r="J88"/>
     </row>
     <row r="89" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>38</v>
@@ -4200,8 +4433,8 @@
       <c r="H89" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J89" s="4" t="s">
-        <v>409</v>
+      <c r="J89" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4209,7 +4442,7 @@
         <v>23</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>38</v>
@@ -4220,8 +4453,8 @@
       <c r="H90" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J90" s="4" t="s">
-        <v>410</v>
+      <c r="J90" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4229,7 +4462,7 @@
         <v>23</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>38</v>
@@ -4240,8 +4473,8 @@
       <c r="H91" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J91" s="4" t="s">
-        <v>411</v>
+      <c r="J91" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4249,7 +4482,7 @@
         <v>23</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>38</v>
@@ -4260,8 +4493,8 @@
       <c r="H92" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J92" s="4" t="s">
-        <v>412</v>
+      <c r="J92" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4269,7 +4502,7 @@
         <v>23</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>38</v>
@@ -4280,8 +4513,8 @@
       <c r="H93" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J93" s="4" t="s">
-        <v>413</v>
+      <c r="J93" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4289,7 +4522,7 @@
         <v>23</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>38</v>
@@ -4300,8 +4533,8 @@
       <c r="H94" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J94" s="4" t="s">
-        <v>414</v>
+      <c r="J94" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4309,7 +4542,7 @@
         <v>23</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>38</v>
@@ -4320,8 +4553,8 @@
       <c r="H95" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J95" s="4" t="s">
-        <v>415</v>
+      <c r="J95" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4329,7 +4562,7 @@
         <v>23</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>38</v>
@@ -4340,8 +4573,8 @@
       <c r="H96" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J96" s="4" t="s">
-        <v>416</v>
+      <c r="J96" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4349,7 +4582,7 @@
         <v>23</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>38</v>
@@ -4360,8 +4593,8 @@
       <c r="H97" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J97" s="4" t="s">
-        <v>417</v>
+      <c r="J97" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4369,7 +4602,7 @@
         <v>23</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>38</v>
@@ -4380,8 +4613,8 @@
       <c r="H98" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J98" s="4" t="s">
-        <v>418</v>
+      <c r="J98" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4389,7 +4622,7 @@
         <v>23</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>38</v>
@@ -4400,8 +4633,8 @@
       <c r="H99" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J99" s="4" t="s">
-        <v>419</v>
+      <c r="J99" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4409,7 +4642,7 @@
         <v>23</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>38</v>
@@ -4420,8 +4653,8 @@
       <c r="H100" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J100" s="4" t="s">
-        <v>420</v>
+      <c r="J100" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4429,7 +4662,7 @@
         <v>23</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>38</v>
@@ -4439,6 +4672,9 @@
       </c>
       <c r="H101" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="J101" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4446,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>38</v>
@@ -4457,16 +4693,14 @@
       <c r="H102" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J102" s="4" t="s">
-        <v>421</v>
-      </c>
+      <c r="J102"/>
     </row>
     <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>38</v>
@@ -4477,8 +4711,8 @@
       <c r="H103" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J103" s="4" t="s">
-        <v>422</v>
+      <c r="J103" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4486,22 +4720,19 @@
         <v>23</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D104" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G104" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H104" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J104" s="4" t="s">
-        <v>423</v>
+      <c r="J104" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4509,7 +4740,7 @@
         <v>23</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>143</v>
@@ -4523,13 +4754,16 @@
       <c r="H105" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J105" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="106" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>143</v>
@@ -4543,33 +4777,35 @@
       <c r="H106" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J106"/>
     </row>
     <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="D107" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G107" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H107" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J107" s="4" t="s">
-        <v>424</v>
-      </c>
+      <c r="J107"/>
     </row>
     <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>38</v>
@@ -4579,6 +4815,9 @@
       </c>
       <c r="H108" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="J108" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4586,7 +4825,7 @@
         <v>23</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>38</v>
@@ -4597,13 +4836,14 @@
       <c r="H109" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="J109"/>
     </row>
     <row r="110" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>38</v>
@@ -4614,16 +4854,14 @@
       <c r="H110" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J110" s="4" t="s">
-        <v>425</v>
-      </c>
+      <c r="J110"/>
     </row>
     <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>38</v>
@@ -4634,8 +4872,8 @@
       <c r="H111" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J111" s="4" t="s">
-        <v>426</v>
+      <c r="J111" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4643,7 +4881,7 @@
         <v>23</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>38</v>
@@ -4654,8 +4892,8 @@
       <c r="H112" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J112" s="4" t="s">
-        <v>427</v>
+      <c r="J112" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4663,7 +4901,7 @@
         <v>23</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>38</v>
@@ -4674,8 +4912,8 @@
       <c r="H113" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J113" s="4" t="s">
-        <v>428</v>
+      <c r="J113" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4683,7 +4921,7 @@
         <v>23</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>38</v>
@@ -4694,8 +4932,8 @@
       <c r="H114" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J114" s="4" t="s">
-        <v>429</v>
+      <c r="J114" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4703,7 +4941,7 @@
         <v>23</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>38</v>
@@ -4714,8 +4952,8 @@
       <c r="H115" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J115" s="4" t="s">
-        <v>430</v>
+      <c r="J115" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4723,7 +4961,7 @@
         <v>23</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>38</v>
@@ -4734,8 +4972,8 @@
       <c r="H116" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J116" s="4" t="s">
-        <v>431</v>
+      <c r="J116" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4743,7 +4981,7 @@
         <v>23</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>38</v>
@@ -4754,8 +4992,8 @@
       <c r="H117" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J117" s="4" t="s">
-        <v>432</v>
+      <c r="J117" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4763,7 +5001,7 @@
         <v>23</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>38</v>
@@ -4774,8 +5012,8 @@
       <c r="H118" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J118" s="4" t="s">
-        <v>433</v>
+      <c r="J118" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4783,7 +5021,7 @@
         <v>23</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>38</v>
@@ -4794,8 +5032,8 @@
       <c r="H119" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J119" s="4" t="s">
-        <v>434</v>
+      <c r="J119" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4803,7 +5041,7 @@
         <v>23</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>38</v>
@@ -4814,8 +5052,8 @@
       <c r="H120" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J120" s="4" t="s">
-        <v>435</v>
+      <c r="J120" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4823,7 +5061,7 @@
         <v>23</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>38</v>
@@ -4834,8 +5072,8 @@
       <c r="H121" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J121" s="4" t="s">
-        <v>436</v>
+      <c r="J121" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4843,7 +5081,7 @@
         <v>23</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>38</v>
@@ -4854,8 +5092,8 @@
       <c r="H122" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J122" s="4" t="s">
-        <v>437</v>
+      <c r="J122" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4863,7 +5101,7 @@
         <v>23</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>38</v>
@@ -4874,8 +5112,8 @@
       <c r="H123" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J123" s="4" t="s">
-        <v>438</v>
+      <c r="J123" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4883,7 +5121,7 @@
         <v>23</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>38</v>
@@ -4894,8 +5132,8 @@
       <c r="H124" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J124" s="4" t="s">
-        <v>439</v>
+      <c r="J124" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4903,7 +5141,7 @@
         <v>23</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>38</v>
@@ -4914,8 +5152,8 @@
       <c r="H125" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J125" s="4" t="s">
-        <v>440</v>
+      <c r="J125" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4923,7 +5161,7 @@
         <v>23</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>38</v>
@@ -4934,8 +5172,8 @@
       <c r="H126" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J126" s="4" t="s">
-        <v>441</v>
+      <c r="J126" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4943,7 +5181,7 @@
         <v>23</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>38</v>
@@ -4954,8 +5192,8 @@
       <c r="H127" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J127" s="4" t="s">
-        <v>442</v>
+      <c r="J127" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4963,7 +5201,7 @@
         <v>23</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>38</v>
@@ -4974,8 +5212,8 @@
       <c r="H128" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J128" s="4" t="s">
-        <v>443</v>
+      <c r="J128" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4983,7 +5221,7 @@
         <v>23</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>38</v>
@@ -4994,8 +5232,8 @@
       <c r="H129" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J129" s="4" t="s">
-        <v>444</v>
+      <c r="J129" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5003,7 +5241,7 @@
         <v>23</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>38</v>
@@ -5014,8 +5252,8 @@
       <c r="H130" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J130" s="4" t="s">
-        <v>445</v>
+      <c r="J130" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5023,10 +5261,10 @@
         <v>23</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D131" s="4" t="b">
         <v>0</v>
@@ -5034,8 +5272,8 @@
       <c r="H131" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J131" s="4" t="s">
-        <v>446</v>
+      <c r="J131" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5043,10 +5281,10 @@
         <v>23</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D132" s="4" t="b">
         <v>0</v>
@@ -5054,8 +5292,8 @@
       <c r="H132" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J132" s="4" t="s">
-        <v>447</v>
+      <c r="J132" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5063,7 +5301,7 @@
         <v>23</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>38</v>
@@ -5074,8 +5312,8 @@
       <c r="H133" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J133" s="4" t="s">
-        <v>448</v>
+      <c r="J133" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5083,7 +5321,7 @@
         <v>23</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>38</v>
@@ -5094,8 +5332,8 @@
       <c r="H134" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J134" s="4" t="s">
-        <v>449</v>
+      <c r="J134" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5103,7 +5341,7 @@
         <v>23</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>38</v>
@@ -5114,8 +5352,8 @@
       <c r="H135" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J135" s="4" t="s">
-        <v>450</v>
+      <c r="J135" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5123,7 +5361,7 @@
         <v>23</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>38</v>
@@ -5134,8 +5372,8 @@
       <c r="H136" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J136" s="4" t="s">
-        <v>451</v>
+      <c r="J136" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5143,7 +5381,7 @@
         <v>23</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>38</v>
@@ -5154,8 +5392,8 @@
       <c r="H137" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J137" s="4" t="s">
-        <v>452</v>
+      <c r="J137" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5163,7 +5401,7 @@
         <v>23</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>38</v>
@@ -5174,8 +5412,8 @@
       <c r="H138" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J138" s="4" t="s">
-        <v>453</v>
+      <c r="J138" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5183,10 +5421,10 @@
         <v>23</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D139" s="4" t="b">
         <v>0</v>
@@ -5194,28 +5432,28 @@
       <c r="H139" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J139" s="4" t="s">
-        <v>454</v>
+      <c r="J139" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D140" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J140" s="4" t="s">
-        <v>455</v>
+      <c r="J140" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5223,22 +5461,19 @@
         <v>27</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D141" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>576</v>
+        <v>1</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J141" s="4" t="s">
-        <v>456</v>
+      <c r="J141" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5246,19 +5481,22 @@
         <v>27</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="D142" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="F142" s="4" t="s">
+        <v>403</v>
+      </c>
       <c r="H142" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J142" s="4" t="s">
-        <v>457</v>
+      <c r="J142" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5266,10 +5504,10 @@
         <v>27</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D143" s="4" t="b">
         <v>0</v>
@@ -5277,8 +5515,8 @@
       <c r="H143" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J143" s="4" t="s">
-        <v>458</v>
+      <c r="J143" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5286,10 +5524,10 @@
         <v>27</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D144" s="4" t="b">
         <v>0</v>
@@ -5297,8 +5535,8 @@
       <c r="H144" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J144" s="4" t="s">
-        <v>459</v>
+      <c r="J144" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5306,10 +5544,10 @@
         <v>27</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D145" s="4" t="b">
         <v>0</v>
@@ -5317,8 +5555,8 @@
       <c r="H145" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J145" s="4" t="s">
-        <v>460</v>
+      <c r="J145" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5326,10 +5564,10 @@
         <v>27</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D146" s="4" t="b">
         <v>0</v>
@@ -5337,8 +5575,8 @@
       <c r="H146" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J146" s="4" t="s">
-        <v>461</v>
+      <c r="J146" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5346,10 +5584,10 @@
         <v>27</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D147" s="4" t="b">
         <v>0</v>
@@ -5357,8 +5595,8 @@
       <c r="H147" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J147" s="4" t="s">
-        <v>460</v>
+      <c r="J147" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5366,10 +5604,10 @@
         <v>27</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D148" s="4" t="b">
         <v>0</v>
@@ -5377,8 +5615,8 @@
       <c r="H148" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J148" s="4" t="s">
-        <v>460</v>
+      <c r="J148" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5386,10 +5624,10 @@
         <v>27</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="D149" s="4" t="b">
         <v>0</v>
@@ -5397,8 +5635,8 @@
       <c r="H149" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J149" s="4" t="s">
-        <v>462</v>
+      <c r="J149" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5406,7 +5644,7 @@
         <v>27</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>180</v>
@@ -5417,8 +5655,8 @@
       <c r="H150" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J150" s="4" t="s">
-        <v>463</v>
+      <c r="J150" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5426,10 +5664,10 @@
         <v>27</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D151" s="4" t="b">
         <v>0</v>
@@ -5437,8 +5675,8 @@
       <c r="H151" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J151" s="4" t="s">
-        <v>464</v>
+      <c r="J151" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5446,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>182</v>
@@ -5457,8 +5695,8 @@
       <c r="H152" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J152" s="4" t="s">
-        <v>465</v>
+      <c r="J152" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5466,10 +5704,10 @@
         <v>27</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="D153" s="4" t="b">
         <v>0</v>
@@ -5477,7 +5715,7 @@
       <c r="H153" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J153" s="4" t="s">
+      <c r="J153" t="s">
         <v>466</v>
       </c>
     </row>
@@ -5486,10 +5724,10 @@
         <v>27</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D154" s="4" t="b">
         <v>0</v>
@@ -5497,8 +5735,8 @@
       <c r="H154" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J154" s="4" t="s">
-        <v>425</v>
+      <c r="J154" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5506,10 +5744,10 @@
         <v>27</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="D155" s="4" t="b">
         <v>0</v>
@@ -5517,8 +5755,8 @@
       <c r="H155" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J155" s="4" t="s">
-        <v>426</v>
+      <c r="J155" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5526,10 +5764,10 @@
         <v>27</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="D156" s="4" t="b">
         <v>0</v>
@@ -5537,8 +5775,8 @@
       <c r="H156" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J156" s="4" t="s">
-        <v>467</v>
+      <c r="J156" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5546,7 +5784,7 @@
         <v>27</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>76</v>
@@ -5557,8 +5795,8 @@
       <c r="H157" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J157" s="4" t="s">
-        <v>468</v>
+      <c r="J157" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5566,10 +5804,10 @@
         <v>27</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D158" s="4" t="b">
         <v>0</v>
@@ -5577,8 +5815,8 @@
       <c r="H158" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J158" s="4" t="s">
-        <v>469</v>
+      <c r="J158" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5586,10 +5824,10 @@
         <v>27</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="D159" s="4" t="b">
         <v>0</v>
@@ -5597,8 +5835,8 @@
       <c r="H159" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J159" s="4" t="s">
-        <v>428</v>
+      <c r="J159" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5606,10 +5844,10 @@
         <v>27</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>38</v>
+        <v>189</v>
       </c>
       <c r="D160" s="4" t="b">
         <v>0</v>
@@ -5617,8 +5855,8 @@
       <c r="H160" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J160" s="4" t="s">
-        <v>470</v>
+      <c r="J160" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5626,10 +5864,10 @@
         <v>27</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D161" s="4" t="b">
         <v>0</v>
@@ -5637,8 +5875,8 @@
       <c r="H161" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J161" s="4" t="s">
-        <v>471</v>
+      <c r="J161" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5646,10 +5884,10 @@
         <v>27</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D162" s="4" t="b">
         <v>0</v>
@@ -5657,8 +5895,8 @@
       <c r="H162" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J162" s="4" t="s">
-        <v>472</v>
+      <c r="J162" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5666,10 +5904,10 @@
         <v>27</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D163" s="4" t="b">
         <v>0</v>
@@ -5677,8 +5915,8 @@
       <c r="H163" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J163" s="4" t="s">
-        <v>473</v>
+      <c r="J163" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5686,10 +5924,10 @@
         <v>27</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="D164" s="4" t="b">
         <v>0</v>
@@ -5697,8 +5935,8 @@
       <c r="H164" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J164" s="4" t="s">
-        <v>472</v>
+      <c r="J164" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5706,10 +5944,10 @@
         <v>27</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="D165" s="4" t="b">
         <v>0</v>
@@ -5717,8 +5955,8 @@
       <c r="H165" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J165" s="4" t="s">
-        <v>474</v>
+      <c r="J165" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5726,10 +5964,10 @@
         <v>27</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D166" s="4" t="b">
         <v>0</v>
@@ -5737,8 +5975,8 @@
       <c r="H166" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J166" s="4" t="s">
-        <v>472</v>
+      <c r="J166" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5746,22 +5984,19 @@
         <v>27</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D167" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E167" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H167" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J167" s="4" t="s">
-        <v>472</v>
+      <c r="J167" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5769,7 +6004,7 @@
         <v>27</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>32</v>
@@ -5777,11 +6012,14 @@
       <c r="D168" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="E168" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="H168" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J168" s="4" t="s">
-        <v>475</v>
+      <c r="J168" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5789,7 +6027,7 @@
         <v>27</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>32</v>
@@ -5800,8 +6038,8 @@
       <c r="H169" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J169" s="4" t="s">
-        <v>476</v>
+      <c r="J169" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5809,10 +6047,10 @@
         <v>27</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D170" s="4" t="b">
         <v>0</v>
@@ -5820,8 +6058,8 @@
       <c r="H170" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J170" s="4" t="s">
-        <v>477</v>
+      <c r="J170" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5829,10 +6067,10 @@
         <v>27</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="D171" s="4" t="b">
         <v>0</v>
@@ -5840,8 +6078,8 @@
       <c r="H171" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J171" s="4" t="s">
-        <v>478</v>
+      <c r="J171" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5849,10 +6087,10 @@
         <v>27</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="D172" s="4" t="b">
         <v>0</v>
@@ -5860,8 +6098,8 @@
       <c r="H172" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J172" s="4" t="s">
-        <v>479</v>
+      <c r="J172" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5869,10 +6107,10 @@
         <v>27</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D173" s="4" t="b">
         <v>0</v>
@@ -5880,8 +6118,8 @@
       <c r="H173" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J173" s="4" t="s">
-        <v>480</v>
+      <c r="J173" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5889,10 +6127,10 @@
         <v>27</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D174" s="4" t="b">
         <v>0</v>
@@ -5900,8 +6138,8 @@
       <c r="H174" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J174" s="4" t="s">
-        <v>481</v>
+      <c r="J174" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5909,7 +6147,7 @@
         <v>27</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>45</v>
@@ -5920,8 +6158,8 @@
       <c r="H175" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J175" s="4" t="s">
-        <v>482</v>
+      <c r="J175" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5929,7 +6167,7 @@
         <v>27</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>45</v>
@@ -5940,8 +6178,8 @@
       <c r="H176" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J176" s="4" t="s">
-        <v>483</v>
+      <c r="J176" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5949,10 +6187,10 @@
         <v>27</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D177" s="4" t="b">
         <v>0</v>
@@ -5960,8 +6198,8 @@
       <c r="H177" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J177" s="4" t="s">
-        <v>484</v>
+      <c r="J177" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5969,10 +6207,10 @@
         <v>27</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D178" s="4" t="b">
         <v>0</v>
@@ -5980,8 +6218,8 @@
       <c r="H178" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J178" s="4" t="s">
-        <v>485</v>
+      <c r="J178" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5989,22 +6227,19 @@
         <v>27</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="D179" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G179" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H179" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J179" s="4" t="s">
-        <v>428</v>
+      <c r="J179" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6012,7 +6247,7 @@
         <v>27</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>210</v>
@@ -6026,8 +6261,8 @@
       <c r="H180" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J180" s="4" t="s">
-        <v>486</v>
+      <c r="J180" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6035,7 +6270,7 @@
         <v>27</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>210</v>
@@ -6049,8 +6284,8 @@
       <c r="H181" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J181" s="4" t="s">
-        <v>487</v>
+      <c r="J181" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6058,7 +6293,7 @@
         <v>27</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>210</v>
@@ -6072,8 +6307,8 @@
       <c r="H182" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J182" s="4" t="s">
-        <v>488</v>
+      <c r="J182" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6081,7 +6316,7 @@
         <v>27</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>210</v>
@@ -6095,8 +6330,8 @@
       <c r="H183" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J183" s="4" t="s">
-        <v>489</v>
+      <c r="J183" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6104,19 +6339,22 @@
         <v>27</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="D184" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G184" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H184" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J184" s="4" t="s">
-        <v>490</v>
+      <c r="J184" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6124,10 +6362,10 @@
         <v>27</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D185" s="4" t="b">
         <v>0</v>
@@ -6135,8 +6373,8 @@
       <c r="H185" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J185" s="4" t="s">
-        <v>491</v>
+      <c r="J185" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6144,7 +6382,7 @@
         <v>27</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>38</v>
@@ -6155,8 +6393,8 @@
       <c r="H186" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J186" s="4" t="s">
-        <v>492</v>
+      <c r="J186" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6164,7 +6402,7 @@
         <v>27</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>38</v>
@@ -6175,8 +6413,8 @@
       <c r="H187" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J187" s="4" t="s">
-        <v>493</v>
+      <c r="J187" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6184,7 +6422,7 @@
         <v>27</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>38</v>
@@ -6195,8 +6433,8 @@
       <c r="H188" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J188" s="4" t="s">
-        <v>494</v>
+      <c r="J188" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6204,7 +6442,7 @@
         <v>27</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>38</v>
@@ -6215,8 +6453,8 @@
       <c r="H189" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J189" s="4" t="s">
-        <v>495</v>
+      <c r="J189" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6224,10 +6462,10 @@
         <v>27</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D190" s="4" t="b">
         <v>0</v>
@@ -6235,8 +6473,8 @@
       <c r="H190" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J190" s="4" t="s">
-        <v>496</v>
+      <c r="J190" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6244,7 +6482,7 @@
         <v>27</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>52</v>
@@ -6255,8 +6493,8 @@
       <c r="H191" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J191" s="4" t="s">
-        <v>497</v>
+      <c r="J191" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6264,10 +6502,10 @@
         <v>27</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D192" s="4" t="b">
         <v>0</v>
@@ -6275,8 +6513,8 @@
       <c r="H192" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J192" s="4" t="s">
-        <v>498</v>
+      <c r="J192" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6284,7 +6522,7 @@
         <v>27</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>38</v>
@@ -6295,8 +6533,8 @@
       <c r="H193" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J193" s="4" t="s">
-        <v>499</v>
+      <c r="J193" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6304,10 +6542,10 @@
         <v>27</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D194" s="4" t="b">
         <v>0</v>
@@ -6315,8 +6553,8 @@
       <c r="H194" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J194" s="4" t="s">
-        <v>436</v>
+      <c r="J194" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6324,10 +6562,10 @@
         <v>27</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D195" s="4" t="b">
         <v>0</v>
@@ -6335,8 +6573,8 @@
       <c r="H195" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J195" s="4" t="s">
-        <v>429</v>
+      <c r="J195" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6344,10 +6582,10 @@
         <v>27</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>224</v>
+        <v>153</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D196" s="4" t="b">
         <v>0</v>
@@ -6355,8 +6593,8 @@
       <c r="H196" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J196" s="4" t="s">
-        <v>500</v>
+      <c r="J196" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6364,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>45</v>
@@ -6375,8 +6613,8 @@
       <c r="H197" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J197" s="4" t="s">
-        <v>500</v>
+      <c r="J197" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6384,7 +6622,7 @@
         <v>27</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>45</v>
@@ -6395,8 +6633,8 @@
       <c r="H198" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J198" s="4" t="s">
-        <v>500</v>
+      <c r="J198" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6404,7 +6642,7 @@
         <v>27</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>45</v>
@@ -6415,8 +6653,8 @@
       <c r="H199" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J199" s="4" t="s">
-        <v>501</v>
+      <c r="J199" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6424,7 +6662,7 @@
         <v>27</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>45</v>
@@ -6435,8 +6673,8 @@
       <c r="H200" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J200" s="4" t="s">
-        <v>428</v>
+      <c r="J200" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6444,7 +6682,7 @@
         <v>27</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>45</v>
@@ -6455,8 +6693,8 @@
       <c r="H201" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J201" s="4" t="s">
-        <v>502</v>
+      <c r="J201" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6464,22 +6702,19 @@
         <v>27</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="D202" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G202" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H202" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J202" s="4" t="s">
-        <v>503</v>
+      <c r="J202" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6487,7 +6722,7 @@
         <v>27</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>210</v>
@@ -6501,8 +6736,8 @@
       <c r="H203" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J203" s="4" t="s">
-        <v>504</v>
+      <c r="J203" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6510,7 +6745,7 @@
         <v>27</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>210</v>
@@ -6524,8 +6759,8 @@
       <c r="H204" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J204" s="4" t="s">
-        <v>503</v>
+      <c r="J204" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6533,7 +6768,7 @@
         <v>27</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>210</v>
@@ -6547,8 +6782,8 @@
       <c r="H205" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J205" s="4" t="s">
-        <v>505</v>
+      <c r="J205" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6556,7 +6791,7 @@
         <v>27</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>210</v>
@@ -6570,8 +6805,8 @@
       <c r="H206" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J206" s="4" t="s">
-        <v>487</v>
+      <c r="J206" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6579,7 +6814,7 @@
         <v>27</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>210</v>
@@ -6593,8 +6828,8 @@
       <c r="H207" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J207" s="4" t="s">
-        <v>506</v>
+      <c r="J207" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6602,7 +6837,7 @@
         <v>27</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>210</v>
@@ -6616,8 +6851,8 @@
       <c r="H208" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J208" s="4" t="s">
-        <v>487</v>
+      <c r="J208" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6625,7 +6860,7 @@
         <v>27</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>210</v>
@@ -6639,8 +6874,8 @@
       <c r="H209" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J209" s="4" t="s">
-        <v>506</v>
+      <c r="J209" s="5" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6648,7 +6883,7 @@
         <v>27</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>210</v>
@@ -6662,8 +6897,8 @@
       <c r="H210" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J210" s="4" t="s">
-        <v>487</v>
+      <c r="J210" s="5" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6671,7 +6906,7 @@
         <v>27</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>210</v>
@@ -6685,8 +6920,8 @@
       <c r="H211" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J211" s="4" t="s">
-        <v>506</v>
+      <c r="J211" s="5" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6694,19 +6929,22 @@
         <v>27</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="D212" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G212" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H212" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J212" s="4" t="s">
-        <v>507</v>
+      <c r="J212" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6714,7 +6952,7 @@
         <v>27</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>38</v>
@@ -6725,8 +6963,8 @@
       <c r="H213" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J213" s="4" t="s">
-        <v>508</v>
+      <c r="J213" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6734,7 +6972,7 @@
         <v>27</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>38</v>
@@ -6745,8 +6983,8 @@
       <c r="H214" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J214" s="4" t="s">
-        <v>509</v>
+      <c r="J214" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6754,22 +6992,19 @@
         <v>27</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="D215" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G215" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H215" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J215" s="4" t="s">
-        <v>510</v>
+      <c r="J215" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6777,7 +7012,7 @@
         <v>27</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>243</v>
@@ -6791,8 +7026,8 @@
       <c r="H216" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J216" s="4" t="s">
-        <v>511</v>
+      <c r="J216" s="5" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6800,7 +7035,7 @@
         <v>27</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>243</v>
@@ -6814,8 +7049,8 @@
       <c r="H217" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J217" s="4" t="s">
-        <v>512</v>
+      <c r="J217" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6823,19 +7058,22 @@
         <v>27</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="D218" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G218" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H218" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J218" s="4" t="s">
-        <v>513</v>
+      <c r="J218" s="5" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6843,10 +7081,10 @@
         <v>27</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D219" s="4" t="b">
         <v>0</v>
@@ -6854,8 +7092,8 @@
       <c r="H219" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J219" s="4" t="s">
-        <v>514</v>
+      <c r="J219" s="5" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6863,10 +7101,10 @@
         <v>27</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D220" s="4" t="b">
         <v>0</v>
@@ -6874,8 +7112,8 @@
       <c r="H220" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J220" s="4" t="s">
-        <v>515</v>
+      <c r="J220" s="5" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6883,10 +7121,10 @@
         <v>27</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="D221" s="4" t="b">
         <v>0</v>
@@ -6894,8 +7132,8 @@
       <c r="H221" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J221" s="4" t="s">
-        <v>515</v>
+      <c r="J221" s="5" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6903,10 +7141,10 @@
         <v>27</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="D222" s="4" t="b">
         <v>0</v>
@@ -6914,8 +7152,8 @@
       <c r="H222" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J222" s="4" t="s">
-        <v>516</v>
+      <c r="J222" s="5" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6923,10 +7161,10 @@
         <v>27</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D223" s="4" t="b">
         <v>0</v>
@@ -6934,8 +7172,8 @@
       <c r="H223" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J223" s="4" t="s">
-        <v>517</v>
+      <c r="J223" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6943,7 +7181,7 @@
         <v>27</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>45</v>
@@ -6954,8 +7192,8 @@
       <c r="H224" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J224" s="4" t="s">
-        <v>517</v>
+      <c r="J224" s="5" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6963,7 +7201,7 @@
         <v>27</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>45</v>
@@ -6974,8 +7212,8 @@
       <c r="H225" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J225" s="4" t="s">
-        <v>517</v>
+      <c r="J225" s="5" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6983,10 +7221,10 @@
         <v>27</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D226" s="4" t="b">
         <v>0</v>
@@ -6994,8 +7232,8 @@
       <c r="H226" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J226" s="4" t="s">
-        <v>476</v>
+      <c r="J226" s="5" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7003,7 +7241,7 @@
         <v>27</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>38</v>
@@ -7014,8 +7252,8 @@
       <c r="H227" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J227" s="4" t="s">
-        <v>518</v>
+      <c r="J227" s="5" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7023,10 +7261,10 @@
         <v>27</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D228" s="4" t="b">
         <v>0</v>
@@ -7034,8 +7272,8 @@
       <c r="H228" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J228" s="4" t="s">
-        <v>519</v>
+      <c r="J228" s="5" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7043,22 +7281,19 @@
         <v>27</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="D229" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G229" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H229" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J229" s="4" t="s">
-        <v>520</v>
+      <c r="J229" s="5" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7066,7 +7301,7 @@
         <v>27</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>210</v>
@@ -7080,8 +7315,8 @@
       <c r="H230" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J230" s="4" t="s">
-        <v>521</v>
+      <c r="J230" s="5" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7089,7 +7324,7 @@
         <v>27</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>210</v>
@@ -7103,8 +7338,8 @@
       <c r="H231" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J231" s="4" t="s">
-        <v>520</v>
+      <c r="J231" s="5" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7112,7 +7347,7 @@
         <v>27</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>210</v>
@@ -7126,8 +7361,8 @@
       <c r="H232" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J232" s="4" t="s">
-        <v>521</v>
+      <c r="J232" s="5" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7135,7 +7370,7 @@
         <v>27</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>210</v>
@@ -7149,8 +7384,8 @@
       <c r="H233" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J233" s="4" t="s">
-        <v>520</v>
+      <c r="J233" s="5" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7158,7 +7393,7 @@
         <v>27</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>210</v>
@@ -7172,8 +7407,8 @@
       <c r="H234" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J234" s="4" t="s">
-        <v>521</v>
+      <c r="J234" s="5" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7181,7 +7416,7 @@
         <v>27</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>210</v>
@@ -7195,8 +7430,8 @@
       <c r="H235" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J235" s="4" t="s">
-        <v>522</v>
+      <c r="J235" s="5" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7204,7 +7439,7 @@
         <v>27</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>210</v>
@@ -7218,8 +7453,8 @@
       <c r="H236" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J236" s="4" t="s">
-        <v>523</v>
+      <c r="J236" s="5" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7227,19 +7462,22 @@
         <v>27</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="D237" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G237" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H237" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J237" s="4" t="s">
-        <v>524</v>
+      <c r="J237" s="5" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7247,22 +7485,19 @@
         <v>27</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>267</v>
+        <v>32</v>
       </c>
       <c r="D238" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G238" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H238" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J238" s="4" t="s">
-        <v>525</v>
+      <c r="J238" s="5" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7270,42 +7505,42 @@
         <v>27</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D239" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G239" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H239" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J239" s="4" t="s">
-        <v>500</v>
+      <c r="J239" s="5" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>32</v>
+        <v>269</v>
       </c>
       <c r="D240" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E240" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H240" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J240" s="4" t="s">
-        <v>526</v>
+      <c r="J240" s="5" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7313,39 +7548,42 @@
         <v>29</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D241" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="E241" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="H241" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J241" s="4" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J241" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D242" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H242" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J242" s="4" t="s">
-        <v>455</v>
+      <c r="J242" s="5" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7353,22 +7591,19 @@
         <v>29</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D243" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>576</v>
+        <v>1</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J243" s="4" t="s">
-        <v>456</v>
+      <c r="J243" s="5" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7376,7 +7611,7 @@
         <v>29</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>270</v>
+        <v>35</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>36</v>
@@ -7384,22 +7619,25 @@
       <c r="D244" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="F244" s="4" t="s">
+        <v>403</v>
+      </c>
       <c r="H244" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J244" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J244" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D245" s="4" t="b">
         <v>0</v>
@@ -7407,8 +7645,8 @@
       <c r="H245" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J245" s="4" t="s">
-        <v>457</v>
+      <c r="J245" s="5" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7416,7 +7654,7 @@
         <v>29</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>38</v>
@@ -7427,19 +7665,19 @@
       <c r="H246" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J246" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J246" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D247" s="4" t="b">
         <v>0</v>
@@ -7447,8 +7685,8 @@
       <c r="H247" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J247" s="4" t="s">
-        <v>459</v>
+      <c r="J247" s="5" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7456,10 +7694,10 @@
         <v>29</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D248" s="4" t="b">
         <v>0</v>
@@ -7467,8 +7705,8 @@
       <c r="H248" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J248" s="4" t="s">
-        <v>460</v>
+      <c r="J248" s="5" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7476,10 +7714,10 @@
         <v>29</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D249" s="4" t="b">
         <v>0</v>
@@ -7487,8 +7725,8 @@
       <c r="H249" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J249" s="4" t="s">
-        <v>461</v>
+      <c r="J249" s="5" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7496,10 +7734,10 @@
         <v>29</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D250" s="4" t="b">
         <v>0</v>
@@ -7507,8 +7745,8 @@
       <c r="H250" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J250" s="4" t="s">
-        <v>460</v>
+      <c r="J250" s="5" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7516,10 +7754,10 @@
         <v>29</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D251" s="4" t="b">
         <v>0</v>
@@ -7527,8 +7765,8 @@
       <c r="H251" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J251" s="4" t="s">
-        <v>460</v>
+      <c r="J251" s="5" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7536,10 +7774,10 @@
         <v>29</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D252" s="4" t="b">
         <v>0</v>
@@ -7547,8 +7785,8 @@
       <c r="H252" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J252" s="4" t="s">
-        <v>462</v>
+      <c r="J252" s="5" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7556,7 +7794,7 @@
         <v>29</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>38</v>
@@ -7567,8 +7805,8 @@
       <c r="H253" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J253" s="4" t="s">
-        <v>463</v>
+      <c r="J253" s="5" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7576,10 +7814,10 @@
         <v>29</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D254" s="4" t="b">
         <v>0</v>
@@ -7587,19 +7825,19 @@
       <c r="H254" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J254" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J254" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D255" s="4" t="b">
         <v>0</v>
@@ -7607,8 +7845,8 @@
       <c r="H255" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J255" s="4" t="s">
-        <v>465</v>
+      <c r="J255" s="5" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7616,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>38</v>
@@ -7627,8 +7865,8 @@
       <c r="H256" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J256" s="4" t="s">
-        <v>466</v>
+      <c r="J256" s="5" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7636,7 +7874,7 @@
         <v>29</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>38</v>
@@ -7647,8 +7885,8 @@
       <c r="H257" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J257" s="4" t="s">
-        <v>425</v>
+      <c r="J257" s="5" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7656,7 +7894,7 @@
         <v>29</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>38</v>
@@ -7667,8 +7905,8 @@
       <c r="H258" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J258" s="4" t="s">
-        <v>426</v>
+      <c r="J258" s="5" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7676,10 +7914,10 @@
         <v>29</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="D259" s="4" t="b">
         <v>0</v>
@@ -7687,8 +7925,8 @@
       <c r="H259" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J259" s="4" t="s">
-        <v>467</v>
+      <c r="J259" s="5" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7696,7 +7934,7 @@
         <v>29</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>189</v>
@@ -7707,8 +7945,8 @@
       <c r="H260" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J260" s="4" t="s">
-        <v>468</v>
+      <c r="J260" s="5" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7716,10 +7954,10 @@
         <v>29</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="D261" s="4" t="b">
         <v>0</v>
@@ -7727,8 +7965,8 @@
       <c r="H261" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J261" s="4" t="s">
-        <v>469</v>
+      <c r="J261" s="5" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7736,10 +7974,10 @@
         <v>29</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D262" s="4" t="b">
         <v>0</v>
@@ -7747,8 +7985,8 @@
       <c r="H262" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J262" s="4" t="s">
-        <v>428</v>
+      <c r="J262" s="5" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7756,10 +7994,10 @@
         <v>29</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="D263" s="4" t="b">
         <v>0</v>
@@ -7767,8 +8005,8 @@
       <c r="H263" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J263" s="4" t="s">
-        <v>470</v>
+      <c r="J263" s="5" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7776,10 +8014,10 @@
         <v>29</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D264" s="4" t="b">
         <v>0</v>
@@ -7787,8 +8025,8 @@
       <c r="H264" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J264" s="4" t="s">
-        <v>471</v>
+      <c r="J264" s="5" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7796,10 +8034,10 @@
         <v>29</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D265" s="4" t="b">
         <v>0</v>
@@ -7807,8 +8045,8 @@
       <c r="H265" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J265" s="4" t="s">
-        <v>472</v>
+      <c r="J265" s="5" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7816,10 +8054,10 @@
         <v>29</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D266" s="4" t="b">
         <v>0</v>
@@ -7827,8 +8065,8 @@
       <c r="H266" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J266" s="4" t="s">
-        <v>473</v>
+      <c r="J266" s="5" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7836,10 +8074,10 @@
         <v>29</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="D267" s="4" t="b">
         <v>0</v>
@@ -7847,8 +8085,8 @@
       <c r="H267" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J267" s="4" t="s">
-        <v>472</v>
+      <c r="J267" s="5" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7856,10 +8094,10 @@
         <v>29</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="D268" s="4" t="b">
         <v>0</v>
@@ -7867,8 +8105,8 @@
       <c r="H268" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J268" s="4" t="s">
-        <v>474</v>
+      <c r="J268" s="5" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7876,10 +8114,10 @@
         <v>29</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D269" s="4" t="b">
         <v>0</v>
@@ -7887,8 +8125,8 @@
       <c r="H269" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J269" s="4" t="s">
-        <v>472</v>
+      <c r="J269" s="5" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7896,10 +8134,10 @@
         <v>29</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D270" s="4" t="b">
         <v>0</v>
@@ -7907,8 +8145,8 @@
       <c r="H270" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J270" s="4" t="s">
-        <v>472</v>
+      <c r="J270" s="5" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7916,7 +8154,7 @@
         <v>29</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>32</v>
@@ -7927,8 +8165,8 @@
       <c r="H271" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J271" s="4" t="s">
-        <v>476</v>
+      <c r="J271" s="5" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7936,10 +8174,10 @@
         <v>29</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D272" s="4" t="b">
         <v>0</v>
@@ -7947,8 +8185,8 @@
       <c r="H272" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J272" s="4" t="s">
-        <v>477</v>
+      <c r="J272" s="5" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7956,10 +8194,10 @@
         <v>29</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="D273" s="4" t="b">
         <v>0</v>
@@ -7967,8 +8205,8 @@
       <c r="H273" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J273" s="4" t="s">
-        <v>478</v>
+      <c r="J273" s="5" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7976,10 +8214,10 @@
         <v>29</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>189</v>
+        <v>273</v>
       </c>
       <c r="D274" s="4" t="b">
         <v>0</v>
@@ -7987,8 +8225,8 @@
       <c r="H274" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J274" s="4" t="s">
-        <v>480</v>
+      <c r="J274" s="5" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7996,10 +8234,10 @@
         <v>29</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="D275" s="4" t="b">
         <v>0</v>
@@ -8007,8 +8245,8 @@
       <c r="H275" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J275" s="4" t="s">
-        <v>481</v>
+      <c r="J275" s="5" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8016,7 +8254,7 @@
         <v>29</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>271</v>
@@ -8027,16 +8265,16 @@
       <c r="H276" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J276" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J276" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>271</v>
@@ -8047,8 +8285,8 @@
       <c r="H277" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J277" s="4" t="s">
-        <v>428</v>
+      <c r="J277" s="5" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8056,10 +8294,10 @@
         <v>29</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D278" s="4" t="b">
         <v>0</v>
@@ -8067,8 +8305,8 @@
       <c r="H278" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J278" s="4" t="s">
-        <v>429</v>
+      <c r="J278" s="5" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8076,10 +8314,10 @@
         <v>29</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>271</v>
+        <v>84</v>
       </c>
       <c r="D279" s="4" t="b">
         <v>0</v>
@@ -8087,8 +8325,8 @@
       <c r="H279" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J279" s="4" t="s">
-        <v>530</v>
+      <c r="J279" s="5" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8096,10 +8334,10 @@
         <v>29</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D280" s="4" t="b">
         <v>0</v>
@@ -8107,8 +8345,8 @@
       <c r="H280" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J280" s="4" t="s">
-        <v>531</v>
+      <c r="J280" s="5" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8116,10 +8354,10 @@
         <v>29</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D281" s="4" t="b">
         <v>0</v>
@@ -8127,8 +8365,8 @@
       <c r="H281" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J281" s="4" t="s">
-        <v>532</v>
+      <c r="J281" s="5" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8136,10 +8374,10 @@
         <v>29</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D282" s="4" t="b">
         <v>0</v>
@@ -8147,8 +8385,8 @@
       <c r="H282" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J282" s="4" t="s">
-        <v>533</v>
+      <c r="J282" s="5" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8156,7 +8394,7 @@
         <v>29</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>32</v>
@@ -8167,7 +8405,7 @@
       <c r="H283" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J283" s="4" t="s">
+      <c r="J283" s="5" t="s">
         <v>534</v>
       </c>
     </row>
@@ -8176,7 +8414,7 @@
         <v>29</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>32</v>
@@ -8187,7 +8425,7 @@
       <c r="H284" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J284" s="4" t="s">
+      <c r="J284" s="5" t="s">
         <v>535</v>
       </c>
     </row>
@@ -8196,10 +8434,10 @@
         <v>29</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D285" s="4" t="b">
         <v>0</v>
@@ -8207,7 +8445,7 @@
       <c r="H285" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J285" s="4" t="s">
+      <c r="J285" s="5" t="s">
         <v>536</v>
       </c>
     </row>
@@ -8216,10 +8454,10 @@
         <v>29</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D286" s="4" t="b">
         <v>0</v>
@@ -8227,7 +8465,7 @@
       <c r="H286" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J286" s="4" t="s">
+      <c r="J286" s="5" t="s">
         <v>537</v>
       </c>
     </row>
@@ -8236,10 +8474,10 @@
         <v>29</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D287" s="4" t="b">
         <v>0</v>
@@ -8247,7 +8485,7 @@
       <c r="H287" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J287" s="4" t="s">
+      <c r="J287" s="5" t="s">
         <v>538</v>
       </c>
     </row>
@@ -8256,10 +8494,10 @@
         <v>29</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D288" s="4" t="b">
         <v>0</v>
@@ -8267,7 +8505,7 @@
       <c r="H288" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J288" s="4" t="s">
+      <c r="J288" s="5" t="s">
         <v>539</v>
       </c>
     </row>
@@ -8276,10 +8514,10 @@
         <v>29</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D289" s="4" t="b">
         <v>0</v>
@@ -8287,7 +8525,7 @@
       <c r="H289" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J289" s="4" t="s">
+      <c r="J289" s="5" t="s">
         <v>540</v>
       </c>
     </row>
@@ -8296,10 +8534,10 @@
         <v>29</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D290" s="4" t="b">
         <v>0</v>
@@ -8307,7 +8545,7 @@
       <c r="H290" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J290" s="4" t="s">
+      <c r="J290" s="5" t="s">
         <v>541</v>
       </c>
     </row>
@@ -8316,10 +8554,10 @@
         <v>29</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="D291" s="4" t="b">
         <v>0</v>
@@ -8327,7 +8565,7 @@
       <c r="H291" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J291" s="4" t="s">
+      <c r="J291" s="5" t="s">
         <v>542</v>
       </c>
     </row>
@@ -8336,7 +8574,7 @@
         <v>29</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>32</v>
@@ -8347,7 +8585,7 @@
       <c r="H292" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J292" s="4" t="s">
+      <c r="J292" s="5" t="s">
         <v>543</v>
       </c>
     </row>
@@ -8356,7 +8594,7 @@
         <v>29</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>12</v>
+        <v>289</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>32</v>
@@ -8367,8 +8605,8 @@
       <c r="H293" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J293" s="4" t="s">
-        <v>484</v>
+      <c r="J293" s="5" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8376,10 +8614,10 @@
         <v>29</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>206</v>
+        <v>12</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D294" s="4" t="b">
         <v>0</v>
@@ -8387,8 +8625,8 @@
       <c r="H294" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J294" s="4" t="s">
-        <v>482</v>
+      <c r="J294" s="5" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8396,10 +8634,10 @@
         <v>29</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D295" s="4" t="b">
         <v>0</v>
@@ -8407,8 +8645,8 @@
       <c r="H295" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J295" s="4" t="s">
-        <v>483</v>
+      <c r="J295" s="5" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8416,10 +8654,10 @@
         <v>29</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D296" s="4" t="b">
         <v>0</v>
@@ -8427,8 +8665,8 @@
       <c r="H296" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J296" s="4" t="s">
-        <v>544</v>
+      <c r="J296" s="5" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8436,22 +8674,19 @@
         <v>29</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D297" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G297" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H297" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J297" s="4" t="s">
-        <v>545</v>
+      <c r="J297" s="5" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8459,10 +8694,10 @@
         <v>29</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="D298" s="4" t="b">
         <v>0</v>
@@ -8473,8 +8708,8 @@
       <c r="H298" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J298" s="4" t="s">
-        <v>546</v>
+      <c r="J298" s="5" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8482,7 +8717,7 @@
         <v>29</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>210</v>
@@ -8496,8 +8731,8 @@
       <c r="H299" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J299" s="4" t="s">
-        <v>547</v>
+      <c r="J299" s="5" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8505,7 +8740,7 @@
         <v>29</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>210</v>
@@ -8519,8 +8754,8 @@
       <c r="H300" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J300" s="4" t="s">
-        <v>547</v>
+      <c r="J300" s="5" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8528,7 +8763,7 @@
         <v>29</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>210</v>
@@ -8542,8 +8777,8 @@
       <c r="H301" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J301" s="4" t="s">
-        <v>548</v>
+      <c r="J301" s="5" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8551,7 +8786,7 @@
         <v>29</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>210</v>
@@ -8565,8 +8800,8 @@
       <c r="H302" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J302" s="4" t="s">
-        <v>548</v>
+      <c r="J302" s="5" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8574,7 +8809,7 @@
         <v>29</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>210</v>
@@ -8588,8 +8823,8 @@
       <c r="H303" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J303" s="4" t="s">
-        <v>549</v>
+      <c r="J303" s="5" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8597,7 +8832,7 @@
         <v>29</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>210</v>
@@ -8611,8 +8846,8 @@
       <c r="H304" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J304" s="4" t="s">
-        <v>550</v>
+      <c r="J304" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8620,7 +8855,7 @@
         <v>29</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>210</v>
@@ -8634,8 +8869,8 @@
       <c r="H305" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J305" s="4" t="s">
-        <v>551</v>
+      <c r="J305" s="5" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8643,7 +8878,7 @@
         <v>29</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>210</v>
@@ -8657,8 +8892,8 @@
       <c r="H306" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J306" s="4" t="s">
-        <v>552</v>
+      <c r="J306" s="5" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8666,7 +8901,7 @@
         <v>29</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>210</v>
@@ -8680,8 +8915,8 @@
       <c r="H307" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J307" s="4" t="s">
-        <v>553</v>
+      <c r="J307" s="5" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8689,7 +8924,7 @@
         <v>29</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>210</v>
@@ -8703,8 +8938,8 @@
       <c r="H308" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J308" s="4" t="s">
-        <v>554</v>
+      <c r="J308" s="5" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8712,7 +8947,7 @@
         <v>29</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>210</v>
@@ -8726,8 +8961,8 @@
       <c r="H309" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J309" s="4" t="s">
-        <v>555</v>
+      <c r="J309" s="5" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8735,7 +8970,7 @@
         <v>29</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>210</v>
@@ -8749,8 +8984,8 @@
       <c r="H310" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J310" s="4" t="s">
-        <v>554</v>
+      <c r="J310" s="5" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8758,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>210</v>
@@ -8772,8 +9007,8 @@
       <c r="H311" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J311" s="4" t="s">
-        <v>556</v>
+      <c r="J311" s="5" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8781,7 +9016,7 @@
         <v>29</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>210</v>
@@ -8795,8 +9030,8 @@
       <c r="H312" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J312" s="4" t="s">
-        <v>557</v>
+      <c r="J312" s="5" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8804,7 +9039,7 @@
         <v>29</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>210</v>
@@ -8818,8 +9053,8 @@
       <c r="H313" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J313" s="4" t="s">
-        <v>558</v>
+      <c r="J313" s="5" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8827,19 +9062,22 @@
         <v>29</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="D314" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G314" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H314" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J314" s="4" t="s">
-        <v>559</v>
+      <c r="J314" s="5" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8847,10 +9085,10 @@
         <v>29</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D315" s="4" t="b">
         <v>0</v>
@@ -8858,8 +9096,8 @@
       <c r="H315" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J315" s="4" t="s">
-        <v>560</v>
+      <c r="J315" s="5" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8867,10 +9105,10 @@
         <v>29</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="D316" s="4" t="b">
         <v>0</v>
@@ -8878,8 +9116,8 @@
       <c r="H316" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J316" s="4" t="s">
-        <v>561</v>
+      <c r="J316" s="5" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8887,7 +9125,7 @@
         <v>29</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>189</v>
@@ -8898,8 +9136,8 @@
       <c r="H317" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J317" s="4" t="s">
-        <v>562</v>
+      <c r="J317" s="5" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8907,10 +9145,10 @@
         <v>29</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="D318" s="4" t="b">
         <v>0</v>
@@ -8918,8 +9156,8 @@
       <c r="H318" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J318" s="4" t="s">
-        <v>563</v>
+      <c r="J318" s="5" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8927,10 +9165,10 @@
         <v>29</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>271</v>
+        <v>32</v>
       </c>
       <c r="D319" s="4" t="b">
         <v>0</v>
@@ -8938,8 +9176,8 @@
       <c r="H319" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J319" s="4" t="s">
-        <v>501</v>
+      <c r="J319" s="5" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8947,7 +9185,7 @@
         <v>29</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>271</v>
@@ -8958,8 +9196,8 @@
       <c r="H320" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J320" s="4" t="s">
-        <v>564</v>
+      <c r="J320" s="5" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8967,7 +9205,7 @@
         <v>29</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>271</v>
@@ -8978,8 +9216,8 @@
       <c r="H321" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J321" s="4" t="s">
-        <v>565</v>
+      <c r="J321" s="5" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8987,7 +9225,7 @@
         <v>29</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>271</v>
@@ -8998,8 +9236,8 @@
       <c r="H322" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J322" s="4" t="s">
-        <v>565</v>
+      <c r="J322" s="5" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9007,7 +9245,7 @@
         <v>29</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>271</v>
@@ -9018,8 +9256,8 @@
       <c r="H323" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J323" s="4" t="s">
-        <v>565</v>
+      <c r="J323" s="5" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9027,10 +9265,10 @@
         <v>29</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D324" s="4" t="b">
         <v>0</v>
@@ -9038,8 +9276,8 @@
       <c r="H324" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J324" s="4" t="s">
-        <v>566</v>
+      <c r="J324" s="5" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9047,22 +9285,19 @@
         <v>29</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>212</v>
+        <v>317</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="D325" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G325" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H325" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J325" s="4" t="s">
-        <v>487</v>
+      <c r="J325" s="5" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9070,7 +9305,7 @@
         <v>29</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>210</v>
@@ -9084,8 +9319,8 @@
       <c r="H326" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J326" s="4" t="s">
-        <v>486</v>
+      <c r="J326" s="5" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9093,7 +9328,7 @@
         <v>29</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>318</v>
+        <v>211</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>210</v>
@@ -9107,8 +9342,8 @@
       <c r="H327" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J327" s="4" t="s">
-        <v>567</v>
+      <c r="J327" s="5" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9116,19 +9351,22 @@
         <v>29</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>224</v>
+        <v>318</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>273</v>
+        <v>210</v>
       </c>
       <c r="D328" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G328" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H328" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J328" s="4" t="s">
-        <v>500</v>
+      <c r="J328" s="5" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9136,7 +9374,7 @@
         <v>29</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>273</v>
@@ -9147,8 +9385,8 @@
       <c r="H329" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J329" s="4" t="s">
-        <v>500</v>
+      <c r="J329" s="5" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9156,7 +9394,7 @@
         <v>29</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>273</v>
@@ -9167,8 +9405,8 @@
       <c r="H330" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J330" s="4" t="s">
-        <v>500</v>
+      <c r="J330" s="5" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9176,7 +9414,7 @@
         <v>29</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>273</v>
@@ -9187,8 +9425,8 @@
       <c r="H331" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J331" s="4" t="s">
-        <v>500</v>
+      <c r="J331" s="5" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9196,7 +9434,7 @@
         <v>29</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>273</v>
@@ -9207,8 +9445,8 @@
       <c r="H332" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J332" s="4" t="s">
-        <v>568</v>
+      <c r="J332" s="5" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9216,22 +9454,19 @@
         <v>29</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
       <c r="D333" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G333" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H333" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J333" s="4" t="s">
-        <v>569</v>
+      <c r="J333" s="5" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9239,7 +9474,7 @@
         <v>29</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>321</v>
@@ -9253,8 +9488,8 @@
       <c r="H334" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J334" s="4" t="s">
-        <v>570</v>
+      <c r="J334" s="5" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9262,19 +9497,22 @@
         <v>29</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>52</v>
+        <v>321</v>
       </c>
       <c r="D335" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G335" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H335" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J335" s="4" t="s">
-        <v>531</v>
+      <c r="J335" s="5" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9282,7 +9520,7 @@
         <v>29</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>52</v>
@@ -9293,8 +9531,8 @@
       <c r="H336" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J336" s="4" t="s">
-        <v>479</v>
+      <c r="J336" s="5" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9302,22 +9540,19 @@
         <v>29</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>326</v>
+        <v>52</v>
       </c>
       <c r="D337" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G337" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H337" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J337" s="4" t="s">
-        <v>571</v>
+      <c r="J337" s="5" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9325,10 +9560,10 @@
         <v>29</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D338" s="4" t="b">
         <v>0</v>
@@ -9339,8 +9574,8 @@
       <c r="H338" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J338" s="4" t="s">
-        <v>572</v>
+      <c r="J338" s="5" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9348,109 +9583,132 @@
         <v>29</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D339" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G339" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H339" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J339" s="4" t="s">
-        <v>573</v>
+      <c r="J339" s="5" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>580</v>
+        <v>29</v>
       </c>
       <c r="B340" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D340" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H340" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J340" s="5" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A341" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B341" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C340" s="4" t="s">
+      <c r="C341" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D340" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F340" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="H340" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J340" s="4" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A341" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="B341" s="4" t="s">
+      <c r="D341" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="H341" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J341" s="5" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A342" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B342" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C341" s="4" t="s">
+      <c r="C342" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D341" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H341" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J341" s="4" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A342" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="B342" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="D342" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H342" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J342" s="4" t="s">
-        <v>425</v>
+      <c r="J342" s="5" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>580</v>
+        <v>407</v>
       </c>
       <c r="B343" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D343" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H343" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J343" s="5" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A344" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B344" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C343" s="4" t="s">
+      <c r="C344" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D343" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E343" s="4" t="b">
+      <c r="D344" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E344" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H343" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J343" s="4" t="s">
-        <v>526</v>
+      <c r="H344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J344" s="5" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J343" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:J344" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9492,10 +9750,10 @@
         <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>586</v>
+        <v>413</v>
       </c>
       <c r="D2" t="s">
-        <v>587</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9506,10 +9764,10 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>590</v>
+        <v>417</v>
       </c>
       <c r="E3" t="s">
-        <v>617</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9520,10 +9778,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>591</v>
+        <v>418</v>
       </c>
       <c r="E4" t="s">
-        <v>618</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9534,10 +9792,10 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>592</v>
+        <v>419</v>
       </c>
       <c r="E5" t="s">
-        <v>619</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9548,13 +9806,13 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>593</v>
+        <v>420</v>
       </c>
       <c r="D6" t="s">
-        <v>622</v>
+        <v>449</v>
       </c>
       <c r="E6" t="s">
-        <v>607</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9565,10 +9823,10 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>594</v>
+        <v>421</v>
       </c>
       <c r="E7" t="s">
-        <v>606</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9579,10 +9837,10 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>595</v>
+        <v>422</v>
       </c>
       <c r="E8" t="s">
-        <v>608</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9593,10 +9851,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>596</v>
+        <v>423</v>
       </c>
       <c r="E9" t="s">
-        <v>609</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9607,10 +9865,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>597</v>
+        <v>424</v>
       </c>
       <c r="E10" t="s">
-        <v>620</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9621,10 +9879,10 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>598</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
-        <v>610</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9635,10 +9893,10 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>599</v>
+        <v>426</v>
       </c>
       <c r="E12" t="s">
-        <v>611</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9649,10 +9907,10 @@
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>600</v>
+        <v>427</v>
       </c>
       <c r="E13" t="s">
-        <v>621</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9663,10 +9921,10 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>601</v>
+        <v>428</v>
       </c>
       <c r="E14" t="s">
-        <v>612</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9677,10 +9935,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>602</v>
+        <v>429</v>
       </c>
       <c r="E15" t="s">
-        <v>613</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9691,10 +9949,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>603</v>
+        <v>430</v>
       </c>
       <c r="E16" t="s">
-        <v>614</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9705,10 +9963,10 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>605</v>
+        <v>432</v>
       </c>
       <c r="E17" t="s">
-        <v>615</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9719,10 +9977,10 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>604</v>
+        <v>431</v>
       </c>
       <c r="E18" t="s">
-        <v>616</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -9752,10 +10010,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>627</v>
+        <v>453</v>
       </c>
       <c r="B2" t="s">
-        <v>578</v>
+        <v>405</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -9763,10 +10021,10 @@
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>626</v>
+        <v>452</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>625</v>
+        <v>451</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F448F407-F0F7-414C-AF7C-83BC65D9BE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8577950B-F469-5D41-B8C7-D3F520D383FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1390,9 +1390,6 @@
     <t>Nasabah aktif</t>
   </si>
   <si>
-    <t>Nilai Transaksi</t>
-  </si>
-  <si>
     <t>No Rek Penerima</t>
   </si>
   <si>
@@ -2138,6 +2135,9 @@
   </si>
   <si>
     <t>Tanggal snapshot customer, digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>Nilai Transaksi / Transaction Amount / Amount Transaksi</t>
   </si>
 </sst>
 </file>
@@ -2612,7 +2612,7 @@
     <col min="7" max="7" width="24.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="76.5" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -2711,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -2734,7 +2734,7 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2960,7 +2960,7 @@
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>454</v>
+        <v>703</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3246,7 +3246,7 @@
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3266,7 +3266,7 @@
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3452,7 +3452,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3535,7 +3535,7 @@
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3961,7 +3961,7 @@
         <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3981,7 +3981,7 @@
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4001,7 +4001,7 @@
         <v>10</v>
       </c>
       <c r="J67" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4024,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4044,7 +4044,7 @@
         <v>10</v>
       </c>
       <c r="J69" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4064,7 +4064,7 @@
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="J73" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4224,7 +4224,7 @@
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4244,7 +4244,7 @@
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4264,7 +4264,7 @@
         <v>10</v>
       </c>
       <c r="J80" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4284,7 +4284,7 @@
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4304,7 +4304,7 @@
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4360,7 +4360,7 @@
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4434,7 +4434,7 @@
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4454,7 +4454,7 @@
         <v>10</v>
       </c>
       <c r="J90" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4474,7 +4474,7 @@
         <v>10</v>
       </c>
       <c r="J91" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4494,7 +4494,7 @@
         <v>10</v>
       </c>
       <c r="J92" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4514,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="J93" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4534,7 +4534,7 @@
         <v>10</v>
       </c>
       <c r="J94" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4554,7 +4554,7 @@
         <v>10</v>
       </c>
       <c r="J95" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4574,7 +4574,7 @@
         <v>10</v>
       </c>
       <c r="J96" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4614,7 +4614,7 @@
         <v>10</v>
       </c>
       <c r="J98" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4634,7 +4634,7 @@
         <v>10</v>
       </c>
       <c r="J99" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4873,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="J111" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="J112" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4913,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="J113" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4933,7 +4933,7 @@
         <v>10</v>
       </c>
       <c r="J114" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4953,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="J115" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4973,7 +4973,7 @@
         <v>10</v>
       </c>
       <c r="J116" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4993,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="J117" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5013,7 +5013,7 @@
         <v>10</v>
       </c>
       <c r="J118" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5033,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="J119" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5053,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="J120" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5073,7 +5073,7 @@
         <v>10</v>
       </c>
       <c r="J121" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5113,7 +5113,7 @@
         <v>10</v>
       </c>
       <c r="J123" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5133,7 +5133,7 @@
         <v>10</v>
       </c>
       <c r="J124" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5153,7 +5153,7 @@
         <v>10</v>
       </c>
       <c r="J125" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5173,7 +5173,7 @@
         <v>10</v>
       </c>
       <c r="J126" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5193,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="J127" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5213,7 +5213,7 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5233,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="J129" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5253,7 +5253,7 @@
         <v>10</v>
       </c>
       <c r="J130" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5273,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="J131" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5293,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="J132" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5313,7 +5313,7 @@
         <v>10</v>
       </c>
       <c r="J133" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5333,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="J134" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5353,7 +5353,7 @@
         <v>10</v>
       </c>
       <c r="J135" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5373,7 +5373,7 @@
         <v>10</v>
       </c>
       <c r="J136" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5393,7 +5393,7 @@
         <v>10</v>
       </c>
       <c r="J137" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5453,7 +5453,7 @@
         <v>10</v>
       </c>
       <c r="J140" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5473,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="J141" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5516,7 +5516,7 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5536,7 +5536,7 @@
         <v>10</v>
       </c>
       <c r="J144" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5556,7 +5556,7 @@
         <v>10</v>
       </c>
       <c r="J145" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5576,7 +5576,7 @@
         <v>10</v>
       </c>
       <c r="J146" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5596,7 +5596,7 @@
         <v>10</v>
       </c>
       <c r="J147" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5616,7 +5616,7 @@
         <v>10</v>
       </c>
       <c r="J148" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5636,7 +5636,7 @@
         <v>10</v>
       </c>
       <c r="J149" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5716,7 +5716,7 @@
         <v>10</v>
       </c>
       <c r="J153" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5736,7 +5736,7 @@
         <v>10</v>
       </c>
       <c r="J154" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5756,7 +5756,7 @@
         <v>10</v>
       </c>
       <c r="J155" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5776,7 +5776,7 @@
         <v>10</v>
       </c>
       <c r="J156" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5796,7 +5796,7 @@
         <v>10</v>
       </c>
       <c r="J157" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5816,7 +5816,7 @@
         <v>10</v>
       </c>
       <c r="J158" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5836,7 +5836,7 @@
         <v>10</v>
       </c>
       <c r="J159" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="J160" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5876,7 +5876,7 @@
         <v>10</v>
       </c>
       <c r="J161" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="J162" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5916,7 +5916,7 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5936,7 +5936,7 @@
         <v>10</v>
       </c>
       <c r="J164" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5956,7 +5956,7 @@
         <v>10</v>
       </c>
       <c r="J165" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5976,7 +5976,7 @@
         <v>10</v>
       </c>
       <c r="J166" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5996,7 +5996,7 @@
         <v>10</v>
       </c>
       <c r="J167" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6019,7 +6019,7 @@
         <v>10</v>
       </c>
       <c r="J168" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6039,7 +6039,7 @@
         <v>10</v>
       </c>
       <c r="J169" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6059,7 +6059,7 @@
         <v>10</v>
       </c>
       <c r="J170" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6079,7 +6079,7 @@
         <v>10</v>
       </c>
       <c r="J171" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6099,7 +6099,7 @@
         <v>10</v>
       </c>
       <c r="J172" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6119,7 +6119,7 @@
         <v>10</v>
       </c>
       <c r="J173" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6139,7 +6139,7 @@
         <v>10</v>
       </c>
       <c r="J174" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6159,7 +6159,7 @@
         <v>10</v>
       </c>
       <c r="J175" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6179,7 +6179,7 @@
         <v>10</v>
       </c>
       <c r="J176" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6199,7 +6199,7 @@
         <v>10</v>
       </c>
       <c r="J177" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6219,7 +6219,7 @@
         <v>10</v>
       </c>
       <c r="J178" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6239,7 +6239,7 @@
         <v>10</v>
       </c>
       <c r="J179" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6262,7 +6262,7 @@
         <v>10</v>
       </c>
       <c r="J180" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6285,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="J181" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6308,7 +6308,7 @@
         <v>10</v>
       </c>
       <c r="J182" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6331,7 +6331,7 @@
         <v>10</v>
       </c>
       <c r="J183" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6354,7 +6354,7 @@
         <v>10</v>
       </c>
       <c r="J184" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6374,7 +6374,7 @@
         <v>10</v>
       </c>
       <c r="J185" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6394,7 +6394,7 @@
         <v>10</v>
       </c>
       <c r="J186" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6414,7 +6414,7 @@
         <v>10</v>
       </c>
       <c r="J187" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6454,7 +6454,7 @@
         <v>10</v>
       </c>
       <c r="J189" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6474,7 +6474,7 @@
         <v>10</v>
       </c>
       <c r="J190" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6494,7 +6494,7 @@
         <v>10</v>
       </c>
       <c r="J191" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6514,7 +6514,7 @@
         <v>10</v>
       </c>
       <c r="J192" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6534,7 +6534,7 @@
         <v>10</v>
       </c>
       <c r="J193" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6554,7 +6554,7 @@
         <v>10</v>
       </c>
       <c r="J194" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6574,7 +6574,7 @@
         <v>10</v>
       </c>
       <c r="J195" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6594,7 +6594,7 @@
         <v>10</v>
       </c>
       <c r="J196" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6614,7 +6614,7 @@
         <v>10</v>
       </c>
       <c r="J197" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6634,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="J198" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6654,7 +6654,7 @@
         <v>10</v>
       </c>
       <c r="J199" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6674,7 +6674,7 @@
         <v>10</v>
       </c>
       <c r="J200" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6694,7 +6694,7 @@
         <v>10</v>
       </c>
       <c r="J201" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6714,7 +6714,7 @@
         <v>10</v>
       </c>
       <c r="J202" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6737,7 +6737,7 @@
         <v>10</v>
       </c>
       <c r="J203" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6760,7 +6760,7 @@
         <v>10</v>
       </c>
       <c r="J204" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6783,7 +6783,7 @@
         <v>10</v>
       </c>
       <c r="J205" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6806,7 +6806,7 @@
         <v>10</v>
       </c>
       <c r="J206" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6829,7 +6829,7 @@
         <v>10</v>
       </c>
       <c r="J207" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6852,10 +6852,10 @@
         <v>10</v>
       </c>
       <c r="J208" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>27</v>
       </c>
@@ -6875,10 +6875,10 @@
         <v>10</v>
       </c>
       <c r="J209" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>27</v>
       </c>
@@ -6898,10 +6898,10 @@
         <v>10</v>
       </c>
       <c r="J210" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>27</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="J211" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6944,10 +6944,10 @@
         <v>10</v>
       </c>
       <c r="J212" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>27</v>
       </c>
@@ -6964,10 +6964,10 @@
         <v>10</v>
       </c>
       <c r="J213" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>27</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>10</v>
       </c>
       <c r="J214" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7004,7 +7004,7 @@
         <v>10</v>
       </c>
       <c r="J215" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7027,7 +7027,7 @@
         <v>10</v>
       </c>
       <c r="J216" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7050,10 +7050,10 @@
         <v>10</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
         <v>27</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>10</v>
       </c>
       <c r="J218" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7093,7 +7093,7 @@
         <v>10</v>
       </c>
       <c r="J219" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7113,10 +7113,10 @@
         <v>10</v>
       </c>
       <c r="J220" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>27</v>
       </c>
@@ -7133,10 +7133,10 @@
         <v>10</v>
       </c>
       <c r="J221" s="5" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>27</v>
       </c>
@@ -7153,10 +7153,10 @@
         <v>10</v>
       </c>
       <c r="J222" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>27</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>10</v>
       </c>
       <c r="J223" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7193,7 +7193,7 @@
         <v>10</v>
       </c>
       <c r="J224" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7213,7 +7213,7 @@
         <v>10</v>
       </c>
       <c r="J225" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="J226" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7253,7 +7253,7 @@
         <v>10</v>
       </c>
       <c r="J227" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7273,10 +7273,10 @@
         <v>10</v>
       </c>
       <c r="J228" s="5" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>27</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>10</v>
       </c>
       <c r="J229" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7316,7 +7316,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7339,7 +7339,7 @@
         <v>10</v>
       </c>
       <c r="J231" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7362,7 +7362,7 @@
         <v>10</v>
       </c>
       <c r="J232" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7385,10 +7385,10 @@
         <v>10</v>
       </c>
       <c r="J233" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
         <v>27</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>10</v>
       </c>
       <c r="J234" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7431,10 +7431,10 @@
         <v>10</v>
       </c>
       <c r="J235" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>27</v>
       </c>
@@ -7454,10 +7454,10 @@
         <v>10</v>
       </c>
       <c r="J236" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
         <v>27</v>
       </c>
@@ -7477,7 +7477,7 @@
         <v>10</v>
       </c>
       <c r="J237" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7497,10 +7497,10 @@
         <v>10</v>
       </c>
       <c r="J238" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>27</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>10</v>
       </c>
       <c r="J239" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7540,7 +7540,7 @@
         <v>10</v>
       </c>
       <c r="J240" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7563,7 +7563,7 @@
         <v>10</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="242" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -7583,7 +7583,7 @@
         <v>10</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7603,7 +7603,7 @@
         <v>10</v>
       </c>
       <c r="J243" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7626,7 +7626,7 @@
         <v>10</v>
       </c>
       <c r="J244" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -7646,7 +7646,7 @@
         <v>10</v>
       </c>
       <c r="J245" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7666,7 +7666,7 @@
         <v>10</v>
       </c>
       <c r="J246" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -7686,7 +7686,7 @@
         <v>10</v>
       </c>
       <c r="J247" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7706,7 +7706,7 @@
         <v>10</v>
       </c>
       <c r="J248" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7726,7 +7726,7 @@
         <v>10</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7746,7 +7746,7 @@
         <v>10</v>
       </c>
       <c r="J250" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7766,7 +7766,7 @@
         <v>10</v>
       </c>
       <c r="J251" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7786,7 +7786,7 @@
         <v>10</v>
       </c>
       <c r="J252" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7806,7 +7806,7 @@
         <v>10</v>
       </c>
       <c r="J253" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7826,7 +7826,7 @@
         <v>10</v>
       </c>
       <c r="J254" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -7846,10 +7846,10 @@
         <v>10</v>
       </c>
       <c r="J255" s="5" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>29</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>10</v>
       </c>
       <c r="J256" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7886,7 +7886,7 @@
         <v>10</v>
       </c>
       <c r="J257" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7906,7 +7906,7 @@
         <v>10</v>
       </c>
       <c r="J258" s="5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7926,7 +7926,7 @@
         <v>10</v>
       </c>
       <c r="J259" s="5" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7946,7 +7946,7 @@
         <v>10</v>
       </c>
       <c r="J260" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7966,7 +7966,7 @@
         <v>10</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7986,10 +7986,10 @@
         <v>10</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>29</v>
       </c>
@@ -8006,10 +8006,10 @@
         <v>10</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>29</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>10</v>
       </c>
       <c r="J264" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8046,7 +8046,7 @@
         <v>10</v>
       </c>
       <c r="J265" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="J266" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8086,7 +8086,7 @@
         <v>10</v>
       </c>
       <c r="J267" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8106,7 +8106,7 @@
         <v>10</v>
       </c>
       <c r="J268" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8126,7 +8126,7 @@
         <v>10</v>
       </c>
       <c r="J269" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8146,7 +8146,7 @@
         <v>10</v>
       </c>
       <c r="J270" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8166,7 +8166,7 @@
         <v>10</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8186,10 +8186,10 @@
         <v>10</v>
       </c>
       <c r="J272" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>29</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>10</v>
       </c>
       <c r="J273" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8226,7 +8226,7 @@
         <v>10</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8246,10 +8246,10 @@
         <v>10</v>
       </c>
       <c r="J275" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>29</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>10</v>
       </c>
       <c r="J276" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -8286,7 +8286,7 @@
         <v>10</v>
       </c>
       <c r="J277" s="5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8306,7 +8306,7 @@
         <v>10</v>
       </c>
       <c r="J278" s="5" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8326,10 +8326,10 @@
         <v>10</v>
       </c>
       <c r="J279" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>29</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>10</v>
       </c>
       <c r="J280" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8366,7 +8366,7 @@
         <v>10</v>
       </c>
       <c r="J281" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8386,7 +8386,7 @@
         <v>10</v>
       </c>
       <c r="J282" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8406,7 +8406,7 @@
         <v>10</v>
       </c>
       <c r="J283" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8426,10 +8426,10 @@
         <v>10</v>
       </c>
       <c r="J284" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>29</v>
       </c>
@@ -8446,10 +8446,10 @@
         <v>10</v>
       </c>
       <c r="J285" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>29</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>10</v>
       </c>
       <c r="J286" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8486,7 +8486,7 @@
         <v>10</v>
       </c>
       <c r="J287" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8506,7 +8506,7 @@
         <v>10</v>
       </c>
       <c r="J288" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8526,7 +8526,7 @@
         <v>10</v>
       </c>
       <c r="J289" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8546,7 +8546,7 @@
         <v>10</v>
       </c>
       <c r="J290" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8566,7 +8566,7 @@
         <v>10</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8586,10 +8586,10 @@
         <v>10</v>
       </c>
       <c r="J292" s="5" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>29</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>10</v>
       </c>
       <c r="J293" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8626,7 +8626,7 @@
         <v>10</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8646,10 +8646,10 @@
         <v>10</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>29</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>10</v>
       </c>
       <c r="J296" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8686,7 +8686,7 @@
         <v>10</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8709,10 +8709,10 @@
         <v>10</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
         <v>29</v>
       </c>
@@ -8732,10 +8732,10 @@
         <v>10</v>
       </c>
       <c r="J299" s="5" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
         <v>29</v>
       </c>
@@ -8755,10 +8755,10 @@
         <v>10</v>
       </c>
       <c r="J300" s="5" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>29</v>
       </c>
@@ -8778,10 +8778,10 @@
         <v>10</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
         <v>29</v>
       </c>
@@ -8801,10 +8801,10 @@
         <v>10</v>
       </c>
       <c r="J302" s="5" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>29</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8847,10 +8847,10 @@
         <v>10</v>
       </c>
       <c r="J304" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
         <v>29</v>
       </c>
@@ -8870,10 +8870,10 @@
         <v>10</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>29</v>
       </c>
@@ -8893,7 +8893,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8916,7 +8916,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8939,10 +8939,10 @@
         <v>10</v>
       </c>
       <c r="J308" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
         <v>29</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8985,10 +8985,10 @@
         <v>10</v>
       </c>
       <c r="J310" s="5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
         <v>29</v>
       </c>
@@ -9008,10 +9008,10 @@
         <v>10</v>
       </c>
       <c r="J311" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>29</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9054,7 +9054,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9077,7 +9077,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9097,7 +9097,7 @@
         <v>10</v>
       </c>
       <c r="J315" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9117,10 +9117,10 @@
         <v>10</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>29</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>10</v>
       </c>
       <c r="J317" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9157,7 +9157,7 @@
         <v>10</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9177,7 +9177,7 @@
         <v>10</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9197,10 +9197,10 @@
         <v>10</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>29</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>10</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9237,7 +9237,7 @@
         <v>10</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9257,7 +9257,7 @@
         <v>10</v>
       </c>
       <c r="J323" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9277,7 +9277,7 @@
         <v>10</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9297,10 +9297,10 @@
         <v>10</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>29</v>
       </c>
@@ -9320,10 +9320,10 @@
         <v>10</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
         <v>29</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9366,7 +9366,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9386,7 +9386,7 @@
         <v>10</v>
       </c>
       <c r="J329" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9406,7 +9406,7 @@
         <v>10</v>
       </c>
       <c r="J330" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="J331" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9446,7 +9446,7 @@
         <v>10</v>
       </c>
       <c r="J332" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9466,7 +9466,7 @@
         <v>10</v>
       </c>
       <c r="J333" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9489,7 +9489,7 @@
         <v>10</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9512,7 +9512,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9532,7 +9532,7 @@
         <v>10</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9552,7 +9552,7 @@
         <v>10</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9575,7 +9575,7 @@
         <v>10</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9598,7 +9598,7 @@
         <v>10</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9618,7 +9618,7 @@
         <v>10</v>
       </c>
       <c r="J340" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="341" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -9641,7 +9641,7 @@
         <v>10</v>
       </c>
       <c r="J341" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -9661,7 +9661,7 @@
         <v>10</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9681,7 +9681,7 @@
         <v>10</v>
       </c>
       <c r="J343" s="5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="344" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9704,7 +9704,7 @@
         <v>10</v>
       </c>
       <c r="J344" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8577950B-F469-5D41-B8C7-D3F520D383FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE2D0E5-A2FC-754C-9BB6-E026923EE0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2648,7 +2648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -3590,9 +3590,6 @@
       </c>
       <c r="D47" s="4" t="b">
         <v>0</v>
-      </c>
-      <c r="E47" s="4" t="b">
-        <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>10</v>
@@ -6855,7 +6852,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>27</v>
       </c>
@@ -6878,7 +6875,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>27</v>
       </c>
@@ -6901,7 +6898,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>27</v>
       </c>
@@ -6947,7 +6944,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>27</v>
       </c>
@@ -6967,7 +6964,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>27</v>
       </c>
@@ -7053,7 +7050,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
         <v>27</v>
       </c>
@@ -7116,7 +7113,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>27</v>
       </c>
@@ -7136,7 +7133,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>27</v>
       </c>
@@ -7156,7 +7153,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>27</v>
       </c>
@@ -7276,7 +7273,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>27</v>
       </c>
@@ -7388,7 +7385,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
         <v>27</v>
       </c>
@@ -7434,7 +7431,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>27</v>
       </c>
@@ -7457,7 +7454,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
         <v>27</v>
       </c>
@@ -7500,7 +7497,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>27</v>
       </c>
@@ -7566,7 +7563,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>29</v>
       </c>
@@ -7629,7 +7626,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
         <v>29</v>
       </c>
@@ -7669,7 +7666,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>29</v>
       </c>
@@ -7829,7 +7826,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>29</v>
       </c>
@@ -7849,7 +7846,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>29</v>
       </c>
@@ -7989,7 +7986,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>29</v>
       </c>
@@ -8009,7 +8006,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>29</v>
       </c>
@@ -8189,7 +8186,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>29</v>
       </c>
@@ -8249,7 +8246,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>29</v>
       </c>
@@ -8269,7 +8266,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>29</v>
       </c>
@@ -8329,7 +8326,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>29</v>
       </c>
@@ -8429,7 +8426,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>29</v>
       </c>
@@ -8449,7 +8446,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>29</v>
       </c>
@@ -8589,7 +8586,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>29</v>
       </c>
@@ -8649,7 +8646,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>29</v>
       </c>
@@ -8712,7 +8709,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
         <v>29</v>
       </c>
@@ -8735,7 +8732,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
         <v>29</v>
       </c>
@@ -8758,7 +8755,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>29</v>
       </c>
@@ -8781,7 +8778,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
         <v>29</v>
       </c>
@@ -8804,7 +8801,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>29</v>
       </c>
@@ -8850,7 +8847,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
         <v>29</v>
       </c>
@@ -8873,7 +8870,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>29</v>
       </c>
@@ -8942,7 +8939,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="309" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
         <v>29</v>
       </c>
@@ -8988,7 +8985,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
         <v>29</v>
       </c>
@@ -9011,7 +9008,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="312" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>29</v>
       </c>
@@ -9120,7 +9117,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>29</v>
       </c>
@@ -9200,7 +9197,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>29</v>
       </c>
@@ -9300,7 +9297,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="326" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>29</v>
       </c>
@@ -9323,7 +9320,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="327" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
         <v>29</v>
       </c>
@@ -9621,7 +9618,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>407</v>
       </c>
@@ -9644,7 +9641,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>407</v>
       </c>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE2D0E5-A2FC-754C-9BB6-E026923EE0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE2D0E5-A2FC-754C-9BB6-E026923EE0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222849E5-03C4-9143-A1A0-2D39E2730B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="Golden_Queries" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$J$344</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$J$345</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="705">
   <si>
     <t>Table Name</t>
   </si>
@@ -1378,9 +1378,6 @@
     <t>Wonder</t>
   </si>
   <si>
-    <t>Tanggal Transaksi Data, digunakan untuk filter tanggal, bulan, tahun</t>
-  </si>
-  <si>
     <t>SELECT * FROM dm_transaction.trxchannel WHERE destination_bankname &lt;&gt; 'BANK NEGARA INDONESIA';</t>
   </si>
   <si>
@@ -1528,9 +1525,6 @@
     <t>Hasil mapping/mirror dari pemilik channel.</t>
   </si>
   <si>
-    <t>Tanggal posisi atau snapshot data.</t>
-  </si>
-  <si>
     <t>ID nasabah/entity pada sistem Master Data Management.</t>
   </si>
   <si>
@@ -1798,9 +1792,6 @@
     <t>Nasabah/perusahaan utama dalam satu kelompok usaha atau grup.</t>
   </si>
   <si>
-    <t>Tanggal posisi/snapshot data.</t>
-  </si>
-  <si>
     <t>CIF Key Nasabah (ID Nasabah)</t>
   </si>
   <si>
@@ -2134,10 +2125,22 @@
     <t>Divisi pemilik segmen.</t>
   </si>
   <si>
-    <t>Tanggal snapshot customer, digunakan untuk filter tanggal, bulan, tahun</t>
-  </si>
-  <si>
     <t>Nilai Transaksi / Transaction Amount / Amount Transaksi</t>
+  </si>
+  <si>
+    <t>Tanggal posisi atau snapshot data pada table funding. Digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>Tanggal posisi atau snapshot data pada table lending. Digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>Tanggal posisi atau snapshot data pada table mapping_group_whs. Digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>Tanggal posisi atau snapshot data pada table customer / nasabah. Digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>Tanggal posisi atau tanggal transaksi data, digunakan untuk filter tanggal, bulan, tahun</t>
   </si>
 </sst>
 </file>
@@ -2600,7 +2603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J344"/>
+  <dimension ref="A1:J345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" style="4" customWidth="1"/>
@@ -2668,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>450</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2711,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -2734,7 +2737,7 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2960,7 +2963,7 @@
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3246,7 +3249,7 @@
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3266,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3432,7 +3435,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -3451,8 +3454,8 @@
       <c r="H40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J40" s="4" t="s">
-        <v>702</v>
+      <c r="J40" s="5" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3535,7 +3538,7 @@
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3958,7 +3961,7 @@
         <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3978,7 +3981,7 @@
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3998,7 +4001,7 @@
         <v>10</v>
       </c>
       <c r="J67" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4021,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4041,7 +4044,7 @@
         <v>10</v>
       </c>
       <c r="J69" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4061,7 +4064,7 @@
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4121,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="J73" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4221,7 +4224,7 @@
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4241,7 +4244,7 @@
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4261,7 +4264,7 @@
         <v>10</v>
       </c>
       <c r="J80" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4281,7 +4284,7 @@
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4301,7 +4304,7 @@
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4357,7 +4360,7 @@
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4431,7 +4434,7 @@
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4451,7 +4454,7 @@
         <v>10</v>
       </c>
       <c r="J90" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4471,7 +4474,7 @@
         <v>10</v>
       </c>
       <c r="J91" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4491,7 +4494,7 @@
         <v>10</v>
       </c>
       <c r="J92" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4511,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="J93" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4531,7 +4534,7 @@
         <v>10</v>
       </c>
       <c r="J94" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4551,7 +4554,7 @@
         <v>10</v>
       </c>
       <c r="J95" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4571,7 +4574,7 @@
         <v>10</v>
       </c>
       <c r="J96" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4611,7 +4614,7 @@
         <v>10</v>
       </c>
       <c r="J98" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4631,7 +4634,7 @@
         <v>10</v>
       </c>
       <c r="J99" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4870,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="J111" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4890,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="J112" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4910,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="J113" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4930,7 +4933,7 @@
         <v>10</v>
       </c>
       <c r="J114" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4950,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="J115" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4970,7 +4973,7 @@
         <v>10</v>
       </c>
       <c r="J116" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4990,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="J117" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5010,7 +5013,7 @@
         <v>10</v>
       </c>
       <c r="J118" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5030,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="J119" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5050,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="J120" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5070,7 +5073,7 @@
         <v>10</v>
       </c>
       <c r="J121" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5090,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5110,7 +5113,7 @@
         <v>10</v>
       </c>
       <c r="J123" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5130,7 +5133,7 @@
         <v>10</v>
       </c>
       <c r="J124" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5150,7 +5153,7 @@
         <v>10</v>
       </c>
       <c r="J125" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5170,7 +5173,7 @@
         <v>10</v>
       </c>
       <c r="J126" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5190,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="J127" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5210,7 +5213,7 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5230,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="J129" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5250,7 +5253,7 @@
         <v>10</v>
       </c>
       <c r="J130" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5270,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="J131" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5290,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="J132" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5310,7 +5313,7 @@
         <v>10</v>
       </c>
       <c r="J133" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5330,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="J134" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5350,7 +5353,7 @@
         <v>10</v>
       </c>
       <c r="J135" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5370,7 +5373,7 @@
         <v>10</v>
       </c>
       <c r="J136" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5390,7 +5393,7 @@
         <v>10</v>
       </c>
       <c r="J137" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5450,7 +5453,7 @@
         <v>10</v>
       </c>
       <c r="J140" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5458,19 +5461,22 @@
         <v>27</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D141" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E141" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J141" t="s">
-        <v>651</v>
+      <c r="J141" s="5" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5478,22 +5484,19 @@
         <v>27</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D142" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>403</v>
+        <v>1</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J142" t="s">
-        <v>402</v>
+        <v>648</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5501,19 +5504,22 @@
         <v>27</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="D143" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="F143" s="4" t="s">
+        <v>403</v>
+      </c>
       <c r="H143" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>653</v>
+        <v>402</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5521,10 +5527,10 @@
         <v>27</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D144" s="4" t="b">
         <v>0</v>
@@ -5533,7 +5539,7 @@
         <v>10</v>
       </c>
       <c r="J144" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5541,10 +5547,10 @@
         <v>27</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D145" s="4" t="b">
         <v>0</v>
@@ -5553,7 +5559,7 @@
         <v>10</v>
       </c>
       <c r="J145" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5561,10 +5567,10 @@
         <v>27</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D146" s="4" t="b">
         <v>0</v>
@@ -5573,7 +5579,7 @@
         <v>10</v>
       </c>
       <c r="J146" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5581,10 +5587,10 @@
         <v>27</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D147" s="4" t="b">
         <v>0</v>
@@ -5593,7 +5599,7 @@
         <v>10</v>
       </c>
       <c r="J147" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5601,10 +5607,10 @@
         <v>27</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D148" s="4" t="b">
         <v>0</v>
@@ -5613,7 +5619,7 @@
         <v>10</v>
       </c>
       <c r="J148" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5621,10 +5627,10 @@
         <v>27</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D149" s="4" t="b">
         <v>0</v>
@@ -5633,7 +5639,7 @@
         <v>10</v>
       </c>
       <c r="J149" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5641,10 +5647,10 @@
         <v>27</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="D150" s="4" t="b">
         <v>0</v>
@@ -5653,7 +5659,7 @@
         <v>10</v>
       </c>
       <c r="J150" t="s">
-        <v>367</v>
+        <v>654</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5661,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>180</v>
@@ -5673,7 +5679,7 @@
         <v>10</v>
       </c>
       <c r="J151" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5681,10 +5687,10 @@
         <v>27</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D152" s="4" t="b">
         <v>0</v>
@@ -5693,7 +5699,7 @@
         <v>10</v>
       </c>
       <c r="J152" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5701,7 +5707,7 @@
         <v>27</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>182</v>
@@ -5713,7 +5719,7 @@
         <v>10</v>
       </c>
       <c r="J153" t="s">
-        <v>465</v>
+        <v>379</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5721,10 +5727,10 @@
         <v>27</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="D154" s="4" t="b">
         <v>0</v>
@@ -5733,7 +5739,7 @@
         <v>10</v>
       </c>
       <c r="J154" t="s">
-        <v>615</v>
+        <v>464</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5741,10 +5747,10 @@
         <v>27</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D155" s="4" t="b">
         <v>0</v>
@@ -5753,7 +5759,7 @@
         <v>10</v>
       </c>
       <c r="J155" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5761,10 +5767,10 @@
         <v>27</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="D156" s="4" t="b">
         <v>0</v>
@@ -5773,7 +5779,7 @@
         <v>10</v>
       </c>
       <c r="J156" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5781,10 +5787,10 @@
         <v>27</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="D157" s="4" t="b">
         <v>0</v>
@@ -5793,7 +5799,7 @@
         <v>10</v>
       </c>
       <c r="J157" t="s">
-        <v>638</v>
+        <v>614</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5801,7 +5807,7 @@
         <v>27</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>76</v>
@@ -5813,7 +5819,7 @@
         <v>10</v>
       </c>
       <c r="J158" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5821,10 +5827,10 @@
         <v>27</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D159" s="4" t="b">
         <v>0</v>
@@ -5833,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="J159" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5841,10 +5847,10 @@
         <v>27</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="D160" s="4" t="b">
         <v>0</v>
@@ -5853,7 +5859,7 @@
         <v>10</v>
       </c>
       <c r="J160" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5861,10 +5867,10 @@
         <v>27</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>38</v>
+        <v>189</v>
       </c>
       <c r="D161" s="4" t="b">
         <v>0</v>
@@ -5873,7 +5879,7 @@
         <v>10</v>
       </c>
       <c r="J161" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5881,10 +5887,10 @@
         <v>27</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D162" s="4" t="b">
         <v>0</v>
@@ -5893,7 +5899,7 @@
         <v>10</v>
       </c>
       <c r="J162" t="s">
-        <v>456</v>
+        <v>630</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5901,10 +5907,10 @@
         <v>27</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D163" s="4" t="b">
         <v>0</v>
@@ -5913,7 +5919,7 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5921,10 +5927,10 @@
         <v>27</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D164" s="4" t="b">
         <v>0</v>
@@ -5933,7 +5939,7 @@
         <v>10</v>
       </c>
       <c r="J164" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5941,10 +5947,10 @@
         <v>27</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="D165" s="4" t="b">
         <v>0</v>
@@ -5953,7 +5959,7 @@
         <v>10</v>
       </c>
       <c r="J165" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5961,10 +5967,10 @@
         <v>27</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="D166" s="4" t="b">
         <v>0</v>
@@ -5973,7 +5979,7 @@
         <v>10</v>
       </c>
       <c r="J166" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5981,10 +5987,10 @@
         <v>27</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D167" s="4" t="b">
         <v>0</v>
@@ -5993,7 +5999,7 @@
         <v>10</v>
       </c>
       <c r="J167" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6001,22 +6007,19 @@
         <v>27</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D168" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E168" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H168" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J168" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6024,7 +6027,7 @@
         <v>27</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>32</v>
@@ -6032,11 +6035,14 @@
       <c r="D169" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="E169" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="H169" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J169" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6044,7 +6050,7 @@
         <v>27</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>32</v>
@@ -6056,7 +6062,7 @@
         <v>10</v>
       </c>
       <c r="J170" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6064,10 +6070,10 @@
         <v>27</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D171" s="4" t="b">
         <v>0</v>
@@ -6076,7 +6082,7 @@
         <v>10</v>
       </c>
       <c r="J171" t="s">
-        <v>634</v>
+        <v>463</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6084,10 +6090,10 @@
         <v>27</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="D172" s="4" t="b">
         <v>0</v>
@@ -6096,7 +6102,7 @@
         <v>10</v>
       </c>
       <c r="J172" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6104,10 +6110,10 @@
         <v>27</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="D173" s="4" t="b">
         <v>0</v>
@@ -6116,7 +6122,7 @@
         <v>10</v>
       </c>
       <c r="J173" t="s">
-        <v>659</v>
+        <v>632</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6124,10 +6130,10 @@
         <v>27</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D174" s="4" t="b">
         <v>0</v>
@@ -6136,7 +6142,7 @@
         <v>10</v>
       </c>
       <c r="J174" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6144,10 +6150,10 @@
         <v>27</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D175" s="4" t="b">
         <v>0</v>
@@ -6156,7 +6162,7 @@
         <v>10</v>
       </c>
       <c r="J175" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6164,7 +6170,7 @@
         <v>27</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>45</v>
@@ -6176,7 +6182,7 @@
         <v>10</v>
       </c>
       <c r="J176" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6184,7 +6190,7 @@
         <v>27</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>45</v>
@@ -6196,7 +6202,7 @@
         <v>10</v>
       </c>
       <c r="J177" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6204,10 +6210,10 @@
         <v>27</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D178" s="4" t="b">
         <v>0</v>
@@ -6216,7 +6222,7 @@
         <v>10</v>
       </c>
       <c r="J178" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6224,10 +6230,10 @@
         <v>27</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D179" s="4" t="b">
         <v>0</v>
@@ -6236,7 +6242,7 @@
         <v>10</v>
       </c>
       <c r="J179" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6244,22 +6250,19 @@
         <v>27</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="D180" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G180" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H180" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J180" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6267,7 +6270,7 @@
         <v>27</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>210</v>
@@ -6282,7 +6285,7 @@
         <v>10</v>
       </c>
       <c r="J181" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6290,7 +6293,7 @@
         <v>27</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>210</v>
@@ -6305,7 +6308,7 @@
         <v>10</v>
       </c>
       <c r="J182" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6313,7 +6316,7 @@
         <v>27</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>210</v>
@@ -6328,7 +6331,7 @@
         <v>10</v>
       </c>
       <c r="J183" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6336,7 +6339,7 @@
         <v>27</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>210</v>
@@ -6351,7 +6354,7 @@
         <v>10</v>
       </c>
       <c r="J184" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6359,19 +6362,22 @@
         <v>27</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="D185" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G185" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H185" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J185" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6379,10 +6385,10 @@
         <v>27</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D186" s="4" t="b">
         <v>0</v>
@@ -6391,7 +6397,7 @@
         <v>10</v>
       </c>
       <c r="J186" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6399,7 +6405,7 @@
         <v>27</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>38</v>
@@ -6411,7 +6417,7 @@
         <v>10</v>
       </c>
       <c r="J187" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6419,7 +6425,7 @@
         <v>27</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>38</v>
@@ -6431,7 +6437,7 @@
         <v>10</v>
       </c>
       <c r="J188" t="s">
-        <v>382</v>
+        <v>669</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6439,7 +6445,7 @@
         <v>27</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>38</v>
@@ -6451,7 +6457,7 @@
         <v>10</v>
       </c>
       <c r="J189" t="s">
-        <v>465</v>
+        <v>382</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6459,7 +6465,7 @@
         <v>27</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>38</v>
@@ -6471,7 +6477,7 @@
         <v>10</v>
       </c>
       <c r="J190" t="s">
-        <v>673</v>
+        <v>464</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6479,10 +6485,10 @@
         <v>27</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D191" s="4" t="b">
         <v>0</v>
@@ -6491,7 +6497,7 @@
         <v>10</v>
       </c>
       <c r="J191" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6499,7 +6505,7 @@
         <v>27</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>52</v>
@@ -6511,7 +6517,7 @@
         <v>10</v>
       </c>
       <c r="J192" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6519,10 +6525,10 @@
         <v>27</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D193" s="4" t="b">
         <v>0</v>
@@ -6531,7 +6537,7 @@
         <v>10</v>
       </c>
       <c r="J193" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6539,7 +6545,7 @@
         <v>27</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>38</v>
@@ -6551,7 +6557,7 @@
         <v>10</v>
       </c>
       <c r="J194" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6559,10 +6565,10 @@
         <v>27</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D195" s="4" t="b">
         <v>0</v>
@@ -6571,7 +6577,7 @@
         <v>10</v>
       </c>
       <c r="J195" t="s">
-        <v>629</v>
+        <v>674</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6579,10 +6585,10 @@
         <v>27</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D196" s="4" t="b">
         <v>0</v>
@@ -6591,7 +6597,7 @@
         <v>10</v>
       </c>
       <c r="J196" t="s">
-        <v>678</v>
+        <v>626</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6599,10 +6605,10 @@
         <v>27</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>224</v>
+        <v>153</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D197" s="4" t="b">
         <v>0</v>
@@ -6611,7 +6617,7 @@
         <v>10</v>
       </c>
       <c r="J197" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6619,7 +6625,7 @@
         <v>27</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>45</v>
@@ -6631,7 +6637,7 @@
         <v>10</v>
       </c>
       <c r="J198" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6639,7 +6645,7 @@
         <v>27</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>45</v>
@@ -6651,7 +6657,7 @@
         <v>10</v>
       </c>
       <c r="J199" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6659,7 +6665,7 @@
         <v>27</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>45</v>
@@ -6671,7 +6677,7 @@
         <v>10</v>
       </c>
       <c r="J200" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6679,7 +6685,7 @@
         <v>27</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>45</v>
@@ -6691,7 +6697,7 @@
         <v>10</v>
       </c>
       <c r="J201" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6699,7 +6705,7 @@
         <v>27</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>45</v>
@@ -6711,7 +6717,7 @@
         <v>10</v>
       </c>
       <c r="J202" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6719,22 +6725,19 @@
         <v>27</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="D203" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G203" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H203" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J203" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6742,7 +6745,7 @@
         <v>27</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>210</v>
@@ -6757,7 +6760,7 @@
         <v>10</v>
       </c>
       <c r="J204" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6765,7 +6768,7 @@
         <v>27</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>210</v>
@@ -6780,7 +6783,7 @@
         <v>10</v>
       </c>
       <c r="J205" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6788,7 +6791,7 @@
         <v>27</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>210</v>
@@ -6803,7 +6806,7 @@
         <v>10</v>
       </c>
       <c r="J206" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6811,7 +6814,7 @@
         <v>27</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>210</v>
@@ -6826,7 +6829,7 @@
         <v>10</v>
       </c>
       <c r="J207" t="s">
-        <v>466</v>
+        <v>685</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6834,7 +6837,7 @@
         <v>27</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>210</v>
@@ -6849,7 +6852,7 @@
         <v>10</v>
       </c>
       <c r="J208" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6857,7 +6860,7 @@
         <v>27</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>210</v>
@@ -6871,8 +6874,8 @@
       <c r="H209" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J209" s="5" t="s">
-        <v>468</v>
+      <c r="J209" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6880,7 +6883,7 @@
         <v>27</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>210</v>
@@ -6895,7 +6898,7 @@
         <v>10</v>
       </c>
       <c r="J210" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6903,7 +6906,7 @@
         <v>27</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>210</v>
@@ -6918,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="J211" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6926,7 +6929,7 @@
         <v>27</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>210</v>
@@ -6941,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="J212" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6949,19 +6952,22 @@
         <v>27</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="D213" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G213" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H213" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J213" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6969,7 +6975,7 @@
         <v>27</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>38</v>
@@ -6981,7 +6987,7 @@
         <v>10</v>
       </c>
       <c r="J214" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6989,7 +6995,7 @@
         <v>27</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>38</v>
@@ -7001,7 +7007,7 @@
         <v>10</v>
       </c>
       <c r="J215" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7009,22 +7015,19 @@
         <v>27</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="D216" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G216" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H216" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J216" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7032,7 +7035,7 @@
         <v>27</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>243</v>
@@ -7047,7 +7050,7 @@
         <v>10</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7055,7 +7058,7 @@
         <v>27</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>243</v>
@@ -7070,7 +7073,7 @@
         <v>10</v>
       </c>
       <c r="J218" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7078,19 +7081,22 @@
         <v>27</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="D219" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G219" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H219" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J219" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7098,10 +7104,10 @@
         <v>27</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D220" s="4" t="b">
         <v>0</v>
@@ -7110,7 +7116,7 @@
         <v>10</v>
       </c>
       <c r="J220" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7118,10 +7124,10 @@
         <v>27</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D221" s="4" t="b">
         <v>0</v>
@@ -7130,7 +7136,7 @@
         <v>10</v>
       </c>
       <c r="J221" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7138,10 +7144,10 @@
         <v>27</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="D222" s="4" t="b">
         <v>0</v>
@@ -7150,7 +7156,7 @@
         <v>10</v>
       </c>
       <c r="J222" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7158,10 +7164,10 @@
         <v>27</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="D223" s="4" t="b">
         <v>0</v>
@@ -7170,7 +7176,7 @@
         <v>10</v>
       </c>
       <c r="J223" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7178,10 +7184,10 @@
         <v>27</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D224" s="4" t="b">
         <v>0</v>
@@ -7190,7 +7196,7 @@
         <v>10</v>
       </c>
       <c r="J224" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7198,7 +7204,7 @@
         <v>27</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>45</v>
@@ -7210,7 +7216,7 @@
         <v>10</v>
       </c>
       <c r="J225" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7218,7 +7224,7 @@
         <v>27</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>45</v>
@@ -7230,7 +7236,7 @@
         <v>10</v>
       </c>
       <c r="J226" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7238,10 +7244,10 @@
         <v>27</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D227" s="4" t="b">
         <v>0</v>
@@ -7250,7 +7256,7 @@
         <v>10</v>
       </c>
       <c r="J227" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7258,7 +7264,7 @@
         <v>27</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>38</v>
@@ -7270,7 +7276,7 @@
         <v>10</v>
       </c>
       <c r="J228" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7278,10 +7284,10 @@
         <v>27</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D229" s="4" t="b">
         <v>0</v>
@@ -7290,7 +7296,7 @@
         <v>10</v>
       </c>
       <c r="J229" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7298,22 +7304,19 @@
         <v>27</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="D230" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G230" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H230" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J230" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7321,7 +7324,7 @@
         <v>27</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>210</v>
@@ -7336,7 +7339,7 @@
         <v>10</v>
       </c>
       <c r="J231" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7344,7 +7347,7 @@
         <v>27</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>210</v>
@@ -7359,7 +7362,7 @@
         <v>10</v>
       </c>
       <c r="J232" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7367,7 +7370,7 @@
         <v>27</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>210</v>
@@ -7382,7 +7385,7 @@
         <v>10</v>
       </c>
       <c r="J233" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7390,7 +7393,7 @@
         <v>27</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>210</v>
@@ -7405,7 +7408,7 @@
         <v>10</v>
       </c>
       <c r="J234" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7413,7 +7416,7 @@
         <v>27</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>210</v>
@@ -7428,7 +7431,7 @@
         <v>10</v>
       </c>
       <c r="J235" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7436,7 +7439,7 @@
         <v>27</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>210</v>
@@ -7451,7 +7454,7 @@
         <v>10</v>
       </c>
       <c r="J236" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7459,7 +7462,7 @@
         <v>27</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>210</v>
@@ -7474,7 +7477,7 @@
         <v>10</v>
       </c>
       <c r="J237" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7482,19 +7485,22 @@
         <v>27</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="D238" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G238" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H238" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J238" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7502,22 +7508,19 @@
         <v>27</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>267</v>
+        <v>32</v>
       </c>
       <c r="D239" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G239" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H239" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J239" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7525,42 +7528,42 @@
         <v>27</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D240" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G240" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H240" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J240" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>32</v>
+        <v>269</v>
       </c>
       <c r="D241" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E241" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H241" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7568,19 +7571,22 @@
         <v>29</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D242" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="E242" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="H242" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>501</v>
+        <v>701</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7588,19 +7594,19 @@
         <v>29</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D243" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J243" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7608,22 +7614,19 @@
         <v>29</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D244" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F244" s="4" t="s">
-        <v>403</v>
+        <v>1</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J244" s="5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7631,7 +7634,7 @@
         <v>29</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>270</v>
+        <v>35</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>36</v>
@@ -7639,11 +7642,14 @@
       <c r="D245" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="F245" s="4" t="s">
+        <v>403</v>
+      </c>
       <c r="H245" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J245" s="5" t="s">
-        <v>689</v>
+        <v>501</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7651,10 +7657,10 @@
         <v>29</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D246" s="4" t="b">
         <v>0</v>
@@ -7663,7 +7669,7 @@
         <v>10</v>
       </c>
       <c r="J246" s="5" t="s">
-        <v>504</v>
+        <v>686</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7671,7 +7677,7 @@
         <v>29</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>38</v>
@@ -7683,7 +7689,7 @@
         <v>10</v>
       </c>
       <c r="J247" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7691,10 +7697,10 @@
         <v>29</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D248" s="4" t="b">
         <v>0</v>
@@ -7703,7 +7709,7 @@
         <v>10</v>
       </c>
       <c r="J248" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7711,10 +7717,10 @@
         <v>29</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D249" s="4" t="b">
         <v>0</v>
@@ -7723,7 +7729,7 @@
         <v>10</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7731,10 +7737,10 @@
         <v>29</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D250" s="4" t="b">
         <v>0</v>
@@ -7743,7 +7749,7 @@
         <v>10</v>
       </c>
       <c r="J250" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7751,10 +7757,10 @@
         <v>29</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D251" s="4" t="b">
         <v>0</v>
@@ -7763,7 +7769,7 @@
         <v>10</v>
       </c>
       <c r="J251" s="5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7771,10 +7777,10 @@
         <v>29</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D252" s="4" t="b">
         <v>0</v>
@@ -7783,7 +7789,7 @@
         <v>10</v>
       </c>
       <c r="J252" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7791,10 +7797,10 @@
         <v>29</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D253" s="4" t="b">
         <v>0</v>
@@ -7803,7 +7809,7 @@
         <v>10</v>
       </c>
       <c r="J253" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7811,7 +7817,7 @@
         <v>29</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>38</v>
@@ -7823,7 +7829,7 @@
         <v>10</v>
       </c>
       <c r="J254" s="5" t="s">
-        <v>690</v>
+        <v>509</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7831,10 +7837,10 @@
         <v>29</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D255" s="4" t="b">
         <v>0</v>
@@ -7843,7 +7849,7 @@
         <v>10</v>
       </c>
       <c r="J255" s="5" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7851,10 +7857,10 @@
         <v>29</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D256" s="4" t="b">
         <v>0</v>
@@ -7863,7 +7869,7 @@
         <v>10</v>
       </c>
       <c r="J256" s="5" t="s">
-        <v>512</v>
+        <v>688</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7871,7 +7877,7 @@
         <v>29</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>38</v>
@@ -7883,7 +7889,7 @@
         <v>10</v>
       </c>
       <c r="J257" s="5" t="s">
-        <v>692</v>
+        <v>510</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7891,7 +7897,7 @@
         <v>29</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>38</v>
@@ -7903,7 +7909,7 @@
         <v>10</v>
       </c>
       <c r="J258" s="5" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7911,7 +7917,7 @@
         <v>29</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>38</v>
@@ -7923,7 +7929,7 @@
         <v>10</v>
       </c>
       <c r="J259" s="5" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7931,10 +7937,10 @@
         <v>29</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="D260" s="4" t="b">
         <v>0</v>
@@ -7943,7 +7949,7 @@
         <v>10</v>
       </c>
       <c r="J260" s="5" t="s">
-        <v>513</v>
+        <v>691</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7951,7 +7957,7 @@
         <v>29</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>189</v>
@@ -7963,7 +7969,7 @@
         <v>10</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7971,10 +7977,10 @@
         <v>29</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="D262" s="4" t="b">
         <v>0</v>
@@ -7983,7 +7989,7 @@
         <v>10</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7991,10 +7997,10 @@
         <v>29</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D263" s="4" t="b">
         <v>0</v>
@@ -8003,7 +8009,7 @@
         <v>10</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8011,10 +8017,10 @@
         <v>29</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="D264" s="4" t="b">
         <v>0</v>
@@ -8023,7 +8029,7 @@
         <v>10</v>
       </c>
       <c r="J264" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8031,10 +8037,10 @@
         <v>29</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D265" s="4" t="b">
         <v>0</v>
@@ -8043,7 +8049,7 @@
         <v>10</v>
       </c>
       <c r="J265" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8051,10 +8057,10 @@
         <v>29</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D266" s="4" t="b">
         <v>0</v>
@@ -8063,7 +8069,7 @@
         <v>10</v>
       </c>
       <c r="J266" s="5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8071,10 +8077,10 @@
         <v>29</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D267" s="4" t="b">
         <v>0</v>
@@ -8083,7 +8089,7 @@
         <v>10</v>
       </c>
       <c r="J267" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8091,10 +8097,10 @@
         <v>29</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="D268" s="4" t="b">
         <v>0</v>
@@ -8103,7 +8109,7 @@
         <v>10</v>
       </c>
       <c r="J268" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8111,10 +8117,10 @@
         <v>29</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="D269" s="4" t="b">
         <v>0</v>
@@ -8123,7 +8129,7 @@
         <v>10</v>
       </c>
       <c r="J269" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8131,10 +8137,10 @@
         <v>29</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D270" s="4" t="b">
         <v>0</v>
@@ -8143,7 +8149,7 @@
         <v>10</v>
       </c>
       <c r="J270" s="5" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8151,10 +8157,10 @@
         <v>29</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D271" s="4" t="b">
         <v>0</v>
@@ -8163,7 +8169,7 @@
         <v>10</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8171,7 +8177,7 @@
         <v>29</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>32</v>
@@ -8183,7 +8189,7 @@
         <v>10</v>
       </c>
       <c r="J272" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8191,10 +8197,10 @@
         <v>29</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D273" s="4" t="b">
         <v>0</v>
@@ -8203,7 +8209,7 @@
         <v>10</v>
       </c>
       <c r="J273" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8211,10 +8217,10 @@
         <v>29</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="D274" s="4" t="b">
         <v>0</v>
@@ -8223,7 +8229,7 @@
         <v>10</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8231,10 +8237,10 @@
         <v>29</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>189</v>
+        <v>273</v>
       </c>
       <c r="D275" s="4" t="b">
         <v>0</v>
@@ -8243,7 +8249,7 @@
         <v>10</v>
       </c>
       <c r="J275" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8251,10 +8257,10 @@
         <v>29</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="D276" s="4" t="b">
         <v>0</v>
@@ -8263,7 +8269,7 @@
         <v>10</v>
       </c>
       <c r="J276" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8271,7 +8277,7 @@
         <v>29</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>271</v>
@@ -8283,7 +8289,7 @@
         <v>10</v>
       </c>
       <c r="J277" s="5" t="s">
-        <v>695</v>
+        <v>527</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8291,7 +8297,7 @@
         <v>29</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>271</v>
@@ -8303,7 +8309,7 @@
         <v>10</v>
       </c>
       <c r="J278" s="5" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8311,10 +8317,10 @@
         <v>29</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D279" s="4" t="b">
         <v>0</v>
@@ -8323,7 +8329,7 @@
         <v>10</v>
       </c>
       <c r="J279" s="5" t="s">
-        <v>530</v>
+        <v>693</v>
       </c>
     </row>
     <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8331,10 +8337,10 @@
         <v>29</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>271</v>
+        <v>84</v>
       </c>
       <c r="D280" s="4" t="b">
         <v>0</v>
@@ -8343,7 +8349,7 @@
         <v>10</v>
       </c>
       <c r="J280" s="5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8351,10 +8357,10 @@
         <v>29</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D281" s="4" t="b">
         <v>0</v>
@@ -8363,7 +8369,7 @@
         <v>10</v>
       </c>
       <c r="J281" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8371,10 +8377,10 @@
         <v>29</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D282" s="4" t="b">
         <v>0</v>
@@ -8383,7 +8389,7 @@
         <v>10</v>
       </c>
       <c r="J282" s="5" t="s">
-        <v>697</v>
+        <v>530</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8391,10 +8397,10 @@
         <v>29</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D283" s="4" t="b">
         <v>0</v>
@@ -8403,7 +8409,7 @@
         <v>10</v>
       </c>
       <c r="J283" s="5" t="s">
-        <v>533</v>
+        <v>694</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8411,7 +8417,7 @@
         <v>29</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>32</v>
@@ -8423,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="J284" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8431,7 +8437,7 @@
         <v>29</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>32</v>
@@ -8443,7 +8449,7 @@
         <v>10</v>
       </c>
       <c r="J285" s="5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8451,10 +8457,10 @@
         <v>29</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D286" s="4" t="b">
         <v>0</v>
@@ -8463,7 +8469,7 @@
         <v>10</v>
       </c>
       <c r="J286" s="5" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8471,10 +8477,10 @@
         <v>29</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="D287" s="4" t="b">
         <v>0</v>
@@ -8483,7 +8489,7 @@
         <v>10</v>
       </c>
       <c r="J287" s="5" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8491,10 +8497,10 @@
         <v>29</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D288" s="4" t="b">
         <v>0</v>
@@ -8503,7 +8509,7 @@
         <v>10</v>
       </c>
       <c r="J288" s="5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8511,10 +8517,10 @@
         <v>29</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D289" s="4" t="b">
         <v>0</v>
@@ -8523,7 +8529,7 @@
         <v>10</v>
       </c>
       <c r="J289" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8531,10 +8537,10 @@
         <v>29</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D290" s="4" t="b">
         <v>0</v>
@@ -8543,7 +8549,7 @@
         <v>10</v>
       </c>
       <c r="J290" s="5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8551,10 +8557,10 @@
         <v>29</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="D291" s="4" t="b">
         <v>0</v>
@@ -8563,7 +8569,7 @@
         <v>10</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8571,10 +8577,10 @@
         <v>29</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="D292" s="4" t="b">
         <v>0</v>
@@ -8583,7 +8589,7 @@
         <v>10</v>
       </c>
       <c r="J292" s="5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8591,7 +8597,7 @@
         <v>29</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>32</v>
@@ -8603,7 +8609,7 @@
         <v>10</v>
       </c>
       <c r="J293" s="5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8611,7 +8617,7 @@
         <v>29</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>12</v>
+        <v>289</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>32</v>
@@ -8623,7 +8629,7 @@
         <v>10</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8631,10 +8637,10 @@
         <v>29</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>206</v>
+        <v>12</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D295" s="4" t="b">
         <v>0</v>
@@ -8643,7 +8649,7 @@
         <v>10</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8651,10 +8657,10 @@
         <v>29</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D296" s="4" t="b">
         <v>0</v>
@@ -8663,7 +8669,7 @@
         <v>10</v>
       </c>
       <c r="J296" s="5" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8671,10 +8677,10 @@
         <v>29</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D297" s="4" t="b">
         <v>0</v>
@@ -8683,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>698</v>
+        <v>544</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8691,22 +8697,19 @@
         <v>29</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D298" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G298" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H298" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>547</v>
+        <v>695</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8714,10 +8717,10 @@
         <v>29</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="D299" s="4" t="b">
         <v>0</v>
@@ -8729,7 +8732,7 @@
         <v>10</v>
       </c>
       <c r="J299" s="5" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8737,7 +8740,7 @@
         <v>29</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>210</v>
@@ -8752,7 +8755,7 @@
         <v>10</v>
       </c>
       <c r="J300" s="5" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8760,7 +8763,7 @@
         <v>29</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>210</v>
@@ -8775,7 +8778,7 @@
         <v>10</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8783,7 +8786,7 @@
         <v>29</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>210</v>
@@ -8798,7 +8801,7 @@
         <v>10</v>
       </c>
       <c r="J302" s="5" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8806,7 +8809,7 @@
         <v>29</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>210</v>
@@ -8821,7 +8824,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8829,7 +8832,7 @@
         <v>29</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>210</v>
@@ -8844,7 +8847,7 @@
         <v>10</v>
       </c>
       <c r="J304" s="5" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8852,7 +8855,7 @@
         <v>29</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>210</v>
@@ -8867,7 +8870,7 @@
         <v>10</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8875,7 +8878,7 @@
         <v>29</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>210</v>
@@ -8890,7 +8893,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8898,7 +8901,7 @@
         <v>29</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>210</v>
@@ -8913,7 +8916,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8921,7 +8924,7 @@
         <v>29</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>210</v>
@@ -8936,7 +8939,7 @@
         <v>10</v>
       </c>
       <c r="J308" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8944,7 +8947,7 @@
         <v>29</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>210</v>
@@ -8959,7 +8962,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8967,7 +8970,7 @@
         <v>29</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>210</v>
@@ -8982,7 +8985,7 @@
         <v>10</v>
       </c>
       <c r="J310" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8990,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>210</v>
@@ -9005,7 +9008,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="5" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9013,7 +9016,7 @@
         <v>29</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>210</v>
@@ -9028,7 +9031,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="5" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9036,7 +9039,7 @@
         <v>29</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>210</v>
@@ -9051,7 +9054,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="5" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9059,7 +9062,7 @@
         <v>29</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>210</v>
@@ -9074,7 +9077,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9082,19 +9085,22 @@
         <v>29</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="D315" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G315" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H315" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J315" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9102,10 +9108,10 @@
         <v>29</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D316" s="4" t="b">
         <v>0</v>
@@ -9114,7 +9120,7 @@
         <v>10</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9122,10 +9128,10 @@
         <v>29</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="D317" s="4" t="b">
         <v>0</v>
@@ -9134,7 +9140,7 @@
         <v>10</v>
       </c>
       <c r="J317" s="5" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9142,7 +9148,7 @@
         <v>29</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>189</v>
@@ -9154,7 +9160,7 @@
         <v>10</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9162,10 +9168,10 @@
         <v>29</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="D319" s="4" t="b">
         <v>0</v>
@@ -9174,7 +9180,7 @@
         <v>10</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9182,10 +9188,10 @@
         <v>29</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>271</v>
+        <v>32</v>
       </c>
       <c r="D320" s="4" t="b">
         <v>0</v>
@@ -9194,7 +9200,7 @@
         <v>10</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9202,7 +9208,7 @@
         <v>29</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>271</v>
@@ -9214,7 +9220,7 @@
         <v>10</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9222,7 +9228,7 @@
         <v>29</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>271</v>
@@ -9234,7 +9240,7 @@
         <v>10</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9242,7 +9248,7 @@
         <v>29</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>271</v>
@@ -9254,7 +9260,7 @@
         <v>10</v>
       </c>
       <c r="J323" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9262,7 +9268,7 @@
         <v>29</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>271</v>
@@ -9274,7 +9280,7 @@
         <v>10</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9282,10 +9288,10 @@
         <v>29</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="D325" s="4" t="b">
         <v>0</v>
@@ -9294,7 +9300,7 @@
         <v>10</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9302,22 +9308,19 @@
         <v>29</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>212</v>
+        <v>317</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="D326" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G326" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H326" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9325,7 +9328,7 @@
         <v>29</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>210</v>
@@ -9340,7 +9343,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9348,7 +9351,7 @@
         <v>29</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>318</v>
+        <v>211</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>210</v>
@@ -9363,7 +9366,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9371,19 +9374,22 @@
         <v>29</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>224</v>
+        <v>318</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>273</v>
+        <v>210</v>
       </c>
       <c r="D329" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G329" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H329" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J329" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9391,7 +9397,7 @@
         <v>29</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>273</v>
@@ -9403,7 +9409,7 @@
         <v>10</v>
       </c>
       <c r="J330" s="5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9411,7 +9417,7 @@
         <v>29</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>273</v>
@@ -9423,7 +9429,7 @@
         <v>10</v>
       </c>
       <c r="J331" s="5" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9431,7 +9437,7 @@
         <v>29</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>273</v>
@@ -9443,7 +9449,7 @@
         <v>10</v>
       </c>
       <c r="J332" s="5" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9451,7 +9457,7 @@
         <v>29</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>273</v>
@@ -9463,7 +9469,7 @@
         <v>10</v>
       </c>
       <c r="J333" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9471,22 +9477,19 @@
         <v>29</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
       <c r="D334" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G334" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H334" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9494,7 +9497,7 @@
         <v>29</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>321</v>
@@ -9509,7 +9512,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9517,19 +9520,22 @@
         <v>29</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>52</v>
+        <v>321</v>
       </c>
       <c r="D336" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G336" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H336" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9537,7 +9543,7 @@
         <v>29</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>52</v>
@@ -9549,7 +9555,7 @@
         <v>10</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>699</v>
+        <v>583</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9557,22 +9563,19 @@
         <v>29</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>326</v>
+        <v>52</v>
       </c>
       <c r="D338" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G338" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="H338" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>586</v>
+        <v>696</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9580,10 +9583,10 @@
         <v>29</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D339" s="4" t="b">
         <v>0</v>
@@ -9595,7 +9598,7 @@
         <v>10</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9603,42 +9606,42 @@
         <v>29</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D340" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G340" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="H340" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J340" s="5" t="s">
-        <v>700</v>
+        <v>585</v>
       </c>
     </row>
     <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>407</v>
+        <v>29</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>36</v>
+        <v>330</v>
       </c>
       <c r="D341" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="F341" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="H341" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J341" s="5" t="s">
-        <v>588</v>
+        <v>697</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9646,19 +9649,22 @@
         <v>407</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D342" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="F342" s="4" t="s">
+        <v>403</v>
+      </c>
       <c r="H342" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9666,10 +9672,10 @@
         <v>407</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>149</v>
+        <v>332</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D343" s="4" t="b">
         <v>0</v>
@@ -9678,7 +9684,7 @@
         <v>10</v>
       </c>
       <c r="J343" s="5" t="s">
-        <v>701</v>
+        <v>587</v>
       </c>
     </row>
     <row r="344" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9686,26 +9692,46 @@
         <v>407</v>
       </c>
       <c r="B344" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D344" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J344" s="5" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A345" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B345" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C344" s="4" t="s">
+      <c r="C345" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D344" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E344" s="4" t="b">
+      <c r="D345" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E345" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H344" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J344" s="5" t="s">
-        <v>590</v>
+      <c r="H345" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J345" s="5" t="s">
+        <v>702</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J344" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:J345" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10007,7 +10033,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B2" t="s">
         <v>405</v>
@@ -10018,10 +10044,10 @@
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222849E5-03C4-9143-A1A0-2D39E2730B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222849E5-03C4-9143-A1A0-2D39E2730B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63F2F6C-EAFA-704C-80B3-981C26B3FB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63F2F6C-EAFA-704C-80B3-981C26B3FB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBE6C08-B2A1-C24B-8DCE-3A0DDC38E841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="702">
   <si>
     <t>Table Name</t>
   </si>
@@ -1126,12 +1126,6 @@
     <t>MDM ID</t>
   </si>
   <si>
-    <t>CIF ID Nasabah</t>
-  </si>
-  <si>
-    <t>Nama Nasabah</t>
-  </si>
-  <si>
     <t>Nama Perusahaan</t>
   </si>
   <si>
@@ -1153,15 +1147,6 @@
     <t>Source Status</t>
   </si>
   <si>
-    <t>Status Customer</t>
-  </si>
-  <si>
-    <t>Kode Type</t>
-  </si>
-  <si>
-    <t>Tipe Customer</t>
-  </si>
-  <si>
     <t>Flag Pemerintah</t>
   </si>
   <si>
@@ -1228,15 +1213,6 @@
     <t>Channel Pembuka CIF</t>
   </si>
   <si>
-    <t>Channel Nasabah ( Consentisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Channel Nasabah ( Consent_Nameisi Pemegang Nasabah)</t>
-  </si>
-  <si>
-    <t>Cif Key Nasabah</t>
-  </si>
-  <si>
     <t>customer_icons.cif_key</t>
   </si>
   <si>
@@ -1489,9 +1465,6 @@
     <t>Channel yang digunakan untuk membuka rekening.</t>
   </si>
   <si>
-    <t>Jenis atau bentuk badan hukum nasabah/perusahaan.</t>
-  </si>
-  <si>
     <t>Saldo akhir untuk periode Month-to-Date.</t>
   </si>
   <si>
@@ -1525,21 +1498,12 @@
     <t>Hasil mapping/mirror dari pemilik channel.</t>
   </si>
   <si>
-    <t>ID nasabah/entity pada sistem Master Data Management.</t>
-  </si>
-  <si>
     <t>Nomor rekening.</t>
   </si>
   <si>
     <t>Kunci/identifier Customer Information File (CIF).</t>
   </si>
   <si>
-    <t>Kode jenis nasabah.</t>
-  </si>
-  <si>
-    <t>Deskripsi jenis nasabah, misalnya individu atau badan usaha.</t>
-  </si>
-  <si>
     <t>Kode region tempat CIF dibuka.</t>
   </si>
   <si>
@@ -1555,9 +1519,6 @@
     <t>Tanggal CIF dibuat atau dibuka.</t>
   </si>
   <si>
-    <t>Nama nasabah.</t>
-  </si>
-  <si>
     <t>Penanda apakah CIF terkait proses/produk Burekol atau buka rekening kolektif.</t>
   </si>
   <si>
@@ -1786,12 +1747,6 @@
     <t>Interest Income atau pendapatan bunga bulanan.</t>
   </si>
   <si>
-    <t>CIF utama/principal apabila nasabah memiliki beberapa CIF terkait.</t>
-  </si>
-  <si>
-    <t>Nasabah/perusahaan utama dalam satu kelompok usaha atau grup.</t>
-  </si>
-  <si>
     <t>CIF Key Nasabah (ID Nasabah)</t>
   </si>
   <si>
@@ -1975,12 +1930,6 @@
     <t>Account Number / Nomor Akun</t>
   </si>
   <si>
-    <t>Tipe nasabah</t>
-  </si>
-  <si>
-    <t>Kode tipe nasabah</t>
-  </si>
-  <si>
     <t>Kode Region pembukaan CIF</t>
   </si>
   <si>
@@ -2101,9 +2050,6 @@
     <t>Divisi yang menjadi pemilik segmen.</t>
   </si>
   <si>
-    <t>Sub segmen nasabah.</t>
-  </si>
-  <si>
     <t>Nama sentra atau unit bisnis yang menangani rekening</t>
   </si>
   <si>
@@ -2141,6 +2087,51 @@
   </si>
   <si>
     <t>Tanggal posisi atau tanggal transaksi data, digunakan untuk filter tanggal, bulan, tahun</t>
+  </si>
+  <si>
+    <t>CIF utama/principal apabila memiliki beberapa CIF terkait.</t>
+  </si>
+  <si>
+    <t>Consent Channel</t>
+  </si>
+  <si>
+    <t>Consent Channel Sebelum (Previous)</t>
+  </si>
+  <si>
+    <t>Cif Key</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Jenis atau bentuk badan hukum</t>
+  </si>
+  <si>
+    <t>ID MDM / Global pada sistem Master Data Management.</t>
+  </si>
+  <si>
+    <t>Sub segment</t>
+  </si>
+  <si>
+    <t>Entity utama dalam satu kelompok usaha atau grup.</t>
+  </si>
+  <si>
+    <t>Kode tipe customer/nasabah</t>
+  </si>
+  <si>
+    <t>CIF Nasabah</t>
+  </si>
+  <si>
+    <t>Status Customer/nasabah</t>
+  </si>
+  <si>
+    <t>Tipe Customer/nasabah</t>
+  </si>
+  <si>
+    <t>Pendapatan Lain</t>
+  </si>
+  <si>
+    <t>Pendapatan Sewa</t>
   </si>
 </sst>
 </file>
@@ -2560,7 +2551,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2571,7 +2562,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2582,18 +2573,18 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C6" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -2633,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
@@ -2671,7 +2662,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2708,13 +2699,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
@@ -2731,13 +2722,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2934,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>10</v>
@@ -2963,7 +2954,7 @@
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -2980,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="J17" t="s">
         <v>344</v>
@@ -3220,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>10</v>
@@ -3243,13 +3234,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3269,7 +3260,7 @@
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3455,7 +3446,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3472,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>10</v>
@@ -3498,7 +3489,7 @@
         <v>10</v>
       </c>
       <c r="J42" t="s">
-        <v>366</v>
+        <v>697</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3538,7 +3529,7 @@
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3558,7 +3549,7 @@
         <v>10</v>
       </c>
       <c r="J45" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3578,7 +3569,7 @@
         <v>10</v>
       </c>
       <c r="J46" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3598,7 +3589,7 @@
         <v>10</v>
       </c>
       <c r="J47" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3618,7 +3609,7 @@
         <v>10</v>
       </c>
       <c r="J48" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3638,7 +3629,7 @@
         <v>10</v>
       </c>
       <c r="J49" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3658,7 +3649,7 @@
         <v>10</v>
       </c>
       <c r="J50" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3678,7 +3669,7 @@
         <v>10</v>
       </c>
       <c r="J51" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3698,7 +3689,7 @@
         <v>10</v>
       </c>
       <c r="J52" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3715,13 +3706,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="J53" t="s">
-        <v>375</v>
+        <v>698</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3741,7 +3732,7 @@
         <v>10</v>
       </c>
       <c r="J54" t="s">
-        <v>376</v>
+        <v>696</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3761,7 +3752,7 @@
         <v>10</v>
       </c>
       <c r="J55" t="s">
-        <v>377</v>
+        <v>699</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3781,7 +3772,7 @@
         <v>10</v>
       </c>
       <c r="J56" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3801,7 +3792,7 @@
         <v>10</v>
       </c>
       <c r="J57" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3821,7 +3812,7 @@
         <v>10</v>
       </c>
       <c r="J58" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3841,7 +3832,7 @@
         <v>10</v>
       </c>
       <c r="J59" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3861,7 +3852,7 @@
         <v>10</v>
       </c>
       <c r="J60" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3881,7 +3872,7 @@
         <v>10</v>
       </c>
       <c r="J61" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3901,7 +3892,7 @@
         <v>10</v>
       </c>
       <c r="J62" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3921,7 +3912,7 @@
         <v>10</v>
       </c>
       <c r="J63" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3941,7 +3932,7 @@
         <v>10</v>
       </c>
       <c r="J64" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3961,7 +3952,7 @@
         <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3981,7 +3972,7 @@
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4001,7 +3992,7 @@
         <v>10</v>
       </c>
       <c r="J67" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4024,7 +4015,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4044,7 +4035,7 @@
         <v>10</v>
       </c>
       <c r="J69" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4064,7 +4055,7 @@
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4084,7 +4075,7 @@
         <v>10</v>
       </c>
       <c r="J71" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4104,7 +4095,7 @@
         <v>10</v>
       </c>
       <c r="J72" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4124,7 +4115,7 @@
         <v>10</v>
       </c>
       <c r="J73" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4144,7 +4135,7 @@
         <v>10</v>
       </c>
       <c r="J74" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4164,7 +4155,7 @@
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4184,7 +4175,7 @@
         <v>10</v>
       </c>
       <c r="J76" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4204,7 +4195,7 @@
         <v>10</v>
       </c>
       <c r="J77" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4224,7 +4215,7 @@
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4244,7 +4235,7 @@
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4264,7 +4255,7 @@
         <v>10</v>
       </c>
       <c r="J80" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4284,7 +4275,7 @@
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4304,7 +4295,7 @@
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>602</v>
+        <v>587</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4360,7 +4351,7 @@
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>603</v>
+        <v>588</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4434,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4454,7 +4445,7 @@
         <v>10</v>
       </c>
       <c r="J90" t="s">
-        <v>605</v>
+        <v>590</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4474,7 +4465,7 @@
         <v>10</v>
       </c>
       <c r="J91" t="s">
-        <v>606</v>
+        <v>591</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4494,7 +4485,7 @@
         <v>10</v>
       </c>
       <c r="J92" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4514,7 +4505,7 @@
         <v>10</v>
       </c>
       <c r="J93" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4534,7 +4525,7 @@
         <v>10</v>
       </c>
       <c r="J94" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4554,7 +4545,7 @@
         <v>10</v>
       </c>
       <c r="J95" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4574,7 +4565,7 @@
         <v>10</v>
       </c>
       <c r="J96" t="s">
-        <v>611</v>
+        <v>596</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4594,7 +4585,7 @@
         <v>10</v>
       </c>
       <c r="J97" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4614,7 +4605,7 @@
         <v>10</v>
       </c>
       <c r="J98" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4634,7 +4625,7 @@
         <v>10</v>
       </c>
       <c r="J99" t="s">
-        <v>613</v>
+        <v>598</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4654,7 +4645,7 @@
         <v>10</v>
       </c>
       <c r="J100" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4674,7 +4665,7 @@
         <v>10</v>
       </c>
       <c r="J101" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4712,7 +4703,7 @@
         <v>10</v>
       </c>
       <c r="J103" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4732,7 +4723,7 @@
         <v>10</v>
       </c>
       <c r="J104" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4755,7 +4746,7 @@
         <v>10</v>
       </c>
       <c r="J105" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4777,7 +4768,9 @@
       <c r="H106" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J106"/>
+      <c r="J106" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
@@ -4798,7 +4791,9 @@
       <c r="H107" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J107"/>
+      <c r="J107" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
@@ -4817,7 +4812,7 @@
         <v>10</v>
       </c>
       <c r="J108" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4873,7 +4868,7 @@
         <v>10</v>
       </c>
       <c r="J111" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4893,7 +4888,7 @@
         <v>10</v>
       </c>
       <c r="J112" t="s">
-        <v>614</v>
+        <v>599</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4913,7 +4908,7 @@
         <v>10</v>
       </c>
       <c r="J113" t="s">
-        <v>615</v>
+        <v>600</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4933,7 +4928,7 @@
         <v>10</v>
       </c>
       <c r="J114" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4953,7 +4948,7 @@
         <v>10</v>
       </c>
       <c r="J115" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4973,7 +4968,7 @@
         <v>10</v>
       </c>
       <c r="J116" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4993,7 +4988,7 @@
         <v>10</v>
       </c>
       <c r="J117" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5013,7 +5008,7 @@
         <v>10</v>
       </c>
       <c r="J118" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5033,7 +5028,7 @@
         <v>10</v>
       </c>
       <c r="J119" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5053,7 +5048,7 @@
         <v>10</v>
       </c>
       <c r="J120" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5073,7 +5068,7 @@
         <v>10</v>
       </c>
       <c r="J121" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5093,7 +5088,7 @@
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5113,7 +5108,7 @@
         <v>10</v>
       </c>
       <c r="J123" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5133,7 +5128,7 @@
         <v>10</v>
       </c>
       <c r="J124" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5153,7 +5148,7 @@
         <v>10</v>
       </c>
       <c r="J125" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5173,7 +5168,7 @@
         <v>10</v>
       </c>
       <c r="J126" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5193,7 +5188,7 @@
         <v>10</v>
       </c>
       <c r="J127" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5213,7 +5208,7 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5233,7 +5228,7 @@
         <v>10</v>
       </c>
       <c r="J129" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5253,7 +5248,7 @@
         <v>10</v>
       </c>
       <c r="J130" t="s">
-        <v>639</v>
+        <v>624</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5273,7 +5268,7 @@
         <v>10</v>
       </c>
       <c r="J131" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5293,7 +5288,7 @@
         <v>10</v>
       </c>
       <c r="J132" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5313,7 +5308,7 @@
         <v>10</v>
       </c>
       <c r="J133" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5333,7 +5328,7 @@
         <v>10</v>
       </c>
       <c r="J134" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5353,7 +5348,7 @@
         <v>10</v>
       </c>
       <c r="J135" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5373,7 +5368,7 @@
         <v>10</v>
       </c>
       <c r="J136" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5393,7 +5388,7 @@
         <v>10</v>
       </c>
       <c r="J137" t="s">
-        <v>645</v>
+        <v>630</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5413,7 +5408,7 @@
         <v>10</v>
       </c>
       <c r="J138" t="s">
-        <v>400</v>
+        <v>688</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5433,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="J139" t="s">
-        <v>401</v>
+        <v>689</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5453,7 +5448,7 @@
         <v>10</v>
       </c>
       <c r="J140" t="s">
-        <v>647</v>
+        <v>632</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5476,7 +5471,7 @@
         <v>10</v>
       </c>
       <c r="J141" s="5" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5496,7 +5491,7 @@
         <v>10</v>
       </c>
       <c r="J142" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5513,13 +5508,13 @@
         <v>0</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>402</v>
+        <v>690</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5539,7 +5534,7 @@
         <v>10</v>
       </c>
       <c r="J144" t="s">
-        <v>650</v>
+        <v>696</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5559,7 +5554,7 @@
         <v>10</v>
       </c>
       <c r="J145" t="s">
-        <v>649</v>
+        <v>699</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5579,7 +5574,7 @@
         <v>10</v>
       </c>
       <c r="J146" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5599,7 +5594,7 @@
         <v>10</v>
       </c>
       <c r="J147" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5619,7 +5614,7 @@
         <v>10</v>
       </c>
       <c r="J148" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5639,7 +5634,7 @@
         <v>10</v>
       </c>
       <c r="J149" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5659,7 +5654,7 @@
         <v>10</v>
       </c>
       <c r="J150" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5679,7 +5674,7 @@
         <v>10</v>
       </c>
       <c r="J151" t="s">
-        <v>367</v>
+        <v>691</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5699,7 +5694,7 @@
         <v>10</v>
       </c>
       <c r="J152" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5719,7 +5714,7 @@
         <v>10</v>
       </c>
       <c r="J153" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5739,7 +5734,7 @@
         <v>10</v>
       </c>
       <c r="J154" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5759,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="J155" t="s">
-        <v>612</v>
+        <v>597</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5779,7 +5774,7 @@
         <v>10</v>
       </c>
       <c r="J156" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5799,7 +5794,7 @@
         <v>10</v>
       </c>
       <c r="J157" t="s">
-        <v>614</v>
+        <v>599</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5819,7 +5814,7 @@
         <v>10</v>
       </c>
       <c r="J158" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5839,7 +5834,7 @@
         <v>10</v>
       </c>
       <c r="J159" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5859,7 +5854,7 @@
         <v>10</v>
       </c>
       <c r="J160" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5879,7 +5874,7 @@
         <v>10</v>
       </c>
       <c r="J161" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5899,7 +5894,7 @@
         <v>10</v>
       </c>
       <c r="J162" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5919,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5939,7 +5934,7 @@
         <v>10</v>
       </c>
       <c r="J164" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5959,7 +5954,7 @@
         <v>10</v>
       </c>
       <c r="J165" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5979,7 +5974,7 @@
         <v>10</v>
       </c>
       <c r="J166" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -5999,7 +5994,7 @@
         <v>10</v>
       </c>
       <c r="J167" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6019,7 +6014,7 @@
         <v>10</v>
       </c>
       <c r="J168" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6042,7 +6037,7 @@
         <v>10</v>
       </c>
       <c r="J169" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6062,7 +6057,7 @@
         <v>10</v>
       </c>
       <c r="J170" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6082,7 +6077,7 @@
         <v>10</v>
       </c>
       <c r="J171" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6102,7 +6097,7 @@
         <v>10</v>
       </c>
       <c r="J172" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6122,7 +6117,7 @@
         <v>10</v>
       </c>
       <c r="J173" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6142,7 +6137,7 @@
         <v>10</v>
       </c>
       <c r="J174" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6162,7 +6157,7 @@
         <v>10</v>
       </c>
       <c r="J175" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6182,7 +6177,7 @@
         <v>10</v>
       </c>
       <c r="J176" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6202,7 +6197,7 @@
         <v>10</v>
       </c>
       <c r="J177" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6222,7 +6217,7 @@
         <v>10</v>
       </c>
       <c r="J178" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6242,7 +6237,7 @@
         <v>10</v>
       </c>
       <c r="J179" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6262,7 +6257,7 @@
         <v>10</v>
       </c>
       <c r="J180" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6285,7 +6280,7 @@
         <v>10</v>
       </c>
       <c r="J181" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6308,7 +6303,7 @@
         <v>10</v>
       </c>
       <c r="J182" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6331,7 +6326,7 @@
         <v>10</v>
       </c>
       <c r="J183" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6354,7 +6349,7 @@
         <v>10</v>
       </c>
       <c r="J184" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6377,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="J185" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6397,7 +6392,7 @@
         <v>10</v>
       </c>
       <c r="J186" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6417,7 +6412,7 @@
         <v>10</v>
       </c>
       <c r="J187" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6437,7 +6432,7 @@
         <v>10</v>
       </c>
       <c r="J188" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6457,7 +6452,7 @@
         <v>10</v>
       </c>
       <c r="J189" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6477,7 +6472,7 @@
         <v>10</v>
       </c>
       <c r="J190" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6497,7 +6492,7 @@
         <v>10</v>
       </c>
       <c r="J191" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6517,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="J192" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6537,7 +6532,7 @@
         <v>10</v>
       </c>
       <c r="J193" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6557,7 +6552,7 @@
         <v>10</v>
       </c>
       <c r="J194" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6577,7 +6572,7 @@
         <v>10</v>
       </c>
       <c r="J195" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6597,7 +6592,7 @@
         <v>10</v>
       </c>
       <c r="J196" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6617,7 +6612,7 @@
         <v>10</v>
       </c>
       <c r="J197" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6637,7 +6632,7 @@
         <v>10</v>
       </c>
       <c r="J198" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6657,7 +6652,7 @@
         <v>10</v>
       </c>
       <c r="J199" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6677,7 +6672,7 @@
         <v>10</v>
       </c>
       <c r="J200" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6697,7 +6692,7 @@
         <v>10</v>
       </c>
       <c r="J201" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6717,7 +6712,7 @@
         <v>10</v>
       </c>
       <c r="J202" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6737,7 +6732,7 @@
         <v>10</v>
       </c>
       <c r="J203" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6760,7 +6755,7 @@
         <v>10</v>
       </c>
       <c r="J204" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6783,7 +6778,7 @@
         <v>10</v>
       </c>
       <c r="J205" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6806,7 +6801,7 @@
         <v>10</v>
       </c>
       <c r="J206" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6829,7 +6824,7 @@
         <v>10</v>
       </c>
       <c r="J207" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6852,7 +6847,7 @@
         <v>10</v>
       </c>
       <c r="J208" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6875,7 +6870,7 @@
         <v>10</v>
       </c>
       <c r="J209" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6898,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="J210" s="5" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6921,7 +6916,7 @@
         <v>10</v>
       </c>
       <c r="J211" s="5" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6944,7 +6939,7 @@
         <v>10</v>
       </c>
       <c r="J212" s="5" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6967,7 +6962,7 @@
         <v>10</v>
       </c>
       <c r="J213" s="5" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6987,7 +6982,7 @@
         <v>10</v>
       </c>
       <c r="J214" s="5" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7007,7 +7002,7 @@
         <v>10</v>
       </c>
       <c r="J215" s="5" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7027,7 +7022,7 @@
         <v>10</v>
       </c>
       <c r="J216" s="5" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7050,7 +7045,7 @@
         <v>10</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7073,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="J218" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7096,7 +7091,7 @@
         <v>10</v>
       </c>
       <c r="J219" s="5" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7116,7 +7111,7 @@
         <v>10</v>
       </c>
       <c r="J220" s="5" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7136,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="J221" s="5" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7156,7 +7151,7 @@
         <v>10</v>
       </c>
       <c r="J222" s="5" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7176,7 +7171,7 @@
         <v>10</v>
       </c>
       <c r="J223" s="5" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7196,7 +7191,7 @@
         <v>10</v>
       </c>
       <c r="J224" s="5" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7216,7 +7211,7 @@
         <v>10</v>
       </c>
       <c r="J225" s="5" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7236,7 +7231,7 @@
         <v>10</v>
       </c>
       <c r="J226" s="5" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7256,7 +7251,7 @@
         <v>10</v>
       </c>
       <c r="J227" s="5" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7276,7 +7271,7 @@
         <v>10</v>
       </c>
       <c r="J228" s="5" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7296,7 +7291,7 @@
         <v>10</v>
       </c>
       <c r="J229" s="5" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7316,7 +7311,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="5" t="s">
-        <v>487</v>
+        <v>692</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7339,7 +7334,7 @@
         <v>10</v>
       </c>
       <c r="J231" s="5" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7362,7 +7357,7 @@
         <v>10</v>
       </c>
       <c r="J232" s="5" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7385,7 +7380,7 @@
         <v>10</v>
       </c>
       <c r="J233" s="5" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7408,7 +7403,7 @@
         <v>10</v>
       </c>
       <c r="J234" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7431,7 +7426,7 @@
         <v>10</v>
       </c>
       <c r="J235" s="5" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7454,7 +7449,7 @@
         <v>10</v>
       </c>
       <c r="J236" s="5" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7477,7 +7472,7 @@
         <v>10</v>
       </c>
       <c r="J237" s="5" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7500,7 +7495,7 @@
         <v>10</v>
       </c>
       <c r="J238" s="5" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7520,7 +7515,7 @@
         <v>10</v>
       </c>
       <c r="J239" s="5" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7543,7 +7538,7 @@
         <v>10</v>
       </c>
       <c r="J240" s="5" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7563,7 +7558,7 @@
         <v>10</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7586,7 +7581,7 @@
         <v>10</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7606,7 +7601,7 @@
         <v>10</v>
       </c>
       <c r="J243" s="5" t="s">
-        <v>499</v>
+        <v>693</v>
       </c>
     </row>
     <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7626,7 +7621,7 @@
         <v>10</v>
       </c>
       <c r="J244" s="5" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7643,13 +7638,13 @@
         <v>0</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J245" s="5" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7669,7 +7664,7 @@
         <v>10</v>
       </c>
       <c r="J246" s="5" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7688,8 +7683,8 @@
       <c r="H247" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J247" s="5" t="s">
-        <v>502</v>
+      <c r="J247" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7708,8 +7703,8 @@
       <c r="H248" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J248" s="5" t="s">
-        <v>503</v>
+      <c r="J248" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7729,7 +7724,7 @@
         <v>10</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7749,7 +7744,7 @@
         <v>10</v>
       </c>
       <c r="J250" s="5" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7769,7 +7764,7 @@
         <v>10</v>
       </c>
       <c r="J251" s="5" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7789,7 +7784,7 @@
         <v>10</v>
       </c>
       <c r="J252" s="5" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7809,7 +7804,7 @@
         <v>10</v>
       </c>
       <c r="J253" s="5" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7829,7 +7824,7 @@
         <v>10</v>
       </c>
       <c r="J254" s="5" t="s">
-        <v>509</v>
+        <v>691</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7849,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="J255" s="5" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7869,7 +7864,7 @@
         <v>10</v>
       </c>
       <c r="J256" s="5" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7889,7 +7884,7 @@
         <v>10</v>
       </c>
       <c r="J257" s="5" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7909,7 +7904,7 @@
         <v>10</v>
       </c>
       <c r="J258" s="5" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7929,7 +7924,7 @@
         <v>10</v>
       </c>
       <c r="J259" s="5" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7949,7 +7944,7 @@
         <v>10</v>
       </c>
       <c r="J260" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7969,7 +7964,7 @@
         <v>10</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7989,7 +7984,7 @@
         <v>10</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8009,7 +8004,7 @@
         <v>10</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8029,7 +8024,7 @@
         <v>10</v>
       </c>
       <c r="J264" s="5" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8049,7 +8044,7 @@
         <v>10</v>
       </c>
       <c r="J265" s="5" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8069,7 +8064,7 @@
         <v>10</v>
       </c>
       <c r="J266" s="5" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
     </row>
     <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8089,7 +8084,7 @@
         <v>10</v>
       </c>
       <c r="J267" s="5" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8109,7 +8104,7 @@
         <v>10</v>
       </c>
       <c r="J268" s="5" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8129,7 +8124,7 @@
         <v>10</v>
       </c>
       <c r="J269" s="5" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8149,7 +8144,7 @@
         <v>10</v>
       </c>
       <c r="J270" s="5" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8169,7 +8164,7 @@
         <v>10</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8189,7 +8184,7 @@
         <v>10</v>
       </c>
       <c r="J272" s="5" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
     </row>
     <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8209,7 +8204,7 @@
         <v>10</v>
       </c>
       <c r="J273" s="5" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8229,7 +8224,7 @@
         <v>10</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
     </row>
     <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8249,7 +8244,7 @@
         <v>10</v>
       </c>
       <c r="J275" s="5" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
     </row>
     <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8269,7 +8264,7 @@
         <v>10</v>
       </c>
       <c r="J276" s="5" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8289,7 +8284,7 @@
         <v>10</v>
       </c>
       <c r="J277" s="5" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8309,7 +8304,7 @@
         <v>10</v>
       </c>
       <c r="J278" s="5" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8329,7 +8324,7 @@
         <v>10</v>
       </c>
       <c r="J279" s="5" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
     </row>
     <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8349,7 +8344,7 @@
         <v>10</v>
       </c>
       <c r="J280" s="5" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
     </row>
     <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8369,7 +8364,7 @@
         <v>10</v>
       </c>
       <c r="J281" s="5" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
     </row>
     <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8389,7 +8384,7 @@
         <v>10</v>
       </c>
       <c r="J282" s="5" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8409,7 +8404,7 @@
         <v>10</v>
       </c>
       <c r="J283" s="5" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8429,7 +8424,7 @@
         <v>10</v>
       </c>
       <c r="J284" s="5" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8449,7 +8444,7 @@
         <v>10</v>
       </c>
       <c r="J285" s="5" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8469,7 +8464,7 @@
         <v>10</v>
       </c>
       <c r="J286" s="5" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8489,7 +8484,7 @@
         <v>10</v>
       </c>
       <c r="J287" s="5" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
     </row>
     <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8509,7 +8504,7 @@
         <v>10</v>
       </c>
       <c r="J288" s="5" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
     </row>
     <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8529,7 +8524,7 @@
         <v>10</v>
       </c>
       <c r="J289" s="5" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
     </row>
     <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8549,7 +8544,7 @@
         <v>10</v>
       </c>
       <c r="J290" s="5" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8569,7 +8564,7 @@
         <v>10</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
     </row>
     <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8589,7 +8584,7 @@
         <v>10</v>
       </c>
       <c r="J292" s="5" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
     </row>
     <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8609,7 +8604,7 @@
         <v>10</v>
       </c>
       <c r="J293" s="5" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8629,7 +8624,7 @@
         <v>10</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
     </row>
     <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8649,7 +8644,7 @@
         <v>10</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8669,7 +8664,7 @@
         <v>10</v>
       </c>
       <c r="J296" s="5" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
     </row>
     <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8689,7 +8684,7 @@
         <v>10</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8709,7 +8704,7 @@
         <v>10</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8732,7 +8727,7 @@
         <v>10</v>
       </c>
       <c r="J299" s="5" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8755,7 +8750,7 @@
         <v>10</v>
       </c>
       <c r="J300" s="5" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8778,7 +8773,7 @@
         <v>10</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8801,7 +8796,7 @@
         <v>10</v>
       </c>
       <c r="J302" s="5" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8824,7 +8819,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8847,7 +8842,7 @@
         <v>10</v>
       </c>
       <c r="J304" s="5" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8870,7 +8865,7 @@
         <v>10</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8893,7 +8888,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="5" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8916,7 +8911,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="5" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8939,7 +8934,7 @@
         <v>10</v>
       </c>
       <c r="J308" s="5" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8962,7 +8957,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="5" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8985,7 +8980,7 @@
         <v>10</v>
       </c>
       <c r="J310" s="5" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9008,7 +9003,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="5" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9031,7 +9026,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="5" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9054,7 +9049,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="5" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9077,7 +9072,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9100,7 +9095,7 @@
         <v>10</v>
       </c>
       <c r="J315" s="5" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9120,7 +9115,7 @@
         <v>10</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
     </row>
     <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9140,7 +9135,7 @@
         <v>10</v>
       </c>
       <c r="J317" s="5" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9160,7 +9155,7 @@
         <v>10</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
     </row>
     <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9180,7 +9175,7 @@
         <v>10</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
     </row>
     <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9200,7 +9195,7 @@
         <v>10</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
     </row>
     <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9220,7 +9215,7 @@
         <v>10</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9240,7 +9235,7 @@
         <v>10</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9260,7 +9255,7 @@
         <v>10</v>
       </c>
       <c r="J323" s="5" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
     </row>
     <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9280,7 +9275,7 @@
         <v>10</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9300,7 +9295,7 @@
         <v>10</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
     </row>
     <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9320,7 +9315,7 @@
         <v>10</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9343,7 +9338,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9366,7 +9361,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="5" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9389,7 +9384,7 @@
         <v>10</v>
       </c>
       <c r="J329" s="5" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9409,7 +9404,7 @@
         <v>10</v>
       </c>
       <c r="J330" s="5" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
     </row>
     <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9429,7 +9424,7 @@
         <v>10</v>
       </c>
       <c r="J331" s="5" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9449,7 +9444,7 @@
         <v>10</v>
       </c>
       <c r="J332" s="5" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9469,7 +9464,7 @@
         <v>10</v>
       </c>
       <c r="J333" s="5" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9489,7 +9484,7 @@
         <v>10</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9512,7 +9507,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="5" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9535,7 +9530,7 @@
         <v>10</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
     </row>
     <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9555,7 +9550,7 @@
         <v>10</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9575,7 +9570,7 @@
         <v>10</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9598,7 +9593,7 @@
         <v>10</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9621,7 +9616,7 @@
         <v>10</v>
       </c>
       <c r="J340" s="5" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
     </row>
     <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9641,12 +9636,12 @@
         <v>10</v>
       </c>
       <c r="J341" s="5" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
     </row>
     <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B342" s="4" t="s">
         <v>331</v>
@@ -9658,18 +9653,18 @@
         <v>0</v>
       </c>
       <c r="F342" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="H342" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>586</v>
+        <v>687</v>
       </c>
     </row>
     <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B343" s="4" t="s">
         <v>332</v>
@@ -9684,12 +9679,12 @@
         <v>10</v>
       </c>
       <c r="J343" s="5" t="s">
-        <v>587</v>
+        <v>695</v>
       </c>
     </row>
     <row r="344" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A344" s="4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B344" s="4" t="s">
         <v>149</v>
@@ -9704,12 +9699,12 @@
         <v>10</v>
       </c>
       <c r="J344" s="5" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
     </row>
     <row r="345" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B345" s="4" t="s">
         <v>31</v>
@@ -9727,7 +9722,7 @@
         <v>10</v>
       </c>
       <c r="J345" s="5" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -9773,10 +9768,10 @@
         <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9787,10 +9782,10 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E3" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9801,10 +9796,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E4" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9815,10 +9810,10 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E5" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9829,13 +9824,13 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="D6" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="E6" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9846,10 +9841,10 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E7" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9860,10 +9855,10 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E8" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9874,10 +9869,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E9" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9888,10 +9883,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E10" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9902,10 +9897,10 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E11" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9916,10 +9911,10 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="E12" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9930,10 +9925,10 @@
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E13" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9944,10 +9939,10 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E14" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9958,10 +9953,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E15" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9972,10 +9967,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E16" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9986,10 +9981,10 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E17" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -10000,10 +9995,10 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E18" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -10033,10 +10028,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -10044,10 +10039,10 @@
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBE6C08-B2A1-C24B-8DCE-3A0DDC38E841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF3AF11-B869-654D-B77E-085C29D3DBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1492,9 +1492,6 @@
     <t>Tanggal transaksi terakhir (last transaction date).</t>
   </si>
   <si>
-    <t>Nilai saldo yang diblokir atau tidak dapat digunakan.</t>
-  </si>
-  <si>
     <t>Hasil mapping/mirror dari pemilik channel.</t>
   </si>
   <si>
@@ -1624,18 +1621,6 @@
     <t>Satuan atau multiplier yang digunakan pada original term, misalnya hari/bulan/tahun.</t>
   </si>
   <si>
-    <t>Nilai pokok pinjaman dalam Rupiah.</t>
-  </si>
-  <si>
-    <t>Saldo pokok kredit yang masih terutang/outstanding.</t>
-  </si>
-  <si>
-    <t>Nilai penyesuaian PSAK dengan kategori/komponen DMA sesuai definisi internal.</t>
-  </si>
-  <si>
-    <t>Nilai penyesuaian PSAK dengan kategori/komponen ACC sesuai definisi internal.</t>
-  </si>
-  <si>
     <t>Rata-rata pokok pinjaman berdasarkan PSAK untuk periode Month-to-Date.</t>
   </si>
   <si>
@@ -2132,6 +2117,21 @@
   </si>
   <si>
     <t>Pendapatan Sewa</t>
+  </si>
+  <si>
+    <t>Nilai saldo diblokir atau tidak dapat digunakan.</t>
+  </si>
+  <si>
+    <t>Nilai pokok pinjaman Rupiah.</t>
+  </si>
+  <si>
+    <t>Saldo pokok kredit masih terutang/outstanding.</t>
+  </si>
+  <si>
+    <t>Nilai penyesuaian PSAK kategori/komponen DMA sesuai definisi internal.</t>
+  </si>
+  <si>
+    <t>Nilai penyesuaian PSAK kategori/komponen ACC sesuai definisi internal.</t>
   </si>
 </sst>
 </file>
@@ -2594,6 +2594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2642,7 +2643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -2662,10 +2663,10 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
@@ -2705,10 +2706,10 @@
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -2728,10 +2729,10 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
@@ -2751,7 +2752,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
@@ -2771,7 +2772,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -2791,7 +2792,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -2811,7 +2812,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -2831,7 +2832,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2871,7 +2872,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -2891,7 +2892,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -2954,10 +2955,10 @@
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
@@ -2977,7 +2978,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -2997,7 +2998,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
@@ -3017,7 +3018,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -3057,7 +3058,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
@@ -3077,7 +3078,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -3097,7 +3098,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
@@ -3137,7 +3138,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
@@ -3157,7 +3158,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
@@ -3177,7 +3178,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>22</v>
       </c>
@@ -3197,7 +3198,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>22</v>
       </c>
@@ -3220,7 +3221,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>22</v>
       </c>
@@ -3243,7 +3244,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>22</v>
       </c>
@@ -3263,7 +3264,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
@@ -3283,7 +3284,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
@@ -3303,7 +3304,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>22</v>
       </c>
@@ -3323,7 +3324,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>22</v>
       </c>
@@ -3343,7 +3344,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>22</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>22</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>22</v>
       </c>
@@ -3426,7 +3427,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -3446,7 +3447,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3472,7 +3473,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>23</v>
       </c>
@@ -3489,10 +3490,10 @@
         <v>10</v>
       </c>
       <c r="J42" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>23</v>
       </c>
@@ -3512,7 +3513,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>23</v>
       </c>
@@ -3529,10 +3530,10 @@
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>23</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>23</v>
       </c>
@@ -3572,7 +3573,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>23</v>
       </c>
@@ -3592,7 +3593,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>23</v>
       </c>
@@ -3612,7 +3613,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>23</v>
       </c>
@@ -3632,7 +3633,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>23</v>
       </c>
@@ -3652,7 +3653,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>23</v>
       </c>
@@ -3672,7 +3673,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>23</v>
       </c>
@@ -3692,7 +3693,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>23</v>
       </c>
@@ -3712,10 +3713,10 @@
         <v>406</v>
       </c>
       <c r="J53" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>23</v>
       </c>
@@ -3732,10 +3733,10 @@
         <v>10</v>
       </c>
       <c r="J54" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>23</v>
       </c>
@@ -3752,10 +3753,10 @@
         <v>10</v>
       </c>
       <c r="J55" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>23</v>
       </c>
@@ -3775,7 +3776,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>23</v>
       </c>
@@ -3795,7 +3796,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>23</v>
       </c>
@@ -3815,7 +3816,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>23</v>
       </c>
@@ -3835,7 +3836,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>23</v>
       </c>
@@ -3855,7 +3856,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>23</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>23</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>23</v>
       </c>
@@ -3915,7 +3916,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>23</v>
       </c>
@@ -3935,7 +3936,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>23</v>
       </c>
@@ -3952,10 +3953,10 @@
         <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>23</v>
       </c>
@@ -3972,10 +3973,10 @@
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>23</v>
       </c>
@@ -3992,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="J67" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4015,10 +4016,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>23</v>
       </c>
@@ -4035,10 +4036,10 @@
         <v>10</v>
       </c>
       <c r="J69" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>23</v>
       </c>
@@ -4055,10 +4056,10 @@
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>23</v>
       </c>
@@ -4078,7 +4079,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>23</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>23</v>
       </c>
@@ -4115,10 +4116,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>23</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>23</v>
       </c>
@@ -4158,7 +4159,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>23</v>
       </c>
@@ -4178,7 +4179,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>23</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>23</v>
       </c>
@@ -4215,10 +4216,10 @@
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>23</v>
       </c>
@@ -4235,10 +4236,10 @@
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>23</v>
       </c>
@@ -4255,10 +4256,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>23</v>
       </c>
@@ -4275,10 +4276,10 @@
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>23</v>
       </c>
@@ -4295,10 +4296,10 @@
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>23</v>
       </c>
@@ -4316,7 +4317,7 @@
       </c>
       <c r="J83"/>
     </row>
-    <row r="84" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>23</v>
       </c>
@@ -4334,7 +4335,7 @@
       </c>
       <c r="J84"/>
     </row>
-    <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>23</v>
       </c>
@@ -4351,10 +4352,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>23</v>
       </c>
@@ -4372,7 +4373,7 @@
       </c>
       <c r="J86"/>
     </row>
-    <row r="87" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>23</v>
       </c>
@@ -4390,7 +4391,7 @@
       </c>
       <c r="J87"/>
     </row>
-    <row r="88" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>23</v>
       </c>
@@ -4408,7 +4409,7 @@
       </c>
       <c r="J88"/>
     </row>
-    <row r="89" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>23</v>
       </c>
@@ -4425,10 +4426,10 @@
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>23</v>
       </c>
@@ -4445,10 +4446,10 @@
         <v>10</v>
       </c>
       <c r="J90" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>23</v>
       </c>
@@ -4465,10 +4466,10 @@
         <v>10</v>
       </c>
       <c r="J91" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>23</v>
       </c>
@@ -4485,10 +4486,10 @@
         <v>10</v>
       </c>
       <c r="J92" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>23</v>
       </c>
@@ -4505,10 +4506,10 @@
         <v>10</v>
       </c>
       <c r="J93" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>23</v>
       </c>
@@ -4525,10 +4526,10 @@
         <v>10</v>
       </c>
       <c r="J94" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>23</v>
       </c>
@@ -4545,10 +4546,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>23</v>
       </c>
@@ -4565,10 +4566,10 @@
         <v>10</v>
       </c>
       <c r="J96" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>23</v>
       </c>
@@ -4588,7 +4589,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>23</v>
       </c>
@@ -4605,10 +4606,10 @@
         <v>10</v>
       </c>
       <c r="J98" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>23</v>
       </c>
@@ -4625,10 +4626,10 @@
         <v>10</v>
       </c>
       <c r="J99" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>23</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>23</v>
       </c>
@@ -4668,7 +4669,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>23</v>
       </c>
@@ -4686,7 +4687,7 @@
       </c>
       <c r="J102"/>
     </row>
-    <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>23</v>
       </c>
@@ -4706,7 +4707,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>23</v>
       </c>
@@ -4769,7 +4770,7 @@
         <v>10</v>
       </c>
       <c r="J106" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4792,10 +4793,10 @@
         <v>10</v>
       </c>
       <c r="J107" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>23</v>
       </c>
@@ -4815,7 +4816,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>23</v>
       </c>
@@ -4833,7 +4834,7 @@
       </c>
       <c r="J109"/>
     </row>
-    <row r="110" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>23</v>
       </c>
@@ -4851,7 +4852,7 @@
       </c>
       <c r="J110"/>
     </row>
-    <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>23</v>
       </c>
@@ -4868,10 +4869,10 @@
         <v>10</v>
       </c>
       <c r="J111" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>23</v>
       </c>
@@ -4888,10 +4889,10 @@
         <v>10</v>
       </c>
       <c r="J112" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>23</v>
       </c>
@@ -4908,10 +4909,10 @@
         <v>10</v>
       </c>
       <c r="J113" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>23</v>
       </c>
@@ -4928,10 +4929,10 @@
         <v>10</v>
       </c>
       <c r="J114" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>23</v>
       </c>
@@ -4948,10 +4949,10 @@
         <v>10</v>
       </c>
       <c r="J115" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>23</v>
       </c>
@@ -4968,10 +4969,10 @@
         <v>10</v>
       </c>
       <c r="J116" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>23</v>
       </c>
@@ -4988,10 +4989,10 @@
         <v>10</v>
       </c>
       <c r="J117" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>23</v>
       </c>
@@ -5008,10 +5009,10 @@
         <v>10</v>
       </c>
       <c r="J118" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>23</v>
       </c>
@@ -5028,10 +5029,10 @@
         <v>10</v>
       </c>
       <c r="J119" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>23</v>
       </c>
@@ -5048,10 +5049,10 @@
         <v>10</v>
       </c>
       <c r="J120" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>23</v>
       </c>
@@ -5068,10 +5069,10 @@
         <v>10</v>
       </c>
       <c r="J121" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>23</v>
       </c>
@@ -5088,10 +5089,10 @@
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>23</v>
       </c>
@@ -5108,10 +5109,10 @@
         <v>10</v>
       </c>
       <c r="J123" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>23</v>
       </c>
@@ -5128,10 +5129,10 @@
         <v>10</v>
       </c>
       <c r="J124" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>23</v>
       </c>
@@ -5148,10 +5149,10 @@
         <v>10</v>
       </c>
       <c r="J125" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>23</v>
       </c>
@@ -5168,10 +5169,10 @@
         <v>10</v>
       </c>
       <c r="J126" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>23</v>
       </c>
@@ -5188,10 +5189,10 @@
         <v>10</v>
       </c>
       <c r="J127" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>23</v>
       </c>
@@ -5208,10 +5209,10 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>23</v>
       </c>
@@ -5228,10 +5229,10 @@
         <v>10</v>
       </c>
       <c r="J129" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>23</v>
       </c>
@@ -5248,10 +5249,10 @@
         <v>10</v>
       </c>
       <c r="J130" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>23</v>
       </c>
@@ -5268,10 +5269,10 @@
         <v>10</v>
       </c>
       <c r="J131" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>23</v>
       </c>
@@ -5288,10 +5289,10 @@
         <v>10</v>
       </c>
       <c r="J132" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>23</v>
       </c>
@@ -5308,10 +5309,10 @@
         <v>10</v>
       </c>
       <c r="J133" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>23</v>
       </c>
@@ -5328,10 +5329,10 @@
         <v>10</v>
       </c>
       <c r="J134" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>23</v>
       </c>
@@ -5348,10 +5349,10 @@
         <v>10</v>
       </c>
       <c r="J135" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>23</v>
       </c>
@@ -5368,10 +5369,10 @@
         <v>10</v>
       </c>
       <c r="J136" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>23</v>
       </c>
@@ -5388,10 +5389,10 @@
         <v>10</v>
       </c>
       <c r="J137" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>23</v>
       </c>
@@ -5408,10 +5409,10 @@
         <v>10</v>
       </c>
       <c r="J138" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>23</v>
       </c>
@@ -5428,10 +5429,10 @@
         <v>10</v>
       </c>
       <c r="J139" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>23</v>
       </c>
@@ -5448,10 +5449,10 @@
         <v>10</v>
       </c>
       <c r="J140" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>27</v>
       </c>
@@ -5471,10 +5472,10 @@
         <v>10</v>
       </c>
       <c r="J141" s="5" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>27</v>
       </c>
@@ -5491,10 +5492,10 @@
         <v>10</v>
       </c>
       <c r="J142" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>27</v>
       </c>
@@ -5514,10 +5515,10 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>27</v>
       </c>
@@ -5534,10 +5535,10 @@
         <v>10</v>
       </c>
       <c r="J144" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>27</v>
       </c>
@@ -5554,10 +5555,10 @@
         <v>10</v>
       </c>
       <c r="J145" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>27</v>
       </c>
@@ -5574,10 +5575,10 @@
         <v>10</v>
       </c>
       <c r="J146" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>27</v>
       </c>
@@ -5594,10 +5595,10 @@
         <v>10</v>
       </c>
       <c r="J147" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>27</v>
       </c>
@@ -5614,10 +5615,10 @@
         <v>10</v>
       </c>
       <c r="J148" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>27</v>
       </c>
@@ -5634,10 +5635,10 @@
         <v>10</v>
       </c>
       <c r="J149" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>27</v>
       </c>
@@ -5654,10 +5655,10 @@
         <v>10</v>
       </c>
       <c r="J150" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>27</v>
       </c>
@@ -5674,10 +5675,10 @@
         <v>10</v>
       </c>
       <c r="J151" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>27</v>
       </c>
@@ -5697,7 +5698,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>27</v>
       </c>
@@ -5717,7 +5718,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>27</v>
       </c>
@@ -5737,7 +5738,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>27</v>
       </c>
@@ -5754,10 +5755,10 @@
         <v>10</v>
       </c>
       <c r="J155" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>27</v>
       </c>
@@ -5774,10 +5775,10 @@
         <v>10</v>
       </c>
       <c r="J156" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>27</v>
       </c>
@@ -5794,10 +5795,10 @@
         <v>10</v>
       </c>
       <c r="J157" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>27</v>
       </c>
@@ -5814,10 +5815,10 @@
         <v>10</v>
       </c>
       <c r="J158" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>27</v>
       </c>
@@ -5834,10 +5835,10 @@
         <v>10</v>
       </c>
       <c r="J159" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>27</v>
       </c>
@@ -5854,10 +5855,10 @@
         <v>10</v>
       </c>
       <c r="J160" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>27</v>
       </c>
@@ -5874,10 +5875,10 @@
         <v>10</v>
       </c>
       <c r="J161" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>27</v>
       </c>
@@ -5894,10 +5895,10 @@
         <v>10</v>
       </c>
       <c r="J162" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>27</v>
       </c>
@@ -5917,7 +5918,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>27</v>
       </c>
@@ -5937,7 +5938,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>27</v>
       </c>
@@ -5957,7 +5958,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>27</v>
       </c>
@@ -5977,7 +5978,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>27</v>
       </c>
@@ -5997,7 +5998,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
         <v>27</v>
       </c>
@@ -6017,7 +6018,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>27</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
         <v>27</v>
       </c>
@@ -6060,7 +6061,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>27</v>
       </c>
@@ -6080,7 +6081,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
         <v>27</v>
       </c>
@@ -6097,10 +6098,10 @@
         <v>10</v>
       </c>
       <c r="J172" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
         <v>27</v>
       </c>
@@ -6117,10 +6118,10 @@
         <v>10</v>
       </c>
       <c r="J173" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
         <v>27</v>
       </c>
@@ -6137,10 +6138,10 @@
         <v>10</v>
       </c>
       <c r="J174" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>27</v>
       </c>
@@ -6157,10 +6158,10 @@
         <v>10</v>
       </c>
       <c r="J175" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
         <v>27</v>
       </c>
@@ -6177,10 +6178,10 @@
         <v>10</v>
       </c>
       <c r="J176" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>27</v>
       </c>
@@ -6197,10 +6198,10 @@
         <v>10</v>
       </c>
       <c r="J177" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
         <v>27</v>
       </c>
@@ -6217,10 +6218,10 @@
         <v>10</v>
       </c>
       <c r="J178" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
         <v>27</v>
       </c>
@@ -6237,10 +6238,10 @@
         <v>10</v>
       </c>
       <c r="J179" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
         <v>27</v>
       </c>
@@ -6257,7 +6258,7 @@
         <v>10</v>
       </c>
       <c r="J180" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6280,7 +6281,7 @@
         <v>10</v>
       </c>
       <c r="J181" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6303,7 +6304,7 @@
         <v>10</v>
       </c>
       <c r="J182" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6326,7 +6327,7 @@
         <v>10</v>
       </c>
       <c r="J183" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6349,7 +6350,7 @@
         <v>10</v>
       </c>
       <c r="J184" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6372,10 +6373,10 @@
         <v>10</v>
       </c>
       <c r="J185" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>27</v>
       </c>
@@ -6392,10 +6393,10 @@
         <v>10</v>
       </c>
       <c r="J186" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>27</v>
       </c>
@@ -6412,10 +6413,10 @@
         <v>10</v>
       </c>
       <c r="J187" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>27</v>
       </c>
@@ -6432,10 +6433,10 @@
         <v>10</v>
       </c>
       <c r="J188" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>27</v>
       </c>
@@ -6455,7 +6456,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
         <v>27</v>
       </c>
@@ -6475,7 +6476,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>27</v>
       </c>
@@ -6492,10 +6493,10 @@
         <v>10</v>
       </c>
       <c r="J191" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
         <v>27</v>
       </c>
@@ -6512,10 +6513,10 @@
         <v>10</v>
       </c>
       <c r="J192" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>27</v>
       </c>
@@ -6532,10 +6533,10 @@
         <v>10</v>
       </c>
       <c r="J193" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
         <v>27</v>
       </c>
@@ -6552,10 +6553,10 @@
         <v>10</v>
       </c>
       <c r="J194" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>27</v>
       </c>
@@ -6572,10 +6573,10 @@
         <v>10</v>
       </c>
       <c r="J195" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
         <v>27</v>
       </c>
@@ -6592,10 +6593,10 @@
         <v>10</v>
       </c>
       <c r="J196" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
         <v>27</v>
       </c>
@@ -6612,10 +6613,10 @@
         <v>10</v>
       </c>
       <c r="J197" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
         <v>27</v>
       </c>
@@ -6632,10 +6633,10 @@
         <v>10</v>
       </c>
       <c r="J198" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>27</v>
       </c>
@@ -6652,10 +6653,10 @@
         <v>10</v>
       </c>
       <c r="J199" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
         <v>27</v>
       </c>
@@ -6672,10 +6673,10 @@
         <v>10</v>
       </c>
       <c r="J200" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>27</v>
       </c>
@@ -6692,10 +6693,10 @@
         <v>10</v>
       </c>
       <c r="J201" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
         <v>27</v>
       </c>
@@ -6712,10 +6713,10 @@
         <v>10</v>
       </c>
       <c r="J202" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
         <v>27</v>
       </c>
@@ -6732,7 +6733,7 @@
         <v>10</v>
       </c>
       <c r="J203" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6755,7 +6756,7 @@
         <v>10</v>
       </c>
       <c r="J204" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6778,7 +6779,7 @@
         <v>10</v>
       </c>
       <c r="J205" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6801,7 +6802,7 @@
         <v>10</v>
       </c>
       <c r="J206" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6824,7 +6825,7 @@
         <v>10</v>
       </c>
       <c r="J207" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6965,7 +6966,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>27</v>
       </c>
@@ -6985,7 +6986,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>27</v>
       </c>
@@ -7005,7 +7006,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>27</v>
       </c>
@@ -7094,7 +7095,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
         <v>27</v>
       </c>
@@ -7114,7 +7115,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>27</v>
       </c>
@@ -7134,7 +7135,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>27</v>
       </c>
@@ -7154,7 +7155,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>27</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
         <v>27</v>
       </c>
@@ -7194,7 +7195,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
         <v>27</v>
       </c>
@@ -7214,7 +7215,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
         <v>27</v>
       </c>
@@ -7234,7 +7235,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>27</v>
       </c>
@@ -7254,7 +7255,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
         <v>27</v>
       </c>
@@ -7274,7 +7275,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>27</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>27</v>
       </c>
@@ -7311,7 +7312,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="5" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7498,7 +7499,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>27</v>
       </c>
@@ -7538,10 +7539,10 @@
         <v>10</v>
       </c>
       <c r="J240" s="5" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>27</v>
       </c>
@@ -7558,10 +7559,10 @@
         <v>10</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>29</v>
       </c>
@@ -7581,10 +7582,10 @@
         <v>10</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
         <v>29</v>
       </c>
@@ -7601,10 +7602,10 @@
         <v>10</v>
       </c>
       <c r="J243" s="5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
         <v>29</v>
       </c>
@@ -7621,10 +7622,10 @@
         <v>10</v>
       </c>
       <c r="J244" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
         <v>29</v>
       </c>
@@ -7644,10 +7645,10 @@
         <v>10</v>
       </c>
       <c r="J245" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
         <v>29</v>
       </c>
@@ -7664,10 +7665,10 @@
         <v>10</v>
       </c>
       <c r="J246" s="5" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>29</v>
       </c>
@@ -7684,10 +7685,10 @@
         <v>10</v>
       </c>
       <c r="J247" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
         <v>29</v>
       </c>
@@ -7704,10 +7705,10 @@
         <v>10</v>
       </c>
       <c r="J248" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
         <v>29</v>
       </c>
@@ -7724,10 +7725,10 @@
         <v>10</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>29</v>
       </c>
@@ -7744,10 +7745,10 @@
         <v>10</v>
       </c>
       <c r="J250" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
         <v>29</v>
       </c>
@@ -7764,10 +7765,10 @@
         <v>10</v>
       </c>
       <c r="J251" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>29</v>
       </c>
@@ -7784,10 +7785,10 @@
         <v>10</v>
       </c>
       <c r="J252" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
         <v>29</v>
       </c>
@@ -7804,10 +7805,10 @@
         <v>10</v>
       </c>
       <c r="J253" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>29</v>
       </c>
@@ -7824,10 +7825,10 @@
         <v>10</v>
       </c>
       <c r="J254" s="5" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>29</v>
       </c>
@@ -7844,10 +7845,10 @@
         <v>10</v>
       </c>
       <c r="J255" s="5" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>29</v>
       </c>
@@ -7864,10 +7865,10 @@
         <v>10</v>
       </c>
       <c r="J256" s="5" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>29</v>
       </c>
@@ -7884,10 +7885,10 @@
         <v>10</v>
       </c>
       <c r="J257" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>29</v>
       </c>
@@ -7904,10 +7905,10 @@
         <v>10</v>
       </c>
       <c r="J258" s="5" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>29</v>
       </c>
@@ -7924,10 +7925,10 @@
         <v>10</v>
       </c>
       <c r="J259" s="5" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>29</v>
       </c>
@@ -7944,10 +7945,10 @@
         <v>10</v>
       </c>
       <c r="J260" s="5" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>29</v>
       </c>
@@ -7964,10 +7965,10 @@
         <v>10</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>29</v>
       </c>
@@ -7984,10 +7985,10 @@
         <v>10</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>29</v>
       </c>
@@ -8004,10 +8005,10 @@
         <v>10</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>29</v>
       </c>
@@ -8024,10 +8025,10 @@
         <v>10</v>
       </c>
       <c r="J264" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>29</v>
       </c>
@@ -8044,10 +8045,10 @@
         <v>10</v>
       </c>
       <c r="J265" s="5" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>29</v>
       </c>
@@ -8064,10 +8065,10 @@
         <v>10</v>
       </c>
       <c r="J266" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>29</v>
       </c>
@@ -8084,10 +8085,10 @@
         <v>10</v>
       </c>
       <c r="J267" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>29</v>
       </c>
@@ -8104,10 +8105,10 @@
         <v>10</v>
       </c>
       <c r="J268" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
         <v>29</v>
       </c>
@@ -8124,10 +8125,10 @@
         <v>10</v>
       </c>
       <c r="J269" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>29</v>
       </c>
@@ -8144,10 +8145,10 @@
         <v>10</v>
       </c>
       <c r="J270" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
         <v>29</v>
       </c>
@@ -8164,10 +8165,10 @@
         <v>10</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
         <v>29</v>
       </c>
@@ -8184,10 +8185,10 @@
         <v>10</v>
       </c>
       <c r="J272" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>29</v>
       </c>
@@ -8204,10 +8205,10 @@
         <v>10</v>
       </c>
       <c r="J273" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>29</v>
       </c>
@@ -8224,10 +8225,10 @@
         <v>10</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
         <v>29</v>
       </c>
@@ -8244,10 +8245,10 @@
         <v>10</v>
       </c>
       <c r="J275" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>29</v>
       </c>
@@ -8264,10 +8265,10 @@
         <v>10</v>
       </c>
       <c r="J276" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>29</v>
       </c>
@@ -8284,10 +8285,10 @@
         <v>10</v>
       </c>
       <c r="J277" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>29</v>
       </c>
@@ -8304,10 +8305,10 @@
         <v>10</v>
       </c>
       <c r="J278" s="5" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>29</v>
       </c>
@@ -8324,10 +8325,10 @@
         <v>10</v>
       </c>
       <c r="J279" s="5" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>29</v>
       </c>
@@ -8344,10 +8345,10 @@
         <v>10</v>
       </c>
       <c r="J280" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
         <v>29</v>
       </c>
@@ -8364,10 +8365,10 @@
         <v>10</v>
       </c>
       <c r="J281" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>29</v>
       </c>
@@ -8384,10 +8385,10 @@
         <v>10</v>
       </c>
       <c r="J282" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>29</v>
       </c>
@@ -8404,10 +8405,10 @@
         <v>10</v>
       </c>
       <c r="J283" s="5" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>29</v>
       </c>
@@ -8424,10 +8425,10 @@
         <v>10</v>
       </c>
       <c r="J284" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>29</v>
       </c>
@@ -8444,10 +8445,10 @@
         <v>10</v>
       </c>
       <c r="J285" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>29</v>
       </c>
@@ -8464,10 +8465,10 @@
         <v>10</v>
       </c>
       <c r="J286" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
         <v>29</v>
       </c>
@@ -8484,10 +8485,10 @@
         <v>10</v>
       </c>
       <c r="J287" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>29</v>
       </c>
@@ -8504,10 +8505,10 @@
         <v>10</v>
       </c>
       <c r="J288" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
         <v>29</v>
       </c>
@@ -8524,10 +8525,10 @@
         <v>10</v>
       </c>
       <c r="J289" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>29</v>
       </c>
@@ -8544,10 +8545,10 @@
         <v>10</v>
       </c>
       <c r="J290" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>29</v>
       </c>
@@ -8564,10 +8565,10 @@
         <v>10</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>29</v>
       </c>
@@ -8584,10 +8585,10 @@
         <v>10</v>
       </c>
       <c r="J292" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>29</v>
       </c>
@@ -8604,10 +8605,10 @@
         <v>10</v>
       </c>
       <c r="J293" s="5" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>29</v>
       </c>
@@ -8624,10 +8625,10 @@
         <v>10</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>29</v>
       </c>
@@ -8644,10 +8645,10 @@
         <v>10</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>29</v>
       </c>
@@ -8664,10 +8665,10 @@
         <v>10</v>
       </c>
       <c r="J296" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>29</v>
       </c>
@@ -8684,10 +8685,10 @@
         <v>10</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>29</v>
       </c>
@@ -8704,7 +8705,7 @@
         <v>10</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8727,7 +8728,7 @@
         <v>10</v>
       </c>
       <c r="J299" s="5" t="s">
-        <v>532</v>
+        <v>698</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8750,7 +8751,7 @@
         <v>10</v>
       </c>
       <c r="J300" s="5" t="s">
-        <v>533</v>
+        <v>699</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8773,7 +8774,7 @@
         <v>10</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>534</v>
+        <v>700</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8796,7 +8797,7 @@
         <v>10</v>
       </c>
       <c r="J302" s="5" t="s">
-        <v>535</v>
+        <v>701</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8819,7 +8820,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8842,7 +8843,7 @@
         <v>10</v>
       </c>
       <c r="J304" s="5" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8865,7 +8866,7 @@
         <v>10</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8888,7 +8889,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="5" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8911,7 +8912,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="5" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8934,7 +8935,7 @@
         <v>10</v>
       </c>
       <c r="J308" s="5" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8957,7 +8958,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="5" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8980,7 +8981,7 @@
         <v>10</v>
       </c>
       <c r="J310" s="5" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9003,7 +9004,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="5" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9026,7 +9027,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="5" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9049,7 +9050,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="5" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9072,7 +9073,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9095,10 +9096,10 @@
         <v>10</v>
       </c>
       <c r="J315" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>29</v>
       </c>
@@ -9115,10 +9116,10 @@
         <v>10</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>29</v>
       </c>
@@ -9135,10 +9136,10 @@
         <v>10</v>
       </c>
       <c r="J317" s="5" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>29</v>
       </c>
@@ -9155,10 +9156,10 @@
         <v>10</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
         <v>29</v>
       </c>
@@ -9175,10 +9176,10 @@
         <v>10</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>29</v>
       </c>
@@ -9195,10 +9196,10 @@
         <v>10</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>29</v>
       </c>
@@ -9215,10 +9216,10 @@
         <v>10</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>29</v>
       </c>
@@ -9235,10 +9236,10 @@
         <v>10</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
         <v>29</v>
       </c>
@@ -9255,10 +9256,10 @@
         <v>10</v>
       </c>
       <c r="J323" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>29</v>
       </c>
@@ -9275,10 +9276,10 @@
         <v>10</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>29</v>
       </c>
@@ -9295,10 +9296,10 @@
         <v>10</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>29</v>
       </c>
@@ -9315,7 +9316,7 @@
         <v>10</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9338,7 +9339,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9361,7 +9362,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9384,10 +9385,10 @@
         <v>10</v>
       </c>
       <c r="J329" s="5" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
         <v>29</v>
       </c>
@@ -9404,10 +9405,10 @@
         <v>10</v>
       </c>
       <c r="J330" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
         <v>29</v>
       </c>
@@ -9424,10 +9425,10 @@
         <v>10</v>
       </c>
       <c r="J331" s="5" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>29</v>
       </c>
@@ -9444,10 +9445,10 @@
         <v>10</v>
       </c>
       <c r="J332" s="5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
         <v>29</v>
       </c>
@@ -9464,10 +9465,10 @@
         <v>10</v>
       </c>
       <c r="J333" s="5" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
         <v>29</v>
       </c>
@@ -9484,7 +9485,7 @@
         <v>10</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9507,7 +9508,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="5" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9530,10 +9531,10 @@
         <v>10</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
         <v>29</v>
       </c>
@@ -9550,10 +9551,10 @@
         <v>10</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
         <v>29</v>
       </c>
@@ -9570,7 +9571,7 @@
         <v>10</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9593,7 +9594,7 @@
         <v>10</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9616,10 +9617,10 @@
         <v>10</v>
       </c>
       <c r="J340" s="5" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>29</v>
       </c>
@@ -9636,10 +9637,10 @@
         <v>10</v>
       </c>
       <c r="J341" s="5" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>399</v>
       </c>
@@ -9659,10 +9660,10 @@
         <v>10</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
         <v>399</v>
       </c>
@@ -9679,10 +9680,10 @@
         <v>10</v>
       </c>
       <c r="J343" s="5" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="344" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="4" t="s">
         <v>399</v>
       </c>
@@ -9699,10 +9700,10 @@
         <v>10</v>
       </c>
       <c r="J344" s="5" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="345" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
         <v>399</v>
       </c>
@@ -9722,11 +9723,17 @@
         <v>10</v>
       </c>
       <c r="J345" s="5" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J345" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:J345" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF3AF11-B869-654D-B77E-085C29D3DBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C754AB3D-C3D6-C14F-B16A-88F9CC6C398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="660" windowWidth="30680" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3820" yWindow="600" windowWidth="30680" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="703">
   <si>
     <t>Table Name</t>
   </si>
@@ -1234,9 +1234,6 @@
     <t>Table datamart informasi lending nasabah, berisi informasi terkait account lending nasabah (loan, pinjaman, kredit)</t>
   </si>
   <si>
-    <t>Table datamart informasi funding nasabah, berisi informasi terkait account funding nasabah (tabungan, giro, deposito)</t>
-  </si>
-  <si>
     <t>Table datamart informasi group nasabah yang dikelompokkan berdasarkan CIF key</t>
   </si>
   <si>
@@ -2132,6 +2129,12 @@
   </si>
   <si>
     <t>Nilai penyesuaian PSAK kategori/komponen ACC sesuai definisi internal.</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Table datamart informasi funding nasabah, berisi informasi terkait account funding nasabah (tabungan, giro, deposito). Table funding juga disebut dengan table DPK.</t>
   </si>
 </sst>
 </file>
@@ -2518,73 +2521,73 @@
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.33203125" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C4" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>398</v>
       </c>
       <c r="B6" t="s">
         <v>399</v>
       </c>
-      <c r="C6" t="s">
-        <v>403</v>
+      <c r="C6" s="4" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -2594,7 +2597,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2625,7 +2627,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
@@ -2643,7 +2645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -2663,10 +2665,10 @@
         <v>10</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2686,7 +2688,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
@@ -2706,10 +2708,10 @@
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -2729,10 +2731,10 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
@@ -2752,7 +2754,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
@@ -2772,7 +2774,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -2792,7 +2794,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -2812,7 +2814,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -2832,7 +2834,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -2852,7 +2854,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2872,7 +2874,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -2892,7 +2894,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -2926,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>10</v>
@@ -2955,10 +2957,10 @@
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
@@ -2972,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J17" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -2998,7 +3000,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
@@ -3018,7 +3020,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
@@ -3038,7 +3040,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -3058,7 +3060,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
@@ -3078,7 +3080,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -3098,7 +3100,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -3118,7 +3120,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
@@ -3138,7 +3140,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
@@ -3158,7 +3160,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
@@ -3178,7 +3180,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>22</v>
       </c>
@@ -3198,7 +3200,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>22</v>
       </c>
@@ -3221,7 +3223,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>22</v>
       </c>
@@ -3241,10 +3243,10 @@
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>22</v>
       </c>
@@ -3261,10 +3263,10 @@
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
@@ -3284,7 +3286,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
@@ -3304,7 +3306,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>22</v>
       </c>
@@ -3324,7 +3326,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>22</v>
       </c>
@@ -3344,7 +3346,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>22</v>
       </c>
@@ -3364,7 +3366,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>22</v>
       </c>
@@ -3384,7 +3386,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>22</v>
       </c>
@@ -3427,7 +3429,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -3447,7 +3449,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -3464,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>10</v>
@@ -3473,7 +3475,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>23</v>
       </c>
@@ -3490,10 +3492,10 @@
         <v>10</v>
       </c>
       <c r="J42" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>23</v>
       </c>
@@ -3513,7 +3515,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>23</v>
       </c>
@@ -3530,10 +3532,10 @@
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>23</v>
       </c>
@@ -3553,7 +3555,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>23</v>
       </c>
@@ -3573,7 +3575,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>23</v>
       </c>
@@ -3593,7 +3595,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>23</v>
       </c>
@@ -3613,7 +3615,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>23</v>
       </c>
@@ -3633,7 +3635,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>23</v>
       </c>
@@ -3653,7 +3655,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>23</v>
       </c>
@@ -3673,7 +3675,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>23</v>
       </c>
@@ -3693,7 +3695,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>23</v>
       </c>
@@ -3707,16 +3709,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J53" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>23</v>
       </c>
@@ -3733,10 +3735,10 @@
         <v>10</v>
       </c>
       <c r="J54" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>23</v>
       </c>
@@ -3753,10 +3755,10 @@
         <v>10</v>
       </c>
       <c r="J55" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>23</v>
       </c>
@@ -3776,7 +3778,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>23</v>
       </c>
@@ -3796,7 +3798,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>23</v>
       </c>
@@ -3816,7 +3818,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>23</v>
       </c>
@@ -3836,7 +3838,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>23</v>
       </c>
@@ -3856,7 +3858,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>23</v>
       </c>
@@ -3876,7 +3878,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>23</v>
       </c>
@@ -3896,7 +3898,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>23</v>
       </c>
@@ -3916,7 +3918,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>23</v>
       </c>
@@ -3936,7 +3938,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>23</v>
       </c>
@@ -3953,10 +3955,10 @@
         <v>10</v>
       </c>
       <c r="J65" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>23</v>
       </c>
@@ -3973,10 +3975,10 @@
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>23</v>
       </c>
@@ -3993,7 +3995,7 @@
         <v>10</v>
       </c>
       <c r="J67" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4016,10 +4018,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>23</v>
       </c>
@@ -4036,10 +4038,10 @@
         <v>10</v>
       </c>
       <c r="J69" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>23</v>
       </c>
@@ -4056,10 +4058,10 @@
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>23</v>
       </c>
@@ -4079,7 +4081,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>23</v>
       </c>
@@ -4099,7 +4101,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>23</v>
       </c>
@@ -4116,10 +4118,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>23</v>
       </c>
@@ -4139,7 +4141,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>23</v>
       </c>
@@ -4159,7 +4161,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>23</v>
       </c>
@@ -4179,7 +4181,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>23</v>
       </c>
@@ -4199,7 +4201,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>23</v>
       </c>
@@ -4216,10 +4218,10 @@
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>23</v>
       </c>
@@ -4236,10 +4238,10 @@
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>23</v>
       </c>
@@ -4256,10 +4258,10 @@
         <v>10</v>
       </c>
       <c r="J80" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>23</v>
       </c>
@@ -4276,10 +4278,10 @@
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>23</v>
       </c>
@@ -4296,10 +4298,10 @@
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>23</v>
       </c>
@@ -4317,7 +4319,7 @@
       </c>
       <c r="J83"/>
     </row>
-    <row r="84" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>23</v>
       </c>
@@ -4335,7 +4337,7 @@
       </c>
       <c r="J84"/>
     </row>
-    <row r="85" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>23</v>
       </c>
@@ -4352,10 +4354,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>23</v>
       </c>
@@ -4373,7 +4375,7 @@
       </c>
       <c r="J86"/>
     </row>
-    <row r="87" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>23</v>
       </c>
@@ -4391,7 +4393,7 @@
       </c>
       <c r="J87"/>
     </row>
-    <row r="88" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>23</v>
       </c>
@@ -4409,7 +4411,7 @@
       </c>
       <c r="J88"/>
     </row>
-    <row r="89" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>23</v>
       </c>
@@ -4426,10 +4428,10 @@
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>23</v>
       </c>
@@ -4446,10 +4448,10 @@
         <v>10</v>
       </c>
       <c r="J90" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>23</v>
       </c>
@@ -4466,10 +4468,10 @@
         <v>10</v>
       </c>
       <c r="J91" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>23</v>
       </c>
@@ -4486,10 +4488,10 @@
         <v>10</v>
       </c>
       <c r="J92" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>23</v>
       </c>
@@ -4506,10 +4508,10 @@
         <v>10</v>
       </c>
       <c r="J93" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>23</v>
       </c>
@@ -4526,10 +4528,10 @@
         <v>10</v>
       </c>
       <c r="J94" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>23</v>
       </c>
@@ -4546,10 +4548,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>23</v>
       </c>
@@ -4566,10 +4568,10 @@
         <v>10</v>
       </c>
       <c r="J96" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>23</v>
       </c>
@@ -4589,7 +4591,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>23</v>
       </c>
@@ -4606,10 +4608,10 @@
         <v>10</v>
       </c>
       <c r="J98" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>23</v>
       </c>
@@ -4626,10 +4628,10 @@
         <v>10</v>
       </c>
       <c r="J99" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>23</v>
       </c>
@@ -4649,7 +4651,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>23</v>
       </c>
@@ -4669,7 +4671,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>23</v>
       </c>
@@ -4687,7 +4689,7 @@
       </c>
       <c r="J102"/>
     </row>
-    <row r="103" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>23</v>
       </c>
@@ -4707,7 +4709,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>23</v>
       </c>
@@ -4770,7 +4772,7 @@
         <v>10</v>
       </c>
       <c r="J106" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -4793,10 +4795,10 @@
         <v>10</v>
       </c>
       <c r="J107" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>23</v>
       </c>
@@ -4816,7 +4818,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>23</v>
       </c>
@@ -4834,7 +4836,7 @@
       </c>
       <c r="J109"/>
     </row>
-    <row r="110" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>23</v>
       </c>
@@ -4852,7 +4854,7 @@
       </c>
       <c r="J110"/>
     </row>
-    <row r="111" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>23</v>
       </c>
@@ -4869,10 +4871,10 @@
         <v>10</v>
       </c>
       <c r="J111" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>23</v>
       </c>
@@ -4889,10 +4891,10 @@
         <v>10</v>
       </c>
       <c r="J112" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>23</v>
       </c>
@@ -4909,10 +4911,10 @@
         <v>10</v>
       </c>
       <c r="J113" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>23</v>
       </c>
@@ -4929,10 +4931,10 @@
         <v>10</v>
       </c>
       <c r="J114" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>23</v>
       </c>
@@ -4949,10 +4951,10 @@
         <v>10</v>
       </c>
       <c r="J115" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>23</v>
       </c>
@@ -4969,10 +4971,10 @@
         <v>10</v>
       </c>
       <c r="J116" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>23</v>
       </c>
@@ -4989,10 +4991,10 @@
         <v>10</v>
       </c>
       <c r="J117" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>23</v>
       </c>
@@ -5009,10 +5011,10 @@
         <v>10</v>
       </c>
       <c r="J118" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>23</v>
       </c>
@@ -5029,10 +5031,10 @@
         <v>10</v>
       </c>
       <c r="J119" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>23</v>
       </c>
@@ -5049,10 +5051,10 @@
         <v>10</v>
       </c>
       <c r="J120" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>23</v>
       </c>
@@ -5069,10 +5071,10 @@
         <v>10</v>
       </c>
       <c r="J121" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>23</v>
       </c>
@@ -5089,10 +5091,10 @@
         <v>10</v>
       </c>
       <c r="J122" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>23</v>
       </c>
@@ -5109,10 +5111,10 @@
         <v>10</v>
       </c>
       <c r="J123" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>23</v>
       </c>
@@ -5129,10 +5131,10 @@
         <v>10</v>
       </c>
       <c r="J124" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>23</v>
       </c>
@@ -5149,10 +5151,10 @@
         <v>10</v>
       </c>
       <c r="J125" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>23</v>
       </c>
@@ -5169,10 +5171,10 @@
         <v>10</v>
       </c>
       <c r="J126" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>23</v>
       </c>
@@ -5189,10 +5191,10 @@
         <v>10</v>
       </c>
       <c r="J127" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>23</v>
       </c>
@@ -5209,10 +5211,10 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>23</v>
       </c>
@@ -5229,10 +5231,10 @@
         <v>10</v>
       </c>
       <c r="J129" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>23</v>
       </c>
@@ -5249,10 +5251,10 @@
         <v>10</v>
       </c>
       <c r="J130" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>23</v>
       </c>
@@ -5269,10 +5271,10 @@
         <v>10</v>
       </c>
       <c r="J131" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>23</v>
       </c>
@@ -5289,10 +5291,10 @@
         <v>10</v>
       </c>
       <c r="J132" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>23</v>
       </c>
@@ -5309,10 +5311,10 @@
         <v>10</v>
       </c>
       <c r="J133" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>23</v>
       </c>
@@ -5329,10 +5331,10 @@
         <v>10</v>
       </c>
       <c r="J134" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>23</v>
       </c>
@@ -5349,10 +5351,10 @@
         <v>10</v>
       </c>
       <c r="J135" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>23</v>
       </c>
@@ -5369,10 +5371,10 @@
         <v>10</v>
       </c>
       <c r="J136" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>23</v>
       </c>
@@ -5389,10 +5391,10 @@
         <v>10</v>
       </c>
       <c r="J137" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>23</v>
       </c>
@@ -5409,10 +5411,10 @@
         <v>10</v>
       </c>
       <c r="J138" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>23</v>
       </c>
@@ -5429,10 +5431,10 @@
         <v>10</v>
       </c>
       <c r="J139" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>23</v>
       </c>
@@ -5449,10 +5451,10 @@
         <v>10</v>
       </c>
       <c r="J140" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>27</v>
       </c>
@@ -5472,10 +5474,10 @@
         <v>10</v>
       </c>
       <c r="J141" s="5" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>27</v>
       </c>
@@ -5492,10 +5494,10 @@
         <v>10</v>
       </c>
       <c r="J142" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>27</v>
       </c>
@@ -5515,10 +5517,10 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>27</v>
       </c>
@@ -5535,10 +5537,10 @@
         <v>10</v>
       </c>
       <c r="J144" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>27</v>
       </c>
@@ -5555,10 +5557,10 @@
         <v>10</v>
       </c>
       <c r="J145" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>27</v>
       </c>
@@ -5575,10 +5577,10 @@
         <v>10</v>
       </c>
       <c r="J146" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>27</v>
       </c>
@@ -5595,10 +5597,10 @@
         <v>10</v>
       </c>
       <c r="J147" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>27</v>
       </c>
@@ -5615,10 +5617,10 @@
         <v>10</v>
       </c>
       <c r="J148" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>27</v>
       </c>
@@ -5635,10 +5637,10 @@
         <v>10</v>
       </c>
       <c r="J149" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>27</v>
       </c>
@@ -5655,10 +5657,10 @@
         <v>10</v>
       </c>
       <c r="J150" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>27</v>
       </c>
@@ -5675,10 +5677,10 @@
         <v>10</v>
       </c>
       <c r="J151" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>27</v>
       </c>
@@ -5698,7 +5700,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>27</v>
       </c>
@@ -5718,7 +5720,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>27</v>
       </c>
@@ -5735,10 +5737,10 @@
         <v>10</v>
       </c>
       <c r="J154" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>27</v>
       </c>
@@ -5755,10 +5757,10 @@
         <v>10</v>
       </c>
       <c r="J155" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>27</v>
       </c>
@@ -5775,10 +5777,10 @@
         <v>10</v>
       </c>
       <c r="J156" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>27</v>
       </c>
@@ -5795,10 +5797,10 @@
         <v>10</v>
       </c>
       <c r="J157" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>27</v>
       </c>
@@ -5815,10 +5817,10 @@
         <v>10</v>
       </c>
       <c r="J158" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>27</v>
       </c>
@@ -5835,10 +5837,10 @@
         <v>10</v>
       </c>
       <c r="J159" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>27</v>
       </c>
@@ -5855,10 +5857,10 @@
         <v>10</v>
       </c>
       <c r="J160" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>27</v>
       </c>
@@ -5875,10 +5877,10 @@
         <v>10</v>
       </c>
       <c r="J161" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>27</v>
       </c>
@@ -5895,10 +5897,10 @@
         <v>10</v>
       </c>
       <c r="J162" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>27</v>
       </c>
@@ -5915,10 +5917,10 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>27</v>
       </c>
@@ -5935,10 +5937,10 @@
         <v>10</v>
       </c>
       <c r="J164" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>27</v>
       </c>
@@ -5955,10 +5957,10 @@
         <v>10</v>
       </c>
       <c r="J165" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>27</v>
       </c>
@@ -5975,10 +5977,10 @@
         <v>10</v>
       </c>
       <c r="J166" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>27</v>
       </c>
@@ -5995,10 +5997,10 @@
         <v>10</v>
       </c>
       <c r="J167" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
         <v>27</v>
       </c>
@@ -6015,10 +6017,10 @@
         <v>10</v>
       </c>
       <c r="J168" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>27</v>
       </c>
@@ -6038,10 +6040,10 @@
         <v>10</v>
       </c>
       <c r="J169" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
         <v>27</v>
       </c>
@@ -6058,10 +6060,10 @@
         <v>10</v>
       </c>
       <c r="J170" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>27</v>
       </c>
@@ -6078,10 +6080,10 @@
         <v>10</v>
       </c>
       <c r="J171" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
         <v>27</v>
       </c>
@@ -6098,10 +6100,10 @@
         <v>10</v>
       </c>
       <c r="J172" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
         <v>27</v>
       </c>
@@ -6118,10 +6120,10 @@
         <v>10</v>
       </c>
       <c r="J173" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
         <v>27</v>
       </c>
@@ -6138,10 +6140,10 @@
         <v>10</v>
       </c>
       <c r="J174" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>27</v>
       </c>
@@ -6158,10 +6160,10 @@
         <v>10</v>
       </c>
       <c r="J175" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
         <v>27</v>
       </c>
@@ -6178,10 +6180,10 @@
         <v>10</v>
       </c>
       <c r="J176" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>27</v>
       </c>
@@ -6198,10 +6200,10 @@
         <v>10</v>
       </c>
       <c r="J177" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
         <v>27</v>
       </c>
@@ -6218,10 +6220,10 @@
         <v>10</v>
       </c>
       <c r="J178" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
         <v>27</v>
       </c>
@@ -6238,10 +6240,10 @@
         <v>10</v>
       </c>
       <c r="J179" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
         <v>27</v>
       </c>
@@ -6258,7 +6260,7 @@
         <v>10</v>
       </c>
       <c r="J180" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6281,7 +6283,7 @@
         <v>10</v>
       </c>
       <c r="J181" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6304,7 +6306,7 @@
         <v>10</v>
       </c>
       <c r="J182" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6327,7 +6329,7 @@
         <v>10</v>
       </c>
       <c r="J183" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6350,7 +6352,7 @@
         <v>10</v>
       </c>
       <c r="J184" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6373,10 +6375,10 @@
         <v>10</v>
       </c>
       <c r="J185" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>27</v>
       </c>
@@ -6393,10 +6395,10 @@
         <v>10</v>
       </c>
       <c r="J186" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>27</v>
       </c>
@@ -6413,10 +6415,10 @@
         <v>10</v>
       </c>
       <c r="J187" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>27</v>
       </c>
@@ -6433,10 +6435,10 @@
         <v>10</v>
       </c>
       <c r="J188" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>27</v>
       </c>
@@ -6456,7 +6458,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
         <v>27</v>
       </c>
@@ -6473,10 +6475,10 @@
         <v>10</v>
       </c>
       <c r="J190" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>27</v>
       </c>
@@ -6493,10 +6495,10 @@
         <v>10</v>
       </c>
       <c r="J191" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
         <v>27</v>
       </c>
@@ -6513,10 +6515,10 @@
         <v>10</v>
       </c>
       <c r="J192" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>27</v>
       </c>
@@ -6533,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="J193" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
         <v>27</v>
       </c>
@@ -6553,10 +6555,10 @@
         <v>10</v>
       </c>
       <c r="J194" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>27</v>
       </c>
@@ -6573,10 +6575,10 @@
         <v>10</v>
       </c>
       <c r="J195" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
         <v>27</v>
       </c>
@@ -6593,10 +6595,10 @@
         <v>10</v>
       </c>
       <c r="J196" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
         <v>27</v>
       </c>
@@ -6613,10 +6615,10 @@
         <v>10</v>
       </c>
       <c r="J197" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
         <v>27</v>
       </c>
@@ -6633,10 +6635,10 @@
         <v>10</v>
       </c>
       <c r="J198" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>27</v>
       </c>
@@ -6653,10 +6655,10 @@
         <v>10</v>
       </c>
       <c r="J199" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
         <v>27</v>
       </c>
@@ -6673,10 +6675,10 @@
         <v>10</v>
       </c>
       <c r="J200" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>27</v>
       </c>
@@ -6693,10 +6695,10 @@
         <v>10</v>
       </c>
       <c r="J201" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
         <v>27</v>
       </c>
@@ -6713,10 +6715,10 @@
         <v>10</v>
       </c>
       <c r="J202" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
         <v>27</v>
       </c>
@@ -6733,7 +6735,7 @@
         <v>10</v>
       </c>
       <c r="J203" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6756,7 +6758,7 @@
         <v>10</v>
       </c>
       <c r="J204" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6779,7 +6781,7 @@
         <v>10</v>
       </c>
       <c r="J205" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6802,7 +6804,7 @@
         <v>10</v>
       </c>
       <c r="J206" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6825,7 +6827,7 @@
         <v>10</v>
       </c>
       <c r="J207" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6848,7 +6850,7 @@
         <v>10</v>
       </c>
       <c r="J208" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6871,7 +6873,7 @@
         <v>10</v>
       </c>
       <c r="J209" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6894,7 +6896,7 @@
         <v>10</v>
       </c>
       <c r="J210" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6917,7 +6919,7 @@
         <v>10</v>
       </c>
       <c r="J211" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6940,7 +6942,7 @@
         <v>10</v>
       </c>
       <c r="J212" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6963,10 +6965,10 @@
         <v>10</v>
       </c>
       <c r="J213" s="5" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>27</v>
       </c>
@@ -6983,10 +6985,10 @@
         <v>10</v>
       </c>
       <c r="J214" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>27</v>
       </c>
@@ -7003,10 +7005,10 @@
         <v>10</v>
       </c>
       <c r="J215" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>27</v>
       </c>
@@ -7023,7 +7025,7 @@
         <v>10</v>
       </c>
       <c r="J216" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7046,7 +7048,7 @@
         <v>10</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7069,7 +7071,7 @@
         <v>10</v>
       </c>
       <c r="J218" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7092,10 +7094,10 @@
         <v>10</v>
       </c>
       <c r="J219" s="5" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
         <v>27</v>
       </c>
@@ -7112,10 +7114,10 @@
         <v>10</v>
       </c>
       <c r="J220" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>27</v>
       </c>
@@ -7132,10 +7134,10 @@
         <v>10</v>
       </c>
       <c r="J221" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>27</v>
       </c>
@@ -7152,10 +7154,10 @@
         <v>10</v>
       </c>
       <c r="J222" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>27</v>
       </c>
@@ -7172,10 +7174,10 @@
         <v>10</v>
       </c>
       <c r="J223" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
         <v>27</v>
       </c>
@@ -7192,10 +7194,10 @@
         <v>10</v>
       </c>
       <c r="J224" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
         <v>27</v>
       </c>
@@ -7212,10 +7214,10 @@
         <v>10</v>
       </c>
       <c r="J225" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
         <v>27</v>
       </c>
@@ -7232,10 +7234,10 @@
         <v>10</v>
       </c>
       <c r="J226" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>27</v>
       </c>
@@ -7252,10 +7254,10 @@
         <v>10</v>
       </c>
       <c r="J227" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
         <v>27</v>
       </c>
@@ -7272,10 +7274,10 @@
         <v>10</v>
       </c>
       <c r="J228" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>27</v>
       </c>
@@ -7292,10 +7294,10 @@
         <v>10</v>
       </c>
       <c r="J229" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>27</v>
       </c>
@@ -7312,7 +7314,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7335,7 +7337,7 @@
         <v>10</v>
       </c>
       <c r="J231" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7358,7 +7360,7 @@
         <v>10</v>
       </c>
       <c r="J232" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7381,7 +7383,7 @@
         <v>10</v>
       </c>
       <c r="J233" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7404,7 +7406,7 @@
         <v>10</v>
       </c>
       <c r="J234" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7427,7 +7429,7 @@
         <v>10</v>
       </c>
       <c r="J235" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7450,7 +7452,7 @@
         <v>10</v>
       </c>
       <c r="J236" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7473,7 +7475,7 @@
         <v>10</v>
       </c>
       <c r="J237" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7496,10 +7498,10 @@
         <v>10</v>
       </c>
       <c r="J238" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>27</v>
       </c>
@@ -7516,7 +7518,7 @@
         <v>10</v>
       </c>
       <c r="J239" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -7539,10 +7541,10 @@
         <v>10</v>
       </c>
       <c r="J240" s="5" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>27</v>
       </c>
@@ -7559,10 +7561,10 @@
         <v>10</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>29</v>
       </c>
@@ -7582,10 +7584,10 @@
         <v>10</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
         <v>29</v>
       </c>
@@ -7602,10 +7604,10 @@
         <v>10</v>
       </c>
       <c r="J243" s="5" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
         <v>29</v>
       </c>
@@ -7622,10 +7624,10 @@
         <v>10</v>
       </c>
       <c r="J244" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
         <v>29</v>
       </c>
@@ -7645,10 +7647,10 @@
         <v>10</v>
       </c>
       <c r="J245" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
         <v>29</v>
       </c>
@@ -7665,10 +7667,10 @@
         <v>10</v>
       </c>
       <c r="J246" s="5" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>29</v>
       </c>
@@ -7685,10 +7687,10 @@
         <v>10</v>
       </c>
       <c r="J247" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
         <v>29</v>
       </c>
@@ -7705,10 +7707,10 @@
         <v>10</v>
       </c>
       <c r="J248" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
         <v>29</v>
       </c>
@@ -7725,10 +7727,10 @@
         <v>10</v>
       </c>
       <c r="J249" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>29</v>
       </c>
@@ -7745,10 +7747,10 @@
         <v>10</v>
       </c>
       <c r="J250" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
         <v>29</v>
       </c>
@@ -7765,10 +7767,10 @@
         <v>10</v>
       </c>
       <c r="J251" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>29</v>
       </c>
@@ -7785,10 +7787,10 @@
         <v>10</v>
       </c>
       <c r="J252" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
         <v>29</v>
       </c>
@@ -7805,10 +7807,10 @@
         <v>10</v>
       </c>
       <c r="J253" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>29</v>
       </c>
@@ -7825,10 +7827,10 @@
         <v>10</v>
       </c>
       <c r="J254" s="5" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>29</v>
       </c>
@@ -7845,10 +7847,10 @@
         <v>10</v>
       </c>
       <c r="J255" s="5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>29</v>
       </c>
@@ -7865,10 +7867,10 @@
         <v>10</v>
       </c>
       <c r="J256" s="5" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>29</v>
       </c>
@@ -7885,10 +7887,10 @@
         <v>10</v>
       </c>
       <c r="J257" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>29</v>
       </c>
@@ -7905,10 +7907,10 @@
         <v>10</v>
       </c>
       <c r="J258" s="5" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>29</v>
       </c>
@@ -7925,10 +7927,10 @@
         <v>10</v>
       </c>
       <c r="J259" s="5" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>29</v>
       </c>
@@ -7945,10 +7947,10 @@
         <v>10</v>
       </c>
       <c r="J260" s="5" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>29</v>
       </c>
@@ -7965,10 +7967,10 @@
         <v>10</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>29</v>
       </c>
@@ -7985,10 +7987,10 @@
         <v>10</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>29</v>
       </c>
@@ -8005,10 +8007,10 @@
         <v>10</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>29</v>
       </c>
@@ -8025,10 +8027,10 @@
         <v>10</v>
       </c>
       <c r="J264" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="265" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>29</v>
       </c>
@@ -8045,10 +8047,10 @@
         <v>10</v>
       </c>
       <c r="J265" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="266" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>29</v>
       </c>
@@ -8065,10 +8067,10 @@
         <v>10</v>
       </c>
       <c r="J266" s="5" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>29</v>
       </c>
@@ -8085,10 +8087,10 @@
         <v>10</v>
       </c>
       <c r="J267" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>29</v>
       </c>
@@ -8105,10 +8107,10 @@
         <v>10</v>
       </c>
       <c r="J268" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="269" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
         <v>29</v>
       </c>
@@ -8125,10 +8127,10 @@
         <v>10</v>
       </c>
       <c r="J269" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>29</v>
       </c>
@@ -8145,10 +8147,10 @@
         <v>10</v>
       </c>
       <c r="J270" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="271" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
         <v>29</v>
       </c>
@@ -8165,10 +8167,10 @@
         <v>10</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
         <v>29</v>
       </c>
@@ -8185,10 +8187,10 @@
         <v>10</v>
       </c>
       <c r="J272" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>29</v>
       </c>
@@ -8205,10 +8207,10 @@
         <v>10</v>
       </c>
       <c r="J273" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>29</v>
       </c>
@@ -8225,10 +8227,10 @@
         <v>10</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
         <v>29</v>
       </c>
@@ -8245,10 +8247,10 @@
         <v>10</v>
       </c>
       <c r="J275" s="5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>29</v>
       </c>
@@ -8265,10 +8267,10 @@
         <v>10</v>
       </c>
       <c r="J276" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>29</v>
       </c>
@@ -8285,10 +8287,10 @@
         <v>10</v>
       </c>
       <c r="J277" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>29</v>
       </c>
@@ -8305,10 +8307,10 @@
         <v>10</v>
       </c>
       <c r="J278" s="5" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>29</v>
       </c>
@@ -8325,10 +8327,10 @@
         <v>10</v>
       </c>
       <c r="J279" s="5" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>29</v>
       </c>
@@ -8345,10 +8347,10 @@
         <v>10</v>
       </c>
       <c r="J280" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
         <v>29</v>
       </c>
@@ -8365,10 +8367,10 @@
         <v>10</v>
       </c>
       <c r="J281" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>29</v>
       </c>
@@ -8385,10 +8387,10 @@
         <v>10</v>
       </c>
       <c r="J282" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>29</v>
       </c>
@@ -8405,10 +8407,10 @@
         <v>10</v>
       </c>
       <c r="J283" s="5" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>29</v>
       </c>
@@ -8425,10 +8427,10 @@
         <v>10</v>
       </c>
       <c r="J284" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>29</v>
       </c>
@@ -8445,10 +8447,10 @@
         <v>10</v>
       </c>
       <c r="J285" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>29</v>
       </c>
@@ -8465,10 +8467,10 @@
         <v>10</v>
       </c>
       <c r="J286" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="287" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
         <v>29</v>
       </c>
@@ -8485,10 +8487,10 @@
         <v>10</v>
       </c>
       <c r="J287" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>29</v>
       </c>
@@ -8505,10 +8507,10 @@
         <v>10</v>
       </c>
       <c r="J288" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
         <v>29</v>
       </c>
@@ -8525,10 +8527,10 @@
         <v>10</v>
       </c>
       <c r="J289" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>29</v>
       </c>
@@ -8545,10 +8547,10 @@
         <v>10</v>
       </c>
       <c r="J290" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>29</v>
       </c>
@@ -8565,10 +8567,10 @@
         <v>10</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>29</v>
       </c>
@@ -8585,10 +8587,10 @@
         <v>10</v>
       </c>
       <c r="J292" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>29</v>
       </c>
@@ -8605,10 +8607,10 @@
         <v>10</v>
       </c>
       <c r="J293" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>29</v>
       </c>
@@ -8625,10 +8627,10 @@
         <v>10</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>29</v>
       </c>
@@ -8645,10 +8647,10 @@
         <v>10</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>29</v>
       </c>
@@ -8665,10 +8667,10 @@
         <v>10</v>
       </c>
       <c r="J296" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>29</v>
       </c>
@@ -8685,10 +8687,10 @@
         <v>10</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>29</v>
       </c>
@@ -8705,7 +8707,7 @@
         <v>10</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="299" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8728,7 +8730,7 @@
         <v>10</v>
       </c>
       <c r="J299" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="300" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8751,7 +8753,7 @@
         <v>10</v>
       </c>
       <c r="J300" s="5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8774,7 +8776,7 @@
         <v>10</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="302" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8797,7 +8799,7 @@
         <v>10</v>
       </c>
       <c r="J302" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="303" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8820,7 +8822,7 @@
         <v>10</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="304" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8843,7 +8845,7 @@
         <v>10</v>
       </c>
       <c r="J304" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="305" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8866,7 +8868,7 @@
         <v>10</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="306" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8889,7 +8891,7 @@
         <v>10</v>
       </c>
       <c r="J306" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8912,7 +8914,7 @@
         <v>10</v>
       </c>
       <c r="J307" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="308" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8935,7 +8937,7 @@
         <v>10</v>
       </c>
       <c r="J308" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="309" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8958,7 +8960,7 @@
         <v>10</v>
       </c>
       <c r="J309" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -8981,7 +8983,7 @@
         <v>10</v>
       </c>
       <c r="J310" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9004,7 +9006,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9027,7 +9029,7 @@
         <v>10</v>
       </c>
       <c r="J312" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9050,7 +9052,7 @@
         <v>10</v>
       </c>
       <c r="J313" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="314" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9073,7 +9075,7 @@
         <v>10</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9096,10 +9098,10 @@
         <v>10</v>
       </c>
       <c r="J315" s="5" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>29</v>
       </c>
@@ -9116,10 +9118,10 @@
         <v>10</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>29</v>
       </c>
@@ -9136,10 +9138,10 @@
         <v>10</v>
       </c>
       <c r="J317" s="5" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="318" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>29</v>
       </c>
@@ -9156,10 +9158,10 @@
         <v>10</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="319" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
         <v>29</v>
       </c>
@@ -9176,10 +9178,10 @@
         <v>10</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="320" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>29</v>
       </c>
@@ -9196,10 +9198,10 @@
         <v>10</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>29</v>
       </c>
@@ -9216,10 +9218,10 @@
         <v>10</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>29</v>
       </c>
@@ -9236,10 +9238,10 @@
         <v>10</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="323" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
         <v>29</v>
       </c>
@@ -9256,10 +9258,10 @@
         <v>10</v>
       </c>
       <c r="J323" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="324" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>29</v>
       </c>
@@ -9276,10 +9278,10 @@
         <v>10</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>29</v>
       </c>
@@ -9296,10 +9298,10 @@
         <v>10</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>29</v>
       </c>
@@ -9316,7 +9318,7 @@
         <v>10</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="327" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9339,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="328" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9362,7 +9364,7 @@
         <v>10</v>
       </c>
       <c r="J328" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9385,10 +9387,10 @@
         <v>10</v>
       </c>
       <c r="J329" s="5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
         <v>29</v>
       </c>
@@ -9405,10 +9407,10 @@
         <v>10</v>
       </c>
       <c r="J330" s="5" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
         <v>29</v>
       </c>
@@ -9425,10 +9427,10 @@
         <v>10</v>
       </c>
       <c r="J331" s="5" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>29</v>
       </c>
@@ -9445,10 +9447,10 @@
         <v>10</v>
       </c>
       <c r="J332" s="5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="333" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
         <v>29</v>
       </c>
@@ -9465,10 +9467,10 @@
         <v>10</v>
       </c>
       <c r="J333" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
         <v>29</v>
       </c>
@@ -9485,7 +9487,7 @@
         <v>10</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9508,7 +9510,7 @@
         <v>10</v>
       </c>
       <c r="J335" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="336" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9531,10 +9533,10 @@
         <v>10</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
         <v>29</v>
       </c>
@@ -9551,10 +9553,10 @@
         <v>10</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="338" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
         <v>29</v>
       </c>
@@ -9571,7 +9573,7 @@
         <v>10</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="339" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9594,7 +9596,7 @@
         <v>10</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="340" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -9617,10 +9619,10 @@
         <v>10</v>
       </c>
       <c r="J340" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>29</v>
       </c>
@@ -9637,10 +9639,10 @@
         <v>10</v>
       </c>
       <c r="J341" s="5" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>399</v>
       </c>
@@ -9660,10 +9662,10 @@
         <v>10</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="343" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
         <v>399</v>
       </c>
@@ -9680,10 +9682,10 @@
         <v>10</v>
       </c>
       <c r="J343" s="5" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="344" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A344" s="4" t="s">
         <v>399</v>
       </c>
@@ -9700,10 +9702,10 @@
         <v>10</v>
       </c>
       <c r="J344" s="5" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="345" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
         <v>399</v>
       </c>
@@ -9723,17 +9725,11 @@
         <v>10</v>
       </c>
       <c r="J345" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J345" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J345" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9775,10 +9771,10 @@
         <v>89</v>
       </c>
       <c r="C2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D2" t="s">
         <v>405</v>
-      </c>
-      <c r="D2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9789,10 +9785,10 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9803,10 +9799,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9817,10 +9813,10 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9831,13 +9827,13 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9848,10 +9844,10 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9862,10 +9858,10 @@
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9876,10 +9872,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9890,10 +9886,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9904,10 +9900,10 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9918,10 +9914,10 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9932,10 +9928,10 @@
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9946,10 +9942,10 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9960,10 +9956,10 @@
         <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9974,10 +9970,10 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -9988,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -10002,10 +9998,10 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E18" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -10015,43 +10011,47 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30159596-74E1-AB4A-8605-D929B81467D2}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="136.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1640625" customWidth="1"/>
+    <col min="3" max="3" width="136.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" t="s">
         <v>397</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>443</v>
-      </c>
-      <c r="B3" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D3" t="s">
         <v>21</v>
       </c>
     </row>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C754AB3D-C3D6-C14F-B16A-88F9CC6C398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52AE528-E134-BC42-9681-B70393F809E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3820" yWindow="600" windowWidth="30680" windowHeight="19060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="705">
   <si>
     <t>Table Name</t>
   </si>
@@ -2135,6 +2135,12 @@
   </si>
   <si>
     <t>Table datamart informasi funding nasabah, berisi informasi terkait account funding nasabah (tabungan, giro, deposito). Table funding juga disebut dengan table DPK.</t>
+  </si>
+  <si>
+    <t>Informasi DPK</t>
+  </si>
+  <si>
+    <t>SELECT cur_book_bal FROM dm_funding.funding;</t>
   </si>
 </sst>
 </file>
@@ -6033,9 +6039,6 @@
       <c r="D169" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E169" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H169" s="4" t="s">
         <v>10</v>
       </c>
@@ -10011,7 +10014,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30159596-74E1-AB4A-8605-D929B81467D2}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.1640625" bestFit="1" customWidth="1"/>
@@ -10055,6 +10058,17 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>703</v>
+      </c>
+      <c r="C4" t="s">
+        <v>704</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52AE528-E134-BC42-9681-B70393F809E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB881D9-1994-1E4C-B0EA-6502DAF1269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -2137,10 +2137,10 @@
     <t>Table datamart informasi funding nasabah, berisi informasi terkait account funding nasabah (tabungan, giro, deposito). Table funding juga disebut dengan table DPK.</t>
   </si>
   <si>
-    <t>Informasi DPK</t>
-  </si>
-  <si>
     <t>SELECT cur_book_bal FROM dm_funding.funding;</t>
+  </si>
+  <si>
+    <t>Informasi DPK / total DPK</t>
   </si>
 </sst>
 </file>
@@ -10060,10 +10060,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C4" t="s">
         <v>703</v>
-      </c>
-      <c r="C4" t="s">
-        <v>704</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB881D9-1994-1E4C-B0EA-6502DAF1269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FAA4D2-03BF-2941-A2F5-55B73B688510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="706">
   <si>
     <t>Table Name</t>
   </si>
@@ -2141,6 +2141,9 @@
   </si>
   <si>
     <t>Informasi DPK / total DPK</t>
+  </si>
+  <si>
+    <t>funding.as_of_date; lending.as_of_date</t>
   </si>
 </sst>
 </file>
@@ -2651,7 +2654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -2666,6 +2669,9 @@
       </c>
       <c r="E2" s="4" t="b">
         <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>705</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>10</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FAA4D2-03BF-2941-A2F5-55B73B688510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEF160A-98D4-7348-9CC3-71D541276420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="726">
   <si>
     <t>Table Name</t>
   </si>
@@ -2144,13 +2144,342 @@
   </si>
   <si>
     <t>funding.as_of_date; lending.as_of_date</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mengambil posisi saldo rekening/customer pada tanggal tertentu. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cur_book_bal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> merupakan end-of-day balance, sehingga tidak boleh dijumlahkan antar tanggal. Setiap row merupakan snapshot saldo pada tanggal tertentu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Total DPK</t>
+  </si>
+  <si>
+    <t>Menghitung total Dana Pihak Ketiga (tabungan, giro, dan deposito) berdasarkan posisi saldo terbaru yang tersedia, bukan menjumlahkan saldo antar tanggal.</t>
+  </si>
+  <si>
+    <t>Balance Change</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menghitung persentase perubahan </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cur_book_bal_idr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> antara dua tanggal untuk account/customer yang sama. Nilai positif menunjukkan peningkatan saldo dan negatif menunjukkan penurunan saldo.</t>
+    </r>
+  </si>
+  <si>
+    <t>MTD Average Balance</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menghitung rata-rata </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cur_book_bal_idr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dari tanggal 1 bulan berjalan sampai tanggal yang diminta. Untuk customer dengan banyak rekening, perhitungan dilakukan per account kemudian diagregasi berdasarkan CIF.</t>
+    </r>
+  </si>
+  <si>
+    <t>Product Ownership</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mengidentifikasi customer yang memiliki produk tertentu. Karena </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>product_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> berupa free text, gunakan case-insensitive pattern matching </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>LOWER(product_name) LIKE '%keyword%'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Keyword harus mengikuti persis produk yang disebut user.</t>
+    </r>
+  </si>
+  <si>
+    <t>Written Off Customer</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menghitung distinct customer yang sudah written off, yaitu customer dengan </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>written_off_date IS NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dan </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>written_off_date &lt;&gt; '1990-01-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cash In</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mengidentifikasi dana yang </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>masuk/diterima oleh customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Customer dianggap sebagai penerima apabila CIF/customer muncul pada kolom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>target_cif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Cash In merupakan transaction flow, bukan saldo, sehingga tidak boleh diperlakukan sebagai balance antar tanggal.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cash Out</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mengidentifikasi dana yang </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>keluar/dikirim oleh customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Customer dianggap sebagai pengirim apabila CIF/customer muncul pada kolom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cif_key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Cash Out merupakan transaction flow, bukan saldo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cash In by Entity</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menganalisis Cash In berdasarkan customer, group, subholding, atau principal. Untuk Cash In, identifikasi customer/pihak penerima melalui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>target_cif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cash Out by Entity</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menganalisis Cash Out berdasarkan customer, group, subholding, atau principal. Untuk Cash Out, identifikasi customer/pihak pengirim melalui </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>cif_key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2171,6 +2500,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2208,7 +2543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2221,6 +2556,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10020,7 +10358,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30159596-74E1-AB4A-8605-D929B81467D2}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.1640625" bestFit="1" customWidth="1"/>
@@ -10075,6 +10413,86 @@
         <v>21</v>
       </c>
     </row>
+    <row r="5" spans="1:4" ht="81" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="65" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="81" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="82" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="50" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="97" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="65" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="49" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="49" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEF160A-98D4-7348-9CC3-71D541276420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A89796E-C692-D44E-A5AC-0F8EA9733354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="729">
   <si>
     <t>Table Name</t>
   </si>
@@ -2473,6 +2473,15 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>Mencari nasabah aktif</t>
+  </si>
+  <si>
+    <t>Mencari aktivitas cash out</t>
+  </si>
+  <si>
+    <t>Mencari informasi DPK / total DPK</t>
   </si>
 </sst>
 </file>
@@ -10384,6 +10393,9 @@
       <c r="A2" t="s">
         <v>443</v>
       </c>
+      <c r="B2" t="s">
+        <v>726</v>
+      </c>
       <c r="C2" t="s">
         <v>397</v>
       </c>
@@ -10395,6 +10407,9 @@
       <c r="A3" t="s">
         <v>442</v>
       </c>
+      <c r="B3" t="s">
+        <v>727</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>441</v>
       </c>
@@ -10405,6 +10420,9 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>704</v>
+      </c>
+      <c r="B4" t="s">
+        <v>728</v>
       </c>
       <c r="C4" t="s">
         <v>703</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A89796E-C692-D44E-A5AC-0F8EA9733354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE9408C-A571-0842-AFB9-D4C6C2115E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="731">
   <si>
     <t>Table Name</t>
   </si>
@@ -2482,6 +2482,12 @@
   </si>
   <si>
     <t>Mencari informasi DPK / total DPK</t>
+  </si>
+  <si>
+    <t>Availability Date</t>
+  </si>
+  <si>
+    <t>D-1</t>
   </si>
 </sst>
 </file>
@@ -2872,15 +2878,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="91.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2890,8 +2897,11 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="D1" s="3" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -2902,7 +2912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2912,8 +2922,11 @@
       <c r="C3" s="4" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="D3" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2923,8 +2936,11 @@
       <c r="C4" s="4" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="D4" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2934,8 +2950,11 @@
       <c r="C5" s="4" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="D5" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>398</v>
       </c>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE9408C-A571-0842-AFB9-D4C6C2115E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379F0FC9-5595-5D4C-92A2-9B89846278BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="728">
   <si>
     <t>Table Name</t>
   </si>
@@ -2473,15 +2473,6 @@
       </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <t>Mencari nasabah aktif</t>
-  </si>
-  <si>
-    <t>Mencari aktivitas cash out</t>
-  </si>
-  <si>
-    <t>Mencari informasi DPK / total DPK</t>
   </si>
   <si>
     <t>Availability Date</t>
@@ -2898,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2923,7 +2914,7 @@
         <v>400</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -2937,7 +2928,7 @@
         <v>702</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2951,7 +2942,7 @@
         <v>401</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -10412,9 +10403,6 @@
       <c r="A2" t="s">
         <v>443</v>
       </c>
-      <c r="B2" t="s">
-        <v>726</v>
-      </c>
       <c r="C2" t="s">
         <v>397</v>
       </c>
@@ -10426,9 +10414,6 @@
       <c r="A3" t="s">
         <v>442</v>
       </c>
-      <c r="B3" t="s">
-        <v>727</v>
-      </c>
       <c r="C3" s="4" t="s">
         <v>441</v>
       </c>
@@ -10439,9 +10424,6 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>704</v>
-      </c>
-      <c r="B4" t="s">
-        <v>728</v>
       </c>
       <c r="C4" t="s">
         <v>703</v>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379F0FC9-5595-5D4C-92A2-9B89846278BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A575BB0E-D092-4D41-AC1E-C7FD184E93BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="727">
   <si>
     <t>Table Name</t>
   </si>
@@ -2141,9 +2141,6 @@
   </si>
   <si>
     <t>Informasi DPK / total DPK</t>
-  </si>
-  <si>
-    <t>funding.as_of_date; lending.as_of_date</t>
   </si>
   <si>
     <t>Balance</t>
@@ -2889,7 +2886,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2914,7 +2911,7 @@
         <v>400</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -2928,7 +2925,7 @@
         <v>702</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2942,7 +2939,7 @@
         <v>401</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -3011,7 +3008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -3026,9 +3023,6 @@
       </c>
       <c r="E2" s="4" t="b">
         <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>705</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>10</v>
@@ -10434,82 +10428,82 @@
     </row>
     <row r="5" spans="1:4" ht="81" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>706</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>708</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="65" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="81" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>712</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="82" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>714</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="50" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>716</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="97" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>718</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="65" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>720</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="49" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>722</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>724</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>725</v>
       </c>
     </row>
   </sheetData>

--- a/ask-data/data/bni_dbt_definitions.xlsx
+++ b/ask-data/data/bni_dbt_definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Documents/Work/Cloudera/GitHub/bni-ai-dev/ask-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A575BB0E-D092-4D41-AC1E-C7FD184E93BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C391AF13-856A-404C-90D5-74CFCF133007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="660" windowWidth="31440" windowHeight="19740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="727">
   <si>
     <t>Table Name</t>
   </si>
@@ -2546,7 +2546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2559,9 +2559,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10397,6 +10394,9 @@
       <c r="A2" t="s">
         <v>443</v>
       </c>
+      <c r="B2" t="s">
+        <v>443</v>
+      </c>
       <c r="C2" t="s">
         <v>397</v>
       </c>
@@ -10408,6 +10408,9 @@
       <c r="A3" t="s">
         <v>442</v>
       </c>
+      <c r="B3" t="s">
+        <v>442</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>441</v>
       </c>
@@ -10419,6 +10422,9 @@
       <c r="A4" t="s">
         <v>704</v>
       </c>
+      <c r="B4" t="s">
+        <v>704</v>
+      </c>
       <c r="C4" t="s">
         <v>703</v>
       </c>
@@ -10427,7 +10433,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="81" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>705</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -10435,7 +10441,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>707</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -10443,7 +10449,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="65" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>709</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -10451,7 +10457,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="81" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>711</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -10459,7 +10465,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="82" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>713</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -10467,7 +10473,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="50" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>715</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -10475,7 +10481,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="97" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>717</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -10483,7 +10489,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="65" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>719</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -10491,7 +10497,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="49" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>721</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -10499,7 +10505,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="49" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>723</v>
       </c>
       <c r="B14" s="5" t="s">
